--- a/data/ar24-072-experiment/AR24-072-SAM-MasterDataTable.xlsx
+++ b/data/ar24-072-experiment/AR24-072-SAM-MasterDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myteams.gsk.com/sites/BiopharmModelPredictiveControl/Shared Documents/General/data/AR24-072-SAM-MPC-1kL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2526" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D65E0C2F-8A87-426B-A65C-25FC250267DD}"/>
+  <xr:revisionPtr revIDLastSave="2618" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1566A155-7771-4B12-A02E-8311A52F93C1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterDataTable" sheetId="1" r:id="rId1"/>
@@ -314,7 +314,7 @@
     <t>Feed Rate based on CSFR (mL/hr)</t>
   </si>
   <si>
-    <t>Something is wrong with Tech code. Nutrient_rate is too high. MPC underfeeding compared to manual. Cannot manually adjust pumps</t>
+    <t xml:space="preserve"> MPC underfeeding 30%  compared to manual (titer information missing from input file from Tech). Cannot manually adjust pumps. </t>
   </si>
 </sst>
 </file>
@@ -7764,7 +7764,7 @@
         <v>91</v>
       </c>
       <c r="G30" s="83">
-        <v>45570.368055555555</v>
+        <v>45571.368055555555</v>
       </c>
       <c r="H30" s="40">
         <v>1505.08</v>
@@ -8487,7 +8487,7 @@
       </c>
       <c r="AR33" s="42">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>6.2890000000000001E-2</v>
       </c>
       <c r="AS33" s="42">
         <f t="shared" si="23"/>
@@ -8519,7 +8519,9 @@
       <c r="BA33" s="43">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BB33" s="11"/>
+      <c r="BB33" s="11">
+        <v>7.6E-3</v>
+      </c>
       <c r="BC33" s="43"/>
       <c r="BD33" s="22"/>
       <c r="BE33" s="43">
@@ -8544,11 +8546,11 @@
       </c>
       <c r="BJ33" s="44">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>90.561599999999999</v>
       </c>
       <c r="BK33" s="44">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>6.2890000000000001E-2</v>
       </c>
       <c r="BL33" s="44" t="str">
         <f t="shared" si="12"/>
@@ -8568,11 +8570,11 @@
       </c>
       <c r="BP33" s="58">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>163.35064935064938</v>
       </c>
       <c r="BQ33" s="46">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>6.2890000000000001E-2</v>
       </c>
       <c r="BR33" s="24">
         <f t="shared" si="22"/>
@@ -8703,7 +8705,7 @@
       </c>
       <c r="AR34" s="42">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>0.16416666666666666</v>
       </c>
       <c r="AS34" s="42">
         <f t="shared" si="23"/>
@@ -8735,7 +8737,9 @@
       <c r="BA34" s="43">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BB34" s="11"/>
+      <c r="BB34" s="11">
+        <v>0.02</v>
+      </c>
       <c r="BD34" s="22"/>
       <c r="BE34" s="43">
         <f t="shared" si="1"/>
@@ -8759,11 +8763,11 @@
       </c>
       <c r="BJ34" s="44">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>236.39999999999998</v>
       </c>
       <c r="BK34" s="44">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>0.16416666666666666</v>
       </c>
       <c r="BL34" s="45" t="str">
         <f t="shared" si="12"/>
@@ -8783,11 +8787,11 @@
       </c>
       <c r="BP34" s="58">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>426.4069264069264</v>
       </c>
       <c r="BQ34" s="46">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>0.16416666666666666</v>
       </c>
       <c r="BR34" s="24">
         <f t="shared" si="22"/>
@@ -8918,7 +8922,7 @@
       </c>
       <c r="AR35" s="42">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>0.12476205211681562</v>
       </c>
       <c r="AS35" s="42">
         <f t="shared" si="23"/>
@@ -8951,7 +8955,14 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BB35" s="11"/>
-      <c r="BD35" s="22"/>
+      <c r="BC35" s="81">
+        <f>0.00207936753528026*24*60/BG35</f>
+        <v>1.5122672983856439E-2</v>
+      </c>
+      <c r="BD35" s="81">
+        <f>0.937837273085801/BG35</f>
+        <v>4.7365518842717221E-3</v>
+      </c>
       <c r="BE35" s="43">
         <f t="shared" ref="BE35:BE66" si="44">BA35*L35*BG35/1000</f>
         <v>1.4315399999999998E-3</v>
@@ -8974,7 +8985,7 @@
       </c>
       <c r="BJ35" s="44">
         <f t="shared" ref="BJ35:BJ66" si="48">AR35*24*60</f>
-        <v>0</v>
+        <v>179.6573550482145</v>
       </c>
       <c r="BK35" s="44" t="str">
         <f t="shared" si="19"/>
@@ -8982,7 +8993,7 @@
       </c>
       <c r="BL35" s="45">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>0.12476205211681562</v>
       </c>
       <c r="BM35" s="45" t="str">
         <f t="shared" si="13"/>
@@ -8994,19 +9005,19 @@
       </c>
       <c r="BO35" s="44">
         <f t="shared" ref="BO35:BO66" si="49">IF(C35="Julia",BD35*BG35,"")</f>
-        <v>0</v>
+        <v>0.937837273085801</v>
       </c>
       <c r="BP35" s="58">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>324.05727822549517</v>
       </c>
       <c r="BQ35" s="46">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>0.12476205211681562</v>
       </c>
       <c r="BR35" s="24">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>0.937837273085801</v>
       </c>
     </row>
     <row r="36" spans="1:70" s="40" customFormat="1" x14ac:dyDescent="0.3">
@@ -9133,7 +9144,7 @@
       </c>
       <c r="AR36" s="42">
         <f>BQ36</f>
-        <v>0</v>
+        <v>0.1136403146599332</v>
       </c>
       <c r="AS36" s="42">
         <f t="shared" si="23"/>
@@ -9166,7 +9177,14 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BB36" s="11"/>
-      <c r="BD36" s="22"/>
+      <c r="BC36" s="81">
+        <f>0.00189400524433222*24*60/BG36</f>
+        <v>1.3732968538964737E-2</v>
+      </c>
+      <c r="BD36" s="81">
+        <f>0.950560138745667/BG36</f>
+        <v>4.7863048275209822E-3</v>
+      </c>
       <c r="BE36" s="43">
         <f t="shared" si="44"/>
         <v>1.5192899999999997E-3</v>
@@ -9189,7 +9207,7 @@
       </c>
       <c r="BJ36" s="44">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>163.64205311030381</v>
       </c>
       <c r="BK36" s="44" t="str">
         <f t="shared" si="19"/>
@@ -9197,7 +9215,7 @@
       </c>
       <c r="BL36" s="45">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>0.1136403146599332</v>
       </c>
       <c r="BM36" s="45" t="str">
         <f t="shared" si="13"/>
@@ -9209,19 +9227,19 @@
       </c>
       <c r="BO36" s="44">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>0.95056013874566703</v>
       </c>
       <c r="BP36" s="58">
         <f>IF(BK36&lt;&gt;"",BK36/0.000385,IF(BL36&lt;&gt;"",BL36/0.000385,BM36/0.000385))</f>
-        <v>0</v>
+        <v>295.16964846735897</v>
       </c>
       <c r="BQ36" s="46">
         <f>IF(BK36&lt;&gt;"",BK36,IF(BL36&lt;&gt;"",BL36,BM36))</f>
-        <v>0</v>
+        <v>0.1136403146599332</v>
       </c>
       <c r="BR36" s="24">
         <f>IF(BN36&lt;&gt;"",BN36,BO36)</f>
-        <v>0</v>
+        <v>0.95056013874566703</v>
       </c>
     </row>
     <row r="37" spans="1:70" s="40" customFormat="1" x14ac:dyDescent="0.3">
@@ -9671,24 +9689,38 @@
         <v>4</v>
       </c>
       <c r="F39" s="3"/>
-      <c r="G39" s="34"/>
+      <c r="G39" s="34">
+        <v>45572.359027777777</v>
+      </c>
       <c r="H39" s="3">
         <v>2119.61</v>
       </c>
       <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6"/>
-      <c r="L39" s="6"/>
-      <c r="M39" s="6"/>
+      <c r="J39" s="6">
+        <v>1588.47</v>
+      </c>
+      <c r="K39" s="6">
+        <v>21.1</v>
+      </c>
+      <c r="L39" s="6">
+        <v>20.8</v>
+      </c>
+      <c r="M39" s="6">
+        <v>98.3</v>
+      </c>
       <c r="N39" s="6"/>
       <c r="O39" s="6"/>
       <c r="P39" s="6"/>
       <c r="Q39" s="6"/>
-      <c r="R39" s="6"/>
+      <c r="R39" s="6">
+        <v>1.76</v>
+      </c>
       <c r="S39" s="6"/>
       <c r="T39" s="6"/>
       <c r="U39" s="6"/>
-      <c r="V39" s="6"/>
+      <c r="V39" s="6">
+        <v>2.6</v>
+      </c>
       <c r="W39" s="6"/>
       <c r="X39" s="6"/>
       <c r="Y39" s="6"/>
@@ -9697,33 +9729,45 @@
       <c r="AB39" s="6"/>
       <c r="AC39" s="6"/>
       <c r="AD39" s="6"/>
-      <c r="AE39" s="16"/>
+      <c r="AE39" s="16">
+        <v>7.306</v>
+      </c>
       <c r="AF39" s="6"/>
-      <c r="AG39" s="6"/>
+      <c r="AG39" s="6">
+        <v>50.000105040413999</v>
+      </c>
       <c r="AH39" s="6"/>
-      <c r="AI39" s="6"/>
+      <c r="AI39" s="6">
+        <v>33.997979719765702</v>
+      </c>
       <c r="AJ39" s="6"/>
       <c r="AK39" s="6"/>
       <c r="AL39" s="6"/>
-      <c r="AM39" s="6"/>
-      <c r="AN39" s="6"/>
-      <c r="AO39" s="6"/>
+      <c r="AM39" s="6">
+        <v>22306.763671875</v>
+      </c>
+      <c r="AN39" s="6">
+        <v>14919.5068359375</v>
+      </c>
+      <c r="AO39" s="6">
+        <v>611400</v>
+      </c>
       <c r="AP39" s="72"/>
       <c r="AQ39" s="32">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>0.50000105040414</v>
       </c>
       <c r="AR39" s="32">
         <f t="shared" ref="AR39:AR70" si="50">BQ39</f>
-        <v>0</v>
+        <v>531.44902002000003</v>
       </c>
       <c r="AS39" s="32">
         <f t="shared" si="23"/>
-        <v>-14699.6376953125</v>
+        <v>7607.1259765625</v>
       </c>
       <c r="AT39" s="32">
         <f t="shared" si="24"/>
-        <v>-10229.482421875</v>
+        <v>4690.0244140625</v>
       </c>
       <c r="AU39" s="32">
         <f t="shared" si="25"/>
@@ -9748,31 +9792,37 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BB39" s="8"/>
-      <c r="BC39" s="9"/>
-      <c r="BD39" s="21"/>
+      <c r="BC39" s="9">
+        <f>8.857483667*24*60/BG39</f>
+        <v>2.0861590579784102E-2</v>
+      </c>
+      <c r="BD39" s="81">
+        <f>2610.0869895953/BG39</f>
+        <v>4.2690333490273142E-3</v>
+      </c>
       <c r="BE39" s="9">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>3.8151359999999999</v>
       </c>
       <c r="BF39" s="9">
         <f t="shared" ref="BF39:BF70" si="51">BE39*24*60</f>
-        <v>0</v>
+        <v>5493.7958400000007</v>
       </c>
       <c r="BG39" s="9">
         <f t="shared" si="45"/>
-        <v>591700</v>
-      </c>
-      <c r="BH39" s="10" t="str">
+        <v>611400</v>
+      </c>
+      <c r="BH39" s="10">
         <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="BI39" s="10" t="str">
+        <v>3.6484729590897942E-2</v>
+      </c>
+      <c r="BI39" s="10">
         <f t="shared" si="47"/>
-        <v/>
+        <v>3.768034404032939E-2</v>
       </c>
       <c r="BJ39" s="10">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>765286.58882880001</v>
       </c>
       <c r="BK39" s="10" t="str">
         <f t="shared" si="19"/>
@@ -9780,7 +9830,7 @@
       </c>
       <c r="BL39" s="10">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>531.44902002000003</v>
       </c>
       <c r="BM39" s="28" t="str">
         <f t="shared" si="13"/>
@@ -9792,19 +9842,19 @@
       </c>
       <c r="BO39" s="10">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>2610.0869895953001</v>
       </c>
       <c r="BP39" s="62">
         <f t="shared" ref="BP39:BP70" si="52">IF(BK39&lt;&gt;"",BK39/0.000385,IF(BL39&lt;&gt;"",BL39/0.000385,BM39/0.000385))</f>
-        <v>0</v>
+        <v>1380387.0649870131</v>
       </c>
       <c r="BQ39" s="30">
         <f t="shared" ref="BQ39:BQ70" si="53">IF(BK39&lt;&gt;"",BK39,IF(BL39&lt;&gt;"",BL39,BM39))</f>
-        <v>0</v>
+        <v>531.44902002000003</v>
       </c>
       <c r="BR39" s="26">
         <f t="shared" ref="BR39:BR70" si="54">IF(BN39&lt;&gt;"",BN39,BO39)</f>
-        <v>0</v>
+        <v>2610.0869895953001</v>
       </c>
     </row>
     <row r="40" spans="1:70" s="40" customFormat="1" x14ac:dyDescent="0.3">
@@ -9823,59 +9873,123 @@
       <c r="E40" s="40">
         <v>4</v>
       </c>
-      <c r="G40" s="35"/>
+      <c r="G40" s="35">
+        <v>45572.402777777781</v>
+      </c>
       <c r="H40" s="40">
         <v>2119.61</v>
       </c>
       <c r="I40" s="41"/>
-      <c r="J40" s="41"/>
-      <c r="K40" s="41"/>
-      <c r="L40" s="41"/>
-      <c r="M40" s="41"/>
-      <c r="N40" s="41"/>
-      <c r="O40" s="41"/>
-      <c r="P40" s="41"/>
-      <c r="Q40" s="41"/>
-      <c r="R40" s="41"/>
+      <c r="J40" s="41">
+        <v>1786.4549999999999</v>
+      </c>
+      <c r="K40" s="41">
+        <v>25.9</v>
+      </c>
+      <c r="L40" s="41">
+        <v>24.5</v>
+      </c>
+      <c r="M40" s="41">
+        <v>94.7</v>
+      </c>
+      <c r="N40" s="41">
+        <v>16.3</v>
+      </c>
+      <c r="O40" s="41">
+        <v>316</v>
+      </c>
+      <c r="P40" s="41">
+        <v>1.46</v>
+      </c>
+      <c r="Q40" s="41">
+        <v>0.41</v>
+      </c>
+      <c r="R40" s="41">
+        <v>2.14</v>
+      </c>
       <c r="S40" s="41"/>
-      <c r="T40" s="41"/>
-      <c r="U40" s="41"/>
-      <c r="V40" s="41"/>
-      <c r="W40" s="41"/>
-      <c r="X40" s="41"/>
-      <c r="Y40" s="41"/>
-      <c r="Z40" s="41"/>
-      <c r="AA40" s="41"/>
-      <c r="AB40" s="41"/>
-      <c r="AC40" s="41"/>
-      <c r="AD40" s="41"/>
-      <c r="AE40" s="17"/>
-      <c r="AF40" s="41"/>
-      <c r="AG40" s="41"/>
-      <c r="AH40" s="41"/>
-      <c r="AI40" s="41"/>
-      <c r="AJ40" s="41"/>
-      <c r="AK40" s="41"/>
-      <c r="AL40" s="41"/>
-      <c r="AM40" s="41"/>
-      <c r="AN40" s="41"/>
-      <c r="AO40" s="41"/>
+      <c r="T40" s="41">
+        <v>0.13</v>
+      </c>
+      <c r="U40" s="41">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="V40" s="41">
+        <v>3.02</v>
+      </c>
+      <c r="W40" s="41">
+        <v>7.2759999999999998</v>
+      </c>
+      <c r="X40" s="41">
+        <v>43.1</v>
+      </c>
+      <c r="Y40" s="41">
+        <v>60.6</v>
+      </c>
+      <c r="Z40" s="41">
+        <v>2.64</v>
+      </c>
+      <c r="AA40" s="41">
+        <v>133.5</v>
+      </c>
+      <c r="AB40" s="41">
+        <v>17.8</v>
+      </c>
+      <c r="AC40" s="41">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="AD40" s="41">
+        <v>49.2</v>
+      </c>
+      <c r="AE40" s="17">
+        <v>7.2359999999999998</v>
+      </c>
+      <c r="AF40" s="41">
+        <v>406</v>
+      </c>
+      <c r="AG40" s="41">
+        <v>52</v>
+      </c>
+      <c r="AH40" s="41">
+        <v>7.3079999999999998</v>
+      </c>
+      <c r="AI40" s="41">
+        <v>33.9</v>
+      </c>
+      <c r="AJ40" s="41">
+        <v>2</v>
+      </c>
+      <c r="AK40" s="41">
+        <v>1.4</v>
+      </c>
+      <c r="AL40" s="41">
+        <v>0.1</v>
+      </c>
+      <c r="AM40" s="41">
+        <v>6.1</v>
+      </c>
+      <c r="AN40" s="41">
+        <v>4</v>
+      </c>
+      <c r="AO40" s="41">
+        <v>197.4</v>
+      </c>
       <c r="AP40" s="74"/>
       <c r="AQ40" s="42">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="AR40" s="42">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>8.7053400000000003E-2</v>
       </c>
       <c r="AS40" s="42">
         <f t="shared" si="23"/>
-        <v>-4.2</v>
+        <v>1.8999999999999995</v>
       </c>
       <c r="AT40" s="42">
         <f t="shared" si="24"/>
-        <v>-2.8</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="AU40" s="42">
         <f t="shared" si="25"/>
@@ -9904,27 +10018,27 @@
       <c r="BD40" s="22"/>
       <c r="BE40" s="43">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1.45089E-3</v>
       </c>
       <c r="BF40" s="43">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>2.0892816000000001</v>
       </c>
       <c r="BG40" s="43">
         <f t="shared" si="45"/>
-        <v>188</v>
-      </c>
-      <c r="BH40" s="44" t="str">
+        <v>197.4</v>
+      </c>
+      <c r="BH40" s="44">
         <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="BI40" s="44" t="str">
+        <v>3.0901722391084092E-2</v>
+      </c>
+      <c r="BI40" s="44">
         <f t="shared" si="47"/>
-        <v/>
+        <v>3.0499999999999999E-2</v>
       </c>
       <c r="BJ40" s="44">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>125.35689600000001</v>
       </c>
       <c r="BK40" s="44" t="str">
         <f t="shared" si="19"/>
@@ -9936,11 +10050,11 @@
       </c>
       <c r="BM40" s="45">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>8.7053400000000003E-2</v>
       </c>
       <c r="BN40" s="44">
         <f t="shared" si="32"/>
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BO40" s="44" t="str">
         <f t="shared" si="49"/>
@@ -9948,15 +10062,15 @@
       </c>
       <c r="BP40" s="58">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>226.11272727272728</v>
       </c>
       <c r="BQ40" s="46">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>8.7053400000000003E-2</v>
       </c>
       <c r="BR40" s="24">
         <f t="shared" si="54"/>
-        <v>1.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:70" s="40" customFormat="1" x14ac:dyDescent="0.3">
@@ -9975,59 +10089,123 @@
       <c r="E41" s="40">
         <v>4</v>
       </c>
-      <c r="G41" s="35"/>
+      <c r="G41" s="35">
+        <v>45572.40347222222</v>
+      </c>
       <c r="H41" s="40">
         <v>2119.61</v>
       </c>
       <c r="I41" s="41"/>
-      <c r="J41" s="41"/>
-      <c r="K41" s="41"/>
-      <c r="L41" s="41"/>
-      <c r="M41" s="41"/>
-      <c r="N41" s="41"/>
-      <c r="O41" s="41"/>
-      <c r="P41" s="41"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="41"/>
+      <c r="J41" s="41">
+        <v>1778.8050000000001</v>
+      </c>
+      <c r="K41" s="41">
+        <v>26.8</v>
+      </c>
+      <c r="L41" s="41">
+        <v>25.2</v>
+      </c>
+      <c r="M41" s="41">
+        <v>94.2</v>
+      </c>
+      <c r="N41" s="41">
+        <v>16.2</v>
+      </c>
+      <c r="O41" s="41">
+        <v>319</v>
+      </c>
+      <c r="P41" s="41">
+        <v>1.45</v>
+      </c>
+      <c r="Q41" s="41">
+        <v>0.41</v>
+      </c>
+      <c r="R41" s="41">
+        <v>2.21</v>
+      </c>
       <c r="S41" s="41"/>
-      <c r="T41" s="41"/>
-      <c r="U41" s="41"/>
-      <c r="V41" s="41"/>
-      <c r="W41" s="41"/>
-      <c r="X41" s="41"/>
-      <c r="Y41" s="41"/>
-      <c r="Z41" s="41"/>
-      <c r="AA41" s="41"/>
-      <c r="AB41" s="41"/>
-      <c r="AC41" s="41"/>
-      <c r="AD41" s="41"/>
-      <c r="AE41" s="17"/>
-      <c r="AF41" s="41"/>
-      <c r="AG41" s="41"/>
-      <c r="AH41" s="41"/>
-      <c r="AI41" s="41"/>
-      <c r="AJ41" s="41"/>
-      <c r="AK41" s="41"/>
-      <c r="AL41" s="41"/>
-      <c r="AM41" s="41"/>
-      <c r="AN41" s="41"/>
-      <c r="AO41" s="41"/>
+      <c r="T41" s="41">
+        <v>0.16</v>
+      </c>
+      <c r="U41" s="41">
+        <v>0.1</v>
+      </c>
+      <c r="V41" s="41">
+        <v>3.11</v>
+      </c>
+      <c r="W41" s="41">
+        <v>7.2750000000000004</v>
+      </c>
+      <c r="X41" s="41">
+        <v>45</v>
+      </c>
+      <c r="Y41" s="41">
+        <v>65.400000000000006</v>
+      </c>
+      <c r="Z41" s="41">
+        <v>2.83</v>
+      </c>
+      <c r="AA41" s="41">
+        <v>135.80000000000001</v>
+      </c>
+      <c r="AB41" s="41">
+        <v>18.5</v>
+      </c>
+      <c r="AC41" s="41">
+        <v>39.4</v>
+      </c>
+      <c r="AD41" s="41">
+        <v>53.3</v>
+      </c>
+      <c r="AE41" s="17">
+        <v>7.234</v>
+      </c>
+      <c r="AF41" s="41">
+        <v>406</v>
+      </c>
+      <c r="AG41" s="41">
+        <v>51.1</v>
+      </c>
+      <c r="AH41" s="41">
+        <v>7.3090000000000002</v>
+      </c>
+      <c r="AI41" s="41">
+        <v>33.9</v>
+      </c>
+      <c r="AJ41" s="41">
+        <v>2.1</v>
+      </c>
+      <c r="AK41" s="41">
+        <v>1.2</v>
+      </c>
+      <c r="AL41" s="41">
+        <v>0.1</v>
+      </c>
+      <c r="AM41" s="41">
+        <v>6</v>
+      </c>
+      <c r="AN41" s="41">
+        <v>4.3</v>
+      </c>
+      <c r="AO41" s="41">
+        <v>197.4</v>
+      </c>
       <c r="AP41" s="74"/>
       <c r="AQ41" s="42">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>0.51100000000000001</v>
       </c>
       <c r="AR41" s="42">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>8.9540639999999991E-2</v>
       </c>
       <c r="AS41" s="42">
         <f t="shared" si="23"/>
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="AT41" s="42">
         <f t="shared" si="24"/>
-        <v>-3</v>
+        <v>1.2999999999999998</v>
       </c>
       <c r="AU41" s="42">
         <f t="shared" si="25"/>
@@ -10056,27 +10234,27 @@
       <c r="BD41" s="22"/>
       <c r="BE41" s="43">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1.4923439999999998E-3</v>
       </c>
       <c r="BF41" s="43">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>2.1489753599999997</v>
       </c>
       <c r="BG41" s="43">
         <f t="shared" si="45"/>
-        <v>188</v>
-      </c>
-      <c r="BH41" s="44" t="str">
+        <v>197.4</v>
+      </c>
+      <c r="BH41" s="44">
         <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="BI41" s="44" t="str">
+        <v>3.0395136778115502E-2</v>
+      </c>
+      <c r="BI41" s="44">
         <f t="shared" si="47"/>
-        <v/>
+        <v>0.03</v>
       </c>
       <c r="BJ41" s="44">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>128.93852159999997</v>
       </c>
       <c r="BK41" s="44" t="str">
         <f t="shared" si="19"/>
@@ -10088,11 +10266,11 @@
       </c>
       <c r="BM41" s="45">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>8.9540639999999991E-2</v>
       </c>
       <c r="BN41" s="44">
         <f t="shared" si="32"/>
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BO41" s="44" t="str">
         <f t="shared" si="49"/>
@@ -10100,15 +10278,15 @@
       </c>
       <c r="BP41" s="58">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>232.57309090909089</v>
       </c>
       <c r="BQ41" s="46">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>8.9540639999999991E-2</v>
       </c>
       <c r="BR41" s="24">
         <f t="shared" si="54"/>
-        <v>1.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:70" s="40" customFormat="1" x14ac:dyDescent="0.3">
@@ -10127,59 +10305,123 @@
       <c r="E42" s="40">
         <v>4</v>
       </c>
-      <c r="G42" s="35"/>
+      <c r="G42" s="35">
+        <v>45572.404166666667</v>
+      </c>
       <c r="H42" s="40">
         <v>2119.61</v>
       </c>
       <c r="I42" s="41"/>
-      <c r="J42" s="41"/>
-      <c r="K42" s="41"/>
-      <c r="L42" s="41"/>
-      <c r="M42" s="41"/>
-      <c r="N42" s="41"/>
-      <c r="O42" s="41"/>
-      <c r="P42" s="41"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="41"/>
+      <c r="J42" s="41">
+        <v>1675.365</v>
+      </c>
+      <c r="K42" s="41">
+        <v>24.8</v>
+      </c>
+      <c r="L42" s="41">
+        <v>22.8</v>
+      </c>
+      <c r="M42" s="41">
+        <v>91.9</v>
+      </c>
+      <c r="N42" s="41">
+        <v>16.7</v>
+      </c>
+      <c r="O42" s="41">
+        <v>350</v>
+      </c>
+      <c r="P42" s="41">
+        <v>2.69</v>
+      </c>
+      <c r="Q42" s="41">
+        <v>0.44</v>
+      </c>
+      <c r="R42" s="41">
+        <v>0.28999999999999998</v>
+      </c>
       <c r="S42" s="41"/>
-      <c r="T42" s="41"/>
-      <c r="U42" s="41"/>
-      <c r="V42" s="41"/>
-      <c r="W42" s="41"/>
-      <c r="X42" s="41"/>
-      <c r="Y42" s="41"/>
-      <c r="Z42" s="41"/>
-      <c r="AA42" s="41"/>
-      <c r="AB42" s="41"/>
-      <c r="AC42" s="41"/>
-      <c r="AD42" s="41"/>
-      <c r="AE42" s="17"/>
-      <c r="AF42" s="41"/>
-      <c r="AG42" s="41"/>
-      <c r="AH42" s="41"/>
-      <c r="AI42" s="41"/>
-      <c r="AJ42" s="41"/>
-      <c r="AK42" s="41"/>
-      <c r="AL42" s="41"/>
-      <c r="AM42" s="41"/>
-      <c r="AN42" s="41"/>
-      <c r="AO42" s="41"/>
+      <c r="T42" s="41">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="U42" s="41">
+        <v>0.09</v>
+      </c>
+      <c r="V42" s="41">
+        <v>5.22</v>
+      </c>
+      <c r="W42" s="41">
+        <v>7.2809999999999997</v>
+      </c>
+      <c r="X42" s="41">
+        <v>40.6</v>
+      </c>
+      <c r="Y42" s="41">
+        <v>61.6</v>
+      </c>
+      <c r="Z42" s="41">
+        <v>2.74</v>
+      </c>
+      <c r="AA42" s="41">
+        <v>155</v>
+      </c>
+      <c r="AB42" s="41">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="AC42" s="41">
+        <v>35.6</v>
+      </c>
+      <c r="AD42" s="41">
+        <v>50.1</v>
+      </c>
+      <c r="AE42" s="17">
+        <v>7.24</v>
+      </c>
+      <c r="AF42" s="41">
+        <v>410</v>
+      </c>
+      <c r="AG42" s="41">
+        <v>51</v>
+      </c>
+      <c r="AH42" s="41">
+        <v>7.3120000000000003</v>
+      </c>
+      <c r="AI42" s="41">
+        <v>33.9</v>
+      </c>
+      <c r="AJ42" s="41">
+        <v>3.4</v>
+      </c>
+      <c r="AK42" s="41">
+        <v>1.7</v>
+      </c>
+      <c r="AL42" s="41">
+        <v>0.1</v>
+      </c>
+      <c r="AM42" s="41">
+        <v>7.5</v>
+      </c>
+      <c r="AN42" s="41">
+        <v>3.1</v>
+      </c>
+      <c r="AO42" s="41">
+        <v>199.8</v>
+      </c>
       <c r="AP42" s="74"/>
       <c r="AQ42" s="42">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="AR42" s="42">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>0.16650000000000001</v>
       </c>
       <c r="AS42" s="42">
         <f t="shared" si="23"/>
-        <v>-6.1</v>
+        <v>1.4000000000000004</v>
       </c>
       <c r="AT42" s="42">
         <f t="shared" si="24"/>
-        <v>-1.7</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="AU42" s="42">
         <f t="shared" si="25"/>
@@ -10203,36 +10445,38 @@
       <c r="BA42" s="43">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BB42" s="11"/>
+      <c r="BB42" s="11">
+        <v>0.02</v>
+      </c>
       <c r="BC42" s="43"/>
       <c r="BD42" s="22"/>
       <c r="BE42" s="43">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1.366632E-3</v>
       </c>
       <c r="BF42" s="43">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>1.9679500800000003</v>
       </c>
       <c r="BG42" s="43">
         <f t="shared" si="45"/>
-        <v>188</v>
-      </c>
-      <c r="BH42" s="44" t="str">
+        <v>199.8</v>
+      </c>
+      <c r="BH42" s="44">
         <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="BI42" s="44" t="str">
+        <v>3.7537537537537538E-2</v>
+      </c>
+      <c r="BI42" s="44">
         <f t="shared" si="47"/>
-        <v/>
+        <v>3.7499999999999999E-2</v>
       </c>
       <c r="BJ42" s="44">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>239.76000000000002</v>
       </c>
       <c r="BK42" s="44">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>0.16650000000000001</v>
       </c>
       <c r="BL42" s="44" t="str">
         <f t="shared" si="12"/>
@@ -10244,7 +10488,7 @@
       </c>
       <c r="BN42" s="44">
         <f t="shared" si="32"/>
-        <v>1.41</v>
+        <v>1.353645</v>
       </c>
       <c r="BO42" s="44" t="str">
         <f t="shared" si="49"/>
@@ -10252,15 +10496,15 @@
       </c>
       <c r="BP42" s="58">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>432.46753246753252</v>
       </c>
       <c r="BQ42" s="46">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>0.16650000000000001</v>
       </c>
       <c r="BR42" s="24">
         <f t="shared" si="54"/>
-        <v>1.41</v>
+        <v>1.353645</v>
       </c>
     </row>
     <row r="43" spans="1:70" s="40" customFormat="1" x14ac:dyDescent="0.3">
@@ -10279,59 +10523,123 @@
       <c r="E43" s="40">
         <v>4</v>
       </c>
-      <c r="G43" s="35"/>
+      <c r="G43" s="35">
+        <v>45572.404861111114</v>
+      </c>
       <c r="H43" s="40">
         <v>2119.61</v>
       </c>
       <c r="I43" s="41"/>
-      <c r="J43" s="41"/>
-      <c r="K43" s="41"/>
-      <c r="L43" s="41"/>
-      <c r="M43" s="41"/>
-      <c r="N43" s="41"/>
-      <c r="O43" s="41"/>
-      <c r="P43" s="41"/>
-      <c r="Q43" s="41"/>
-      <c r="R43" s="41"/>
+      <c r="J43" s="41">
+        <v>1739.34</v>
+      </c>
+      <c r="K43" s="41">
+        <v>25.9</v>
+      </c>
+      <c r="L43" s="41">
+        <v>23.9</v>
+      </c>
+      <c r="M43" s="41">
+        <v>92.1</v>
+      </c>
+      <c r="N43" s="41">
+        <v>16.7</v>
+      </c>
+      <c r="O43" s="41">
+        <v>333</v>
+      </c>
+      <c r="P43" s="41">
+        <v>1.4</v>
+      </c>
+      <c r="Q43" s="41">
+        <v>0.44</v>
+      </c>
+      <c r="R43" s="41">
+        <v>2.78</v>
+      </c>
       <c r="S43" s="41"/>
-      <c r="T43" s="41"/>
-      <c r="U43" s="41"/>
-      <c r="V43" s="41"/>
-      <c r="W43" s="41"/>
-      <c r="X43" s="41"/>
-      <c r="Y43" s="41"/>
-      <c r="Z43" s="41"/>
-      <c r="AA43" s="41"/>
-      <c r="AB43" s="41"/>
-      <c r="AC43" s="41"/>
-      <c r="AD43" s="41"/>
-      <c r="AE43" s="17"/>
-      <c r="AF43" s="41"/>
-      <c r="AG43" s="41"/>
-      <c r="AH43" s="41"/>
-      <c r="AI43" s="41"/>
-      <c r="AJ43" s="41"/>
-      <c r="AK43" s="41"/>
-      <c r="AL43" s="41"/>
-      <c r="AM43" s="41"/>
-      <c r="AN43" s="41"/>
-      <c r="AO43" s="41"/>
+      <c r="T43" s="41">
+        <v>0.17</v>
+      </c>
+      <c r="U43" s="41">
+        <v>0.08</v>
+      </c>
+      <c r="V43" s="41">
+        <v>3.71</v>
+      </c>
+      <c r="W43" s="41">
+        <v>7.2320000000000002</v>
+      </c>
+      <c r="X43" s="41">
+        <v>36.1</v>
+      </c>
+      <c r="Y43" s="41">
+        <v>56.8</v>
+      </c>
+      <c r="Z43" s="41">
+        <v>2.13</v>
+      </c>
+      <c r="AA43" s="41">
+        <v>138.1</v>
+      </c>
+      <c r="AB43" s="41">
+        <v>13.5</v>
+      </c>
+      <c r="AC43" s="41">
+        <v>31.7</v>
+      </c>
+      <c r="AD43" s="41">
+        <v>46.1</v>
+      </c>
+      <c r="AE43" s="17">
+        <v>7.1920000000000002</v>
+      </c>
+      <c r="AF43" s="41">
+        <v>412</v>
+      </c>
+      <c r="AG43" s="41">
+        <v>50.2</v>
+      </c>
+      <c r="AH43" s="41">
+        <v>7.2770000000000001</v>
+      </c>
+      <c r="AI43" s="41">
+        <v>33.9</v>
+      </c>
+      <c r="AJ43" s="41">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AK43" s="41">
+        <v>1.3</v>
+      </c>
+      <c r="AL43" s="41">
+        <v>0.1</v>
+      </c>
+      <c r="AM43" s="41">
+        <v>7.6</v>
+      </c>
+      <c r="AN43" s="41">
+        <v>3.9</v>
+      </c>
+      <c r="AO43" s="41">
+        <v>199.2</v>
+      </c>
       <c r="AP43" s="74"/>
       <c r="AQ43" s="42">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>0.502</v>
       </c>
       <c r="AR43" s="42">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>0.16600000000000001</v>
       </c>
       <c r="AS43" s="42">
         <f t="shared" si="23"/>
-        <v>-4</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="AT43" s="42">
         <f t="shared" si="24"/>
-        <v>-2.5</v>
+        <v>1.4</v>
       </c>
       <c r="AU43" s="42">
         <f t="shared" si="25"/>
@@ -10355,35 +10663,37 @@
       <c r="BA43" s="43">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BB43" s="11"/>
+      <c r="BB43" s="11">
+        <v>0.02</v>
+      </c>
       <c r="BD43" s="22"/>
       <c r="BE43" s="43">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1.4282639999999998E-3</v>
       </c>
       <c r="BF43" s="43">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>2.0567001599999997</v>
       </c>
       <c r="BG43" s="43">
         <f t="shared" si="45"/>
-        <v>188</v>
-      </c>
-      <c r="BH43" s="44" t="str">
+        <v>199.2</v>
+      </c>
+      <c r="BH43" s="44">
         <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="BI43" s="44" t="str">
+        <v>3.8152610441767071E-2</v>
+      </c>
+      <c r="BI43" s="44">
         <f t="shared" si="47"/>
-        <v/>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="BJ43" s="44">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>239.04</v>
       </c>
       <c r="BK43" s="44">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>0.16600000000000001</v>
       </c>
       <c r="BL43" s="45" t="str">
         <f t="shared" si="12"/>
@@ -10395,7 +10705,7 @@
       </c>
       <c r="BN43" s="44">
         <f t="shared" si="32"/>
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BO43" s="44" t="str">
         <f t="shared" si="49"/>
@@ -10403,15 +10713,15 @@
       </c>
       <c r="BP43" s="58">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>431.16883116883122</v>
       </c>
       <c r="BQ43" s="46">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>0.16600000000000001</v>
       </c>
       <c r="BR43" s="24">
         <f t="shared" si="54"/>
-        <v>1.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:70" s="40" customFormat="1" x14ac:dyDescent="0.3">
@@ -10430,59 +10740,123 @@
       <c r="E44" s="40">
         <v>4</v>
       </c>
-      <c r="G44" s="35"/>
+      <c r="G44" s="35">
+        <v>45572.40625</v>
+      </c>
       <c r="H44" s="40">
         <v>2119.61</v>
       </c>
       <c r="I44" s="41"/>
-      <c r="J44" s="41"/>
-      <c r="K44" s="41"/>
-      <c r="L44" s="41"/>
-      <c r="M44" s="41"/>
-      <c r="N44" s="41"/>
-      <c r="O44" s="41"/>
-      <c r="P44" s="41"/>
-      <c r="Q44" s="41"/>
-      <c r="R44" s="41"/>
+      <c r="J44" s="41">
+        <v>1851.24</v>
+      </c>
+      <c r="K44" s="41">
+        <v>26.4</v>
+      </c>
+      <c r="L44" s="41">
+        <v>24.8</v>
+      </c>
+      <c r="M44" s="41">
+        <v>94</v>
+      </c>
+      <c r="N44" s="41">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="O44" s="41">
+        <v>324</v>
+      </c>
+      <c r="P44" s="41">
+        <v>1.34</v>
+      </c>
+      <c r="Q44" s="41">
+        <v>0.39</v>
+      </c>
+      <c r="R44" s="41">
+        <v>1.64</v>
+      </c>
       <c r="S44" s="41"/>
-      <c r="T44" s="41"/>
-      <c r="U44" s="41"/>
-      <c r="V44" s="41"/>
-      <c r="W44" s="41"/>
-      <c r="X44" s="41"/>
-      <c r="Y44" s="41"/>
-      <c r="Z44" s="41"/>
-      <c r="AA44" s="41"/>
-      <c r="AB44" s="41"/>
-      <c r="AC44" s="41"/>
-      <c r="AD44" s="41"/>
-      <c r="AE44" s="17"/>
-      <c r="AF44" s="41"/>
-      <c r="AG44" s="41"/>
-      <c r="AH44" s="41"/>
-      <c r="AI44" s="41"/>
-      <c r="AJ44" s="41"/>
-      <c r="AK44" s="41"/>
-      <c r="AL44" s="41"/>
-      <c r="AM44" s="41"/>
-      <c r="AN44" s="41"/>
-      <c r="AO44" s="41"/>
+      <c r="T44" s="41">
+        <v>0.16</v>
+      </c>
+      <c r="U44" s="41">
+        <v>0.08</v>
+      </c>
+      <c r="V44" s="41">
+        <v>3.51</v>
+      </c>
+      <c r="W44" s="41">
+        <v>7.2720000000000002</v>
+      </c>
+      <c r="X44" s="41">
+        <v>32.4</v>
+      </c>
+      <c r="Y44" s="41">
+        <v>48.5</v>
+      </c>
+      <c r="Z44" s="41">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="AA44" s="41">
+        <v>139.4</v>
+      </c>
+      <c r="AB44" s="41">
+        <v>13.2</v>
+      </c>
+      <c r="AC44" s="41">
+        <v>28.5</v>
+      </c>
+      <c r="AD44" s="41">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="AE44" s="17">
+        <v>7.2309999999999999</v>
+      </c>
+      <c r="AF44" s="41">
+        <v>407</v>
+      </c>
+      <c r="AG44" s="41">
+        <v>51</v>
+      </c>
+      <c r="AH44" s="41">
+        <v>7.298</v>
+      </c>
+      <c r="AI44" s="41">
+        <v>33.9</v>
+      </c>
+      <c r="AJ44" s="41">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AK44" s="41">
+        <v>0.5</v>
+      </c>
+      <c r="AL44" s="41">
+        <v>0.1</v>
+      </c>
+      <c r="AM44" s="41">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="AN44" s="41">
+        <v>3.6</v>
+      </c>
+      <c r="AO44" s="41">
+        <v>198.1</v>
+      </c>
       <c r="AP44" s="74"/>
       <c r="AQ44" s="42">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="AR44" s="42">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>0.14890513359397919</v>
       </c>
       <c r="AS44" s="42">
         <f t="shared" ref="AS44:AS75" si="55">AM44-AM35</f>
-        <v>-5.8</v>
+        <v>2.8999999999999995</v>
       </c>
       <c r="AT44" s="42">
         <f t="shared" ref="AT44:AT75" si="56">AN44-AN35</f>
-        <v>-2.6</v>
+        <v>1</v>
       </c>
       <c r="AU44" s="42">
         <f t="shared" ref="AU44:AU75" si="57">AP35-AP44</f>
@@ -10507,30 +10881,37 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BB44" s="11"/>
-      <c r="BD44" s="22"/>
+      <c r="BC44" s="81">
+        <f>0.00248175222656632*24*60/BG44</f>
+        <v>1.8039995993213025E-2</v>
+      </c>
+      <c r="BD44" s="81">
+        <f>0.176367129335544/BG44</f>
+        <v>8.9029343430360426E-4</v>
+      </c>
       <c r="BE44" s="43">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1.4738639999999999E-3</v>
       </c>
       <c r="BF44" s="43">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>2.1223641599999996</v>
       </c>
       <c r="BG44" s="43">
         <f t="shared" si="45"/>
-        <v>188</v>
-      </c>
-      <c r="BH44" s="44" t="str">
+        <v>198.1</v>
+      </c>
+      <c r="BH44" s="44">
         <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="BI44" s="44" t="str">
+        <v>4.3917213528520946E-2</v>
+      </c>
+      <c r="BI44" s="44">
         <f t="shared" si="47"/>
-        <v/>
+        <v>4.3499999999999997E-2</v>
       </c>
       <c r="BJ44" s="44">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>214.42339237533005</v>
       </c>
       <c r="BK44" s="44" t="str">
         <f t="shared" si="19"/>
@@ -10538,7 +10919,7 @@
       </c>
       <c r="BL44" s="45">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>0.14890513359397919</v>
       </c>
       <c r="BM44" s="45" t="str">
         <f t="shared" si="13"/>
@@ -10550,19 +10931,19 @@
       </c>
       <c r="BO44" s="44">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>0.17636712933554399</v>
       </c>
       <c r="BP44" s="58">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>386.76658076358234</v>
       </c>
       <c r="BQ44" s="46">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>0.14890513359397919</v>
       </c>
       <c r="BR44" s="24">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>0.17636712933554399</v>
       </c>
     </row>
     <row r="45" spans="1:70" s="40" customFormat="1" x14ac:dyDescent="0.3">
@@ -10581,59 +10962,123 @@
       <c r="E45" s="40">
         <v>4</v>
       </c>
-      <c r="G45" s="35"/>
+      <c r="G45" s="35">
+        <v>45572.406944444447</v>
+      </c>
       <c r="H45" s="40">
         <v>2119.61</v>
       </c>
       <c r="I45" s="41"/>
-      <c r="J45" s="41"/>
-      <c r="K45" s="41"/>
-      <c r="L45" s="41"/>
-      <c r="M45" s="41"/>
-      <c r="N45" s="41"/>
-      <c r="O45" s="41"/>
-      <c r="P45" s="41"/>
-      <c r="Q45" s="41"/>
-      <c r="R45" s="41"/>
+      <c r="J45" s="41">
+        <v>1865.34</v>
+      </c>
+      <c r="K45" s="41">
+        <v>28.1</v>
+      </c>
+      <c r="L45" s="41">
+        <v>26.4</v>
+      </c>
+      <c r="M45" s="41">
+        <v>94</v>
+      </c>
+      <c r="N45" s="41">
+        <v>16.7</v>
+      </c>
+      <c r="O45" s="41">
+        <v>325</v>
+      </c>
+      <c r="P45" s="41">
+        <v>1.4</v>
+      </c>
+      <c r="Q45" s="41">
+        <v>0.39</v>
+      </c>
+      <c r="R45" s="41">
+        <v>1.78</v>
+      </c>
       <c r="S45" s="41"/>
-      <c r="T45" s="41"/>
-      <c r="U45" s="41"/>
-      <c r="V45" s="41"/>
-      <c r="W45" s="41"/>
-      <c r="X45" s="41"/>
-      <c r="Y45" s="41"/>
-      <c r="Z45" s="41"/>
-      <c r="AA45" s="41"/>
-      <c r="AB45" s="41"/>
-      <c r="AC45" s="41"/>
-      <c r="AD45" s="41"/>
-      <c r="AE45" s="17"/>
-      <c r="AF45" s="41"/>
-      <c r="AG45" s="41"/>
-      <c r="AH45" s="41"/>
-      <c r="AI45" s="41"/>
-      <c r="AJ45" s="41"/>
-      <c r="AK45" s="41"/>
-      <c r="AL45" s="41"/>
-      <c r="AM45" s="41"/>
-      <c r="AN45" s="41"/>
-      <c r="AO45" s="41"/>
+      <c r="T45" s="41">
+        <v>0.16</v>
+      </c>
+      <c r="U45" s="41">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="V45" s="41">
+        <v>3.47</v>
+      </c>
+      <c r="W45" s="41">
+        <v>7.26</v>
+      </c>
+      <c r="X45" s="41">
+        <v>33.1</v>
+      </c>
+      <c r="Y45" s="41">
+        <v>52.9</v>
+      </c>
+      <c r="Z45" s="41">
+        <v>2.17</v>
+      </c>
+      <c r="AA45" s="41">
+        <v>138</v>
+      </c>
+      <c r="AB45" s="41">
+        <v>13.2</v>
+      </c>
+      <c r="AC45" s="41">
+        <v>29.1</v>
+      </c>
+      <c r="AD45" s="41">
+        <v>43</v>
+      </c>
+      <c r="AE45" s="17">
+        <v>7.22</v>
+      </c>
+      <c r="AF45" s="41">
+        <v>409</v>
+      </c>
+      <c r="AG45" s="41">
+        <v>52.6</v>
+      </c>
+      <c r="AH45" s="41">
+        <v>7.3040000000000003</v>
+      </c>
+      <c r="AI45" s="41">
+        <v>33.9</v>
+      </c>
+      <c r="AJ45" s="41">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AK45" s="41">
+        <v>1</v>
+      </c>
+      <c r="AL45" s="41">
+        <v>0.1</v>
+      </c>
+      <c r="AM45" s="41">
+        <v>8.5</v>
+      </c>
+      <c r="AN45" s="41">
+        <v>3.7</v>
+      </c>
+      <c r="AO45" s="41">
+        <v>198.9</v>
+      </c>
       <c r="AP45" s="74"/>
       <c r="AQ45" s="42">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>0.52600000000000002</v>
       </c>
       <c r="AR45" s="42">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>0.16320476690989325</v>
       </c>
       <c r="AS45" s="42">
         <f t="shared" si="55"/>
-        <v>-5.9</v>
+        <v>2.5999999999999996</v>
       </c>
       <c r="AT45" s="42">
         <f t="shared" si="56"/>
-        <v>-2.7</v>
+        <v>1</v>
       </c>
       <c r="AU45" s="42">
         <f t="shared" si="57"/>
@@ -10658,30 +11103,37 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BB45" s="11"/>
-      <c r="BD45" s="22"/>
+      <c r="BC45" s="81">
+        <f>0.00272007944849822*24*60/BG45</f>
+        <v>1.9692882885054989E-2</v>
+      </c>
+      <c r="BD45" s="81">
+        <f>0.507148200573381/BG45</f>
+        <v>2.5497647087651129E-3</v>
+      </c>
       <c r="BE45" s="43">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1.5752879999999998E-3</v>
       </c>
       <c r="BF45" s="43">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>2.26841472</v>
       </c>
       <c r="BG45" s="43">
         <f t="shared" si="45"/>
-        <v>188</v>
-      </c>
-      <c r="BH45" s="44" t="str">
+        <v>198.9</v>
+      </c>
+      <c r="BH45" s="44">
         <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="BI45" s="44" t="str">
+        <v>4.2735042735042736E-2</v>
+      </c>
+      <c r="BI45" s="44">
         <f t="shared" si="47"/>
-        <v/>
+        <v>4.2500000000000003E-2</v>
       </c>
       <c r="BJ45" s="44">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>235.01486435024626</v>
       </c>
       <c r="BK45" s="44" t="str">
         <f t="shared" si="19"/>
@@ -10689,7 +11141,7 @@
       </c>
       <c r="BL45" s="45">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>0.16320476690989325</v>
       </c>
       <c r="BM45" s="45" t="str">
         <f t="shared" si="13"/>
@@ -10701,19 +11153,19 @@
       </c>
       <c r="BO45" s="44">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>0.50714820057338095</v>
       </c>
       <c r="BP45" s="58">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>423.90848548024223</v>
       </c>
       <c r="BQ45" s="46">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>0.16320476690989325</v>
       </c>
       <c r="BR45" s="24">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>0.50714820057338095</v>
       </c>
     </row>
     <row r="46" spans="1:70" s="40" customFormat="1" x14ac:dyDescent="0.3">
@@ -10732,58 +11184,122 @@
       <c r="E46" s="40">
         <v>4</v>
       </c>
-      <c r="G46" s="35"/>
+      <c r="G46" s="35">
+        <v>45572.407638888886</v>
+      </c>
       <c r="H46" s="40">
         <v>2119.61</v>
       </c>
-      <c r="J46" s="41"/>
-      <c r="K46" s="41"/>
-      <c r="L46" s="41"/>
-      <c r="M46" s="41"/>
-      <c r="N46" s="41"/>
-      <c r="O46" s="41"/>
-      <c r="P46" s="41"/>
-      <c r="Q46" s="41"/>
-      <c r="R46" s="41"/>
+      <c r="J46" s="41">
+        <v>1668.4349999999999</v>
+      </c>
+      <c r="K46" s="41">
+        <v>25.5</v>
+      </c>
+      <c r="L46" s="41">
+        <v>23.5</v>
+      </c>
+      <c r="M46" s="41">
+        <v>92.4</v>
+      </c>
+      <c r="N46" s="41">
+        <v>16.3</v>
+      </c>
+      <c r="O46" s="41">
+        <v>330</v>
+      </c>
+      <c r="P46" s="41">
+        <v>1.47</v>
+      </c>
+      <c r="Q46" s="41">
+        <v>0.44</v>
+      </c>
+      <c r="R46" s="41">
+        <v>1.81</v>
+      </c>
       <c r="S46" s="41"/>
-      <c r="T46" s="41"/>
-      <c r="U46" s="41"/>
-      <c r="V46" s="41"/>
-      <c r="W46" s="41"/>
-      <c r="X46" s="41"/>
-      <c r="Y46" s="41"/>
-      <c r="Z46" s="41"/>
-      <c r="AA46" s="41"/>
-      <c r="AB46" s="41"/>
-      <c r="AC46" s="41"/>
-      <c r="AD46" s="41"/>
-      <c r="AE46" s="17"/>
-      <c r="AF46" s="41"/>
-      <c r="AG46" s="41"/>
-      <c r="AH46" s="41"/>
-      <c r="AI46" s="41"/>
-      <c r="AJ46" s="41"/>
-      <c r="AK46" s="41"/>
-      <c r="AL46" s="41"/>
-      <c r="AM46" s="41"/>
-      <c r="AN46" s="41"/>
-      <c r="AO46" s="41"/>
+      <c r="T46" s="41">
+        <v>0.13</v>
+      </c>
+      <c r="U46" s="41">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="V46" s="41">
+        <v>3.76</v>
+      </c>
+      <c r="W46" s="41">
+        <v>7.27</v>
+      </c>
+      <c r="X46" s="41">
+        <v>53.6</v>
+      </c>
+      <c r="Y46" s="41">
+        <v>59.9</v>
+      </c>
+      <c r="Z46" s="41">
+        <v>2.6</v>
+      </c>
+      <c r="AA46" s="41">
+        <v>143</v>
+      </c>
+      <c r="AB46" s="41">
+        <v>21.8</v>
+      </c>
+      <c r="AC46" s="41">
+        <v>47</v>
+      </c>
+      <c r="AD46" s="41">
+        <v>48.7</v>
+      </c>
+      <c r="AE46" s="17">
+        <v>7.2290000000000001</v>
+      </c>
+      <c r="AF46" s="41">
+        <v>680</v>
+      </c>
+      <c r="AG46" s="41">
+        <v>0.5</v>
+      </c>
+      <c r="AH46" s="41">
+        <v>7.2930000000000001</v>
+      </c>
+      <c r="AI46" s="41">
+        <v>33.9</v>
+      </c>
+      <c r="AJ46" s="41">
+        <v>2.6</v>
+      </c>
+      <c r="AK46" s="41">
+        <v>1.2</v>
+      </c>
+      <c r="AL46" s="41">
+        <v>0.1</v>
+      </c>
+      <c r="AM46" s="41">
+        <v>5.7</v>
+      </c>
+      <c r="AN46" s="41">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AO46" s="41">
+        <v>198.4</v>
+      </c>
       <c r="AP46" s="74"/>
       <c r="AQ46" s="42">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="AR46" s="42">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>8.3923199999999989E-2</v>
       </c>
       <c r="AS46" s="42">
         <f t="shared" si="55"/>
-        <v>-3.7</v>
+        <v>2</v>
       </c>
       <c r="AT46" s="42">
         <f t="shared" si="56"/>
-        <v>-3</v>
+        <v>1.4000000000000004</v>
       </c>
       <c r="AU46" s="42">
         <f t="shared" si="57"/>
@@ -10811,27 +11327,27 @@
       <c r="BD46" s="22"/>
       <c r="BE46" s="43">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1.3987199999999998E-3</v>
       </c>
       <c r="BF46" s="43">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>2.0141567999999994</v>
       </c>
       <c r="BG46" s="43">
         <f t="shared" si="45"/>
-        <v>188</v>
-      </c>
-      <c r="BH46" s="44" t="str">
+        <v>198.4</v>
+      </c>
+      <c r="BH46" s="44">
         <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="BI46" s="44" t="str">
+        <v>2.8729838709677418E-2</v>
+      </c>
+      <c r="BI46" s="44">
         <f t="shared" si="47"/>
-        <v/>
+        <v>2.8500000000000001E-2</v>
       </c>
       <c r="BJ46" s="44">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>120.849408</v>
       </c>
       <c r="BK46" s="44" t="str">
         <f t="shared" si="19"/>
@@ -10843,11 +11359,11 @@
       </c>
       <c r="BM46" s="45">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>8.3923199999999989E-2</v>
       </c>
       <c r="BN46" s="44">
         <f t="shared" si="32"/>
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BO46" s="44" t="str">
         <f t="shared" si="49"/>
@@ -10855,15 +11371,15 @@
       </c>
       <c r="BP46" s="58">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>217.98233766233764</v>
       </c>
       <c r="BQ46" s="46">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>8.3923199999999989E-2</v>
       </c>
       <c r="BR46" s="24">
         <f t="shared" si="54"/>
-        <v>1.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:70" s="40" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -10882,58 +11398,122 @@
       <c r="E47" s="40">
         <v>4</v>
       </c>
-      <c r="G47" s="35"/>
+      <c r="G47" s="35">
+        <v>45572.408333333333</v>
+      </c>
       <c r="H47" s="40">
         <v>2119.61</v>
       </c>
-      <c r="J47" s="41"/>
-      <c r="K47" s="41"/>
-      <c r="L47" s="41"/>
-      <c r="M47" s="41"/>
-      <c r="N47" s="41"/>
-      <c r="O47" s="41"/>
-      <c r="P47" s="41"/>
-      <c r="Q47" s="41"/>
-      <c r="R47" s="41"/>
+      <c r="J47" s="41">
+        <v>1775.5350000000001</v>
+      </c>
+      <c r="K47" s="41">
+        <v>26.8</v>
+      </c>
+      <c r="L47" s="41">
+        <v>25.3</v>
+      </c>
+      <c r="M47" s="41">
+        <v>94.3</v>
+      </c>
+      <c r="N47" s="41">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="O47" s="41">
+        <v>322</v>
+      </c>
+      <c r="P47" s="41">
+        <v>1.43</v>
+      </c>
+      <c r="Q47" s="41">
+        <v>0.41</v>
+      </c>
+      <c r="R47" s="41">
+        <v>2.1</v>
+      </c>
       <c r="S47" s="41"/>
-      <c r="T47" s="41"/>
-      <c r="U47" s="41"/>
-      <c r="V47" s="41"/>
-      <c r="W47" s="41"/>
-      <c r="X47" s="41"/>
-      <c r="Y47" s="41"/>
-      <c r="Z47" s="41"/>
-      <c r="AA47" s="41"/>
-      <c r="AB47" s="41"/>
-      <c r="AC47" s="41"/>
-      <c r="AD47" s="41"/>
-      <c r="AE47" s="17"/>
-      <c r="AF47" s="41"/>
-      <c r="AG47" s="41"/>
-      <c r="AH47" s="41"/>
-      <c r="AI47" s="41"/>
-      <c r="AJ47" s="41"/>
-      <c r="AK47" s="41"/>
-      <c r="AL47" s="41"/>
-      <c r="AM47" s="41"/>
-      <c r="AN47" s="41"/>
-      <c r="AO47" s="41"/>
+      <c r="T47" s="41">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="U47" s="41">
+        <v>0.08</v>
+      </c>
+      <c r="V47" s="41">
+        <v>3.38</v>
+      </c>
+      <c r="W47" s="41">
+        <v>7.2690000000000001</v>
+      </c>
+      <c r="X47" s="41">
+        <v>43.2</v>
+      </c>
+      <c r="Y47" s="41">
+        <v>60.6</v>
+      </c>
+      <c r="Z47" s="41">
+        <v>2.66</v>
+      </c>
+      <c r="AA47" s="41">
+        <v>137.4</v>
+      </c>
+      <c r="AB47" s="41">
+        <v>17.5</v>
+      </c>
+      <c r="AC47" s="41">
+        <v>37.9</v>
+      </c>
+      <c r="AD47" s="41">
+        <v>49.3</v>
+      </c>
+      <c r="AE47" s="17">
+        <v>7.2290000000000001</v>
+      </c>
+      <c r="AF47" s="41">
+        <v>469</v>
+      </c>
+      <c r="AG47" s="41">
+        <v>22.8</v>
+      </c>
+      <c r="AH47" s="41">
+        <v>7.298</v>
+      </c>
+      <c r="AI47" s="41">
+        <v>33.9</v>
+      </c>
+      <c r="AJ47" s="41">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AK47" s="41">
+        <v>1.4</v>
+      </c>
+      <c r="AL47" s="41">
+        <v>0.1</v>
+      </c>
+      <c r="AM47" s="41">
+        <v>5.9</v>
+      </c>
+      <c r="AN47" s="41">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AO47" s="41">
+        <v>198.2</v>
+      </c>
       <c r="AP47" s="75"/>
       <c r="AQ47" s="42">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>0.22800000000000001</v>
       </c>
       <c r="AR47" s="42">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>9.0260279999999998E-2</v>
       </c>
       <c r="AS47" s="42">
         <f t="shared" si="55"/>
-        <v>-3.9</v>
+        <v>2.0000000000000004</v>
       </c>
       <c r="AT47" s="42">
         <f t="shared" si="56"/>
-        <v>-3.1</v>
+        <v>1.3000000000000003</v>
       </c>
       <c r="AU47" s="42">
         <f t="shared" si="57"/>
@@ -10961,27 +11541,27 @@
       <c r="BD47" s="22"/>
       <c r="BE47" s="43">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1.5043379999999998E-3</v>
       </c>
       <c r="BF47" s="43">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>2.1662467199999997</v>
       </c>
       <c r="BG47" s="43">
         <f t="shared" si="45"/>
-        <v>188</v>
-      </c>
-      <c r="BH47" s="44" t="str">
+        <v>198.2</v>
+      </c>
+      <c r="BH47" s="44">
         <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="BI47" s="44" t="str">
+        <v>2.9767911200807268E-2</v>
+      </c>
+      <c r="BI47" s="44">
         <f t="shared" si="47"/>
-        <v/>
+        <v>2.9500000000000002E-2</v>
       </c>
       <c r="BJ47" s="44">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>129.9748032</v>
       </c>
       <c r="BK47" s="44" t="str">
         <f t="shared" si="19"/>
@@ -10993,11 +11573,11 @@
       </c>
       <c r="BM47" s="45">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>9.0260279999999998E-2</v>
       </c>
       <c r="BN47" s="44">
         <f t="shared" si="32"/>
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BO47" s="44" t="str">
         <f t="shared" si="49"/>
@@ -11005,15 +11585,15 @@
       </c>
       <c r="BP47" s="58">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>234.44228571428573</v>
       </c>
       <c r="BQ47" s="46">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>9.0260279999999998E-2</v>
       </c>
       <c r="BR47" s="24">
         <f t="shared" si="54"/>
-        <v>1.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:70" s="40" customFormat="1" x14ac:dyDescent="0.3">
@@ -11033,24 +11613,38 @@
         <v>5</v>
       </c>
       <c r="F48" s="3"/>
-      <c r="G48" s="34"/>
+      <c r="G48" s="34">
+        <v>45573.359722222223</v>
+      </c>
       <c r="H48" s="3">
         <v>2716.05</v>
       </c>
       <c r="I48" s="3"/>
-      <c r="J48" s="6"/>
-      <c r="K48" s="6"/>
-      <c r="L48" s="6"/>
-      <c r="M48" s="6"/>
+      <c r="J48" s="6">
+        <v>1932.48</v>
+      </c>
+      <c r="K48" s="6">
+        <v>22.2</v>
+      </c>
+      <c r="L48" s="6">
+        <v>21.1</v>
+      </c>
+      <c r="M48" s="6">
+        <v>95</v>
+      </c>
       <c r="N48" s="6"/>
       <c r="O48" s="6"/>
       <c r="P48" s="6"/>
       <c r="Q48" s="6"/>
-      <c r="R48" s="6"/>
+      <c r="R48" s="6">
+        <v>2.31</v>
+      </c>
       <c r="S48" s="6"/>
       <c r="T48" s="6"/>
       <c r="U48" s="6"/>
-      <c r="V48" s="6"/>
+      <c r="V48" s="6">
+        <v>2.23</v>
+      </c>
       <c r="W48" s="6"/>
       <c r="X48" s="6"/>
       <c r="Y48" s="6"/>
@@ -11059,21 +11653,33 @@
       <c r="AB48" s="6"/>
       <c r="AC48" s="6"/>
       <c r="AD48" s="6"/>
-      <c r="AE48" s="16"/>
+      <c r="AE48" s="16">
+        <v>7.31</v>
+      </c>
       <c r="AF48" s="6"/>
-      <c r="AG48" s="6"/>
+      <c r="AG48" s="6">
+        <v>49.9998439730619</v>
+      </c>
       <c r="AH48" s="6"/>
-      <c r="AI48" s="6"/>
+      <c r="AI48" s="6">
+        <v>33.998356455407396</v>
+      </c>
       <c r="AJ48" s="6"/>
       <c r="AK48" s="6"/>
       <c r="AL48" s="6"/>
-      <c r="AM48" s="6"/>
-      <c r="AN48" s="6"/>
-      <c r="AO48" s="6"/>
+      <c r="AM48" s="6">
+        <v>35159.5078125</v>
+      </c>
+      <c r="AN48" s="6">
+        <v>17535.712890625</v>
+      </c>
+      <c r="AO48" s="6">
+        <v>617400</v>
+      </c>
       <c r="AP48" s="72"/>
       <c r="AQ48" s="32">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>0.49999843973061897</v>
       </c>
       <c r="AR48" s="32">
         <f t="shared" si="50"/>
@@ -11081,11 +11687,11 @@
       </c>
       <c r="AS48" s="32">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>12852.744140625</v>
       </c>
       <c r="AT48" s="32">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>2616.2060546875</v>
       </c>
       <c r="AU48" s="32">
         <f t="shared" si="57"/>
@@ -11111,26 +11717,29 @@
       </c>
       <c r="BB48" s="8"/>
       <c r="BC48" s="9"/>
-      <c r="BD48" s="21"/>
+      <c r="BD48" s="21">
+        <f>3886.90413432793/BG48</f>
+        <v>6.2956011245998223E-3</v>
+      </c>
       <c r="BE48" s="9">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>5.2108560000000006</v>
       </c>
       <c r="BF48" s="9">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>7503.6326400000016</v>
       </c>
       <c r="BG48" s="9">
         <f t="shared" si="45"/>
-        <v>591640</v>
-      </c>
-      <c r="BH48" s="10" t="str">
+        <v>617400</v>
+      </c>
+      <c r="BH48" s="10">
         <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="BI48" s="10" t="str">
+        <v>5.6947696489310008E-2</v>
+      </c>
+      <c r="BI48" s="10">
         <f t="shared" si="47"/>
-        <v/>
+        <v>5.9391060494087836E-2</v>
       </c>
       <c r="BJ48" s="10">
         <f t="shared" si="48"/>
@@ -11154,7 +11763,7 @@
       </c>
       <c r="BO48" s="10">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>3886.9041343279305</v>
       </c>
       <c r="BP48" s="62">
         <f t="shared" si="52"/>
@@ -11166,7 +11775,7 @@
       </c>
       <c r="BR48" s="26">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>3886.9041343279305</v>
       </c>
     </row>
     <row r="49" spans="1:70" s="40" customFormat="1" x14ac:dyDescent="0.3">
@@ -11185,54 +11794,118 @@
       <c r="E49" s="40">
         <v>5</v>
       </c>
-      <c r="G49" s="35"/>
+      <c r="G49" s="35">
+        <v>45573.445590277777</v>
+      </c>
       <c r="H49" s="40">
         <v>2716.05</v>
       </c>
-      <c r="J49" s="41"/>
-      <c r="K49" s="41"/>
-      <c r="L49" s="41"/>
-      <c r="M49" s="41"/>
-      <c r="N49" s="41"/>
-      <c r="O49" s="41"/>
-      <c r="P49" s="41"/>
-      <c r="Q49" s="41"/>
-      <c r="R49" s="41"/>
+      <c r="J49" s="41">
+        <v>2466.585</v>
+      </c>
+      <c r="K49" s="41">
+        <v>23.280999999999999</v>
+      </c>
+      <c r="L49" s="41">
+        <v>21.760999999999999</v>
+      </c>
+      <c r="M49" s="41">
+        <v>93.5</v>
+      </c>
+      <c r="N49" s="41">
+        <v>15.73</v>
+      </c>
+      <c r="O49" s="41">
+        <v>322</v>
+      </c>
+      <c r="P49" s="41">
+        <v>1.43</v>
+      </c>
+      <c r="Q49" s="41">
+        <v>0.37</v>
+      </c>
+      <c r="R49" s="41">
+        <v>2.25</v>
+      </c>
       <c r="S49" s="41"/>
-      <c r="T49" s="41"/>
-      <c r="U49" s="41"/>
-      <c r="V49" s="41"/>
-      <c r="W49" s="41"/>
-      <c r="X49" s="41"/>
-      <c r="Y49" s="41"/>
-      <c r="Z49" s="41"/>
-      <c r="AA49" s="41"/>
-      <c r="AB49" s="41"/>
-      <c r="AC49" s="41"/>
-      <c r="AD49" s="41"/>
-      <c r="AE49" s="17"/>
-      <c r="AF49" s="41"/>
-      <c r="AG49" s="41"/>
-      <c r="AH49" s="41"/>
-      <c r="AI49" s="41"/>
-      <c r="AJ49" s="41"/>
-      <c r="AK49" s="41"/>
-      <c r="AL49" s="41"/>
-      <c r="AM49" s="41"/>
-      <c r="AN49" s="41"/>
-      <c r="AO49" s="41"/>
+      <c r="T49" s="41">
+        <v>0.15</v>
+      </c>
+      <c r="U49" s="41">
+        <v>0.11</v>
+      </c>
+      <c r="V49" s="41">
+        <v>2.7</v>
+      </c>
+      <c r="W49" s="41">
+        <v>7.266</v>
+      </c>
+      <c r="X49" s="41">
+        <v>46.3</v>
+      </c>
+      <c r="Y49" s="41">
+        <v>66.3</v>
+      </c>
+      <c r="Z49" s="41">
+        <v>2.64</v>
+      </c>
+      <c r="AA49" s="41">
+        <v>136.4</v>
+      </c>
+      <c r="AB49" s="41">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="AC49" s="41">
+        <v>40.6</v>
+      </c>
+      <c r="AD49" s="41">
+        <v>54</v>
+      </c>
+      <c r="AE49" s="17">
+        <v>7.2249999999999996</v>
+      </c>
+      <c r="AF49" s="41">
+        <v>407</v>
+      </c>
+      <c r="AG49" s="41">
+        <v>50.8</v>
+      </c>
+      <c r="AH49" s="41">
+        <v>7.3070000000000004</v>
+      </c>
+      <c r="AI49" s="41">
+        <v>34</v>
+      </c>
+      <c r="AJ49" s="41">
+        <v>2</v>
+      </c>
+      <c r="AK49" s="41">
+        <v>2.9</v>
+      </c>
+      <c r="AL49" s="41">
+        <v>0.1</v>
+      </c>
+      <c r="AM49" s="41">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="AN49" s="41">
+        <v>4</v>
+      </c>
+      <c r="AO49" s="41">
+        <v>197</v>
+      </c>
       <c r="AP49" s="74"/>
       <c r="AQ49" s="42">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>0.50800000000000001</v>
       </c>
       <c r="AR49" s="42">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>0.10288600799999999</v>
       </c>
       <c r="AS49" s="42">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>2.2000000000000011</v>
       </c>
       <c r="AT49" s="42">
         <f t="shared" si="56"/>
@@ -11265,27 +11938,27 @@
       <c r="BD49" s="22"/>
       <c r="BE49" s="43">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1.7147667999999998E-3</v>
       </c>
       <c r="BF49" s="43">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>2.4692641919999998</v>
       </c>
       <c r="BG49" s="43">
         <f t="shared" si="45"/>
-        <v>185.6</v>
-      </c>
-      <c r="BH49" s="44" t="str">
+        <v>197</v>
+      </c>
+      <c r="BH49" s="44">
         <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="BI49" s="44" t="str">
+        <v>4.2131979695431476E-2</v>
+      </c>
+      <c r="BI49" s="44">
         <f t="shared" si="47"/>
-        <v/>
+        <v>4.1500000000000002E-2</v>
       </c>
       <c r="BJ49" s="44">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>148.15585152</v>
       </c>
       <c r="BK49" s="44" t="str">
         <f t="shared" si="19"/>
@@ -11297,11 +11970,11 @@
       </c>
       <c r="BM49" s="45">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>0.10288600799999999</v>
       </c>
       <c r="BN49" s="44">
         <f t="shared" si="32"/>
-        <v>1.3919999999999999</v>
+        <v>0</v>
       </c>
       <c r="BO49" s="44" t="str">
         <f t="shared" si="49"/>
@@ -11309,15 +11982,15 @@
       </c>
       <c r="BP49" s="58">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>267.23638441558438</v>
       </c>
       <c r="BQ49" s="46">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>0.10288600799999999</v>
       </c>
       <c r="BR49" s="24">
         <f t="shared" si="54"/>
-        <v>1.3919999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:70" s="40" customFormat="1" x14ac:dyDescent="0.3">
@@ -11336,54 +12009,118 @@
       <c r="E50" s="40">
         <v>5</v>
       </c>
-      <c r="G50" s="35"/>
+      <c r="G50" s="35">
+        <v>45573.421898148146</v>
+      </c>
       <c r="H50" s="40">
         <v>2716.05</v>
       </c>
-      <c r="J50" s="41"/>
-      <c r="K50" s="41"/>
-      <c r="L50" s="41"/>
-      <c r="M50" s="41"/>
-      <c r="N50" s="41"/>
-      <c r="O50" s="41"/>
-      <c r="P50" s="41"/>
-      <c r="Q50" s="41"/>
-      <c r="R50" s="41"/>
+      <c r="J50" s="41">
+        <v>2406.1950000000002</v>
+      </c>
+      <c r="K50" s="41">
+        <v>27.155999999999999</v>
+      </c>
+      <c r="L50" s="41">
+        <v>25.081</v>
+      </c>
+      <c r="M50" s="41">
+        <v>92.4</v>
+      </c>
+      <c r="N50" s="41">
+        <v>15.18</v>
+      </c>
+      <c r="O50" s="41">
+        <v>325</v>
+      </c>
+      <c r="P50" s="41">
+        <v>1.38</v>
+      </c>
+      <c r="Q50" s="41">
+        <v>0.37</v>
+      </c>
+      <c r="R50" s="41">
+        <v>2.25</v>
+      </c>
       <c r="S50" s="41"/>
-      <c r="T50" s="41"/>
-      <c r="U50" s="41"/>
-      <c r="V50" s="41"/>
-      <c r="W50" s="41"/>
-      <c r="X50" s="41"/>
-      <c r="Y50" s="41"/>
-      <c r="Z50" s="41"/>
-      <c r="AA50" s="41"/>
-      <c r="AB50" s="41"/>
-      <c r="AC50" s="41"/>
-      <c r="AD50" s="41"/>
-      <c r="AE50" s="17"/>
-      <c r="AF50" s="41"/>
-      <c r="AG50" s="41"/>
-      <c r="AH50" s="41"/>
-      <c r="AI50" s="41"/>
-      <c r="AJ50" s="41"/>
-      <c r="AK50" s="41"/>
-      <c r="AL50" s="41"/>
-      <c r="AM50" s="41"/>
-      <c r="AN50" s="41"/>
-      <c r="AO50" s="41"/>
+      <c r="T50" s="41">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="U50" s="41">
+        <v>0.11</v>
+      </c>
+      <c r="V50" s="41">
+        <v>3.08</v>
+      </c>
+      <c r="W50" s="41">
+        <v>7.2430000000000003</v>
+      </c>
+      <c r="X50" s="41">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="Y50" s="41">
+        <v>66</v>
+      </c>
+      <c r="Z50" s="41">
+        <v>2.75</v>
+      </c>
+      <c r="AA50" s="41">
+        <v>136.19999999999999</v>
+      </c>
+      <c r="AB50" s="41">
+        <v>12.9</v>
+      </c>
+      <c r="AC50" s="41">
+        <v>29.6</v>
+      </c>
+      <c r="AD50" s="41">
+        <v>53.8</v>
+      </c>
+      <c r="AE50" s="17">
+        <v>7.2030000000000003</v>
+      </c>
+      <c r="AF50" s="41">
+        <v>408</v>
+      </c>
+      <c r="AG50" s="41">
+        <v>49.9</v>
+      </c>
+      <c r="AH50" s="41">
+        <v>7.2830000000000004</v>
+      </c>
+      <c r="AI50" s="41">
+        <v>34</v>
+      </c>
+      <c r="AJ50" s="41">
+        <v>2.1</v>
+      </c>
+      <c r="AK50" s="41">
+        <v>2.8</v>
+      </c>
+      <c r="AL50" s="41">
+        <v>0.1</v>
+      </c>
+      <c r="AM50" s="41">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="AN50" s="41">
+        <v>4.3</v>
+      </c>
+      <c r="AO50" s="41">
+        <v>197.6</v>
+      </c>
       <c r="AP50" s="74"/>
       <c r="AQ50" s="42">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>0.499</v>
       </c>
       <c r="AR50" s="42">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>0.11894413440000001</v>
       </c>
       <c r="AS50" s="42">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>2.1999999999999993</v>
       </c>
       <c r="AT50" s="42">
         <f t="shared" si="56"/>
@@ -11416,27 +12153,27 @@
       <c r="BD50" s="22"/>
       <c r="BE50" s="43">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1.9824022400000002E-3</v>
       </c>
       <c r="BF50" s="43">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>2.8546592256000003</v>
       </c>
       <c r="BG50" s="43">
         <f t="shared" si="45"/>
-        <v>185.6</v>
-      </c>
-      <c r="BH50" s="44" t="str">
+        <v>197.6</v>
+      </c>
+      <c r="BH50" s="44">
         <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="BI50" s="44" t="str">
+        <v>4.149797570850202E-2</v>
+      </c>
+      <c r="BI50" s="44">
         <f t="shared" si="47"/>
-        <v/>
+        <v>4.0999999999999995E-2</v>
       </c>
       <c r="BJ50" s="44">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>171.27955353600001</v>
       </c>
       <c r="BK50" s="44" t="str">
         <f t="shared" si="19"/>
@@ -11448,11 +12185,11 @@
       </c>
       <c r="BM50" s="45">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>0.11894413440000001</v>
       </c>
       <c r="BN50" s="44">
         <f t="shared" si="32"/>
-        <v>1.3919999999999999</v>
+        <v>0</v>
       </c>
       <c r="BO50" s="44" t="str">
         <f t="shared" si="49"/>
@@ -11460,15 +12197,15 @@
       </c>
       <c r="BP50" s="58">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>308.94580363636368</v>
       </c>
       <c r="BQ50" s="46">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>0.11894413440000001</v>
       </c>
       <c r="BR50" s="24">
         <f t="shared" si="54"/>
-        <v>1.3919999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:70" s="40" customFormat="1" x14ac:dyDescent="0.3">
@@ -11487,46 +12224,110 @@
       <c r="E51" s="40">
         <v>5</v>
       </c>
-      <c r="G51" s="35"/>
+      <c r="G51" s="35">
+        <v>45573.422743055555</v>
+      </c>
       <c r="H51" s="40">
         <v>2716.05</v>
       </c>
-      <c r="J51" s="41"/>
-      <c r="K51" s="41"/>
-      <c r="L51" s="41"/>
-      <c r="M51" s="41"/>
-      <c r="N51" s="41"/>
-      <c r="O51" s="41"/>
-      <c r="P51" s="41"/>
-      <c r="Q51" s="41"/>
-      <c r="R51" s="41"/>
+      <c r="J51" s="41">
+        <v>2279.1149999999998</v>
+      </c>
+      <c r="K51" s="41">
+        <v>23.099</v>
+      </c>
+      <c r="L51" s="41">
+        <v>20.533000000000001</v>
+      </c>
+      <c r="M51" s="41">
+        <v>88.9</v>
+      </c>
+      <c r="N51" s="41">
+        <v>16.61</v>
+      </c>
+      <c r="O51" s="41">
+        <v>374</v>
+      </c>
+      <c r="P51" s="41">
+        <v>1.19</v>
+      </c>
+      <c r="Q51" s="41">
+        <v>0.39</v>
+      </c>
+      <c r="R51" s="41">
+        <v>3.27</v>
+      </c>
       <c r="S51" s="41"/>
-      <c r="T51" s="41"/>
-      <c r="U51" s="41"/>
-      <c r="V51" s="41"/>
-      <c r="W51" s="41"/>
-      <c r="X51" s="41"/>
-      <c r="Y51" s="41"/>
-      <c r="Z51" s="41"/>
-      <c r="AA51" s="41"/>
-      <c r="AB51" s="41"/>
-      <c r="AC51" s="41"/>
-      <c r="AD51" s="41"/>
-      <c r="AE51" s="17"/>
-      <c r="AF51" s="41"/>
-      <c r="AG51" s="41"/>
-      <c r="AH51" s="41"/>
-      <c r="AI51" s="41"/>
-      <c r="AJ51" s="41"/>
-      <c r="AK51" s="41"/>
-      <c r="AL51" s="41"/>
-      <c r="AM51" s="41"/>
-      <c r="AN51" s="41"/>
-      <c r="AO51" s="41"/>
+      <c r="T51" s="41">
+        <v>0.18</v>
+      </c>
+      <c r="U51" s="41">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="V51" s="41">
+        <v>4.45</v>
+      </c>
+      <c r="W51" s="41">
+        <v>7.2389999999999999</v>
+      </c>
+      <c r="X51" s="41">
+        <v>39.1</v>
+      </c>
+      <c r="Y51" s="41">
+        <v>52.2</v>
+      </c>
+      <c r="Z51" s="41">
+        <v>1.85</v>
+      </c>
+      <c r="AA51" s="41">
+        <v>153.9</v>
+      </c>
+      <c r="AB51" s="41">
+        <v>14.8</v>
+      </c>
+      <c r="AC51" s="41">
+        <v>34.299999999999997</v>
+      </c>
+      <c r="AD51" s="41">
+        <v>42.4</v>
+      </c>
+      <c r="AE51" s="17">
+        <v>7.1989999999999998</v>
+      </c>
+      <c r="AF51" s="41">
+        <v>407</v>
+      </c>
+      <c r="AG51" s="41">
+        <v>49.1</v>
+      </c>
+      <c r="AH51" s="41">
+        <v>7.2430000000000003</v>
+      </c>
+      <c r="AI51" s="41">
+        <v>34</v>
+      </c>
+      <c r="AJ51" s="41">
+        <v>3.4</v>
+      </c>
+      <c r="AK51" s="41">
+        <v>2.7</v>
+      </c>
+      <c r="AL51" s="41">
+        <v>0.2</v>
+      </c>
+      <c r="AM51" s="41">
+        <v>11.3</v>
+      </c>
+      <c r="AN51" s="41">
+        <v>4.5</v>
+      </c>
+      <c r="AO51" s="41">
+        <v>202.2</v>
+      </c>
       <c r="AP51" s="74"/>
       <c r="AQ51" s="42">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>0.49099999999999999</v>
       </c>
       <c r="AR51" s="42">
         <f t="shared" si="50"/>
@@ -11534,11 +12335,11 @@
       </c>
       <c r="AS51" s="42">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>3.8000000000000007</v>
       </c>
       <c r="AT51" s="42">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AU51" s="42">
         <f t="shared" si="57"/>
@@ -11567,23 +12368,23 @@
       <c r="BD51" s="22"/>
       <c r="BE51" s="43">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1.6607090400000001E-3</v>
       </c>
       <c r="BF51" s="43">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>2.3914210176000004</v>
       </c>
       <c r="BG51" s="43">
         <f t="shared" si="45"/>
-        <v>185.6</v>
-      </c>
-      <c r="BH51" s="44" t="str">
+        <v>202.2</v>
+      </c>
+      <c r="BH51" s="44">
         <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="BI51" s="44" t="str">
+        <v>5.5885262116716128E-2</v>
+      </c>
+      <c r="BI51" s="44">
         <f t="shared" si="47"/>
-        <v/>
+        <v>5.6500000000000002E-2</v>
       </c>
       <c r="BJ51" s="44">
         <f t="shared" si="48"/>
@@ -11603,7 +12404,7 @@
       </c>
       <c r="BN51" s="44">
         <f t="shared" si="32"/>
-        <v>1.3919999999999999</v>
+        <v>0</v>
       </c>
       <c r="BO51" s="44" t="str">
         <f t="shared" si="49"/>
@@ -11619,7 +12420,7 @@
       </c>
       <c r="BR51" s="24">
         <f t="shared" si="54"/>
-        <v>1.3919999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:70" s="40" customFormat="1" x14ac:dyDescent="0.3">
@@ -11638,46 +12439,110 @@
       <c r="E52" s="40">
         <v>5</v>
       </c>
-      <c r="G52" s="35"/>
+      <c r="G52" s="35">
+        <v>45573.423587962963</v>
+      </c>
       <c r="H52" s="40">
         <v>2716.05</v>
       </c>
-      <c r="J52" s="41"/>
-      <c r="K52" s="41"/>
-      <c r="L52" s="41"/>
-      <c r="M52" s="41"/>
-      <c r="N52" s="41"/>
-      <c r="O52" s="41"/>
-      <c r="P52" s="41"/>
-      <c r="Q52" s="41"/>
-      <c r="R52" s="41"/>
+      <c r="J52" s="41">
+        <v>2461.2449999999999</v>
+      </c>
+      <c r="K52" s="41">
+        <v>21.51</v>
+      </c>
+      <c r="L52" s="41">
+        <v>19.835999999999999</v>
+      </c>
+      <c r="M52" s="41">
+        <v>92.2</v>
+      </c>
+      <c r="N52" s="41">
+        <v>16.559999999999999</v>
+      </c>
+      <c r="O52" s="41">
+        <v>339</v>
+      </c>
+      <c r="P52" s="41">
+        <v>1.26</v>
+      </c>
+      <c r="Q52" s="41">
+        <v>0.39</v>
+      </c>
+      <c r="R52" s="41">
+        <v>2.81</v>
+      </c>
       <c r="S52" s="41"/>
-      <c r="T52" s="41"/>
-      <c r="U52" s="41"/>
-      <c r="V52" s="41"/>
-      <c r="W52" s="41"/>
-      <c r="X52" s="41"/>
-      <c r="Y52" s="41"/>
-      <c r="Z52" s="41"/>
-      <c r="AA52" s="41"/>
-      <c r="AB52" s="41"/>
-      <c r="AC52" s="41"/>
-      <c r="AD52" s="41"/>
-      <c r="AE52" s="17"/>
-      <c r="AF52" s="41"/>
-      <c r="AG52" s="41"/>
-      <c r="AH52" s="41"/>
-      <c r="AI52" s="41"/>
-      <c r="AJ52" s="41"/>
-      <c r="AK52" s="41"/>
-      <c r="AL52" s="41"/>
-      <c r="AM52" s="41"/>
-      <c r="AN52" s="41"/>
-      <c r="AO52" s="41"/>
+      <c r="T52" s="41">
+        <v>0.2</v>
+      </c>
+      <c r="U52" s="41">
+        <v>0.12</v>
+      </c>
+      <c r="V52" s="41">
+        <v>3.34</v>
+      </c>
+      <c r="W52" s="41">
+        <v>7.2460000000000004</v>
+      </c>
+      <c r="X52" s="41">
+        <v>35.700000000000003</v>
+      </c>
+      <c r="Y52" s="41">
+        <v>47.5</v>
+      </c>
+      <c r="Z52" s="41">
+        <v>1.82</v>
+      </c>
+      <c r="AA52" s="41">
+        <v>143.19999999999999</v>
+      </c>
+      <c r="AB52" s="41">
+        <v>13.7</v>
+      </c>
+      <c r="AC52" s="41">
+        <v>31.3</v>
+      </c>
+      <c r="AD52" s="41">
+        <v>38.5</v>
+      </c>
+      <c r="AE52" s="17">
+        <v>7.2060000000000004</v>
+      </c>
+      <c r="AF52" s="41">
+        <v>409</v>
+      </c>
+      <c r="AG52" s="41">
+        <v>49.7</v>
+      </c>
+      <c r="AH52" s="41">
+        <v>7.2539999999999996</v>
+      </c>
+      <c r="AI52" s="41">
+        <v>34</v>
+      </c>
+      <c r="AJ52" s="41">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AK52" s="41">
+        <v>2</v>
+      </c>
+      <c r="AL52" s="41">
+        <v>0.1</v>
+      </c>
+      <c r="AM52" s="41">
+        <v>11.7</v>
+      </c>
+      <c r="AN52" s="41">
+        <v>3.9</v>
+      </c>
+      <c r="AO52" s="41">
+        <v>200.1</v>
+      </c>
       <c r="AP52" s="74"/>
       <c r="AQ52" s="42">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>0.49700000000000005</v>
       </c>
       <c r="AR52" s="42">
         <f t="shared" si="50"/>
@@ -11685,7 +12550,7 @@
       </c>
       <c r="AS52" s="42">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="AT52" s="42">
         <f t="shared" si="56"/>
@@ -11717,23 +12582,23 @@
       <c r="BD52" s="22"/>
       <c r="BE52" s="43">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1.5876734399999999E-3</v>
       </c>
       <c r="BF52" s="43">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>2.2862497535999999</v>
       </c>
       <c r="BG52" s="43">
         <f t="shared" si="45"/>
-        <v>185.6</v>
-      </c>
-      <c r="BH52" s="44" t="str">
+        <v>200.1</v>
+      </c>
+      <c r="BH52" s="44">
         <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="BI52" s="44" t="str">
+        <v>5.847076461769115E-2</v>
+      </c>
+      <c r="BI52" s="44">
         <f t="shared" si="47"/>
-        <v/>
+        <v>5.8499999999999996E-2</v>
       </c>
       <c r="BJ52" s="44">
         <f t="shared" si="48"/>
@@ -11753,7 +12618,7 @@
       </c>
       <c r="BN52" s="44">
         <f t="shared" si="32"/>
-        <v>1.3919999999999999</v>
+        <v>0</v>
       </c>
       <c r="BO52" s="44" t="str">
         <f t="shared" si="49"/>
@@ -11769,7 +12634,7 @@
       </c>
       <c r="BR52" s="24">
         <f t="shared" si="54"/>
-        <v>1.3919999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:70" s="40" customFormat="1" x14ac:dyDescent="0.3">
@@ -11788,46 +12653,110 @@
       <c r="E53" s="40">
         <v>5</v>
       </c>
-      <c r="G53" s="35"/>
+      <c r="G53" s="35">
+        <v>45573.424444444441</v>
+      </c>
       <c r="H53" s="40">
         <v>2716.05</v>
       </c>
-      <c r="J53" s="41"/>
-      <c r="K53" s="41"/>
-      <c r="L53" s="41"/>
-      <c r="M53" s="41"/>
-      <c r="N53" s="41"/>
-      <c r="O53" s="41"/>
-      <c r="P53" s="41"/>
-      <c r="Q53" s="41"/>
-      <c r="R53" s="41"/>
+      <c r="J53" s="41">
+        <v>2561.79</v>
+      </c>
+      <c r="K53" s="41">
+        <v>22.911999999999999</v>
+      </c>
+      <c r="L53" s="41">
+        <v>21.283000000000001</v>
+      </c>
+      <c r="M53" s="41">
+        <v>92.9</v>
+      </c>
+      <c r="N53" s="41">
+        <v>16.23</v>
+      </c>
+      <c r="O53" s="41">
+        <v>327</v>
+      </c>
+      <c r="P53" s="41">
+        <v>1.3</v>
+      </c>
+      <c r="Q53" s="41">
+        <v>0.35</v>
+      </c>
+      <c r="R53" s="41">
+        <v>1.49</v>
+      </c>
       <c r="S53" s="41"/>
-      <c r="T53" s="41"/>
-      <c r="U53" s="41"/>
-      <c r="V53" s="41"/>
-      <c r="W53" s="41"/>
-      <c r="X53" s="41"/>
-      <c r="Y53" s="41"/>
-      <c r="Z53" s="41"/>
-      <c r="AA53" s="41"/>
-      <c r="AB53" s="41"/>
-      <c r="AC53" s="41"/>
-      <c r="AD53" s="41"/>
-      <c r="AE53" s="17"/>
-      <c r="AF53" s="41"/>
-      <c r="AG53" s="41"/>
-      <c r="AH53" s="41"/>
-      <c r="AI53" s="41"/>
-      <c r="AJ53" s="41"/>
-      <c r="AK53" s="41"/>
-      <c r="AL53" s="41"/>
-      <c r="AM53" s="41"/>
-      <c r="AN53" s="41"/>
-      <c r="AO53" s="41"/>
+      <c r="T53" s="41">
+        <v>0.2</v>
+      </c>
+      <c r="U53" s="41">
+        <v>0.11</v>
+      </c>
+      <c r="V53" s="41">
+        <v>3.06</v>
+      </c>
+      <c r="W53" s="41">
+        <v>7.2729999999999997</v>
+      </c>
+      <c r="X53" s="41">
+        <v>32.299999999999997</v>
+      </c>
+      <c r="Y53" s="41">
+        <v>49</v>
+      </c>
+      <c r="Z53" s="41">
+        <v>1.98</v>
+      </c>
+      <c r="AA53" s="41">
+        <v>140.9</v>
+      </c>
+      <c r="AB53" s="41">
+        <v>13.2</v>
+      </c>
+      <c r="AC53" s="41">
+        <v>28.3</v>
+      </c>
+      <c r="AD53" s="41">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="AE53" s="17">
+        <v>7.2320000000000002</v>
+      </c>
+      <c r="AF53" s="41">
+        <v>411</v>
+      </c>
+      <c r="AG53" s="41">
+        <v>49.4</v>
+      </c>
+      <c r="AH53" s="41">
+        <v>7.2770000000000001</v>
+      </c>
+      <c r="AI53" s="41">
+        <v>34</v>
+      </c>
+      <c r="AJ53" s="41">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AK53" s="41">
+        <v>1.2</v>
+      </c>
+      <c r="AL53" s="41">
+        <v>0.1</v>
+      </c>
+      <c r="AM53" s="41">
+        <v>12.3</v>
+      </c>
+      <c r="AN53" s="41">
+        <v>3.8</v>
+      </c>
+      <c r="AO53" s="41">
+        <v>198.5</v>
+      </c>
       <c r="AP53" s="74"/>
       <c r="AQ53" s="42">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>0.49399999999999999</v>
       </c>
       <c r="AR53" s="42">
         <f t="shared" si="50"/>
@@ -11835,11 +12764,11 @@
       </c>
       <c r="AS53" s="42">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>3.6000000000000014</v>
       </c>
       <c r="AT53" s="42">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>0.19999999999999973</v>
       </c>
       <c r="AU53" s="42">
         <f t="shared" si="57"/>
@@ -11867,23 +12796,23 @@
       <c r="BD53" s="22"/>
       <c r="BE53" s="43">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1.6898702000000001E-3</v>
       </c>
       <c r="BF53" s="43">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>2.433413088</v>
       </c>
       <c r="BG53" s="43">
         <f t="shared" si="45"/>
-        <v>185.6</v>
-      </c>
-      <c r="BH53" s="44" t="str">
+        <v>198.5</v>
+      </c>
+      <c r="BH53" s="44">
         <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="BI53" s="44" t="str">
+        <v>6.1964735516372799E-2</v>
+      </c>
+      <c r="BI53" s="44">
         <f t="shared" si="47"/>
-        <v/>
+        <v>6.1500000000000006E-2</v>
       </c>
       <c r="BJ53" s="44">
         <f t="shared" si="48"/>
@@ -11938,46 +12867,110 @@
       <c r="E54" s="40">
         <v>5</v>
       </c>
-      <c r="G54" s="35"/>
+      <c r="G54" s="35">
+        <v>45573.432638888888</v>
+      </c>
       <c r="H54" s="40">
         <v>2716.05</v>
       </c>
-      <c r="J54" s="41"/>
-      <c r="K54" s="41"/>
-      <c r="L54" s="41"/>
-      <c r="M54" s="41"/>
-      <c r="N54" s="41"/>
-      <c r="O54" s="41"/>
-      <c r="P54" s="41"/>
-      <c r="Q54" s="41"/>
-      <c r="R54" s="41"/>
+      <c r="J54" s="41">
+        <v>2546.25</v>
+      </c>
+      <c r="K54" s="41">
+        <v>24.582000000000001</v>
+      </c>
+      <c r="L54" s="41">
+        <v>23.151</v>
+      </c>
+      <c r="M54" s="41">
+        <v>94.2</v>
+      </c>
+      <c r="N54" s="41">
+        <v>16.29</v>
+      </c>
+      <c r="O54" s="41">
+        <v>333</v>
+      </c>
+      <c r="P54" s="41">
+        <v>1.32</v>
+      </c>
+      <c r="Q54" s="41">
+        <v>0.35</v>
+      </c>
+      <c r="R54" s="41">
+        <v>2.38</v>
+      </c>
       <c r="S54" s="41"/>
-      <c r="T54" s="41"/>
-      <c r="U54" s="41"/>
-      <c r="V54" s="41"/>
-      <c r="W54" s="41"/>
-      <c r="X54" s="41"/>
-      <c r="Y54" s="41"/>
-      <c r="Z54" s="41"/>
-      <c r="AA54" s="41"/>
-      <c r="AB54" s="41"/>
-      <c r="AC54" s="41"/>
-      <c r="AD54" s="41"/>
-      <c r="AE54" s="17"/>
-      <c r="AF54" s="41"/>
-      <c r="AG54" s="41"/>
-      <c r="AH54" s="41"/>
-      <c r="AI54" s="41"/>
-      <c r="AJ54" s="41"/>
-      <c r="AK54" s="41"/>
-      <c r="AL54" s="41"/>
-      <c r="AM54" s="41"/>
-      <c r="AN54" s="41"/>
-      <c r="AO54" s="41"/>
+      <c r="T54" s="41">
+        <v>0.19</v>
+      </c>
+      <c r="U54" s="41">
+        <v>0.13</v>
+      </c>
+      <c r="V54" s="41">
+        <v>3.08</v>
+      </c>
+      <c r="W54" s="41">
+        <v>7.2539999999999996</v>
+      </c>
+      <c r="X54" s="41">
+        <v>33.5</v>
+      </c>
+      <c r="Y54" s="41">
+        <v>54.6</v>
+      </c>
+      <c r="Z54" s="41">
+        <v>1.92</v>
+      </c>
+      <c r="AA54" s="41">
+        <v>142.19999999999999</v>
+      </c>
+      <c r="AB54" s="41">
+        <v>13.2</v>
+      </c>
+      <c r="AC54" s="41">
+        <v>29.5</v>
+      </c>
+      <c r="AD54" s="41">
+        <v>44.4</v>
+      </c>
+      <c r="AE54" s="17">
+        <v>7.2140000000000004</v>
+      </c>
+      <c r="AF54" s="41">
+        <v>411</v>
+      </c>
+      <c r="AG54" s="41">
+        <v>51.4</v>
+      </c>
+      <c r="AH54" s="41">
+        <v>7.3019999999999996</v>
+      </c>
+      <c r="AI54" s="41">
+        <v>34</v>
+      </c>
+      <c r="AJ54" s="41">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AK54" s="41">
+        <v>1.7</v>
+      </c>
+      <c r="AL54" s="41">
+        <v>0.1</v>
+      </c>
+      <c r="AM54" s="41">
+        <v>12.4</v>
+      </c>
+      <c r="AN54" s="41">
+        <v>4.2</v>
+      </c>
+      <c r="AO54" s="41">
+        <v>199.4</v>
+      </c>
       <c r="AP54" s="74"/>
       <c r="AQ54" s="42">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>0.51400000000000001</v>
       </c>
       <c r="AR54" s="42">
         <f t="shared" si="50"/>
@@ -11985,11 +12978,11 @@
       </c>
       <c r="AS54" s="42">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>3.9000000000000004</v>
       </c>
       <c r="AT54" s="42">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AU54" s="42">
         <f t="shared" si="57"/>
@@ -12017,23 +13010,23 @@
       <c r="BD54" s="22"/>
       <c r="BE54" s="43">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1.8465237600000001E-3</v>
       </c>
       <c r="BF54" s="43">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>2.6589942144000003</v>
       </c>
       <c r="BG54" s="43">
         <f t="shared" si="45"/>
-        <v>185.6</v>
-      </c>
-      <c r="BH54" s="44" t="str">
+        <v>199.4</v>
+      </c>
+      <c r="BH54" s="44">
         <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="BI54" s="44" t="str">
+        <v>6.2186559679037114E-2</v>
+      </c>
+      <c r="BI54" s="44">
         <f t="shared" si="47"/>
-        <v/>
+        <v>6.2E-2</v>
       </c>
       <c r="BJ54" s="44">
         <f t="shared" si="48"/>
@@ -12088,54 +13081,118 @@
       <c r="E55" s="40">
         <v>5</v>
       </c>
-      <c r="G55" s="35"/>
+      <c r="G55" s="35">
+        <v>45573.437222222223</v>
+      </c>
       <c r="H55" s="40">
         <v>2716.05</v>
       </c>
-      <c r="J55" s="41"/>
-      <c r="K55" s="41"/>
-      <c r="L55" s="41"/>
-      <c r="M55" s="41"/>
-      <c r="N55" s="41"/>
-      <c r="O55" s="41"/>
-      <c r="P55" s="41"/>
-      <c r="Q55" s="41"/>
-      <c r="R55" s="41"/>
+      <c r="J55" s="41">
+        <v>2277.6750000000002</v>
+      </c>
+      <c r="K55" s="41">
+        <v>21.408999999999999</v>
+      </c>
+      <c r="L55" s="41">
+        <v>19.666</v>
+      </c>
+      <c r="M55" s="41">
+        <v>91.9</v>
+      </c>
+      <c r="N55" s="41">
+        <v>15.94</v>
+      </c>
+      <c r="O55" s="41">
+        <v>331</v>
+      </c>
+      <c r="P55" s="41">
+        <v>1.35</v>
+      </c>
+      <c r="Q55" s="41">
+        <v>0.39</v>
+      </c>
+      <c r="R55" s="41">
+        <v>1.77</v>
+      </c>
       <c r="S55" s="41"/>
-      <c r="T55" s="41"/>
-      <c r="U55" s="41"/>
-      <c r="V55" s="41"/>
-      <c r="W55" s="41"/>
-      <c r="X55" s="41"/>
-      <c r="Y55" s="41"/>
-      <c r="Z55" s="41"/>
-      <c r="AA55" s="41"/>
-      <c r="AB55" s="41"/>
-      <c r="AC55" s="41"/>
-      <c r="AD55" s="41"/>
-      <c r="AE55" s="17"/>
-      <c r="AF55" s="41"/>
-      <c r="AG55" s="41"/>
-      <c r="AH55" s="41"/>
-      <c r="AI55" s="41"/>
-      <c r="AJ55" s="41"/>
-      <c r="AK55" s="41"/>
-      <c r="AL55" s="41"/>
-      <c r="AM55" s="41"/>
-      <c r="AN55" s="41"/>
-      <c r="AO55" s="41"/>
+      <c r="T55" s="41">
+        <v>0.16</v>
+      </c>
+      <c r="U55" s="41">
+        <v>0.1</v>
+      </c>
+      <c r="V55" s="41">
+        <v>3.43</v>
+      </c>
+      <c r="W55" s="41">
+        <v>7.2649999999999997</v>
+      </c>
+      <c r="X55" s="41">
+        <v>51.9</v>
+      </c>
+      <c r="Y55" s="41">
+        <v>67.599999999999994</v>
+      </c>
+      <c r="Z55" s="41">
+        <v>2.6</v>
+      </c>
+      <c r="AA55" s="41">
+        <v>142.80000000000001</v>
+      </c>
+      <c r="AB55" s="41">
+        <v>20.9</v>
+      </c>
+      <c r="AC55" s="41">
+        <v>45.6</v>
+      </c>
+      <c r="AD55" s="41">
+        <v>55.2</v>
+      </c>
+      <c r="AE55" s="17">
+        <v>7.2240000000000002</v>
+      </c>
+      <c r="AF55" s="41">
+        <v>516</v>
+      </c>
+      <c r="AG55" s="41">
+        <v>52.2</v>
+      </c>
+      <c r="AH55" s="41">
+        <v>7.31</v>
+      </c>
+      <c r="AI55" s="41">
+        <v>34</v>
+      </c>
+      <c r="AJ55" s="41">
+        <v>2.6</v>
+      </c>
+      <c r="AK55" s="41">
+        <v>2.8</v>
+      </c>
+      <c r="AL55" s="41">
+        <v>0.1</v>
+      </c>
+      <c r="AM55" s="41">
+        <v>7.7</v>
+      </c>
+      <c r="AN55" s="41">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AO55" s="41">
+        <v>198.1</v>
+      </c>
       <c r="AP55" s="74"/>
       <c r="AQ55" s="42">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>0.52200000000000002</v>
       </c>
       <c r="AR55" s="42">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>9.3500030400000003E-2</v>
       </c>
       <c r="AS55" s="42">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT55" s="42">
         <f t="shared" si="56"/>
@@ -12167,27 +13224,27 @@
       <c r="BD55" s="22"/>
       <c r="BE55" s="43">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1.5583338400000002E-3</v>
       </c>
       <c r="BF55" s="43">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>2.2440007296000002</v>
       </c>
       <c r="BG55" s="43">
         <f t="shared" si="45"/>
-        <v>185.6</v>
-      </c>
-      <c r="BH55" s="44" t="str">
+        <v>198.1</v>
+      </c>
+      <c r="BH55" s="44">
         <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="BI55" s="44" t="str">
+        <v>3.8869257950530034E-2</v>
+      </c>
+      <c r="BI55" s="44">
         <f t="shared" si="47"/>
-        <v/>
+        <v>3.85E-2</v>
       </c>
       <c r="BJ55" s="44">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>134.640043776</v>
       </c>
       <c r="BK55" s="44" t="str">
         <f t="shared" si="19"/>
@@ -12199,11 +13256,11 @@
       </c>
       <c r="BM55" s="45">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>9.3500030400000003E-2</v>
       </c>
       <c r="BN55" s="44">
         <f t="shared" si="58"/>
-        <v>1.3919999999999999</v>
+        <v>0</v>
       </c>
       <c r="BO55" s="44" t="str">
         <f t="shared" si="49"/>
@@ -12211,15 +13268,15 @@
       </c>
       <c r="BP55" s="58">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>242.85722181818184</v>
       </c>
       <c r="BQ55" s="46">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>9.3500030400000003E-2</v>
       </c>
       <c r="BR55" s="24">
         <f t="shared" si="54"/>
-        <v>1.3919999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:70" s="40" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -12238,54 +13295,118 @@
       <c r="E56" s="40">
         <v>5</v>
       </c>
-      <c r="G56" s="35"/>
+      <c r="G56" s="35">
+        <v>45573.441099537034</v>
+      </c>
       <c r="H56" s="40">
         <v>2716.05</v>
       </c>
-      <c r="J56" s="41"/>
-      <c r="K56" s="41"/>
-      <c r="L56" s="41"/>
-      <c r="M56" s="41"/>
-      <c r="N56" s="41"/>
-      <c r="O56" s="41"/>
-      <c r="P56" s="41"/>
-      <c r="Q56" s="41"/>
-      <c r="R56" s="41"/>
+      <c r="J56" s="41">
+        <v>2410.7399999999998</v>
+      </c>
+      <c r="K56" s="41">
+        <v>21.79</v>
+      </c>
+      <c r="L56" s="41">
+        <v>20.309999999999999</v>
+      </c>
+      <c r="M56" s="41">
+        <v>93.2</v>
+      </c>
+      <c r="N56" s="41">
+        <v>15.73</v>
+      </c>
+      <c r="O56" s="41">
+        <v>327</v>
+      </c>
+      <c r="P56" s="41">
+        <v>1.37</v>
+      </c>
+      <c r="Q56" s="41">
+        <v>0.37</v>
+      </c>
+      <c r="R56" s="41">
+        <v>2.14</v>
+      </c>
       <c r="S56" s="41"/>
-      <c r="T56" s="41"/>
-      <c r="U56" s="41"/>
-      <c r="V56" s="41"/>
-      <c r="W56" s="41"/>
-      <c r="X56" s="41"/>
-      <c r="Y56" s="41"/>
-      <c r="Z56" s="41"/>
-      <c r="AA56" s="41"/>
-      <c r="AB56" s="41"/>
-      <c r="AC56" s="41"/>
-      <c r="AD56" s="41"/>
-      <c r="AE56" s="17"/>
-      <c r="AF56" s="41"/>
-      <c r="AG56" s="41"/>
-      <c r="AH56" s="41"/>
-      <c r="AI56" s="41"/>
-      <c r="AJ56" s="41"/>
-      <c r="AK56" s="41"/>
-      <c r="AL56" s="41"/>
-      <c r="AM56" s="41"/>
-      <c r="AN56" s="41"/>
-      <c r="AO56" s="41"/>
+      <c r="T56" s="41">
+        <v>0.16</v>
+      </c>
+      <c r="U56" s="41">
+        <v>0.09</v>
+      </c>
+      <c r="V56" s="41">
+        <v>2.91</v>
+      </c>
+      <c r="W56" s="41">
+        <v>7.2750000000000004</v>
+      </c>
+      <c r="X56" s="41">
+        <v>47.4</v>
+      </c>
+      <c r="Y56" s="41">
+        <v>65.8</v>
+      </c>
+      <c r="Z56" s="41">
+        <v>2.63</v>
+      </c>
+      <c r="AA56" s="41">
+        <v>138.9</v>
+      </c>
+      <c r="AB56" s="41">
+        <v>19.5</v>
+      </c>
+      <c r="AC56" s="41">
+        <v>41.6</v>
+      </c>
+      <c r="AD56" s="41">
+        <v>53.7</v>
+      </c>
+      <c r="AE56" s="17">
+        <v>7.234</v>
+      </c>
+      <c r="AF56" s="41">
+        <v>406</v>
+      </c>
+      <c r="AG56" s="41">
+        <v>50.2</v>
+      </c>
+      <c r="AH56" s="41">
+        <v>7.3090000000000002</v>
+      </c>
+      <c r="AI56" s="41">
+        <v>34</v>
+      </c>
+      <c r="AJ56" s="41">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AK56" s="41">
+        <v>2.8</v>
+      </c>
+      <c r="AL56" s="41">
+        <v>0.1</v>
+      </c>
+      <c r="AM56" s="41">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="AN56" s="41">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AO56" s="41">
+        <v>197.8</v>
+      </c>
       <c r="AP56" s="75"/>
       <c r="AQ56" s="42">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>0.502</v>
       </c>
       <c r="AR56" s="42">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>9.6415632000000001E-2</v>
       </c>
       <c r="AS56" s="42">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>2.2999999999999989</v>
       </c>
       <c r="AT56" s="42">
         <f t="shared" si="56"/>
@@ -12317,27 +13438,27 @@
       <c r="BD56" s="22"/>
       <c r="BE56" s="43">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1.6069271999999998E-3</v>
       </c>
       <c r="BF56" s="43">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>2.3139751679999994</v>
       </c>
       <c r="BG56" s="43">
         <f t="shared" si="45"/>
-        <v>185.6</v>
-      </c>
-      <c r="BH56" s="44" t="str">
+        <v>197.8</v>
+      </c>
+      <c r="BH56" s="44">
         <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="BI56" s="44" t="str">
+        <v>4.1456016177957529E-2</v>
+      </c>
+      <c r="BI56" s="44">
         <f t="shared" si="47"/>
-        <v/>
+        <v>4.0999999999999995E-2</v>
       </c>
       <c r="BJ56" s="44">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>138.83851007999999</v>
       </c>
       <c r="BK56" s="44" t="str">
         <f t="shared" si="19"/>
@@ -12349,11 +13470,11 @@
       </c>
       <c r="BM56" s="45">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>9.6415632000000001E-2</v>
       </c>
       <c r="BN56" s="44">
         <f t="shared" si="58"/>
-        <v>1.3919999999999999</v>
+        <v>0</v>
       </c>
       <c r="BO56" s="44" t="str">
         <f t="shared" si="49"/>
@@ -12361,15 +13482,15 @@
       </c>
       <c r="BP56" s="58">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>250.43021298701299</v>
       </c>
       <c r="BQ56" s="46">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>9.6415632000000001E-2</v>
       </c>
       <c r="BR56" s="24">
         <f t="shared" si="54"/>
-        <v>1.3919999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:70" s="40" customFormat="1" x14ac:dyDescent="0.3">
@@ -12437,11 +13558,11 @@
       </c>
       <c r="AS57" s="32">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>-35159.5078125</v>
       </c>
       <c r="AT57" s="32">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>-17535.712890625</v>
       </c>
       <c r="AU57" s="32">
         <f t="shared" si="57"/>
@@ -12588,11 +13709,11 @@
       </c>
       <c r="AS58" s="42">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>-8.3000000000000007</v>
       </c>
       <c r="AT58" s="42">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AU58" s="42">
         <f t="shared" si="57"/>
@@ -12739,11 +13860,11 @@
       </c>
       <c r="AS59" s="42">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>-8.1999999999999993</v>
       </c>
       <c r="AT59" s="42">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>-4.3</v>
       </c>
       <c r="AU59" s="42">
         <f t="shared" si="57"/>
@@ -12890,11 +14011,11 @@
       </c>
       <c r="AS60" s="42">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>-11.3</v>
       </c>
       <c r="AT60" s="42">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>-4.5</v>
       </c>
       <c r="AU60" s="42">
         <f t="shared" si="57"/>
@@ -13041,11 +14162,11 @@
       </c>
       <c r="AS61" s="42">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>-11.7</v>
       </c>
       <c r="AT61" s="42">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>-3.9</v>
       </c>
       <c r="AU61" s="42">
         <f t="shared" si="57"/>
@@ -13191,11 +14312,11 @@
       </c>
       <c r="AS62" s="42">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>-12.3</v>
       </c>
       <c r="AT62" s="42">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>-3.8</v>
       </c>
       <c r="AU62" s="42">
         <f t="shared" si="57"/>
@@ -13341,11 +14462,11 @@
       </c>
       <c r="AS63" s="42">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>-12.4</v>
       </c>
       <c r="AT63" s="42">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>-4.2</v>
       </c>
       <c r="AU63" s="42">
         <f t="shared" si="57"/>
@@ -13491,11 +14612,11 @@
       </c>
       <c r="AS64" s="42">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>-7.7</v>
       </c>
       <c r="AT64" s="42">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>-4.4000000000000004</v>
       </c>
       <c r="AU64" s="42">
         <f t="shared" si="57"/>
@@ -13641,11 +14762,11 @@
       </c>
       <c r="AS65" s="42">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>-8.1999999999999993</v>
       </c>
       <c r="AT65" s="42">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>-4.4000000000000004</v>
       </c>
       <c r="AU65" s="42">
         <f t="shared" si="57"/>
@@ -21477,33 +22598,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="34d8c884-fe7e-4d4f-a833-b92a2823f74b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <SharedWithUsers xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B75172DAFC2BB6479729CB287362C7E3" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0fc11b0946794a47057850b4f6c92dd7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="34d8c884-fe7e-4d4f-a833-b92a2823f74b" xmlns:ns3="a198008e-c7f6-4ed0-9865-26ace3c97b59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fb90ec7fe59ed1d44226abab88cd233b" ns2:_="" ns3:_="">
     <xsd:import namespace="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
@@ -21726,32 +22820,34 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="34d8c884-fe7e-4d4f-a833-b92a2823f74b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SharedWithUsers xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F43DC28-AE43-4EFF-8739-4E0C557B415B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -21768,4 +22864,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
+    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/ar24-072-experiment/AR24-072-SAM-MasterDataTable.xlsx
+++ b/data/ar24-072-experiment/AR24-072-SAM-MasterDataTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myteams.gsk.com/sites/BiopharmModelPredictiveControl/Shared Documents/General/data/AR24-072-SAM-MPC-1kL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2656" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9927A10-495E-4B6C-B3CE-B00CAE9C2F63}"/>
+  <xr:revisionPtr revIDLastSave="2760" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{841454D0-012A-4EEA-AA4B-8800E808BAB9}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="41265" yWindow="-1455" windowWidth="25935" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterDataTable" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="93">
   <si>
     <t>Batch Data</t>
   </si>
@@ -316,6 +316,9 @@
   <si>
     <t xml:space="preserve"> MPC underfeeding 30%  compared to manual (titer information missing from input file from Tech). Cannot manually adjust pumps. </t>
   </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
 </sst>
 </file>
 
@@ -328,7 +331,7 @@
     <numFmt numFmtId="167" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -530,7 +533,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -755,6 +758,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1036,7 +1045,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
@@ -1129,6 +1138,11 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="22" fontId="0" fillId="41" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="41" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="41" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="38" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1171,7 +1185,10 @@
     <xf numFmtId="0" fontId="19" fillId="34" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="26" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1288,6 +1305,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1589,113 +1610,113 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:BR119"/>
-  <sheetFormatPr defaultColWidth="14.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="14.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" customWidth="1"/>
-    <col min="3" max="5" width="10.7109375" customWidth="1"/>
-    <col min="6" max="6" width="28.28515625" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="19" width="12.7109375" customWidth="1"/>
-    <col min="20" max="20" width="15.140625" customWidth="1"/>
-    <col min="21" max="21" width="16.140625" customWidth="1"/>
-    <col min="22" max="40" width="12.7109375" customWidth="1"/>
-    <col min="41" max="41" width="12.5703125" customWidth="1"/>
-    <col min="42" max="47" width="12.7109375" customWidth="1"/>
-    <col min="48" max="48" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="49" max="50" width="14.85546875" customWidth="1"/>
-    <col min="51" max="67" width="12.7109375" customWidth="1"/>
-    <col min="68" max="68" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="69" max="70" width="16.28515625" customWidth="1"/>
+    <col min="1" max="1" width="24.6640625" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" customWidth="1"/>
+    <col min="3" max="5" width="10.6640625" customWidth="1"/>
+    <col min="6" max="6" width="28.33203125" customWidth="1"/>
+    <col min="7" max="7" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="19" width="12.6640625" customWidth="1"/>
+    <col min="20" max="20" width="15.109375" customWidth="1"/>
+    <col min="21" max="21" width="16.109375" customWidth="1"/>
+    <col min="22" max="40" width="12.6640625" customWidth="1"/>
+    <col min="41" max="41" width="12.5546875" customWidth="1"/>
+    <col min="42" max="47" width="12.6640625" customWidth="1"/>
+    <col min="48" max="48" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="49" max="50" width="14.88671875" customWidth="1"/>
+    <col min="51" max="67" width="12.6640625" customWidth="1"/>
+    <col min="68" max="68" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="69" max="70" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:70" ht="21.6" thickBot="1">
-      <c r="A1" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="77" t="s">
+    <row r="1" spans="1:70" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="81" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
-      <c r="O1" s="77"/>
-      <c r="P1" s="77"/>
-      <c r="Q1" s="77"/>
-      <c r="R1" s="77"/>
-      <c r="S1" s="77"/>
-      <c r="T1" s="77"/>
-      <c r="U1" s="77"/>
-      <c r="V1" s="77"/>
-      <c r="W1" s="77"/>
-      <c r="X1" s="77"/>
-      <c r="Y1" s="77"/>
-      <c r="Z1" s="77"/>
-      <c r="AA1" s="77"/>
-      <c r="AB1" s="77"/>
-      <c r="AC1" s="77"/>
-      <c r="AD1" s="77"/>
-      <c r="AE1" s="77"/>
-      <c r="AF1" s="83" t="s">
+      <c r="I1" s="82"/>
+      <c r="J1" s="82"/>
+      <c r="K1" s="82"/>
+      <c r="L1" s="82"/>
+      <c r="M1" s="82"/>
+      <c r="N1" s="82"/>
+      <c r="O1" s="82"/>
+      <c r="P1" s="82"/>
+      <c r="Q1" s="82"/>
+      <c r="R1" s="82"/>
+      <c r="S1" s="82"/>
+      <c r="T1" s="82"/>
+      <c r="U1" s="82"/>
+      <c r="V1" s="82"/>
+      <c r="W1" s="82"/>
+      <c r="X1" s="82"/>
+      <c r="Y1" s="82"/>
+      <c r="Z1" s="82"/>
+      <c r="AA1" s="82"/>
+      <c r="AB1" s="82"/>
+      <c r="AC1" s="82"/>
+      <c r="AD1" s="82"/>
+      <c r="AE1" s="82"/>
+      <c r="AF1" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="AG1" s="84"/>
-      <c r="AH1" s="84"/>
-      <c r="AI1" s="84"/>
-      <c r="AJ1" s="84"/>
-      <c r="AK1" s="84"/>
-      <c r="AL1" s="84"/>
-      <c r="AM1" s="84"/>
-      <c r="AN1" s="84"/>
-      <c r="AO1" s="84"/>
-      <c r="AP1" s="84"/>
-      <c r="AQ1" s="84"/>
-      <c r="AR1" s="84"/>
-      <c r="AS1" s="84"/>
-      <c r="AT1" s="84"/>
-      <c r="AU1" s="84"/>
-      <c r="AV1" s="85"/>
-      <c r="AW1" s="78" t="s">
+      <c r="AG1" s="89"/>
+      <c r="AH1" s="89"/>
+      <c r="AI1" s="89"/>
+      <c r="AJ1" s="89"/>
+      <c r="AK1" s="89"/>
+      <c r="AL1" s="89"/>
+      <c r="AM1" s="89"/>
+      <c r="AN1" s="89"/>
+      <c r="AO1" s="89"/>
+      <c r="AP1" s="89"/>
+      <c r="AQ1" s="89"/>
+      <c r="AR1" s="89"/>
+      <c r="AS1" s="89"/>
+      <c r="AT1" s="89"/>
+      <c r="AU1" s="89"/>
+      <c r="AV1" s="90"/>
+      <c r="AW1" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="AX1" s="79"/>
-      <c r="AY1" s="79"/>
-      <c r="AZ1" s="79"/>
-      <c r="BA1" s="80"/>
-      <c r="BB1" s="77" t="s">
+      <c r="AX1" s="84"/>
+      <c r="AY1" s="84"/>
+      <c r="AZ1" s="84"/>
+      <c r="BA1" s="85"/>
+      <c r="BB1" s="82" t="s">
         <v>4</v>
       </c>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="82"/>
-      <c r="BE1" s="74" t="s">
+      <c r="BC1" s="86"/>
+      <c r="BD1" s="87"/>
+      <c r="BE1" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="BF1" s="75"/>
-      <c r="BG1" s="75"/>
-      <c r="BH1" s="75"/>
-      <c r="BI1" s="75"/>
-      <c r="BJ1" s="75"/>
-      <c r="BK1" s="75"/>
-      <c r="BL1" s="75"/>
-      <c r="BM1" s="75"/>
-      <c r="BN1" s="75"/>
-      <c r="BO1" s="75"/>
-      <c r="BP1" s="75"/>
-      <c r="BQ1" s="72" t="s">
+      <c r="BF1" s="80"/>
+      <c r="BG1" s="80"/>
+      <c r="BH1" s="80"/>
+      <c r="BI1" s="80"/>
+      <c r="BJ1" s="80"/>
+      <c r="BK1" s="80"/>
+      <c r="BL1" s="80"/>
+      <c r="BM1" s="80"/>
+      <c r="BN1" s="80"/>
+      <c r="BO1" s="80"/>
+      <c r="BP1" s="80"/>
+      <c r="BQ1" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="BR1" s="73"/>
+      <c r="BR1" s="78"/>
     </row>
-    <row r="2" spans="1:70" ht="60.6" thickBot="1">
+    <row r="2" spans="1:70" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="20" t="s">
         <v>7</v>
       </c>
@@ -1907,7 +1928,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:70">
+    <row r="3" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>76</v>
       </c>
@@ -2087,7 +2108,7 @@
         <v>233.3070779</v>
       </c>
     </row>
-    <row r="4" spans="1:70">
+    <row r="4" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>79</v>
       </c>
@@ -2303,7 +2324,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:70">
+    <row r="5" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>81</v>
       </c>
@@ -2519,7 +2540,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:70">
+    <row r="6" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>82</v>
       </c>
@@ -2734,7 +2755,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:70">
+    <row r="7" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>84</v>
       </c>
@@ -2948,7 +2969,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:70">
+    <row r="8" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>85</v>
       </c>
@@ -3170,7 +3191,7 @@
         <v>0.48308408305717904</v>
       </c>
     </row>
-    <row r="9" spans="1:70">
+    <row r="9" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>86</v>
       </c>
@@ -3392,7 +3413,7 @@
         <v>0.18905479737033201</v>
       </c>
     </row>
-    <row r="10" spans="1:70">
+    <row r="10" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>87</v>
       </c>
@@ -3607,7 +3628,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:70" ht="15" thickBot="1">
+    <row r="11" spans="1:70" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>88</v>
       </c>
@@ -3822,7 +3843,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:70">
+    <row r="12" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>76</v>
       </c>
@@ -4009,7 +4030,7 @@
         <v>5358.6430859999991</v>
       </c>
     </row>
-    <row r="13" spans="1:70">
+    <row r="13" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>79</v>
       </c>
@@ -4228,7 +4249,7 @@
         <v>1.6506000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:70">
+    <row r="14" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>81</v>
       </c>
@@ -4447,7 +4468,7 @@
         <v>1.7014549999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:70">
+    <row r="15" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>82</v>
       </c>
@@ -4668,7 +4689,7 @@
         <v>0.6081700000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:70">
+    <row r="16" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>84</v>
       </c>
@@ -4888,7 +4909,7 @@
         <v>1.2844</v>
       </c>
     </row>
-    <row r="17" spans="1:70">
+    <row r="17" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>85</v>
       </c>
@@ -5113,7 +5134,7 @@
         <v>1.2643743018569999</v>
       </c>
     </row>
-    <row r="18" spans="1:70">
+    <row r="18" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>86</v>
       </c>
@@ -5338,7 +5359,7 @@
         <v>1.2827024808204199</v>
       </c>
     </row>
-    <row r="19" spans="1:70">
+    <row r="19" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>87</v>
       </c>
@@ -5556,7 +5577,7 @@
         <v>1.79179</v>
       </c>
     </row>
-    <row r="20" spans="1:70" ht="15" thickBot="1">
+    <row r="20" spans="1:70" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>88</v>
       </c>
@@ -5774,7 +5795,7 @@
         <v>1.9286400000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:70">
+    <row r="21" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>76</v>
       </c>
@@ -5961,7 +5982,7 @@
         <v>4609.1968360000001</v>
       </c>
     </row>
-    <row r="22" spans="1:70">
+    <row r="22" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>79</v>
       </c>
@@ -6180,7 +6201,7 @@
         <v>1.1425999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:70">
+    <row r="23" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>81</v>
       </c>
@@ -6399,7 +6420,7 @@
         <v>1.2700050000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:70">
+    <row r="24" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>82</v>
       </c>
@@ -6620,7 +6641,7 @@
         <v>1.1005799999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:70">
+    <row r="25" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>84</v>
       </c>
@@ -6840,7 +6861,7 @@
         <v>1.2553949999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:70">
+    <row r="26" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>85</v>
       </c>
@@ -7065,7 +7086,7 @@
         <v>0.89764770150802109</v>
       </c>
     </row>
-    <row r="27" spans="1:70">
+    <row r="27" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>86</v>
       </c>
@@ -7290,7 +7311,7 @@
         <v>1.18909849474202</v>
       </c>
     </row>
-    <row r="28" spans="1:70">
+    <row r="28" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>87</v>
       </c>
@@ -7508,7 +7529,7 @@
         <v>1.1843999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:70" ht="15" thickBot="1">
+    <row r="29" spans="1:70" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>88</v>
       </c>
@@ -7727,7 +7748,7 @@
         <v>1.155375</v>
       </c>
     </row>
-    <row r="30" spans="1:70">
+    <row r="30" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>76</v>
       </c>
@@ -7914,7 +7935,7 @@
         <v>4682</v>
       </c>
     </row>
-    <row r="31" spans="1:70">
+    <row r="31" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>79</v>
       </c>
@@ -8130,7 +8151,7 @@
         <v>1.2342924999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:70">
+    <row r="32" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>81</v>
       </c>
@@ -8346,7 +8367,7 @@
         <v>1.3270500000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:70">
+    <row r="33" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>82</v>
       </c>
@@ -8564,7 +8585,7 @@
         <v>1.395165</v>
       </c>
     </row>
-    <row r="34" spans="1:70">
+    <row r="34" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>84</v>
       </c>
@@ -8781,7 +8802,7 @@
         <v>1.3839250000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:70">
+    <row r="35" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>85</v>
       </c>
@@ -9003,7 +9024,7 @@
         <v>0.937837273085801</v>
       </c>
     </row>
-    <row r="36" spans="1:70">
+    <row r="36" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>86</v>
       </c>
@@ -9225,7 +9246,7 @@
         <v>0.95056013874566703</v>
       </c>
     </row>
-    <row r="37" spans="1:70">
+    <row r="37" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>87</v>
       </c>
@@ -9440,7 +9461,7 @@
         <v>1.3733199999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:70" ht="15" thickBot="1">
+    <row r="38" spans="1:70" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>88</v>
       </c>
@@ -9655,7 +9676,7 @@
         <v>1.3317750000000002</v>
       </c>
     </row>
-    <row r="39" spans="1:70">
+    <row r="39" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>76</v>
       </c>
@@ -9840,7 +9861,7 @@
         <v>2610.0869895953001</v>
       </c>
     </row>
-    <row r="40" spans="1:70">
+    <row r="40" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>79</v>
       </c>
@@ -10056,7 +10077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:70">
+    <row r="41" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>81</v>
       </c>
@@ -10272,7 +10293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:70">
+    <row r="42" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>82</v>
       </c>
@@ -10490,7 +10511,7 @@
         <v>1.353645</v>
       </c>
     </row>
-    <row r="43" spans="1:70">
+    <row r="43" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>84</v>
       </c>
@@ -10707,7 +10728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:70">
+    <row r="44" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>85</v>
       </c>
@@ -10929,7 +10950,7 @@
         <v>0.17636712933554399</v>
       </c>
     </row>
-    <row r="45" spans="1:70">
+    <row r="45" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>86</v>
       </c>
@@ -11151,7 +11172,7 @@
         <v>0.50714820057338095</v>
       </c>
     </row>
-    <row r="46" spans="1:70">
+    <row r="46" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>87</v>
       </c>
@@ -11365,7 +11386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:70" ht="15" thickBot="1">
+    <row r="47" spans="1:70" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>88</v>
       </c>
@@ -11579,7 +11600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:70">
+    <row r="48" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>76</v>
       </c>
@@ -11764,7 +11785,7 @@
         <v>3886.9041343279305</v>
       </c>
     </row>
-    <row r="49" spans="1:70">
+    <row r="49" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>79</v>
       </c>
@@ -11979,7 +12000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:70">
+    <row r="50" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>81</v>
       </c>
@@ -12194,7 +12215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:70">
+    <row r="51" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>82</v>
       </c>
@@ -12411,7 +12432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:70">
+    <row r="52" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>84</v>
       </c>
@@ -12627,7 +12648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:70">
+    <row r="53" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>85</v>
       </c>
@@ -12848,7 +12869,7 @@
         <v>0.78854210138625414</v>
       </c>
     </row>
-    <row r="54" spans="1:70">
+    <row r="54" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>86</v>
       </c>
@@ -13069,7 +13090,7 @@
         <v>0.70564158544459499</v>
       </c>
     </row>
-    <row r="55" spans="1:70">
+    <row r="55" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>87</v>
       </c>
@@ -13283,7 +13304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:70" ht="15" thickBot="1">
+    <row r="56" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>88</v>
       </c>
@@ -13497,7 +13518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:70">
+    <row r="57" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>76</v>
       </c>
@@ -13584,7 +13605,7 @@
       </c>
       <c r="AR57" s="32">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>293.1306760317288</v>
       </c>
       <c r="AS57" s="32">
         <f t="shared" si="55"/>
@@ -13617,8 +13638,14 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="BB57" s="8"/>
-      <c r="BC57" s="9"/>
-      <c r="BD57" s="21"/>
+      <c r="BC57" s="9">
+        <f>4.88551126719548*24*60/BG57</f>
+        <v>1.1071980208941599E-2</v>
+      </c>
+      <c r="BD57" s="21">
+        <f>608.5464479/BG57</f>
+        <v>9.5773756358199559E-4</v>
+      </c>
       <c r="BE57" s="9">
         <f t="shared" si="44"/>
         <v>4.8544560000000008</v>
@@ -13641,7 +13668,7 @@
       </c>
       <c r="BJ57" s="10">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>422108.17348568945</v>
       </c>
       <c r="BK57" s="10" t="str">
         <f t="shared" si="19"/>
@@ -13649,7 +13676,7 @@
       </c>
       <c r="BL57" s="10">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>293.1306760317288</v>
       </c>
       <c r="BM57" s="28" t="str">
         <f t="shared" si="13"/>
@@ -13660,23 +13687,23 @@
         <v/>
       </c>
       <c r="BO57" s="10">
-        <f t="shared" si="49"/>
-        <v>0</v>
+        <f>IF(C57="Julia",BD57*BG57,"")</f>
+        <v>608.54644789999998</v>
       </c>
       <c r="BP57" s="58">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>761378.37930319167</v>
       </c>
       <c r="BQ57" s="30">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>293.1306760317288</v>
       </c>
       <c r="BR57" s="26">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>608.54644789999998</v>
       </c>
     </row>
-    <row r="58" spans="1:70" ht="15">
+    <row r="58" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>79</v>
       </c>
@@ -13732,7 +13759,7 @@
       <c r="U58" s="40">
         <v>0.12</v>
       </c>
-      <c r="V58" s="86">
+      <c r="V58" s="72">
         <v>2.39</v>
       </c>
       <c r="W58" s="40">
@@ -13875,7 +13902,7 @@
         <v>0</v>
       </c>
       <c r="BO58" s="43" t="str">
-        <f t="shared" si="49"/>
+        <f>IF(C58="Julia",BD58*BG58,"")</f>
         <v/>
       </c>
       <c r="BP58" s="55">
@@ -13891,7 +13918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:70">
+    <row r="59" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>81</v>
       </c>
@@ -14106,7 +14133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:70">
+    <row r="60" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>82</v>
       </c>
@@ -14229,7 +14256,7 @@
       </c>
       <c r="AR60" s="41">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>0.16891666666666669</v>
       </c>
       <c r="AS60" s="41">
         <f t="shared" si="55"/>
@@ -14261,7 +14288,9 @@
       <c r="BA60" s="42">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="BB60" s="11"/>
+      <c r="BB60" s="11">
+        <v>0.02</v>
+      </c>
       <c r="BC60" s="42"/>
       <c r="BD60" s="22"/>
       <c r="BE60" s="42">
@@ -14286,11 +14315,11 @@
       </c>
       <c r="BJ60" s="43">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>243.24</v>
       </c>
       <c r="BK60" s="43">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>0.16891666666666669</v>
       </c>
       <c r="BL60" s="43" t="str">
         <f t="shared" si="12"/>
@@ -14310,18 +14339,18 @@
       </c>
       <c r="BP60" s="55">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>438.74458874458884</v>
       </c>
       <c r="BQ60" s="45">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>0.16891666666666669</v>
       </c>
       <c r="BR60" s="24">
         <f t="shared" si="54"/>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:70">
+    <row r="61" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>84</v>
       </c>
@@ -14444,7 +14473,7 @@
       </c>
       <c r="AR61" s="41">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>0.10938500000000001</v>
       </c>
       <c r="AS61" s="41">
         <f t="shared" si="55"/>
@@ -14476,7 +14505,9 @@
       <c r="BA61" s="42">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="BB61" s="11"/>
+      <c r="BB61" s="11">
+        <v>1.3100000000000001E-2</v>
+      </c>
       <c r="BD61" s="22"/>
       <c r="BE61" s="42">
         <f t="shared" si="44"/>
@@ -14500,11 +14531,11 @@
       </c>
       <c r="BJ61" s="43">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>157.51440000000002</v>
       </c>
       <c r="BK61" s="43">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>0.10938500000000001</v>
       </c>
       <c r="BL61" s="44" t="str">
         <f t="shared" si="12"/>
@@ -14524,18 +14555,18 @@
       </c>
       <c r="BP61" s="55">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>284.11688311688317</v>
       </c>
       <c r="BQ61" s="45">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>0.10938500000000001</v>
       </c>
       <c r="BR61" s="24">
         <f t="shared" si="54"/>
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:70">
+    <row r="62" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>85</v>
       </c>
@@ -14658,7 +14689,7 @@
       </c>
       <c r="AR62" s="41">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>0.12559798840033018</v>
       </c>
       <c r="AS62" s="41">
         <f t="shared" si="55"/>
@@ -14691,7 +14722,14 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="BB62" s="11"/>
-      <c r="BD62" s="22"/>
+      <c r="BC62" s="42">
+        <f>0.00209329980667217*24*60/BG62</f>
+        <v>1.5162735018148512E-2</v>
+      </c>
+      <c r="BD62" s="73">
+        <f>0.00001988/BG62</f>
+        <v>9.9999999999999995E-8</v>
+      </c>
       <c r="BE62" s="42">
         <f t="shared" si="44"/>
         <v>1.6782696000000002E-3</v>
@@ -14714,7 +14752,7 @@
       </c>
       <c r="BJ62" s="43">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>180.86110329647545</v>
       </c>
       <c r="BK62" s="43" t="str">
         <f t="shared" si="19"/>
@@ -14722,7 +14760,7 @@
       </c>
       <c r="BL62" s="44">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>0.12559798840033018</v>
       </c>
       <c r="BM62" s="44" t="str">
         <f t="shared" si="13"/>
@@ -14734,22 +14772,22 @@
       </c>
       <c r="BO62" s="43">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1.9879999999999999E-5</v>
       </c>
       <c r="BP62" s="55">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>326.22854129955891</v>
       </c>
       <c r="BQ62" s="45">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>0.12559798840033018</v>
       </c>
       <c r="BR62" s="24">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>1.9879999999999999E-5</v>
       </c>
     </row>
-    <row r="63" spans="1:70">
+    <row r="63" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>86</v>
       </c>
@@ -14872,7 +14910,7 @@
       </c>
       <c r="AR63" s="41">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>0.11309088181131839</v>
       </c>
       <c r="AS63" s="41">
         <f t="shared" si="55"/>
@@ -14905,7 +14943,14 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="BB63" s="11"/>
-      <c r="BD63" s="22"/>
+      <c r="BC63" s="42">
+        <f>0.00188484803018864*24*60/BG63</f>
+        <v>1.3557348468889318E-2</v>
+      </c>
+      <c r="BD63" s="73">
+        <f>0.00002002/BG63</f>
+        <v>1.0000000000000001E-7</v>
+      </c>
       <c r="BE63" s="42">
         <f t="shared" si="44"/>
         <v>1.9006988E-3</v>
@@ -14928,7 +14973,7 @@
       </c>
       <c r="BJ63" s="43">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>162.85086980829848</v>
       </c>
       <c r="BK63" s="43" t="str">
         <f t="shared" si="19"/>
@@ -14936,7 +14981,7 @@
       </c>
       <c r="BL63" s="44">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>0.11309088181131839</v>
       </c>
       <c r="BM63" s="44" t="str">
         <f t="shared" si="13"/>
@@ -14948,22 +14993,22 @@
       </c>
       <c r="BO63" s="43">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>2.0020000000000001E-5</v>
       </c>
       <c r="BP63" s="55">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>293.74255015926855</v>
       </c>
       <c r="BQ63" s="45">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>0.11309088181131839</v>
       </c>
       <c r="BR63" s="24">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>2.0020000000000001E-5</v>
       </c>
     </row>
-    <row r="64" spans="1:70">
+    <row r="64" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>87</v>
       </c>
@@ -15177,7 +15222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:70" ht="15">
+    <row r="65" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>88</v>
       </c>
@@ -15233,7 +15278,7 @@
       <c r="U65" s="40">
         <v>0.11</v>
       </c>
-      <c r="V65" s="86">
+      <c r="V65" s="72">
         <v>2.76</v>
       </c>
       <c r="W65" s="40">
@@ -15391,7 +15436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:70">
+    <row r="66" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>76</v>
       </c>
@@ -15408,24 +15453,38 @@
         <v>7</v>
       </c>
       <c r="F66" s="3"/>
-      <c r="G66" s="34"/>
+      <c r="G66" s="34">
+        <v>45575.356249999997</v>
+      </c>
       <c r="H66" s="3">
         <v>3888.32</v>
       </c>
       <c r="I66" s="3"/>
-      <c r="J66" s="6"/>
-      <c r="K66" s="6"/>
-      <c r="L66" s="6"/>
-      <c r="M66" s="6"/>
+      <c r="J66" s="6">
+        <v>2722.32</v>
+      </c>
+      <c r="K66" s="6">
+        <v>19</v>
+      </c>
+      <c r="L66" s="6">
+        <v>17.8</v>
+      </c>
+      <c r="M66" s="6">
+        <v>93.7</v>
+      </c>
       <c r="N66" s="6"/>
       <c r="O66" s="6"/>
       <c r="P66" s="6"/>
       <c r="Q66" s="6"/>
-      <c r="R66" s="6"/>
+      <c r="R66" s="6">
+        <v>6.5</v>
+      </c>
       <c r="S66" s="6"/>
       <c r="T66" s="6"/>
       <c r="U66" s="6"/>
-      <c r="V66" s="6"/>
+      <c r="V66" s="6">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="W66" s="6"/>
       <c r="X66" s="6"/>
       <c r="Y66" s="6"/>
@@ -15434,33 +15493,45 @@
       <c r="AB66" s="6"/>
       <c r="AC66" s="6"/>
       <c r="AD66" s="6"/>
-      <c r="AE66" s="16"/>
+      <c r="AE66" s="16">
+        <v>7.327</v>
+      </c>
       <c r="AF66" s="6"/>
-      <c r="AG66" s="6"/>
+      <c r="AG66" s="6">
+        <v>49.996602779481499</v>
+      </c>
       <c r="AH66" s="6"/>
-      <c r="AI66" s="6"/>
+      <c r="AI66" s="6">
+        <v>34.000473865150198</v>
+      </c>
       <c r="AJ66" s="6"/>
       <c r="AK66" s="6"/>
       <c r="AL66" s="6"/>
-      <c r="AM66" s="6"/>
-      <c r="AN66" s="6"/>
-      <c r="AO66" s="6"/>
+      <c r="AM66" s="6">
+        <v>54921.08203125</v>
+      </c>
+      <c r="AN66" s="6">
+        <v>22041.2578125</v>
+      </c>
+      <c r="AO66" s="6">
+        <v>643200.01220703102</v>
+      </c>
       <c r="AP66" s="6"/>
       <c r="AQ66" s="32">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>0.49996602779481497</v>
       </c>
       <c r="AR66" s="32">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>322.38396781074897</v>
       </c>
       <c r="AS66" s="32">
         <f t="shared" si="55"/>
-        <v>-47996.265625</v>
+        <v>6924.81640625</v>
       </c>
       <c r="AT66" s="32">
         <f t="shared" si="56"/>
-        <v>-21432.216796875</v>
+        <v>609.041015625</v>
       </c>
       <c r="AU66" s="32">
         <f t="shared" si="57"/>
@@ -15485,31 +15556,37 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="BB66" s="8"/>
-      <c r="BC66" s="9"/>
-      <c r="BD66" s="21"/>
+      <c r="BC66" s="9">
+        <f>5.37306613017915*24*60/BG66</f>
+        <v>1.2029252301953543E-2</v>
+      </c>
+      <c r="BD66" s="21">
+        <f>994.549312093751/BG66</f>
+        <v>1.5462520106010646E-3</v>
+      </c>
       <c r="BE66" s="9">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>4.5795840869140614</v>
       </c>
       <c r="BF66" s="9">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>6594.6010851562487</v>
       </c>
       <c r="BG66" s="9">
         <f t="shared" si="45"/>
-        <v>591520</v>
-      </c>
-      <c r="BH66" s="10" t="str">
+        <v>643200.01220703102</v>
+      </c>
+      <c r="BH66" s="10">
         <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="BI66" s="10" t="str">
+        <v>8.5387252781289114E-2</v>
+      </c>
+      <c r="BI66" s="10">
         <f t="shared" si="47"/>
-        <v/>
+        <v>9.2772098025760141E-2</v>
       </c>
       <c r="BJ66" s="10">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>464232.9136474785</v>
       </c>
       <c r="BK66" s="10" t="str">
         <f t="shared" si="19"/>
@@ -15517,7 +15594,7 @@
       </c>
       <c r="BL66" s="10">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>322.38396781074897</v>
       </c>
       <c r="BM66" s="28" t="str">
         <f t="shared" si="13"/>
@@ -15529,22 +15606,22 @@
       </c>
       <c r="BO66" s="10">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>994.54931209375104</v>
       </c>
       <c r="BP66" s="58">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>837360.95535259473</v>
       </c>
       <c r="BQ66" s="30">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>322.38396781074897</v>
       </c>
       <c r="BR66" s="26">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>994.54931209375104</v>
       </c>
     </row>
-    <row r="67" spans="1:70">
+    <row r="67" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>79</v>
       </c>
@@ -15560,58 +15637,122 @@
       <c r="E67">
         <v>7</v>
       </c>
-      <c r="G67" s="35"/>
+      <c r="G67" s="35">
+        <v>45575.468657407408</v>
+      </c>
       <c r="H67">
         <v>3888.32</v>
       </c>
-      <c r="J67" s="40"/>
-      <c r="K67" s="40"/>
-      <c r="L67" s="40"/>
-      <c r="M67" s="40"/>
-      <c r="N67" s="40"/>
-      <c r="O67" s="40"/>
-      <c r="P67" s="40"/>
-      <c r="Q67" s="40"/>
-      <c r="R67" s="40"/>
+      <c r="J67" s="40">
+        <v>3736.0050000000001</v>
+      </c>
+      <c r="K67" s="40">
+        <v>22.940999999999999</v>
+      </c>
+      <c r="L67" s="40">
+        <v>20.937999999999999</v>
+      </c>
+      <c r="M67" s="40">
+        <v>91.3</v>
+      </c>
+      <c r="N67" s="40">
+        <v>15.94</v>
+      </c>
+      <c r="O67" s="40">
+        <v>337</v>
+      </c>
+      <c r="P67" s="40">
+        <v>1.39</v>
+      </c>
+      <c r="Q67" s="40">
+        <v>0.33</v>
+      </c>
+      <c r="R67" s="40">
+        <v>3.2</v>
+      </c>
       <c r="S67" s="40"/>
-      <c r="T67" s="40"/>
-      <c r="U67" s="40"/>
-      <c r="V67" s="40"/>
-      <c r="W67" s="40"/>
-      <c r="X67" s="40"/>
-      <c r="Y67" s="40"/>
-      <c r="Z67" s="40"/>
-      <c r="AA67" s="40"/>
-      <c r="AB67" s="40"/>
-      <c r="AC67" s="40"/>
-      <c r="AD67" s="40"/>
-      <c r="AE67" s="17"/>
-      <c r="AF67" s="40"/>
-      <c r="AG67" s="40"/>
-      <c r="AH67" s="40"/>
-      <c r="AI67" s="40"/>
-      <c r="AJ67" s="40"/>
-      <c r="AK67" s="40"/>
-      <c r="AL67" s="47"/>
-      <c r="AM67" s="40"/>
-      <c r="AN67" s="40"/>
-      <c r="AO67" s="40"/>
+      <c r="T67" s="40">
+        <v>0.21</v>
+      </c>
+      <c r="U67" s="40">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="V67" s="40">
+        <v>2.09</v>
+      </c>
+      <c r="W67" s="40">
+        <v>7.3070000000000004</v>
+      </c>
+      <c r="X67" s="40">
+        <v>43.6</v>
+      </c>
+      <c r="Y67" s="40">
+        <v>65.900000000000006</v>
+      </c>
+      <c r="Z67" s="40">
+        <v>2.31</v>
+      </c>
+      <c r="AA67" s="40">
+        <v>140.5</v>
+      </c>
+      <c r="AB67" s="40">
+        <v>19.3</v>
+      </c>
+      <c r="AC67" s="40">
+        <v>38.200000000000003</v>
+      </c>
+      <c r="AD67" s="40">
+        <v>53.8</v>
+      </c>
+      <c r="AE67" s="17">
+        <v>7.266</v>
+      </c>
+      <c r="AF67" s="40">
+        <v>409</v>
+      </c>
+      <c r="AG67" s="40">
+        <v>50.4</v>
+      </c>
+      <c r="AH67" s="40">
+        <v>7.3049999999999997</v>
+      </c>
+      <c r="AI67" s="40">
+        <v>34</v>
+      </c>
+      <c r="AJ67" s="40">
+        <v>2</v>
+      </c>
+      <c r="AK67" s="40">
+        <v>5.6</v>
+      </c>
+      <c r="AL67" s="47">
+        <v>0.2</v>
+      </c>
+      <c r="AM67" s="40">
+        <v>13.4</v>
+      </c>
+      <c r="AN67" s="40">
+        <v>4</v>
+      </c>
+      <c r="AO67" s="40">
+        <v>198.3</v>
+      </c>
       <c r="AP67" s="40"/>
       <c r="AQ67" s="41">
         <f t="shared" ref="AQ67:AQ98" si="59">AG67/100</f>
-        <v>0</v>
+        <v>0.504</v>
       </c>
       <c r="AR67" s="41">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>9.964812960000001E-2</v>
       </c>
       <c r="AS67" s="41">
         <f t="shared" si="55"/>
-        <v>-10.6</v>
+        <v>2.8000000000000007</v>
       </c>
       <c r="AT67" s="41">
         <f t="shared" si="56"/>
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AU67" s="41">
         <f t="shared" si="57"/>
@@ -15640,27 +15781,27 @@
       <c r="BD67" s="22"/>
       <c r="BE67" s="42">
         <f t="shared" ref="BE67:BE98" si="60">BA67*L67*BG67/1000</f>
-        <v>0</v>
+        <v>1.6608021600000001E-3</v>
       </c>
       <c r="BF67" s="42">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>2.3915551103999997</v>
       </c>
       <c r="BG67" s="42">
         <f t="shared" ref="BG67:BG98" si="61">IF(ISBLANK(AO67), AW67+SUM(AJ67:AL67,AM67:AN67)-(AV67*(E67+1)), AO67)</f>
-        <v>180.8</v>
-      </c>
-      <c r="BH67" s="43" t="str">
+        <v>198.3</v>
+      </c>
+      <c r="BH67" s="43">
         <f t="shared" ref="BH67:BH98" si="62">IF(ISBLANK(AM67),"",IFERROR(AM67/BG67,0))</f>
-        <v/>
-      </c>
-      <c r="BI67" s="43" t="str">
+        <v>6.7574382249117493E-2</v>
+      </c>
+      <c r="BI67" s="43">
         <f t="shared" ref="BI67:BI98" si="63">IF(ISBLANK(AM67),"",AM67/AW67)</f>
-        <v/>
+        <v>6.7000000000000004E-2</v>
       </c>
       <c r="BJ67" s="43">
         <f t="shared" ref="BJ67:BJ98" si="64">AR67*24*60</f>
-        <v>0</v>
+        <v>143.49330662400001</v>
       </c>
       <c r="BK67" s="43" t="str">
         <f t="shared" si="19"/>
@@ -15672,11 +15813,11 @@
       </c>
       <c r="BM67" s="44">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>9.964812960000001E-2</v>
       </c>
       <c r="BN67" s="43">
         <f t="shared" si="58"/>
-        <v>1.3560000000000003</v>
+        <v>0</v>
       </c>
       <c r="BO67" s="43" t="str">
         <f t="shared" ref="BO67:BO98" si="65">IF(C67="Julia",BD67*BG67,"")</f>
@@ -15684,18 +15825,18 @@
       </c>
       <c r="BP67" s="55">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>258.82631064935072</v>
       </c>
       <c r="BQ67" s="45">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>9.964812960000001E-2</v>
       </c>
       <c r="BR67" s="24">
         <f t="shared" si="54"/>
-        <v>1.3560000000000003</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:70">
+    <row r="68" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>81</v>
       </c>
@@ -15711,58 +15852,122 @@
       <c r="E68">
         <v>7</v>
       </c>
-      <c r="G68" s="35"/>
+      <c r="G68" s="35">
+        <v>45575.469490740739</v>
+      </c>
       <c r="H68">
         <v>3888.32</v>
       </c>
-      <c r="J68" s="40"/>
-      <c r="K68" s="40"/>
-      <c r="L68" s="40"/>
-      <c r="M68" s="40"/>
-      <c r="N68" s="40"/>
-      <c r="O68" s="40"/>
-      <c r="P68" s="40"/>
-      <c r="Q68" s="40"/>
-      <c r="R68" s="40"/>
+      <c r="J68" s="40">
+        <v>3687.12</v>
+      </c>
+      <c r="K68" s="40">
+        <v>21.161000000000001</v>
+      </c>
+      <c r="L68" s="40">
+        <v>18.928000000000001</v>
+      </c>
+      <c r="M68" s="40">
+        <v>89.4</v>
+      </c>
+      <c r="N68" s="40">
+        <v>15.92</v>
+      </c>
+      <c r="O68" s="40">
+        <v>328</v>
+      </c>
+      <c r="P68" s="40">
+        <v>1.36</v>
+      </c>
+      <c r="Q68" s="40">
+        <v>0.34</v>
+      </c>
+      <c r="R68" s="40">
+        <v>2.76</v>
+      </c>
       <c r="S68" s="40"/>
-      <c r="T68" s="40"/>
-      <c r="U68" s="40"/>
-      <c r="V68" s="40"/>
-      <c r="W68" s="40"/>
-      <c r="X68" s="40"/>
-      <c r="Y68" s="40"/>
-      <c r="Z68" s="40"/>
-      <c r="AA68" s="40"/>
-      <c r="AB68" s="40"/>
-      <c r="AC68" s="40"/>
-      <c r="AD68" s="40"/>
-      <c r="AE68" s="17"/>
-      <c r="AF68" s="40"/>
-      <c r="AG68" s="40"/>
-      <c r="AH68" s="40"/>
-      <c r="AI68" s="40"/>
-      <c r="AJ68" s="40"/>
-      <c r="AK68" s="40"/>
-      <c r="AL68" s="47"/>
-      <c r="AM68" s="40"/>
-      <c r="AN68" s="40"/>
-      <c r="AO68" s="40"/>
+      <c r="T68" s="40">
+        <v>0.15</v>
+      </c>
+      <c r="U68" s="40">
+        <v>0.13</v>
+      </c>
+      <c r="V68" s="40">
+        <v>2.48</v>
+      </c>
+      <c r="W68" s="40">
+        <v>7.2889999999999997</v>
+      </c>
+      <c r="X68" s="40">
+        <v>30.7</v>
+      </c>
+      <c r="Y68" s="40">
+        <v>68.599999999999994</v>
+      </c>
+      <c r="Z68" s="40">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="AA68" s="40">
+        <v>140.4</v>
+      </c>
+      <c r="AB68" s="40">
+        <v>13</v>
+      </c>
+      <c r="AC68" s="40">
+        <v>26.9</v>
+      </c>
+      <c r="AD68" s="40">
+        <v>56</v>
+      </c>
+      <c r="AE68" s="17">
+        <v>7.2480000000000002</v>
+      </c>
+      <c r="AF68" s="40">
+        <v>410</v>
+      </c>
+      <c r="AG68" s="40">
+        <v>49</v>
+      </c>
+      <c r="AH68" s="40">
+        <v>7.3040000000000003</v>
+      </c>
+      <c r="AI68" s="40">
+        <v>34</v>
+      </c>
+      <c r="AJ68" s="40">
+        <v>2.1</v>
+      </c>
+      <c r="AK68" s="40">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="AL68" s="47">
+        <v>0.2</v>
+      </c>
+      <c r="AM68" s="40">
+        <v>13.3</v>
+      </c>
+      <c r="AN68" s="40">
+        <v>4.3</v>
+      </c>
+      <c r="AO68" s="40">
+        <v>197.3</v>
+      </c>
       <c r="AP68" s="40"/>
       <c r="AQ68" s="41">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="AR68" s="41">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>8.9627865600000009E-2</v>
       </c>
       <c r="AS68" s="41">
         <f t="shared" si="55"/>
-        <v>-10.9</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="AT68" s="41">
         <f t="shared" si="56"/>
-        <v>-4.3</v>
+        <v>0</v>
       </c>
       <c r="AU68" s="41">
         <f t="shared" si="57"/>
@@ -15791,27 +15996,27 @@
       <c r="BD68" s="22"/>
       <c r="BE68" s="42">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>1.4937977600000003E-3</v>
       </c>
       <c r="BF68" s="42">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>2.1510687744000005</v>
       </c>
       <c r="BG68" s="42">
         <f t="shared" si="61"/>
-        <v>180.8</v>
-      </c>
-      <c r="BH68" s="43" t="str">
+        <v>197.3</v>
+      </c>
+      <c r="BH68" s="43">
         <f t="shared" si="62"/>
-        <v/>
-      </c>
-      <c r="BI68" s="43" t="str">
+        <v>6.7410035478966041E-2</v>
+      </c>
+      <c r="BI68" s="43">
         <f t="shared" si="63"/>
-        <v/>
+        <v>6.6500000000000004E-2</v>
       </c>
       <c r="BJ68" s="43">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>129.064126464</v>
       </c>
       <c r="BK68" s="43" t="str">
         <f t="shared" si="19"/>
@@ -15823,11 +16028,11 @@
       </c>
       <c r="BM68" s="44">
         <f t="shared" ref="BM68:BM119" si="67">IF(C68="No MPC", 60*BA68*L68*BG68/1000,"")</f>
-        <v>0</v>
+        <v>8.9627865600000009E-2</v>
       </c>
       <c r="BN68" s="43">
         <f t="shared" si="58"/>
-        <v>1.3560000000000003</v>
+        <v>0</v>
       </c>
       <c r="BO68" s="43" t="str">
         <f t="shared" si="65"/>
@@ -15835,18 +16040,18 @@
       </c>
       <c r="BP68" s="55">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>232.79965090909096</v>
       </c>
       <c r="BQ68" s="45">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>8.9627865600000009E-2</v>
       </c>
       <c r="BR68" s="24">
         <f t="shared" si="54"/>
-        <v>1.3560000000000003</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:70">
+    <row r="69" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>82</v>
       </c>
@@ -15862,42 +16067,104 @@
       <c r="E69">
         <v>7</v>
       </c>
-      <c r="G69" s="35"/>
+      <c r="G69" s="35">
+        <v>45575.470335648148</v>
+      </c>
       <c r="H69">
         <v>3888.32</v>
       </c>
-      <c r="J69" s="40"/>
-      <c r="K69" s="40"/>
-      <c r="L69" s="40"/>
-      <c r="M69" s="40"/>
-      <c r="N69" s="40"/>
-      <c r="O69" s="40"/>
-      <c r="P69" s="40"/>
-      <c r="Q69" s="40"/>
-      <c r="R69" s="40"/>
+      <c r="J69" s="40">
+        <v>3167.31</v>
+      </c>
+      <c r="K69" s="40">
+        <v>20.071000000000002</v>
+      </c>
+      <c r="L69" s="40">
+        <v>5.5369999999999999</v>
+      </c>
+      <c r="M69" s="40">
+        <v>27.6</v>
+      </c>
+      <c r="N69" s="40">
+        <v>12.68</v>
+      </c>
+      <c r="O69" s="40">
+        <v>439</v>
+      </c>
+      <c r="P69" s="40">
+        <v>5.22</v>
+      </c>
+      <c r="Q69" s="40">
+        <v>0.35</v>
+      </c>
+      <c r="R69" s="40">
+        <v>0.16</v>
+      </c>
       <c r="S69" s="40"/>
-      <c r="T69" s="40"/>
-      <c r="U69" s="40"/>
-      <c r="V69" s="40"/>
-      <c r="W69" s="40"/>
-      <c r="X69" s="40"/>
-      <c r="Y69" s="40"/>
-      <c r="Z69" s="40"/>
-      <c r="AA69" s="40"/>
-      <c r="AB69" s="40"/>
-      <c r="AC69" s="40"/>
-      <c r="AD69" s="40"/>
-      <c r="AE69" s="17"/>
-      <c r="AF69" s="40"/>
-      <c r="AG69" s="40"/>
-      <c r="AH69" s="40"/>
-      <c r="AI69" s="40"/>
-      <c r="AJ69" s="40"/>
-      <c r="AK69" s="40"/>
-      <c r="AL69" s="47"/>
-      <c r="AM69" s="40"/>
-      <c r="AN69" s="40"/>
-      <c r="AO69" s="40"/>
+      <c r="T69" s="40">
+        <v>0.15</v>
+      </c>
+      <c r="U69" s="40">
+        <v>0.94</v>
+      </c>
+      <c r="V69" s="40">
+        <v>4.42</v>
+      </c>
+      <c r="W69" s="40">
+        <v>7.0549999999999997</v>
+      </c>
+      <c r="X69" s="40">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="Y69" s="40">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="40">
+        <v>6.92</v>
+      </c>
+      <c r="AA69" s="40">
+        <v>183.1</v>
+      </c>
+      <c r="AB69" s="40">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="AC69" s="40">
+        <v>34.4</v>
+      </c>
+      <c r="AD69" s="40">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="17">
+        <v>7.0190000000000001</v>
+      </c>
+      <c r="AF69" s="40">
+        <v>408</v>
+      </c>
+      <c r="AG69" s="46"/>
+      <c r="AH69" s="40">
+        <v>7.085</v>
+      </c>
+      <c r="AI69" s="40">
+        <v>34</v>
+      </c>
+      <c r="AJ69" s="40">
+        <v>6.4</v>
+      </c>
+      <c r="AK69" s="40">
+        <v>3.2</v>
+      </c>
+      <c r="AL69" s="47">
+        <v>0.2</v>
+      </c>
+      <c r="AM69" s="40">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="AN69" s="40">
+        <v>4.5</v>
+      </c>
+      <c r="AO69" s="40">
+        <v>206.1</v>
+      </c>
       <c r="AP69" s="40"/>
       <c r="AQ69" s="41">
         <f t="shared" si="59"/>
@@ -15905,15 +16172,15 @@
       </c>
       <c r="AR69" s="41">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>0.17174999999999999</v>
       </c>
       <c r="AS69" s="41">
         <f t="shared" si="55"/>
-        <v>-15.2</v>
+        <v>4.4000000000000021</v>
       </c>
       <c r="AT69" s="41">
         <f t="shared" si="56"/>
-        <v>-4.5</v>
+        <v>0</v>
       </c>
       <c r="AU69" s="41">
         <f t="shared" si="57"/>
@@ -15937,36 +16204,38 @@
       <c r="BA69" s="42">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="BB69" s="11"/>
+      <c r="BB69" s="11">
+        <v>0.02</v>
+      </c>
       <c r="BC69" s="42"/>
       <c r="BD69" s="22"/>
       <c r="BE69" s="42">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>4.5647028000000007E-4</v>
       </c>
       <c r="BF69" s="42">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>0.65731720320000009</v>
       </c>
       <c r="BG69" s="42">
         <f t="shared" si="61"/>
-        <v>180.8</v>
-      </c>
-      <c r="BH69" s="43" t="str">
+        <v>206.1</v>
+      </c>
+      <c r="BH69" s="43">
         <f t="shared" si="62"/>
-        <v/>
-      </c>
-      <c r="BI69" s="43" t="str">
+        <v>9.5099466278505587E-2</v>
+      </c>
+      <c r="BI69" s="43">
         <f t="shared" si="63"/>
-        <v/>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="BJ69" s="43">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>247.32</v>
       </c>
       <c r="BK69" s="43">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>0.17174999999999999</v>
       </c>
       <c r="BL69" s="43" t="str">
         <f t="shared" si="66"/>
@@ -15978,7 +16247,7 @@
       </c>
       <c r="BN69" s="43">
         <f t="shared" si="58"/>
-        <v>1.3560000000000003</v>
+        <v>1.4633099999999999</v>
       </c>
       <c r="BO69" s="43" t="str">
         <f t="shared" si="65"/>
@@ -15986,18 +16255,18 @@
       </c>
       <c r="BP69" s="55">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>446.10389610389609</v>
       </c>
       <c r="BQ69" s="45">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>0.17174999999999999</v>
       </c>
       <c r="BR69" s="24">
         <f t="shared" si="54"/>
-        <v>1.3560000000000003</v>
+        <v>1.4633099999999999</v>
       </c>
     </row>
-    <row r="70" spans="1:70">
+    <row r="70" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>84</v>
       </c>
@@ -16013,58 +16282,122 @@
       <c r="E70">
         <v>7</v>
       </c>
-      <c r="G70" s="35"/>
+      <c r="G70" s="35">
+        <v>45575.471192129633</v>
+      </c>
       <c r="H70">
         <v>3888.32</v>
       </c>
-      <c r="J70" s="40"/>
-      <c r="K70" s="40"/>
-      <c r="L70" s="40"/>
-      <c r="M70" s="40"/>
-      <c r="N70" s="40"/>
-      <c r="O70" s="40"/>
-      <c r="P70" s="40"/>
-      <c r="Q70" s="40"/>
-      <c r="R70" s="40"/>
+      <c r="J70" s="40">
+        <v>3814.8449999999998</v>
+      </c>
+      <c r="K70" s="40">
+        <v>23.63</v>
+      </c>
+      <c r="L70" s="40">
+        <v>21.545999999999999</v>
+      </c>
+      <c r="M70" s="40">
+        <v>91.2</v>
+      </c>
+      <c r="N70" s="40">
+        <v>16.510000000000002</v>
+      </c>
+      <c r="O70" s="40">
+        <v>337</v>
+      </c>
+      <c r="P70" s="40">
+        <v>1.38</v>
+      </c>
+      <c r="Q70" s="40">
+        <v>0.32</v>
+      </c>
+      <c r="R70" s="40">
+        <v>0.9</v>
+      </c>
       <c r="S70" s="40"/>
-      <c r="T70" s="40"/>
-      <c r="U70" s="40"/>
-      <c r="V70" s="40"/>
-      <c r="W70" s="40"/>
-      <c r="X70" s="40"/>
-      <c r="Y70" s="40"/>
-      <c r="Z70" s="40"/>
-      <c r="AA70" s="40"/>
-      <c r="AB70" s="40"/>
-      <c r="AC70" s="40"/>
-      <c r="AD70" s="40"/>
-      <c r="AE70" s="17"/>
-      <c r="AF70" s="40"/>
-      <c r="AG70" s="40"/>
-      <c r="AH70" s="40"/>
-      <c r="AI70" s="40"/>
-      <c r="AJ70" s="40"/>
-      <c r="AK70" s="40"/>
-      <c r="AL70" s="47"/>
-      <c r="AM70" s="40"/>
-      <c r="AN70" s="40"/>
-      <c r="AO70" s="40"/>
+      <c r="T70" s="40">
+        <v>0.22</v>
+      </c>
+      <c r="U70" s="40">
+        <v>0.16</v>
+      </c>
+      <c r="V70" s="40">
+        <v>2.65</v>
+      </c>
+      <c r="W70" s="40">
+        <v>7.31</v>
+      </c>
+      <c r="X70" s="40">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="Y70" s="40">
+        <v>51.9</v>
+      </c>
+      <c r="Z70" s="40">
+        <v>1.74</v>
+      </c>
+      <c r="AA70" s="40">
+        <v>147.5</v>
+      </c>
+      <c r="AB70" s="40">
+        <v>16.2</v>
+      </c>
+      <c r="AC70" s="40">
+        <v>31.8</v>
+      </c>
+      <c r="AD70" s="40">
+        <v>42.1</v>
+      </c>
+      <c r="AE70" s="17">
+        <v>7.2690000000000001</v>
+      </c>
+      <c r="AF70" s="40">
+        <v>407</v>
+      </c>
+      <c r="AG70" s="40">
+        <v>49.7</v>
+      </c>
+      <c r="AH70" s="40">
+        <v>7.3090000000000002</v>
+      </c>
+      <c r="AI70" s="40">
+        <v>34</v>
+      </c>
+      <c r="AJ70" s="40">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AK70" s="40">
+        <v>3.3</v>
+      </c>
+      <c r="AL70" s="47">
+        <v>0.2</v>
+      </c>
+      <c r="AM70" s="40">
+        <v>18.3</v>
+      </c>
+      <c r="AN70" s="40">
+        <v>3.9</v>
+      </c>
+      <c r="AO70" s="40">
+        <v>200.2</v>
+      </c>
       <c r="AP70" s="40"/>
       <c r="AQ70" s="41">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>0.49700000000000005</v>
       </c>
       <c r="AR70" s="41">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>0.10677333333333333</v>
       </c>
       <c r="AS70" s="41">
         <f t="shared" si="55"/>
-        <v>-15.3</v>
+        <v>3</v>
       </c>
       <c r="AT70" s="41">
         <f t="shared" si="56"/>
-        <v>-3.9</v>
+        <v>0</v>
       </c>
       <c r="AU70" s="41">
         <f t="shared" si="57"/>
@@ -16088,35 +16421,37 @@
       <c r="BA70" s="42">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="BB70" s="11"/>
+      <c r="BB70" s="11">
+        <v>1.2800000000000001E-2</v>
+      </c>
       <c r="BD70" s="22"/>
       <c r="BE70" s="42">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>1.7254036799999998E-3</v>
       </c>
       <c r="BF70" s="42">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>2.4845812991999998</v>
       </c>
       <c r="BG70" s="42">
         <f t="shared" si="61"/>
-        <v>180.8</v>
-      </c>
-      <c r="BH70" s="43" t="str">
+        <v>200.2</v>
+      </c>
+      <c r="BH70" s="43">
         <f t="shared" si="62"/>
-        <v/>
-      </c>
-      <c r="BI70" s="43" t="str">
+        <v>9.1408591408591422E-2</v>
+      </c>
+      <c r="BI70" s="43">
         <f t="shared" si="63"/>
-        <v/>
+        <v>9.1499999999999998E-2</v>
       </c>
       <c r="BJ70" s="43">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>153.75360000000001</v>
       </c>
       <c r="BK70" s="43">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>0.10677333333333333</v>
       </c>
       <c r="BL70" s="44" t="str">
         <f t="shared" si="66"/>
@@ -16128,7 +16463,7 @@
       </c>
       <c r="BN70" s="43">
         <f t="shared" si="58"/>
-        <v>1.3560000000000003</v>
+        <v>1.05105</v>
       </c>
       <c r="BO70" s="43" t="str">
         <f t="shared" si="65"/>
@@ -16136,18 +16471,18 @@
       </c>
       <c r="BP70" s="55">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>277.33333333333331</v>
       </c>
       <c r="BQ70" s="45">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>0.10677333333333333</v>
       </c>
       <c r="BR70" s="24">
         <f t="shared" si="54"/>
-        <v>1.3560000000000003</v>
+        <v>1.05105</v>
       </c>
     </row>
-    <row r="71" spans="1:70">
+    <row r="71" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>85</v>
       </c>
@@ -16163,58 +16498,122 @@
       <c r="E71">
         <v>7</v>
       </c>
-      <c r="G71" s="35"/>
+      <c r="G71" s="35">
+        <v>45575.472037037034</v>
+      </c>
       <c r="H71">
         <v>3888.32</v>
       </c>
-      <c r="J71" s="40"/>
-      <c r="K71" s="40"/>
-      <c r="L71" s="40"/>
-      <c r="M71" s="40"/>
-      <c r="N71" s="40"/>
-      <c r="O71" s="40"/>
-      <c r="P71" s="40"/>
-      <c r="Q71" s="40"/>
-      <c r="R71" s="40"/>
+      <c r="J71" s="40">
+        <v>3932.895</v>
+      </c>
+      <c r="K71" s="40">
+        <v>23.419</v>
+      </c>
+      <c r="L71" s="40">
+        <v>21.161000000000001</v>
+      </c>
+      <c r="M71" s="40">
+        <v>90.4</v>
+      </c>
+      <c r="N71" s="40">
+        <v>16.38</v>
+      </c>
+      <c r="O71" s="40">
+        <v>336</v>
+      </c>
+      <c r="P71" s="40">
+        <v>1.43</v>
+      </c>
+      <c r="Q71" s="40">
+        <v>0.31</v>
+      </c>
+      <c r="R71" s="40">
+        <v>1.04</v>
+      </c>
       <c r="S71" s="40"/>
-      <c r="T71" s="40"/>
-      <c r="U71" s="40"/>
-      <c r="V71" s="40"/>
-      <c r="W71" s="40"/>
-      <c r="X71" s="40"/>
-      <c r="Y71" s="40"/>
-      <c r="Z71" s="40"/>
-      <c r="AA71" s="40"/>
-      <c r="AB71" s="40"/>
-      <c r="AC71" s="40"/>
-      <c r="AD71" s="40"/>
-      <c r="AE71" s="17"/>
-      <c r="AF71" s="40"/>
-      <c r="AG71" s="40"/>
-      <c r="AH71" s="40"/>
-      <c r="AI71" s="40"/>
-      <c r="AJ71" s="40"/>
-      <c r="AK71" s="40"/>
-      <c r="AL71" s="47"/>
-      <c r="AM71" s="40"/>
-      <c r="AN71" s="40"/>
-      <c r="AO71" s="40"/>
+      <c r="T71" s="40">
+        <v>0.22</v>
+      </c>
+      <c r="U71" s="40">
+        <v>0.15</v>
+      </c>
+      <c r="V71" s="40">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="W71" s="40">
+        <v>7.3070000000000004</v>
+      </c>
+      <c r="X71" s="40">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="Y71" s="40">
+        <v>45.9</v>
+      </c>
+      <c r="Z71" s="40">
+        <v>1.85</v>
+      </c>
+      <c r="AA71" s="40">
+        <v>146.80000000000001</v>
+      </c>
+      <c r="AB71" s="40">
+        <v>14.7</v>
+      </c>
+      <c r="AC71" s="40">
+        <v>29.1</v>
+      </c>
+      <c r="AD71" s="40">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="AE71" s="17">
+        <v>7.266</v>
+      </c>
+      <c r="AF71" s="40">
+        <v>407</v>
+      </c>
+      <c r="AG71" s="40">
+        <v>50</v>
+      </c>
+      <c r="AH71" s="40">
+        <v>7.3040000000000003</v>
+      </c>
+      <c r="AI71" s="40">
+        <v>34</v>
+      </c>
+      <c r="AJ71" s="40">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AK71" s="40">
+        <v>2</v>
+      </c>
+      <c r="AL71" s="47">
+        <v>0.2</v>
+      </c>
+      <c r="AM71" s="40">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="AN71" s="40">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AO71" s="40">
+        <v>199.1</v>
+      </c>
       <c r="AP71" s="40"/>
       <c r="AQ71" s="41">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR71" s="41">
         <f t="shared" ref="AR71:AR102" si="68">BQ71</f>
-        <v>0</v>
+        <v>0.12528233500386121</v>
       </c>
       <c r="AS71" s="41">
         <f t="shared" si="55"/>
-        <v>-16</v>
+        <v>3.3999999999999986</v>
       </c>
       <c r="AT71" s="41">
         <f t="shared" si="56"/>
-        <v>-4.5999999999999996</v>
+        <v>0</v>
       </c>
       <c r="AU71" s="41">
         <f t="shared" si="57"/>
@@ -16239,30 +16638,37 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="BB71" s="11"/>
-      <c r="BD71" s="22"/>
+      <c r="BC71" s="42">
+        <f>0.00208803891673102*24*60/BG71</f>
+        <v>1.5101838473594521E-2</v>
+      </c>
+      <c r="BD71" s="73">
+        <f>0.00001991/BG71</f>
+        <v>1.0000000000000001E-7</v>
+      </c>
       <c r="BE71" s="42">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>1.6852620399999999E-3</v>
       </c>
       <c r="BF71" s="42">
         <f t="shared" ref="BF71:BF102" si="69">BE71*24*60</f>
-        <v>0</v>
+        <v>2.4267773375999999</v>
       </c>
       <c r="BG71" s="42">
         <f t="shared" si="61"/>
-        <v>180.8</v>
-      </c>
-      <c r="BH71" s="43" t="str">
+        <v>199.1</v>
+      </c>
+      <c r="BH71" s="43">
         <f t="shared" si="62"/>
-        <v/>
-      </c>
-      <c r="BI71" s="43" t="str">
+        <v>9.7438473129080855E-2</v>
+      </c>
+      <c r="BI71" s="43">
         <f t="shared" si="63"/>
-        <v/>
+        <v>9.6999999999999989E-2</v>
       </c>
       <c r="BJ71" s="43">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>180.40656240556015</v>
       </c>
       <c r="BK71" s="43" t="str">
         <f t="shared" ref="BK71:BK119" si="70">IF(C71="Python",BB71*BG71/24,"")</f>
@@ -16270,7 +16676,7 @@
       </c>
       <c r="BL71" s="44">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>0.12528233500386121</v>
       </c>
       <c r="BM71" s="44" t="str">
         <f t="shared" si="67"/>
@@ -16282,22 +16688,22 @@
       </c>
       <c r="BO71" s="43">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>1.9910000000000001E-5</v>
       </c>
       <c r="BP71" s="55">
         <f t="shared" ref="BP71:BP102" si="71">IF(BK71&lt;&gt;"",BK71/0.000385,IF(BL71&lt;&gt;"",BL71/0.000385,BM71/0.000385))</f>
-        <v>0</v>
+        <v>325.40866234769146</v>
       </c>
       <c r="BQ71" s="45">
         <f t="shared" ref="BQ71:BQ102" si="72">IF(BK71&lt;&gt;"",BK71,IF(BL71&lt;&gt;"",BL71,BM71))</f>
-        <v>0</v>
+        <v>0.12528233500386121</v>
       </c>
       <c r="BR71" s="24">
         <f t="shared" ref="BR71:BR102" si="73">IF(BN71&lt;&gt;"",BN71,BO71)</f>
-        <v>0</v>
+        <v>1.9910000000000001E-5</v>
       </c>
     </row>
-    <row r="72" spans="1:70">
+    <row r="72" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>86</v>
       </c>
@@ -16313,58 +16719,122 @@
       <c r="E72">
         <v>7</v>
       </c>
-      <c r="G72" s="35"/>
+      <c r="G72" s="35">
+        <v>45575.472905092596</v>
+      </c>
       <c r="H72">
         <v>3888.32</v>
       </c>
-      <c r="J72" s="40"/>
-      <c r="K72" s="40"/>
-      <c r="L72" s="40"/>
-      <c r="M72" s="40"/>
-      <c r="N72" s="40"/>
-      <c r="O72" s="40"/>
-      <c r="P72" s="40"/>
-      <c r="Q72" s="40"/>
-      <c r="R72" s="40"/>
+      <c r="J72" s="40">
+        <v>4031.79</v>
+      </c>
+      <c r="K72" s="40">
+        <v>23.832000000000001</v>
+      </c>
+      <c r="L72" s="40">
+        <v>21.452999999999999</v>
+      </c>
+      <c r="M72" s="40">
+        <v>90</v>
+      </c>
+      <c r="N72" s="40">
+        <v>16.329999999999998</v>
+      </c>
+      <c r="O72" s="40">
+        <v>336</v>
+      </c>
+      <c r="P72" s="40">
+        <v>1.39</v>
+      </c>
+      <c r="Q72" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="R72" s="40">
+        <v>1.25</v>
+      </c>
       <c r="S72" s="40"/>
-      <c r="T72" s="40"/>
-      <c r="U72" s="40"/>
-      <c r="V72" s="46"/>
-      <c r="W72" s="40"/>
-      <c r="X72" s="40"/>
-      <c r="Y72" s="40"/>
-      <c r="Z72" s="40"/>
-      <c r="AA72" s="40"/>
-      <c r="AB72" s="40"/>
-      <c r="AC72" s="40"/>
-      <c r="AD72" s="40"/>
-      <c r="AE72" s="17"/>
-      <c r="AF72" s="40"/>
-      <c r="AG72" s="40"/>
-      <c r="AH72" s="40"/>
-      <c r="AI72" s="40"/>
-      <c r="AJ72" s="40"/>
-      <c r="AK72" s="40"/>
-      <c r="AL72" s="47"/>
-      <c r="AM72" s="40"/>
-      <c r="AN72" s="40"/>
-      <c r="AO72" s="40"/>
+      <c r="T72" s="40">
+        <v>0.21</v>
+      </c>
+      <c r="U72" s="40">
+        <v>0.13</v>
+      </c>
+      <c r="V72" s="46">
+        <v>2.37</v>
+      </c>
+      <c r="W72" s="40">
+        <v>7.2949999999999999</v>
+      </c>
+      <c r="X72" s="40">
+        <v>34.6</v>
+      </c>
+      <c r="Y72" s="40">
+        <v>46.7</v>
+      </c>
+      <c r="Z72" s="40">
+        <v>1.71</v>
+      </c>
+      <c r="AA72" s="40">
+        <v>145.30000000000001</v>
+      </c>
+      <c r="AB72" s="40">
+        <v>14.9</v>
+      </c>
+      <c r="AC72" s="40">
+        <v>30.3</v>
+      </c>
+      <c r="AD72" s="40">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="AE72" s="17">
+        <v>7.2530000000000001</v>
+      </c>
+      <c r="AF72" s="40">
+        <v>408</v>
+      </c>
+      <c r="AG72" s="40">
+        <v>50</v>
+      </c>
+      <c r="AH72" s="40">
+        <v>7.3040000000000003</v>
+      </c>
+      <c r="AI72" s="40">
+        <v>34</v>
+      </c>
+      <c r="AJ72" s="40">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AK72" s="40">
+        <v>2.4</v>
+      </c>
+      <c r="AL72" s="47">
+        <v>0.2</v>
+      </c>
+      <c r="AM72" s="40">
+        <v>19.3</v>
+      </c>
+      <c r="AN72" s="40">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="AO72" s="40">
+        <v>200.3</v>
+      </c>
       <c r="AP72" s="40"/>
       <c r="AQ72" s="41">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR72" s="41">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>0.12608010420086038</v>
       </c>
       <c r="AS72" s="41">
         <f t="shared" si="55"/>
-        <v>-16.2</v>
+        <v>3.1000000000000014</v>
       </c>
       <c r="AT72" s="41">
         <f t="shared" si="56"/>
-        <v>-4.9000000000000004</v>
+        <v>0</v>
       </c>
       <c r="AU72" s="41">
         <f t="shared" si="57"/>
@@ -16389,30 +16859,37 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="BB72" s="11"/>
-      <c r="BD72" s="22"/>
+      <c r="BC72" s="42">
+        <f>0.00210133507001434*24*60/BG72</f>
+        <v>1.5106952075989262E-2</v>
+      </c>
+      <c r="BD72" s="73">
+        <f>0.00002003/BG72</f>
+        <v>9.9999999999999995E-8</v>
+      </c>
       <c r="BE72" s="42">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>1.7188143600000002E-3</v>
       </c>
       <c r="BF72" s="42">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>2.4750926784000002</v>
       </c>
       <c r="BG72" s="42">
         <f t="shared" si="61"/>
-        <v>180.8</v>
-      </c>
-      <c r="BH72" s="43" t="str">
+        <v>200.3</v>
+      </c>
+      <c r="BH72" s="43">
         <f t="shared" si="62"/>
-        <v/>
-      </c>
-      <c r="BI72" s="43" t="str">
+        <v>9.6355466799800296E-2</v>
+      </c>
+      <c r="BI72" s="43">
         <f t="shared" si="63"/>
-        <v/>
+        <v>9.6500000000000002E-2</v>
       </c>
       <c r="BJ72" s="43">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>181.55535004923897</v>
       </c>
       <c r="BK72" s="43" t="str">
         <f t="shared" si="70"/>
@@ -16420,7 +16897,7 @@
       </c>
       <c r="BL72" s="44">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>0.12608010420086038</v>
       </c>
       <c r="BM72" s="44" t="str">
         <f t="shared" si="67"/>
@@ -16432,22 +16909,22 @@
       </c>
       <c r="BO72" s="43">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>2.003E-5</v>
       </c>
       <c r="BP72" s="55">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>327.48079013210491</v>
       </c>
       <c r="BQ72" s="45">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>0.12608010420086038</v>
       </c>
       <c r="BR72" s="24">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>2.003E-5</v>
       </c>
     </row>
-    <row r="73" spans="1:70">
+    <row r="73" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>87</v>
       </c>
@@ -16463,58 +16940,122 @@
       <c r="E73">
         <v>7</v>
       </c>
-      <c r="G73" s="35"/>
+      <c r="G73" s="35">
+        <v>45575.473749999997</v>
+      </c>
       <c r="H73">
         <v>3888.32</v>
       </c>
-      <c r="J73" s="40"/>
-      <c r="K73" s="40"/>
-      <c r="L73" s="40"/>
-      <c r="M73" s="40"/>
-      <c r="N73" s="40"/>
-      <c r="O73" s="40"/>
-      <c r="P73" s="40"/>
-      <c r="Q73" s="40"/>
-      <c r="R73" s="40"/>
+      <c r="J73" s="40">
+        <v>3377.0549999999998</v>
+      </c>
+      <c r="K73" s="40">
+        <v>21.202000000000002</v>
+      </c>
+      <c r="L73" s="40">
+        <v>19.155000000000001</v>
+      </c>
+      <c r="M73" s="40">
+        <v>90.3</v>
+      </c>
+      <c r="N73" s="40">
+        <v>16.05</v>
+      </c>
+      <c r="O73" s="40">
+        <v>342</v>
+      </c>
+      <c r="P73" s="40">
+        <v>1.3</v>
+      </c>
+      <c r="Q73" s="40">
+        <v>0.34</v>
+      </c>
+      <c r="R73" s="40">
+        <v>2.4700000000000002</v>
+      </c>
       <c r="S73" s="40"/>
-      <c r="T73" s="40"/>
-      <c r="U73" s="40"/>
-      <c r="V73" s="40"/>
-      <c r="W73" s="40"/>
-      <c r="X73" s="40"/>
-      <c r="Y73" s="40"/>
-      <c r="Z73" s="40"/>
-      <c r="AA73" s="40"/>
-      <c r="AB73" s="40"/>
-      <c r="AC73" s="40"/>
-      <c r="AD73" s="40"/>
-      <c r="AE73" s="17"/>
-      <c r="AF73" s="40"/>
-      <c r="AG73" s="40"/>
-      <c r="AH73" s="40"/>
-      <c r="AI73" s="40"/>
-      <c r="AJ73" s="40"/>
-      <c r="AK73" s="40"/>
-      <c r="AL73" s="47"/>
-      <c r="AM73" s="40"/>
-      <c r="AN73" s="40"/>
-      <c r="AO73" s="40"/>
+      <c r="T73" s="40">
+        <v>0.19</v>
+      </c>
+      <c r="U73" s="40">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="V73" s="40">
+        <v>2.77</v>
+      </c>
+      <c r="W73" s="40">
+        <v>7.3029999999999999</v>
+      </c>
+      <c r="X73" s="40">
+        <v>53</v>
+      </c>
+      <c r="Y73" s="40">
+        <v>44.6</v>
+      </c>
+      <c r="Z73" s="40">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="AA73" s="40">
+        <v>143.1</v>
+      </c>
+      <c r="AB73" s="40">
+        <v>23.2</v>
+      </c>
+      <c r="AC73" s="40">
+        <v>46.4</v>
+      </c>
+      <c r="AD73" s="40">
+        <v>36</v>
+      </c>
+      <c r="AE73" s="17">
+        <v>7.2610000000000001</v>
+      </c>
+      <c r="AF73" s="40">
+        <v>446</v>
+      </c>
+      <c r="AG73" s="40">
+        <v>50.8</v>
+      </c>
+      <c r="AH73" s="40">
+        <v>7.3049999999999997</v>
+      </c>
+      <c r="AI73" s="40">
+        <v>34</v>
+      </c>
+      <c r="AJ73" s="40">
+        <v>2.6</v>
+      </c>
+      <c r="AK73" s="40">
+        <v>5.5</v>
+      </c>
+      <c r="AL73" s="47">
+        <v>0.1</v>
+      </c>
+      <c r="AM73" s="40">
+        <v>12.3</v>
+      </c>
+      <c r="AN73" s="40">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AO73" s="40">
+        <v>199.1</v>
+      </c>
       <c r="AP73" s="40"/>
       <c r="AQ73" s="41">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>0.50800000000000001</v>
       </c>
       <c r="AR73" s="41">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>9.1530252000000006E-2</v>
       </c>
       <c r="AS73" s="41">
         <f t="shared" si="55"/>
-        <v>-9.8000000000000007</v>
+        <v>2.5</v>
       </c>
       <c r="AT73" s="41">
         <f t="shared" si="56"/>
-        <v>-4.4000000000000004</v>
+        <v>0</v>
       </c>
       <c r="AU73" s="41">
         <f t="shared" si="57"/>
@@ -16542,27 +17083,27 @@
       <c r="BD73" s="22"/>
       <c r="BE73" s="42">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>1.5255042000000001E-3</v>
       </c>
       <c r="BF73" s="42">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>2.1967260480000004</v>
       </c>
       <c r="BG73" s="42">
         <f t="shared" si="61"/>
-        <v>180.8</v>
-      </c>
-      <c r="BH73" s="43" t="str">
+        <v>199.1</v>
+      </c>
+      <c r="BH73" s="43">
         <f t="shared" si="62"/>
-        <v/>
-      </c>
-      <c r="BI73" s="43" t="str">
+        <v>6.1778001004520348E-2</v>
+      </c>
+      <c r="BI73" s="43">
         <f t="shared" si="63"/>
-        <v/>
+        <v>6.1500000000000006E-2</v>
       </c>
       <c r="BJ73" s="43">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>131.80356288000002</v>
       </c>
       <c r="BK73" s="43" t="str">
         <f t="shared" si="70"/>
@@ -16574,11 +17115,11 @@
       </c>
       <c r="BM73" s="44">
         <f t="shared" si="67"/>
-        <v>0</v>
+        <v>9.1530252000000006E-2</v>
       </c>
       <c r="BN73" s="43">
         <f t="shared" si="58"/>
-        <v>1.3560000000000003</v>
+        <v>0</v>
       </c>
       <c r="BO73" s="43" t="str">
         <f t="shared" si="65"/>
@@ -16586,18 +17127,18 @@
       </c>
       <c r="BP73" s="55">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>237.74091428571433</v>
       </c>
       <c r="BQ73" s="45">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>9.1530252000000006E-2</v>
       </c>
       <c r="BR73" s="24">
         <f t="shared" si="73"/>
-        <v>1.3560000000000003</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:70" ht="15" thickBot="1">
+    <row r="74" spans="1:70" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>88</v>
       </c>
@@ -16613,58 +17154,122 @@
       <c r="E74">
         <v>7</v>
       </c>
-      <c r="G74" s="35"/>
+      <c r="G74" s="35">
+        <v>45575.474618055552</v>
+      </c>
       <c r="H74">
         <v>3888.32</v>
       </c>
-      <c r="J74" s="40"/>
-      <c r="K74" s="40"/>
-      <c r="L74" s="40"/>
-      <c r="M74" s="40"/>
-      <c r="N74" s="40"/>
-      <c r="O74" s="40"/>
-      <c r="P74" s="40"/>
-      <c r="Q74" s="40"/>
-      <c r="R74" s="40"/>
+      <c r="J74" s="40">
+        <v>3609.27</v>
+      </c>
+      <c r="K74" s="40">
+        <v>19.338000000000001</v>
+      </c>
+      <c r="L74" s="40">
+        <v>17.457000000000001</v>
+      </c>
+      <c r="M74" s="40">
+        <v>90.3</v>
+      </c>
+      <c r="N74" s="40">
+        <v>15.94</v>
+      </c>
+      <c r="O74" s="40">
+        <v>330</v>
+      </c>
+      <c r="P74" s="40">
+        <v>1.32</v>
+      </c>
+      <c r="Q74" s="40">
+        <v>0.33</v>
+      </c>
+      <c r="R74" s="40">
+        <v>2.61</v>
+      </c>
       <c r="S74" s="40"/>
-      <c r="T74" s="40"/>
-      <c r="U74" s="40"/>
-      <c r="V74" s="40"/>
-      <c r="W74" s="40"/>
-      <c r="X74" s="40"/>
-      <c r="Y74" s="40"/>
-      <c r="Z74" s="40"/>
-      <c r="AA74" s="40"/>
-      <c r="AB74" s="40"/>
-      <c r="AC74" s="40"/>
-      <c r="AD74" s="40"/>
-      <c r="AE74" s="17"/>
-      <c r="AF74" s="40"/>
-      <c r="AG74" s="40"/>
-      <c r="AH74" s="40"/>
-      <c r="AI74" s="40"/>
-      <c r="AJ74" s="40"/>
-      <c r="AK74" s="40"/>
-      <c r="AL74" s="40"/>
-      <c r="AM74" s="40"/>
-      <c r="AN74" s="40"/>
-      <c r="AO74" s="40"/>
+      <c r="T74" s="40">
+        <v>0.19</v>
+      </c>
+      <c r="U74" s="40">
+        <v>0.13</v>
+      </c>
+      <c r="V74" s="40">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="W74" s="40">
+        <v>7.3049999999999997</v>
+      </c>
+      <c r="X74" s="40">
+        <v>41.9</v>
+      </c>
+      <c r="Y74" s="40">
+        <v>63.3</v>
+      </c>
+      <c r="Z74" s="40">
+        <v>2.41</v>
+      </c>
+      <c r="AA74" s="40">
+        <v>139.4</v>
+      </c>
+      <c r="AB74" s="40">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="AC74" s="40">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="AD74" s="40">
+        <v>51.5</v>
+      </c>
+      <c r="AE74" s="17">
+        <v>7.2640000000000002</v>
+      </c>
+      <c r="AF74" s="40">
+        <v>406</v>
+      </c>
+      <c r="AG74" s="40">
+        <v>52.2</v>
+      </c>
+      <c r="AH74" s="40">
+        <v>7.3029999999999999</v>
+      </c>
+      <c r="AI74" s="40">
+        <v>34</v>
+      </c>
+      <c r="AJ74" s="40">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AK74" s="40">
+        <v>5.5</v>
+      </c>
+      <c r="AL74" s="40">
+        <v>0.2</v>
+      </c>
+      <c r="AM74" s="40">
+        <v>12.8</v>
+      </c>
+      <c r="AN74" s="40">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AO74" s="40">
+        <v>198.6</v>
+      </c>
       <c r="AP74" s="7"/>
       <c r="AQ74" s="41">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>0.52200000000000002</v>
       </c>
       <c r="AR74" s="41">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>8.3207044800000005E-2</v>
       </c>
       <c r="AS74" s="41">
         <f t="shared" si="55"/>
-        <v>-10.3</v>
+        <v>2.5</v>
       </c>
       <c r="AT74" s="41">
         <f t="shared" si="56"/>
-        <v>-4.4000000000000004</v>
+        <v>0</v>
       </c>
       <c r="AU74" s="41">
         <f t="shared" si="57"/>
@@ -16688,31 +17293,33 @@
       <c r="BA74" s="42">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="BB74" s="11"/>
+      <c r="BB74" s="11" t="s">
+        <v>92</v>
+      </c>
       <c r="BD74" s="22"/>
       <c r="BE74" s="42">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>1.3867840800000002E-3</v>
       </c>
       <c r="BF74" s="42">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>1.9969690752000004</v>
       </c>
       <c r="BG74" s="42">
         <f t="shared" si="61"/>
-        <v>180.8</v>
-      </c>
-      <c r="BH74" s="43" t="str">
+        <v>198.6</v>
+      </c>
+      <c r="BH74" s="43">
         <f t="shared" si="62"/>
-        <v/>
-      </c>
-      <c r="BI74" s="43" t="str">
+        <v>6.4451158106747231E-2</v>
+      </c>
+      <c r="BI74" s="43">
         <f t="shared" si="63"/>
-        <v/>
+        <v>6.4000000000000001E-2</v>
       </c>
       <c r="BJ74" s="43">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>119.818144512</v>
       </c>
       <c r="BK74" s="43" t="str">
         <f t="shared" si="70"/>
@@ -16724,11 +17331,11 @@
       </c>
       <c r="BM74" s="44">
         <f t="shared" si="67"/>
-        <v>0</v>
+        <v>8.3207044800000005E-2</v>
       </c>
       <c r="BN74" s="43">
         <f t="shared" si="58"/>
-        <v>1.3560000000000003</v>
+        <v>0</v>
       </c>
       <c r="BO74" s="43" t="str">
         <f t="shared" si="65"/>
@@ -16736,18 +17343,18 @@
       </c>
       <c r="BP74" s="55">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>216.1221942857143</v>
       </c>
       <c r="BQ74" s="45">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>8.3207044800000005E-2</v>
       </c>
       <c r="BR74" s="24">
         <f t="shared" si="73"/>
-        <v>1.3560000000000003</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:70">
+    <row r="75" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>76</v>
       </c>
@@ -16764,24 +17371,26 @@
         <v>8</v>
       </c>
       <c r="F75" s="3"/>
-      <c r="G75" s="34"/>
+      <c r="G75" s="74"/>
       <c r="H75" s="3">
         <v>4309.7</v>
       </c>
       <c r="I75" s="3"/>
-      <c r="J75" s="6"/>
-      <c r="K75" s="6"/>
-      <c r="L75" s="6"/>
-      <c r="M75" s="6"/>
+      <c r="J75" s="6">
+        <v>3221.7150000000001</v>
+      </c>
+      <c r="K75" s="75"/>
+      <c r="L75" s="75"/>
+      <c r="M75" s="75"/>
       <c r="N75" s="6"/>
       <c r="O75" s="6"/>
       <c r="P75" s="6"/>
       <c r="Q75" s="6"/>
-      <c r="R75" s="6"/>
+      <c r="R75" s="75"/>
       <c r="S75" s="6"/>
       <c r="T75" s="6"/>
       <c r="U75" s="6"/>
-      <c r="V75" s="6"/>
+      <c r="V75" s="75"/>
       <c r="W75" s="6"/>
       <c r="X75" s="6"/>
       <c r="Y75" s="6"/>
@@ -16790,17 +17399,19 @@
       <c r="AB75" s="6"/>
       <c r="AC75" s="6"/>
       <c r="AD75" s="6"/>
-      <c r="AE75" s="16"/>
+      <c r="AE75" s="76"/>
       <c r="AF75" s="6"/>
-      <c r="AG75" s="6"/>
+      <c r="AG75" s="75"/>
       <c r="AH75" s="6"/>
-      <c r="AI75" s="6"/>
+      <c r="AI75" s="75"/>
       <c r="AJ75" s="6"/>
       <c r="AK75" s="6"/>
       <c r="AL75" s="6"/>
-      <c r="AM75" s="6"/>
-      <c r="AN75" s="6"/>
-      <c r="AO75" s="6"/>
+      <c r="AM75" s="75"/>
+      <c r="AN75" s="75"/>
+      <c r="AO75" s="75">
+        <v>658799.98779296805</v>
+      </c>
       <c r="AP75" s="6"/>
       <c r="AQ75" s="32">
         <f t="shared" si="59"/>
@@ -16812,11 +17423,11 @@
       </c>
       <c r="AS75" s="32">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>-54921.08203125</v>
       </c>
       <c r="AT75" s="32">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>-22041.2578125</v>
       </c>
       <c r="AU75" s="32">
         <f t="shared" si="57"/>
@@ -16842,7 +17453,10 @@
       </c>
       <c r="BB75" s="8"/>
       <c r="BC75" s="9"/>
-      <c r="BD75" s="21"/>
+      <c r="BD75" s="21">
+        <f>792.953496967818/BG75</f>
+        <v>1.2036331385255102E-3</v>
+      </c>
       <c r="BE75" s="9">
         <f t="shared" si="60"/>
         <v>0</v>
@@ -16853,7 +17467,7 @@
       </c>
       <c r="BG75" s="9">
         <f t="shared" si="61"/>
-        <v>591460</v>
+        <v>658799.98779296805</v>
       </c>
       <c r="BH75" s="10" t="str">
         <f t="shared" si="62"/>
@@ -16885,7 +17499,7 @@
       </c>
       <c r="BO75" s="10">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>792.95349696781796</v>
       </c>
       <c r="BP75" s="58">
         <f t="shared" si="71"/>
@@ -16897,10 +17511,10 @@
       </c>
       <c r="BR75" s="26">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>792.95349696781796</v>
       </c>
     </row>
-    <row r="76" spans="1:70">
+    <row r="76" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>79</v>
       </c>
@@ -16920,50 +17534,112 @@
       <c r="H76">
         <v>4309.7</v>
       </c>
-      <c r="J76" s="40"/>
-      <c r="K76" s="40"/>
-      <c r="L76" s="40"/>
-      <c r="M76" s="40"/>
-      <c r="N76" s="40"/>
-      <c r="O76" s="40"/>
-      <c r="P76" s="40"/>
-      <c r="Q76" s="40"/>
-      <c r="R76" s="40"/>
+      <c r="J76" s="40">
+        <v>4151.3100000000004</v>
+      </c>
+      <c r="K76" s="40">
+        <v>20.934000000000001</v>
+      </c>
+      <c r="L76" s="40">
+        <v>19.114999999999998</v>
+      </c>
+      <c r="M76" s="40">
+        <v>91.3</v>
+      </c>
+      <c r="N76" s="40">
+        <v>16.260000000000002</v>
+      </c>
+      <c r="O76" s="40">
+        <v>332</v>
+      </c>
+      <c r="P76" s="40">
+        <v>1.39</v>
+      </c>
+      <c r="Q76" s="40">
+        <v>0.32</v>
+      </c>
+      <c r="R76" s="40">
+        <v>3.17</v>
+      </c>
       <c r="S76" s="40"/>
-      <c r="T76" s="40"/>
-      <c r="U76" s="40"/>
-      <c r="V76" s="40"/>
-      <c r="W76" s="40"/>
-      <c r="X76" s="40"/>
-      <c r="Y76" s="40"/>
-      <c r="Z76" s="40"/>
-      <c r="AA76" s="40"/>
-      <c r="AB76" s="40"/>
-      <c r="AC76" s="40"/>
-      <c r="AD76" s="40"/>
-      <c r="AE76" s="17"/>
-      <c r="AF76" s="40"/>
-      <c r="AG76" s="40"/>
-      <c r="AH76" s="40"/>
-      <c r="AI76" s="40"/>
-      <c r="AJ76" s="40"/>
-      <c r="AK76" s="40"/>
-      <c r="AL76" s="40"/>
-      <c r="AM76" s="40"/>
-      <c r="AN76" s="40"/>
-      <c r="AO76" s="40"/>
+      <c r="T76" s="40">
+        <v>0.22</v>
+      </c>
+      <c r="U76" s="40">
+        <v>0.15</v>
+      </c>
+      <c r="V76" s="40">
+        <v>1.91</v>
+      </c>
+      <c r="W76" s="40">
+        <v>7.3129999999999997</v>
+      </c>
+      <c r="X76" s="40">
+        <v>38.9</v>
+      </c>
+      <c r="Y76" s="40">
+        <v>61.3</v>
+      </c>
+      <c r="Z76" s="40">
+        <v>2.12</v>
+      </c>
+      <c r="AA76" s="40">
+        <v>139.5</v>
+      </c>
+      <c r="AB76" s="40">
+        <v>17.5</v>
+      </c>
+      <c r="AC76" s="40">
+        <v>34.1</v>
+      </c>
+      <c r="AD76" s="40">
+        <v>49.9</v>
+      </c>
+      <c r="AE76" s="17">
+        <v>7.2720000000000002</v>
+      </c>
+      <c r="AF76" s="40">
+        <v>408</v>
+      </c>
+      <c r="AG76" s="40">
+        <v>49.9</v>
+      </c>
+      <c r="AH76" s="40">
+        <v>7.3070000000000004</v>
+      </c>
+      <c r="AI76" s="40">
+        <v>34</v>
+      </c>
+      <c r="AJ76" s="40">
+        <v>2</v>
+      </c>
+      <c r="AK76" s="40">
+        <v>6.6</v>
+      </c>
+      <c r="AL76" s="40">
+        <v>0.2</v>
+      </c>
+      <c r="AM76" s="40">
+        <v>15.6</v>
+      </c>
+      <c r="AN76" s="40">
+        <v>4</v>
+      </c>
+      <c r="AO76" s="40">
+        <v>197.9</v>
+      </c>
       <c r="AP76" s="40"/>
       <c r="AQ76" s="41">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>0.499</v>
       </c>
       <c r="AR76" s="41">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>9.0788603999999995E-2</v>
       </c>
       <c r="AS76" s="41">
         <f t="shared" ref="AS76:AS107" si="74">AM76-AM67</f>
-        <v>0</v>
+        <v>2.1999999999999993</v>
       </c>
       <c r="AT76" s="41">
         <f t="shared" ref="AT76:AT107" si="75">AN76-AN67</f>
@@ -16996,27 +17672,27 @@
       <c r="BD76" s="22"/>
       <c r="BE76" s="42">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>1.5131434000000001E-3</v>
       </c>
       <c r="BF76" s="42">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>2.1789264960000003</v>
       </c>
       <c r="BG76" s="42">
         <f t="shared" si="61"/>
-        <v>178.4</v>
-      </c>
-      <c r="BH76" s="43" t="str">
+        <v>197.9</v>
+      </c>
+      <c r="BH76" s="43">
         <f t="shared" si="62"/>
-        <v/>
-      </c>
-      <c r="BI76" s="43" t="str">
+        <v>7.8827690752905508E-2</v>
+      </c>
+      <c r="BI76" s="43">
         <f t="shared" si="63"/>
-        <v/>
+        <v>7.8E-2</v>
       </c>
       <c r="BJ76" s="43">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>130.73558975999998</v>
       </c>
       <c r="BK76" s="43" t="str">
         <f t="shared" si="70"/>
@@ -17028,11 +17704,11 @@
       </c>
       <c r="BM76" s="44">
         <f t="shared" si="67"/>
-        <v>0</v>
+        <v>9.0788603999999995E-2</v>
       </c>
       <c r="BN76" s="43">
         <f t="shared" si="58"/>
-        <v>1.3380000000000001</v>
+        <v>0</v>
       </c>
       <c r="BO76" s="43" t="str">
         <f t="shared" si="65"/>
@@ -17040,18 +17716,18 @@
       </c>
       <c r="BP76" s="55">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>235.81455584415585</v>
       </c>
       <c r="BQ76" s="45">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>9.0788603999999995E-2</v>
       </c>
       <c r="BR76" s="24">
         <f t="shared" si="73"/>
-        <v>1.3380000000000001</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:70">
+    <row r="77" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>81</v>
       </c>
@@ -17071,50 +17747,112 @@
       <c r="H77">
         <v>4309.7</v>
       </c>
-      <c r="J77" s="40"/>
-      <c r="K77" s="40"/>
-      <c r="L77" s="40"/>
-      <c r="M77" s="40"/>
-      <c r="N77" s="40"/>
-      <c r="O77" s="40"/>
-      <c r="P77" s="40"/>
-      <c r="Q77" s="40"/>
-      <c r="R77" s="40"/>
+      <c r="J77" s="40">
+        <v>4252.2</v>
+      </c>
+      <c r="K77" s="40">
+        <v>24.87</v>
+      </c>
+      <c r="L77" s="40">
+        <v>22.106000000000002</v>
+      </c>
+      <c r="M77" s="40">
+        <v>88.9</v>
+      </c>
+      <c r="N77" s="40">
+        <v>16.170000000000002</v>
+      </c>
+      <c r="O77" s="40">
+        <v>334</v>
+      </c>
+      <c r="P77" s="40">
+        <v>1.39</v>
+      </c>
+      <c r="Q77" s="40">
+        <v>0.33</v>
+      </c>
+      <c r="R77" s="40">
+        <v>2.59</v>
+      </c>
       <c r="S77" s="40"/>
-      <c r="T77" s="40"/>
-      <c r="U77" s="40"/>
-      <c r="V77" s="40"/>
-      <c r="W77" s="40"/>
-      <c r="X77" s="40"/>
-      <c r="Y77" s="40"/>
-      <c r="Z77" s="40"/>
-      <c r="AA77" s="40"/>
-      <c r="AB77" s="40"/>
-      <c r="AC77" s="40"/>
-      <c r="AD77" s="40"/>
-      <c r="AE77" s="17"/>
-      <c r="AF77" s="40"/>
-      <c r="AG77" s="40"/>
-      <c r="AH77" s="40"/>
-      <c r="AI77" s="40"/>
-      <c r="AJ77" s="40"/>
-      <c r="AK77" s="40"/>
-      <c r="AL77" s="40"/>
-      <c r="AM77" s="40"/>
-      <c r="AN77" s="40"/>
-      <c r="AO77" s="40"/>
+      <c r="T77" s="40">
+        <v>0.17</v>
+      </c>
+      <c r="U77" s="40">
+        <v>0.15</v>
+      </c>
+      <c r="V77" s="40">
+        <v>2.08</v>
+      </c>
+      <c r="W77" s="40">
+        <v>7.3330000000000002</v>
+      </c>
+      <c r="X77" s="40">
+        <v>34.1</v>
+      </c>
+      <c r="Y77" s="40">
+        <v>67</v>
+      </c>
+      <c r="Z77" s="40">
+        <v>2.41</v>
+      </c>
+      <c r="AA77" s="40">
+        <v>138.5</v>
+      </c>
+      <c r="AB77" s="40">
+        <v>16</v>
+      </c>
+      <c r="AC77" s="40">
+        <v>29.9</v>
+      </c>
+      <c r="AD77" s="40">
+        <v>54.6</v>
+      </c>
+      <c r="AE77" s="17">
+        <v>7.2910000000000004</v>
+      </c>
+      <c r="AF77" s="40">
+        <v>408</v>
+      </c>
+      <c r="AG77" s="40">
+        <v>52.2</v>
+      </c>
+      <c r="AH77" s="40">
+        <v>7.3079999999999998</v>
+      </c>
+      <c r="AI77" s="40">
+        <v>34</v>
+      </c>
+      <c r="AJ77" s="40">
+        <v>2.1</v>
+      </c>
+      <c r="AK77" s="40">
+        <v>6.1</v>
+      </c>
+      <c r="AL77" s="40">
+        <v>0.2</v>
+      </c>
+      <c r="AM77" s="40">
+        <v>15.3</v>
+      </c>
+      <c r="AN77" s="40">
+        <v>4.3</v>
+      </c>
+      <c r="AO77" s="40">
+        <v>196.6</v>
+      </c>
       <c r="AP77" s="40"/>
       <c r="AQ77" s="41">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>0.52200000000000002</v>
       </c>
       <c r="AR77" s="41">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>0.1043049504</v>
       </c>
       <c r="AS77" s="41">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT77" s="41">
         <f t="shared" si="75"/>
@@ -17147,27 +17885,27 @@
       <c r="BD77" s="22"/>
       <c r="BE77" s="42">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>1.73841584E-3</v>
       </c>
       <c r="BF77" s="42">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>2.5033188096000001</v>
       </c>
       <c r="BG77" s="42">
         <f t="shared" si="61"/>
-        <v>178.4</v>
-      </c>
-      <c r="BH77" s="43" t="str">
+        <v>196.6</v>
+      </c>
+      <c r="BH77" s="43">
         <f t="shared" si="62"/>
-        <v/>
-      </c>
-      <c r="BI77" s="43" t="str">
+        <v>7.7822990844354026E-2</v>
+      </c>
+      <c r="BI77" s="43">
         <f t="shared" si="63"/>
-        <v/>
+        <v>7.6499999999999999E-2</v>
       </c>
       <c r="BJ77" s="43">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>150.19912857599999</v>
       </c>
       <c r="BK77" s="43" t="str">
         <f t="shared" si="70"/>
@@ -17179,11 +17917,11 @@
       </c>
       <c r="BM77" s="44">
         <f t="shared" si="67"/>
-        <v>0</v>
+        <v>0.1043049504</v>
       </c>
       <c r="BN77" s="43">
         <f t="shared" si="58"/>
-        <v>1.3380000000000001</v>
+        <v>0</v>
       </c>
       <c r="BO77" s="43" t="str">
         <f t="shared" si="65"/>
@@ -17191,18 +17929,18 @@
       </c>
       <c r="BP77" s="55">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>270.9219490909091</v>
       </c>
       <c r="BQ77" s="45">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>0.1043049504</v>
       </c>
       <c r="BR77" s="24">
         <f t="shared" si="73"/>
-        <v>1.3380000000000001</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:70">
+    <row r="78" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>82</v>
       </c>
@@ -17223,41 +17961,101 @@
         <v>4309.7</v>
       </c>
       <c r="J78" s="40"/>
-      <c r="K78" s="40"/>
-      <c r="L78" s="40"/>
-      <c r="M78" s="40"/>
-      <c r="N78" s="40"/>
-      <c r="O78" s="40"/>
-      <c r="P78" s="40"/>
-      <c r="Q78" s="40"/>
-      <c r="R78" s="40"/>
+      <c r="K78" s="40">
+        <v>20.071000000000002</v>
+      </c>
+      <c r="L78" s="40">
+        <v>5.5369999999999999</v>
+      </c>
+      <c r="M78" s="40">
+        <v>27.6</v>
+      </c>
+      <c r="N78" s="40">
+        <v>12.68</v>
+      </c>
+      <c r="O78" s="40">
+        <v>439</v>
+      </c>
+      <c r="P78" s="40">
+        <v>5.22</v>
+      </c>
+      <c r="Q78" s="40">
+        <v>0.35</v>
+      </c>
+      <c r="R78" s="40">
+        <v>0.16</v>
+      </c>
       <c r="S78" s="40"/>
-      <c r="T78" s="40"/>
-      <c r="U78" s="40"/>
-      <c r="V78" s="40"/>
-      <c r="W78" s="40"/>
-      <c r="X78" s="40"/>
-      <c r="Y78" s="40"/>
-      <c r="Z78" s="40"/>
-      <c r="AA78" s="40"/>
-      <c r="AB78" s="40"/>
-      <c r="AC78" s="40"/>
-      <c r="AD78" s="40"/>
-      <c r="AE78" s="17"/>
-      <c r="AF78" s="40"/>
-      <c r="AG78" s="40"/>
-      <c r="AH78" s="40"/>
-      <c r="AI78" s="40"/>
-      <c r="AJ78" s="40"/>
-      <c r="AK78" s="40"/>
-      <c r="AL78" s="40"/>
-      <c r="AM78" s="40"/>
-      <c r="AN78" s="40"/>
-      <c r="AO78" s="40"/>
+      <c r="T78" s="40">
+        <v>0.15</v>
+      </c>
+      <c r="U78" s="40">
+        <v>0.94</v>
+      </c>
+      <c r="V78" s="40">
+        <v>4.42</v>
+      </c>
+      <c r="W78" s="40">
+        <v>7.0549999999999997</v>
+      </c>
+      <c r="X78" s="40">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="Y78" s="40">
+        <v>0</v>
+      </c>
+      <c r="Z78" s="40">
+        <v>6.92</v>
+      </c>
+      <c r="AA78" s="40">
+        <v>183.1</v>
+      </c>
+      <c r="AB78" s="40">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="AC78" s="40">
+        <v>34.4</v>
+      </c>
+      <c r="AD78" s="40">
+        <v>0</v>
+      </c>
+      <c r="AE78" s="17">
+        <v>7.0190000000000001</v>
+      </c>
+      <c r="AF78" s="40">
+        <v>408</v>
+      </c>
+      <c r="AG78" s="40">
+        <v>-0.2</v>
+      </c>
+      <c r="AH78" s="40">
+        <v>7.085</v>
+      </c>
+      <c r="AI78" s="40">
+        <v>34</v>
+      </c>
+      <c r="AJ78" s="40">
+        <v>6.4</v>
+      </c>
+      <c r="AK78" s="40">
+        <v>3.2</v>
+      </c>
+      <c r="AL78" s="40">
+        <v>0.2</v>
+      </c>
+      <c r="AM78" s="40">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="AN78" s="40">
+        <v>4.5</v>
+      </c>
+      <c r="AO78" s="40">
+        <v>206.1</v>
+      </c>
       <c r="AP78" s="40"/>
       <c r="AQ78" s="41">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>-2E-3</v>
       </c>
       <c r="AR78" s="41">
         <f t="shared" si="68"/>
@@ -17298,23 +18096,23 @@
       <c r="BD78" s="22"/>
       <c r="BE78" s="42">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>4.5647028000000007E-4</v>
       </c>
       <c r="BF78" s="42">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>0.65731720320000009</v>
       </c>
       <c r="BG78" s="42">
         <f t="shared" si="61"/>
-        <v>178.4</v>
-      </c>
-      <c r="BH78" s="43" t="str">
+        <v>206.1</v>
+      </c>
+      <c r="BH78" s="43">
         <f t="shared" si="62"/>
-        <v/>
-      </c>
-      <c r="BI78" s="43" t="str">
+        <v>9.5099466278505587E-2</v>
+      </c>
+      <c r="BI78" s="43">
         <f t="shared" si="63"/>
-        <v/>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="BJ78" s="43">
         <f t="shared" si="64"/>
@@ -17334,7 +18132,7 @@
       </c>
       <c r="BN78" s="43">
         <f t="shared" si="58"/>
-        <v>1.3380000000000001</v>
+        <v>1.4633099999999999</v>
       </c>
       <c r="BO78" s="43" t="str">
         <f t="shared" si="65"/>
@@ -17350,10 +18148,10 @@
       </c>
       <c r="BR78" s="24">
         <f t="shared" si="73"/>
-        <v>1.3380000000000001</v>
+        <v>1.4633099999999999</v>
       </c>
     </row>
-    <row r="79" spans="1:70">
+    <row r="79" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>84</v>
       </c>
@@ -17373,42 +18171,104 @@
       <c r="H79">
         <v>4309.7</v>
       </c>
-      <c r="J79" s="40"/>
-      <c r="K79" s="40"/>
-      <c r="L79" s="40"/>
-      <c r="M79" s="40"/>
-      <c r="N79" s="40"/>
-      <c r="O79" s="40"/>
-      <c r="P79" s="40"/>
-      <c r="Q79" s="40"/>
-      <c r="R79" s="40"/>
+      <c r="J79" s="40">
+        <v>4328.1750000000002</v>
+      </c>
+      <c r="K79" s="40">
+        <v>21.445</v>
+      </c>
+      <c r="L79" s="40">
+        <v>19.353999999999999</v>
+      </c>
+      <c r="M79" s="40">
+        <v>90.2</v>
+      </c>
+      <c r="N79" s="40">
+        <v>16.760000000000002</v>
+      </c>
+      <c r="O79" s="40">
+        <v>340</v>
+      </c>
+      <c r="P79" s="40">
+        <v>1.45</v>
+      </c>
+      <c r="Q79" s="40">
+        <v>0.31</v>
+      </c>
+      <c r="R79" s="40">
+        <v>1.75</v>
+      </c>
       <c r="S79" s="40"/>
-      <c r="T79" s="40"/>
-      <c r="U79" s="40"/>
-      <c r="V79" s="46"/>
-      <c r="W79" s="40"/>
-      <c r="X79" s="40"/>
-      <c r="Y79" s="40"/>
-      <c r="Z79" s="40"/>
-      <c r="AA79" s="40"/>
-      <c r="AB79" s="40"/>
-      <c r="AC79" s="40"/>
-      <c r="AD79" s="40"/>
-      <c r="AE79" s="17"/>
-      <c r="AF79" s="40"/>
-      <c r="AG79" s="40"/>
-      <c r="AH79" s="40"/>
-      <c r="AI79" s="40"/>
-      <c r="AJ79" s="40"/>
-      <c r="AK79" s="40"/>
-      <c r="AL79" s="40"/>
-      <c r="AM79" s="40"/>
-      <c r="AN79" s="40"/>
-      <c r="AO79" s="40"/>
+      <c r="T79" s="40">
+        <v>0.23</v>
+      </c>
+      <c r="U79" s="40">
+        <v>0.17</v>
+      </c>
+      <c r="V79" s="46">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="W79" s="40">
+        <v>7.3109999999999999</v>
+      </c>
+      <c r="X79" s="40">
+        <v>36</v>
+      </c>
+      <c r="Y79" s="40">
+        <v>45.6</v>
+      </c>
+      <c r="Z79" s="40">
+        <v>1.71</v>
+      </c>
+      <c r="AA79" s="40">
+        <v>149.6</v>
+      </c>
+      <c r="AB79" s="40">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="AC79" s="40">
+        <v>31.6</v>
+      </c>
+      <c r="AD79" s="40">
+        <v>36.9</v>
+      </c>
+      <c r="AE79" s="17">
+        <v>7.2690000000000001</v>
+      </c>
+      <c r="AF79" s="40">
+        <v>408</v>
+      </c>
+      <c r="AG79" s="40">
+        <v>50.6</v>
+      </c>
+      <c r="AH79" s="40">
+        <v>7.3040000000000003</v>
+      </c>
+      <c r="AI79" s="40">
+        <v>33.9</v>
+      </c>
+      <c r="AJ79" s="40">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AK79" s="40">
+        <v>4</v>
+      </c>
+      <c r="AL79" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="AM79" s="40">
+        <v>20.6</v>
+      </c>
+      <c r="AN79" s="40">
+        <v>5</v>
+      </c>
+      <c r="AO79" s="40">
+        <v>200.5</v>
+      </c>
       <c r="AP79" s="40"/>
       <c r="AQ79" s="41">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>0.50600000000000001</v>
       </c>
       <c r="AR79" s="41">
         <f t="shared" si="68"/>
@@ -17416,11 +18276,11 @@
       </c>
       <c r="AS79" s="41">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>2.3000000000000007</v>
       </c>
       <c r="AT79" s="41">
         <f t="shared" si="75"/>
-        <v>0</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="AU79" s="41">
         <f t="shared" si="76"/>
@@ -17448,23 +18308,23 @@
       <c r="BD79" s="22"/>
       <c r="BE79" s="42">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>1.5521908E-3</v>
       </c>
       <c r="BF79" s="42">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>2.2351547519999997</v>
       </c>
       <c r="BG79" s="42">
         <f t="shared" si="61"/>
-        <v>178.4</v>
-      </c>
-      <c r="BH79" s="43" t="str">
+        <v>200.5</v>
+      </c>
+      <c r="BH79" s="43">
         <f t="shared" si="62"/>
-        <v/>
-      </c>
-      <c r="BI79" s="43" t="str">
+        <v>0.10274314214463841</v>
+      </c>
+      <c r="BI79" s="43">
         <f t="shared" si="63"/>
-        <v/>
+        <v>0.10300000000000001</v>
       </c>
       <c r="BJ79" s="43">
         <f t="shared" si="64"/>
@@ -17484,7 +18344,7 @@
       </c>
       <c r="BN79" s="43">
         <f t="shared" si="58"/>
-        <v>1.3380000000000001</v>
+        <v>0</v>
       </c>
       <c r="BO79" s="43" t="str">
         <f t="shared" si="65"/>
@@ -17500,10 +18360,10 @@
       </c>
       <c r="BR79" s="24">
         <f t="shared" si="73"/>
-        <v>1.3380000000000001</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:70">
+    <row r="80" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>85</v>
       </c>
@@ -17523,50 +18383,112 @@
       <c r="H80">
         <v>4309.7</v>
       </c>
-      <c r="J80" s="40"/>
-      <c r="K80" s="40"/>
-      <c r="L80" s="40"/>
-      <c r="M80" s="40"/>
-      <c r="N80" s="40"/>
-      <c r="O80" s="40"/>
-      <c r="P80" s="40"/>
-      <c r="Q80" s="40"/>
-      <c r="R80" s="40"/>
+      <c r="J80" s="40">
+        <v>4470.4350000000004</v>
+      </c>
+      <c r="K80" s="40">
+        <v>31.463999999999999</v>
+      </c>
+      <c r="L80" s="40">
+        <v>27.488</v>
+      </c>
+      <c r="M80" s="40">
+        <v>87.4</v>
+      </c>
+      <c r="N80" s="40">
+        <v>16.43</v>
+      </c>
+      <c r="O80" s="40">
+        <v>340</v>
+      </c>
+      <c r="P80" s="40">
+        <v>1.54</v>
+      </c>
+      <c r="Q80" s="40">
+        <v>0.31</v>
+      </c>
+      <c r="R80" s="40">
+        <v>0.62</v>
+      </c>
       <c r="S80" s="40"/>
-      <c r="T80" s="40"/>
-      <c r="U80" s="40"/>
-      <c r="V80" s="40"/>
-      <c r="W80" s="40"/>
-      <c r="X80" s="40"/>
-      <c r="Y80" s="40"/>
-      <c r="Z80" s="40"/>
-      <c r="AA80" s="40"/>
-      <c r="AB80" s="40"/>
-      <c r="AC80" s="40"/>
-      <c r="AD80" s="40"/>
-      <c r="AE80" s="17"/>
-      <c r="AF80" s="40"/>
-      <c r="AG80" s="40"/>
-      <c r="AH80" s="40"/>
-      <c r="AI80" s="40"/>
-      <c r="AJ80" s="40"/>
-      <c r="AK80" s="40"/>
-      <c r="AL80" s="40"/>
-      <c r="AM80" s="40"/>
-      <c r="AN80" s="40"/>
-      <c r="AO80" s="40"/>
+      <c r="T80" s="40">
+        <v>0.27</v>
+      </c>
+      <c r="U80" s="40">
+        <v>0.18</v>
+      </c>
+      <c r="V80" s="40">
+        <v>2.16</v>
+      </c>
+      <c r="W80" s="40">
+        <v>7.3159999999999998</v>
+      </c>
+      <c r="X80" s="40">
+        <v>31.9</v>
+      </c>
+      <c r="Y80" s="40">
+        <v>44.6</v>
+      </c>
+      <c r="Z80" s="40">
+        <v>1.9</v>
+      </c>
+      <c r="AA80" s="40">
+        <v>148.5</v>
+      </c>
+      <c r="AB80" s="40">
+        <v>14.4</v>
+      </c>
+      <c r="AC80" s="40">
+        <v>28</v>
+      </c>
+      <c r="AD80" s="40">
+        <v>36.1</v>
+      </c>
+      <c r="AE80" s="17">
+        <v>7.274</v>
+      </c>
+      <c r="AF80" s="40">
+        <v>407</v>
+      </c>
+      <c r="AG80" s="40">
+        <v>50</v>
+      </c>
+      <c r="AH80" s="40">
+        <v>7.3049999999999997</v>
+      </c>
+      <c r="AI80" s="40">
+        <v>34</v>
+      </c>
+      <c r="AJ80" s="40">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AK80" s="40">
+        <v>2.9</v>
+      </c>
+      <c r="AL80" s="40">
+        <v>0.2</v>
+      </c>
+      <c r="AM80" s="40">
+        <v>22.1</v>
+      </c>
+      <c r="AN80" s="40">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AO80" s="40">
+        <v>198.6</v>
+      </c>
       <c r="AP80" s="40"/>
       <c r="AQ80" s="41">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR80" s="41">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>0.131818314836991</v>
       </c>
       <c r="AS80" s="41">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>2.7000000000000028</v>
       </c>
       <c r="AT80" s="41">
         <f t="shared" si="75"/>
@@ -17595,30 +18517,37 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="BB80" s="11"/>
-      <c r="BD80" s="22"/>
+      <c r="BC80" s="42">
+        <f>0.00219697191394985*24*60/BG80</f>
+        <v>1.5929705720482294E-2</v>
+      </c>
+      <c r="BD80" s="42">
+        <f>0.208163106754803/BG80</f>
+        <v>1.0481526019879305E-3</v>
+      </c>
       <c r="BE80" s="42">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>2.1836467200000002E-3</v>
       </c>
       <c r="BF80" s="42">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>3.1444512768000004</v>
       </c>
       <c r="BG80" s="42">
         <f t="shared" si="61"/>
-        <v>178.4</v>
-      </c>
-      <c r="BH80" s="43" t="str">
+        <v>198.6</v>
+      </c>
+      <c r="BH80" s="43">
         <f t="shared" si="62"/>
-        <v/>
-      </c>
-      <c r="BI80" s="43" t="str">
+        <v>0.11127895266868078</v>
+      </c>
+      <c r="BI80" s="43">
         <f t="shared" si="63"/>
-        <v/>
+        <v>0.1105</v>
       </c>
       <c r="BJ80" s="43">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>189.81837336526701</v>
       </c>
       <c r="BK80" s="43" t="str">
         <f t="shared" si="70"/>
@@ -17626,7 +18555,7 @@
       </c>
       <c r="BL80" s="44">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>0.131818314836991</v>
       </c>
       <c r="BM80" s="44" t="str">
         <f t="shared" si="67"/>
@@ -17638,22 +18567,22 @@
       </c>
       <c r="BO80" s="43">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>0.20816310675480301</v>
       </c>
       <c r="BP80" s="55">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>342.38523334283377</v>
       </c>
       <c r="BQ80" s="45">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>0.131818314836991</v>
       </c>
       <c r="BR80" s="24">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>0.20816310675480301</v>
       </c>
     </row>
-    <row r="81" spans="1:70">
+    <row r="81" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>86</v>
       </c>
@@ -17674,50 +18603,112 @@
         <v>4309.7</v>
       </c>
       <c r="I81" s="48"/>
-      <c r="J81" s="46"/>
-      <c r="K81" s="40"/>
-      <c r="L81" s="40"/>
-      <c r="M81" s="40"/>
-      <c r="N81" s="40"/>
-      <c r="O81" s="40"/>
-      <c r="P81" s="40"/>
-      <c r="Q81" s="40"/>
-      <c r="R81" s="40"/>
+      <c r="J81" s="72">
+        <v>4489.7250000000004</v>
+      </c>
+      <c r="K81" s="40">
+        <v>24.68</v>
+      </c>
+      <c r="L81" s="40">
+        <v>21.777000000000001</v>
+      </c>
+      <c r="M81" s="40">
+        <v>88.2</v>
+      </c>
+      <c r="N81" s="40">
+        <v>16.309999999999999</v>
+      </c>
+      <c r="O81" s="40">
+        <v>340</v>
+      </c>
+      <c r="P81" s="40">
+        <v>1.48</v>
+      </c>
+      <c r="Q81" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="R81" s="40">
+        <v>0.69</v>
+      </c>
       <c r="S81" s="40"/>
-      <c r="T81" s="40"/>
-      <c r="U81" s="40"/>
-      <c r="V81" s="40"/>
-      <c r="W81" s="40"/>
-      <c r="X81" s="40"/>
-      <c r="Y81" s="40"/>
-      <c r="Z81" s="40"/>
-      <c r="AA81" s="40"/>
-      <c r="AB81" s="40"/>
-      <c r="AC81" s="40"/>
-      <c r="AD81" s="40"/>
-      <c r="AE81" s="17"/>
-      <c r="AF81" s="40"/>
-      <c r="AG81" s="40"/>
-      <c r="AH81" s="40"/>
-      <c r="AI81" s="40"/>
-      <c r="AJ81" s="40"/>
-      <c r="AK81" s="40"/>
-      <c r="AL81" s="40"/>
-      <c r="AM81" s="40"/>
-      <c r="AN81" s="40"/>
-      <c r="AO81" s="40"/>
+      <c r="T81" s="40">
+        <v>0.24</v>
+      </c>
+      <c r="U81" s="40">
+        <v>0.18</v>
+      </c>
+      <c r="V81" s="40">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="W81" s="40">
+        <v>7.33</v>
+      </c>
+      <c r="X81" s="40">
+        <v>33.1</v>
+      </c>
+      <c r="Y81" s="40">
+        <v>42.8</v>
+      </c>
+      <c r="Z81" s="40">
+        <v>1.78</v>
+      </c>
+      <c r="AA81" s="40">
+        <v>149</v>
+      </c>
+      <c r="AB81" s="40">
+        <v>15.4</v>
+      </c>
+      <c r="AC81" s="40">
+        <v>29</v>
+      </c>
+      <c r="AD81" s="40">
+        <v>34.6</v>
+      </c>
+      <c r="AE81" s="17">
+        <v>7.2880000000000003</v>
+      </c>
+      <c r="AF81" s="40">
+        <v>406</v>
+      </c>
+      <c r="AG81" s="40">
+        <v>51.4</v>
+      </c>
+      <c r="AH81" s="40">
+        <v>7.3049999999999997</v>
+      </c>
+      <c r="AI81" s="40">
+        <v>33.9</v>
+      </c>
+      <c r="AJ81" s="40">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AK81" s="40">
+        <v>3.3</v>
+      </c>
+      <c r="AL81" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="AM81" s="40">
+        <v>22</v>
+      </c>
+      <c r="AN81" s="40">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="AO81" s="40">
+        <v>200.1</v>
+      </c>
       <c r="AP81" s="40"/>
       <c r="AQ81" s="41">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>0.51400000000000001</v>
       </c>
       <c r="AR81" s="41">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>0.13049272090479661</v>
       </c>
       <c r="AS81" s="41">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>2.6999999999999993</v>
       </c>
       <c r="AT81" s="41">
         <f t="shared" si="75"/>
@@ -17746,30 +18737,37 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="BB81" s="11"/>
-      <c r="BD81" s="22"/>
+      <c r="BC81" s="42">
+        <f>0.00217487868174661*24*60/BG81</f>
+        <v>1.5651300858146519E-2</v>
+      </c>
+      <c r="BD81" s="42">
+        <f>0.269836303208401/BG81</f>
+        <v>1.3485072624107998E-3</v>
+      </c>
       <c r="BE81" s="42">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>1.7430310800000003E-3</v>
       </c>
       <c r="BF81" s="42">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>2.5099647552000004</v>
       </c>
       <c r="BG81" s="42">
         <f t="shared" si="61"/>
-        <v>178.4</v>
-      </c>
-      <c r="BH81" s="43" t="str">
+        <v>200.1</v>
+      </c>
+      <c r="BH81" s="43">
         <f t="shared" si="62"/>
-        <v/>
-      </c>
-      <c r="BI81" s="43" t="str">
+        <v>0.10994502748625687</v>
+      </c>
+      <c r="BI81" s="43">
         <f t="shared" si="63"/>
-        <v/>
+        <v>0.11</v>
       </c>
       <c r="BJ81" s="43">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>187.90951810290713</v>
       </c>
       <c r="BK81" s="43" t="str">
         <f t="shared" si="70"/>
@@ -17777,7 +18775,7 @@
       </c>
       <c r="BL81" s="44">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>0.13049272090479661</v>
       </c>
       <c r="BM81" s="44" t="str">
         <f t="shared" si="67"/>
@@ -17789,22 +18787,22 @@
       </c>
       <c r="BO81" s="43">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>0.26983630320840102</v>
       </c>
       <c r="BP81" s="55">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>338.94213222025093</v>
       </c>
       <c r="BQ81" s="45">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>0.13049272090479661</v>
       </c>
       <c r="BR81" s="24">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>0.26983630320840102</v>
       </c>
     </row>
-    <row r="82" spans="1:70">
+    <row r="82" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>87</v>
       </c>
@@ -17825,50 +18823,112 @@
         <v>4309.7</v>
       </c>
       <c r="I82" s="48"/>
-      <c r="J82" s="46"/>
-      <c r="K82" s="40"/>
-      <c r="L82" s="40"/>
-      <c r="M82" s="40"/>
-      <c r="N82" s="40"/>
-      <c r="O82" s="40"/>
-      <c r="P82" s="40"/>
-      <c r="Q82" s="40"/>
-      <c r="R82" s="40"/>
+      <c r="J82" s="72">
+        <v>3788.91</v>
+      </c>
+      <c r="K82" s="40">
+        <v>27.675000000000001</v>
+      </c>
+      <c r="L82" s="40">
+        <v>25.376999999999999</v>
+      </c>
+      <c r="M82" s="40">
+        <v>91.7</v>
+      </c>
+      <c r="N82" s="40">
+        <v>16.71</v>
+      </c>
+      <c r="O82" s="40">
+        <v>343</v>
+      </c>
+      <c r="P82" s="40">
+        <v>1.32</v>
+      </c>
+      <c r="Q82" s="40">
+        <v>0.33</v>
+      </c>
+      <c r="R82" s="40">
+        <v>2.5499999999999998</v>
+      </c>
       <c r="S82" s="40"/>
-      <c r="T82" s="40"/>
-      <c r="U82" s="40"/>
-      <c r="V82" s="40"/>
-      <c r="W82" s="40"/>
-      <c r="X82" s="40"/>
-      <c r="Y82" s="40"/>
-      <c r="Z82" s="40"/>
-      <c r="AA82" s="40"/>
-      <c r="AB82" s="40"/>
-      <c r="AC82" s="40"/>
-      <c r="AD82" s="40"/>
-      <c r="AE82" s="17"/>
-      <c r="AF82" s="40"/>
-      <c r="AG82" s="40"/>
-      <c r="AH82" s="40"/>
-      <c r="AI82" s="40"/>
-      <c r="AJ82" s="40"/>
-      <c r="AK82" s="40"/>
-      <c r="AL82" s="40"/>
-      <c r="AM82" s="40"/>
-      <c r="AN82" s="40"/>
-      <c r="AO82" s="40"/>
+      <c r="T82" s="40">
+        <v>0.22</v>
+      </c>
+      <c r="U82" s="40">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="V82" s="40">
+        <v>2.48</v>
+      </c>
+      <c r="W82" s="40">
+        <v>7.319</v>
+      </c>
+      <c r="X82" s="40">
+        <v>52.5</v>
+      </c>
+      <c r="Y82" s="40">
+        <v>62.2</v>
+      </c>
+      <c r="Z82" s="40">
+        <v>2.27</v>
+      </c>
+      <c r="AA82" s="40">
+        <v>144.6</v>
+      </c>
+      <c r="AB82" s="40">
+        <v>23.9</v>
+      </c>
+      <c r="AC82" s="40">
+        <v>46.1</v>
+      </c>
+      <c r="AD82" s="40">
+        <v>50.6</v>
+      </c>
+      <c r="AE82" s="17">
+        <v>7.2770000000000001</v>
+      </c>
+      <c r="AF82" s="40">
+        <v>484</v>
+      </c>
+      <c r="AG82" s="40">
+        <v>52.1</v>
+      </c>
+      <c r="AH82" s="40">
+        <v>7.306</v>
+      </c>
+      <c r="AI82" s="40">
+        <v>34</v>
+      </c>
+      <c r="AJ82" s="40">
+        <v>2.6</v>
+      </c>
+      <c r="AK82" s="40">
+        <v>6.6</v>
+      </c>
+      <c r="AL82" s="40">
+        <v>0.1</v>
+      </c>
+      <c r="AM82" s="40">
+        <v>14.4</v>
+      </c>
+      <c r="AN82" s="40">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AO82" s="40">
+        <v>198.9</v>
+      </c>
       <c r="AP82" s="40"/>
       <c r="AQ82" s="41">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>0.52100000000000002</v>
       </c>
       <c r="AR82" s="41">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>0.12113964720000002</v>
       </c>
       <c r="AS82" s="41">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>2.0999999999999996</v>
       </c>
       <c r="AT82" s="41">
         <f t="shared" si="75"/>
@@ -17900,27 +18960,27 @@
       <c r="BD82" s="22"/>
       <c r="BE82" s="42">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>2.01899412E-3</v>
       </c>
       <c r="BF82" s="42">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>2.9073515327999999</v>
       </c>
       <c r="BG82" s="42">
         <f t="shared" si="61"/>
-        <v>178.4</v>
-      </c>
-      <c r="BH82" s="43" t="str">
+        <v>198.9</v>
+      </c>
+      <c r="BH82" s="43">
         <f t="shared" si="62"/>
-        <v/>
-      </c>
-      <c r="BI82" s="43" t="str">
+        <v>7.2398190045248875E-2</v>
+      </c>
+      <c r="BI82" s="43">
         <f t="shared" si="63"/>
-        <v/>
+        <v>7.2000000000000008E-2</v>
       </c>
       <c r="BJ82" s="43">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>174.44109196800002</v>
       </c>
       <c r="BK82" s="43" t="str">
         <f t="shared" si="70"/>
@@ -17932,11 +18992,11 @@
       </c>
       <c r="BM82" s="44">
         <f t="shared" si="67"/>
-        <v>0</v>
+        <v>0.12113964720000002</v>
       </c>
       <c r="BN82" s="43">
         <f t="shared" si="58"/>
-        <v>1.3380000000000001</v>
+        <v>0</v>
       </c>
       <c r="BO82" s="43" t="str">
         <f t="shared" si="65"/>
@@ -17944,18 +19004,18 @@
       </c>
       <c r="BP82" s="55">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>314.64843428571436</v>
       </c>
       <c r="BQ82" s="45">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>0.12113964720000002</v>
       </c>
       <c r="BR82" s="24">
         <f t="shared" si="73"/>
-        <v>1.3380000000000001</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:70" ht="15" thickBot="1">
+    <row r="83" spans="1:70" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>88</v>
       </c>
@@ -17976,50 +19036,112 @@
         <v>4309.7</v>
       </c>
       <c r="I83" s="48"/>
-      <c r="J83" s="46"/>
-      <c r="K83" s="40"/>
-      <c r="L83" s="40"/>
-      <c r="M83" s="40"/>
-      <c r="N83" s="40"/>
-      <c r="O83" s="40"/>
-      <c r="P83" s="40"/>
-      <c r="Q83" s="40"/>
-      <c r="R83" s="40"/>
+      <c r="J83" s="72">
+        <v>4070.835</v>
+      </c>
+      <c r="K83" s="40">
+        <v>21.449000000000002</v>
+      </c>
+      <c r="L83" s="40">
+        <v>19.5</v>
+      </c>
+      <c r="M83" s="40">
+        <v>90.9</v>
+      </c>
+      <c r="N83" s="40">
+        <v>16.350000000000001</v>
+      </c>
+      <c r="O83" s="40">
+        <v>333</v>
+      </c>
+      <c r="P83" s="40">
+        <v>1.37</v>
+      </c>
+      <c r="Q83" s="40">
+        <v>0.32</v>
+      </c>
+      <c r="R83" s="40">
+        <v>2.5499999999999998</v>
+      </c>
       <c r="S83" s="40"/>
-      <c r="T83" s="40"/>
-      <c r="U83" s="40"/>
-      <c r="V83" s="40"/>
-      <c r="W83" s="40"/>
-      <c r="X83" s="40"/>
-      <c r="Y83" s="40"/>
-      <c r="Z83" s="40"/>
-      <c r="AA83" s="40"/>
-      <c r="AB83" s="40"/>
-      <c r="AC83" s="40"/>
-      <c r="AD83" s="40"/>
-      <c r="AE83" s="17"/>
-      <c r="AF83" s="40"/>
-      <c r="AG83" s="40"/>
-      <c r="AH83" s="40"/>
-      <c r="AI83" s="40"/>
-      <c r="AJ83" s="40"/>
-      <c r="AK83" s="40"/>
-      <c r="AL83" s="40"/>
-      <c r="AM83" s="40"/>
-      <c r="AN83" s="40"/>
-      <c r="AO83" s="40"/>
+      <c r="T83" s="40">
+        <v>0.21</v>
+      </c>
+      <c r="U83" s="40">
+        <v>0.16</v>
+      </c>
+      <c r="V83" s="40">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="W83" s="40">
+        <v>7.3129999999999997</v>
+      </c>
+      <c r="X83" s="40">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="Y83" s="40">
+        <v>61</v>
+      </c>
+      <c r="Z83" s="40">
+        <v>2.42</v>
+      </c>
+      <c r="AA83" s="40">
+        <v>143.6</v>
+      </c>
+      <c r="AB83" s="40">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="AC83" s="40">
+        <v>35.4</v>
+      </c>
+      <c r="AD83" s="40">
+        <v>49.6</v>
+      </c>
+      <c r="AE83" s="17">
+        <v>7.2709999999999999</v>
+      </c>
+      <c r="AF83" s="40">
+        <v>408</v>
+      </c>
+      <c r="AG83" s="40">
+        <v>56.7</v>
+      </c>
+      <c r="AH83" s="40">
+        <v>7.3029999999999999</v>
+      </c>
+      <c r="AI83" s="40">
+        <v>34</v>
+      </c>
+      <c r="AJ83" s="40">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AK83" s="40">
+        <v>6.7</v>
+      </c>
+      <c r="AL83" s="40">
+        <v>0.2</v>
+      </c>
+      <c r="AM83" s="40">
+        <v>14.6</v>
+      </c>
+      <c r="AN83" s="40">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AO83" s="40">
+        <v>198</v>
+      </c>
       <c r="AP83" s="7"/>
       <c r="AQ83" s="41">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>0.56700000000000006</v>
       </c>
       <c r="AR83" s="41">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>9.2663999999999996E-2</v>
       </c>
       <c r="AS83" s="41">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>1.7999999999999989</v>
       </c>
       <c r="AT83" s="41">
         <f t="shared" si="75"/>
@@ -18051,27 +19173,27 @@
       <c r="BD83" s="22"/>
       <c r="BE83" s="42">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>1.5444E-3</v>
       </c>
       <c r="BF83" s="42">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>2.2239360000000001</v>
       </c>
       <c r="BG83" s="42">
         <f t="shared" si="61"/>
-        <v>178.4</v>
-      </c>
-      <c r="BH83" s="43" t="str">
+        <v>198</v>
+      </c>
+      <c r="BH83" s="43">
         <f t="shared" si="62"/>
-        <v/>
-      </c>
-      <c r="BI83" s="43" t="str">
+        <v>7.373737373737374E-2</v>
+      </c>
+      <c r="BI83" s="43">
         <f t="shared" si="63"/>
-        <v/>
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="BJ83" s="43">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>133.43616</v>
       </c>
       <c r="BK83" s="43" t="str">
         <f t="shared" si="70"/>
@@ -18083,11 +19205,11 @@
       </c>
       <c r="BM83" s="44">
         <f t="shared" si="67"/>
-        <v>0</v>
+        <v>9.2663999999999996E-2</v>
       </c>
       <c r="BN83" s="43">
         <f t="shared" si="58"/>
-        <v>1.3380000000000001</v>
+        <v>0</v>
       </c>
       <c r="BO83" s="43" t="str">
         <f t="shared" si="65"/>
@@ -18095,18 +19217,18 @@
       </c>
       <c r="BP83" s="55">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>240.68571428571428</v>
       </c>
       <c r="BQ83" s="45">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>9.2663999999999996E-2</v>
       </c>
       <c r="BR83" s="24">
         <f t="shared" si="73"/>
-        <v>1.3380000000000001</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:70">
+    <row r="84" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>76</v>
       </c>
@@ -18128,7 +19250,7 @@
         <v>4805.7299999999996</v>
       </c>
       <c r="I84" s="37"/>
-      <c r="J84" s="39"/>
+      <c r="J84" s="91"/>
       <c r="K84" s="6"/>
       <c r="L84" s="6"/>
       <c r="M84" s="6"/>
@@ -18259,7 +19381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:70">
+    <row r="85" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>79</v>
       </c>
@@ -18280,7 +19402,7 @@
         <v>4805.7299999999996</v>
       </c>
       <c r="I85" s="48"/>
-      <c r="J85" s="46"/>
+      <c r="J85" s="72"/>
       <c r="K85" s="40"/>
       <c r="L85" s="40"/>
       <c r="M85" s="40"/>
@@ -18323,11 +19445,11 @@
       </c>
       <c r="AS85" s="41">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>-15.6</v>
       </c>
       <c r="AT85" s="41">
         <f t="shared" si="75"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AU85" s="41">
         <f t="shared" si="76"/>
@@ -18411,7 +19533,7 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="86" spans="1:70">
+    <row r="86" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>81</v>
       </c>
@@ -18432,7 +19554,7 @@
         <v>4805.7299999999996</v>
       </c>
       <c r="I86" s="48"/>
-      <c r="J86" s="46"/>
+      <c r="J86" s="72"/>
       <c r="K86" s="40"/>
       <c r="L86" s="40"/>
       <c r="M86" s="40"/>
@@ -18474,11 +19596,11 @@
       </c>
       <c r="AS86" s="41">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>-15.3</v>
       </c>
       <c r="AT86" s="41">
         <f t="shared" si="75"/>
-        <v>0</v>
+        <v>-4.3</v>
       </c>
       <c r="AU86" s="41">
         <f t="shared" si="76"/>
@@ -18562,7 +19684,7 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="87" spans="1:70">
+    <row r="87" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>82</v>
       </c>
@@ -18583,7 +19705,7 @@
         <v>4805.7299999999996</v>
       </c>
       <c r="I87" s="48"/>
-      <c r="J87" s="46"/>
+      <c r="J87" s="72"/>
       <c r="K87" s="40"/>
       <c r="L87" s="40"/>
       <c r="M87" s="40"/>
@@ -18626,11 +19748,11 @@
       </c>
       <c r="AS87" s="41">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>-19.600000000000001</v>
       </c>
       <c r="AT87" s="41">
         <f t="shared" si="75"/>
-        <v>0</v>
+        <v>-4.5</v>
       </c>
       <c r="AU87" s="41">
         <f t="shared" si="76"/>
@@ -18714,7 +19836,7 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="88" spans="1:70">
+    <row r="88" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>84</v>
       </c>
@@ -18735,7 +19857,7 @@
         <v>4805.7299999999996</v>
       </c>
       <c r="I88" s="48"/>
-      <c r="J88" s="40"/>
+      <c r="J88" s="72"/>
       <c r="K88" s="40"/>
       <c r="L88" s="40"/>
       <c r="M88" s="40"/>
@@ -18778,11 +19900,11 @@
       </c>
       <c r="AS88" s="41">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>-20.6</v>
       </c>
       <c r="AT88" s="41">
         <f t="shared" si="75"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AU88" s="41">
         <f t="shared" si="76"/>
@@ -18865,7 +19987,7 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="89" spans="1:70">
+    <row r="89" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>85</v>
       </c>
@@ -18886,7 +20008,7 @@
         <v>4805.7299999999996</v>
       </c>
       <c r="I89" s="48"/>
-      <c r="J89" s="40"/>
+      <c r="J89" s="72"/>
       <c r="K89" s="40"/>
       <c r="L89" s="40"/>
       <c r="M89" s="40"/>
@@ -18929,11 +20051,11 @@
       </c>
       <c r="AS89" s="41">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>-22.1</v>
       </c>
       <c r="AT89" s="41">
         <f t="shared" si="75"/>
-        <v>0</v>
+        <v>-4.5999999999999996</v>
       </c>
       <c r="AU89" s="41">
         <f t="shared" si="76"/>
@@ -19016,7 +20138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:70">
+    <row r="90" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>86</v>
       </c>
@@ -19037,7 +20159,7 @@
         <v>4805.7299999999996</v>
       </c>
       <c r="I90" s="48"/>
-      <c r="J90" s="40"/>
+      <c r="J90" s="72"/>
       <c r="K90" s="40"/>
       <c r="L90" s="40"/>
       <c r="M90" s="40"/>
@@ -19080,11 +20202,11 @@
       </c>
       <c r="AS90" s="41">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="AT90" s="41">
         <f t="shared" si="75"/>
-        <v>0</v>
+        <v>-4.9000000000000004</v>
       </c>
       <c r="AU90" s="41">
         <f t="shared" si="76"/>
@@ -19167,7 +20289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:70">
+    <row r="91" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>87</v>
       </c>
@@ -19188,7 +20310,7 @@
         <v>4805.7299999999996</v>
       </c>
       <c r="I91" s="48"/>
-      <c r="J91" s="40"/>
+      <c r="J91" s="72"/>
       <c r="K91" s="40"/>
       <c r="L91" s="40"/>
       <c r="M91" s="40"/>
@@ -19231,11 +20353,11 @@
       </c>
       <c r="AS91" s="41">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>-14.4</v>
       </c>
       <c r="AT91" s="41">
         <f t="shared" si="75"/>
-        <v>0</v>
+        <v>-4.4000000000000004</v>
       </c>
       <c r="AU91" s="41">
         <f t="shared" si="76"/>
@@ -19318,7 +20440,7 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="92" spans="1:70" ht="15" thickBot="1">
+    <row r="92" spans="1:70" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>88</v>
       </c>
@@ -19339,7 +20461,7 @@
         <v>4805.7299999999996</v>
       </c>
       <c r="I92" s="48"/>
-      <c r="J92" s="40"/>
+      <c r="J92" s="72"/>
       <c r="K92" s="40"/>
       <c r="L92" s="40"/>
       <c r="M92" s="40"/>
@@ -19382,11 +20504,11 @@
       </c>
       <c r="AS92" s="41">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>-14.6</v>
       </c>
       <c r="AT92" s="41">
         <f t="shared" si="75"/>
-        <v>0</v>
+        <v>-4.4000000000000004</v>
       </c>
       <c r="AU92" s="41">
         <f t="shared" si="76"/>
@@ -19469,7 +20591,7 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="93" spans="1:70">
+    <row r="93" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>76</v>
       </c>
@@ -19491,7 +20613,7 @@
         <v>5497.99</v>
       </c>
       <c r="I93" s="37"/>
-      <c r="J93" s="6"/>
+      <c r="J93" s="91"/>
       <c r="K93" s="6"/>
       <c r="L93" s="6"/>
       <c r="M93" s="6"/>
@@ -19622,7 +20744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:70">
+    <row r="94" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>79</v>
       </c>
@@ -19643,7 +20765,7 @@
         <v>5497.99</v>
       </c>
       <c r="I94" s="48"/>
-      <c r="J94" s="40"/>
+      <c r="J94" s="72"/>
       <c r="K94" s="40"/>
       <c r="L94" s="40"/>
       <c r="M94" s="40"/>
@@ -19774,7 +20896,7 @@
         <v>1.3019999999999998</v>
       </c>
     </row>
-    <row r="95" spans="1:70">
+    <row r="95" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>81</v>
       </c>
@@ -19795,7 +20917,7 @@
         <v>5497.99</v>
       </c>
       <c r="I95" s="48"/>
-      <c r="J95" s="40"/>
+      <c r="J95" s="72"/>
       <c r="K95" s="40"/>
       <c r="L95" s="40"/>
       <c r="M95" s="40"/>
@@ -19926,7 +21048,7 @@
         <v>1.3019999999999998</v>
       </c>
     </row>
-    <row r="96" spans="1:70">
+    <row r="96" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>82</v>
       </c>
@@ -19947,7 +21069,7 @@
         <v>5497.99</v>
       </c>
       <c r="I96" s="48"/>
-      <c r="J96" s="40"/>
+      <c r="J96" s="72"/>
       <c r="K96" s="40"/>
       <c r="L96" s="40"/>
       <c r="M96" s="40"/>
@@ -20078,7 +21200,7 @@
         <v>1.3019999999999998</v>
       </c>
     </row>
-    <row r="97" spans="1:70">
+    <row r="97" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>84</v>
       </c>
@@ -20099,7 +21221,7 @@
         <v>5497.99</v>
       </c>
       <c r="I97" s="48"/>
-      <c r="J97" s="40"/>
+      <c r="J97" s="72"/>
       <c r="K97" s="40"/>
       <c r="L97" s="40"/>
       <c r="M97" s="40"/>
@@ -20229,7 +21351,7 @@
         <v>1.3019999999999998</v>
       </c>
     </row>
-    <row r="98" spans="1:70">
+    <row r="98" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>85</v>
       </c>
@@ -20250,7 +21372,7 @@
         <v>5497.99</v>
       </c>
       <c r="I98" s="48"/>
-      <c r="J98" s="40"/>
+      <c r="J98" s="72"/>
       <c r="K98" s="40"/>
       <c r="L98" s="40"/>
       <c r="M98" s="40"/>
@@ -20380,7 +21502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:70">
+    <row r="99" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>86</v>
       </c>
@@ -20401,7 +21523,7 @@
         <v>5497.99</v>
       </c>
       <c r="I99" s="48"/>
-      <c r="J99" s="40"/>
+      <c r="J99" s="72"/>
       <c r="K99" s="40"/>
       <c r="L99" s="40"/>
       <c r="M99" s="40"/>
@@ -20531,7 +21653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:70">
+    <row r="100" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>87</v>
       </c>
@@ -20552,7 +21674,7 @@
         <v>5497.99</v>
       </c>
       <c r="I100" s="48"/>
-      <c r="J100" s="40"/>
+      <c r="J100" s="72"/>
       <c r="K100" s="40"/>
       <c r="L100" s="40"/>
       <c r="M100" s="40"/>
@@ -20682,7 +21804,7 @@
         <v>1.3019999999999998</v>
       </c>
     </row>
-    <row r="101" spans="1:70" ht="15" thickBot="1">
+    <row r="101" spans="1:70" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>88</v>
       </c>
@@ -20703,7 +21825,7 @@
         <v>5497.99</v>
       </c>
       <c r="I101" s="48"/>
-      <c r="J101" s="40"/>
+      <c r="J101" s="72"/>
       <c r="K101" s="40"/>
       <c r="L101" s="40"/>
       <c r="M101" s="40"/>
@@ -20833,7 +21955,7 @@
         <v>1.3019999999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:70">
+    <row r="102" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>76</v>
       </c>
@@ -20855,7 +21977,7 @@
         <v>6057.48</v>
       </c>
       <c r="I102" s="3"/>
-      <c r="J102" s="3"/>
+      <c r="J102" s="92"/>
       <c r="K102" s="3"/>
       <c r="L102" s="3"/>
       <c r="M102" s="3"/>
@@ -20986,7 +22108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:70">
+    <row r="103" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>79</v>
       </c>
@@ -21006,6 +22128,7 @@
       <c r="H103" s="48">
         <v>6057.48</v>
       </c>
+      <c r="J103" s="93"/>
       <c r="AE103" s="54"/>
       <c r="AP103" s="40"/>
       <c r="AQ103" s="41">
@@ -21106,7 +22229,7 @@
         <v>1.2839999999999998</v>
       </c>
     </row>
-    <row r="104" spans="1:70">
+    <row r="104" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>81</v>
       </c>
@@ -21126,6 +22249,7 @@
       <c r="H104" s="48">
         <v>6057.48</v>
       </c>
+      <c r="J104" s="93"/>
       <c r="T104" s="56"/>
       <c r="AE104" s="54"/>
       <c r="AP104" s="40"/>
@@ -21227,7 +22351,7 @@
         <v>1.2839999999999998</v>
       </c>
     </row>
-    <row r="105" spans="1:70">
+    <row r="105" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>82</v>
       </c>
@@ -21247,6 +22371,7 @@
       <c r="H105" s="48">
         <v>6057.48</v>
       </c>
+      <c r="J105" s="93"/>
       <c r="AE105" s="54"/>
       <c r="AP105" s="40"/>
       <c r="AQ105" s="41">
@@ -21347,7 +22472,7 @@
         <v>1.2839999999999998</v>
       </c>
     </row>
-    <row r="106" spans="1:70">
+    <row r="106" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>84</v>
       </c>
@@ -21367,6 +22492,7 @@
       <c r="H106" s="48">
         <v>6057.48</v>
       </c>
+      <c r="J106" s="93"/>
       <c r="AE106" s="54"/>
       <c r="AP106" s="40"/>
       <c r="AQ106" s="41">
@@ -21466,7 +22592,7 @@
         <v>1.2839999999999998</v>
       </c>
     </row>
-    <row r="107" spans="1:70">
+    <row r="107" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>85</v>
       </c>
@@ -21486,6 +22612,7 @@
       <c r="H107" s="48">
         <v>6057.48</v>
       </c>
+      <c r="J107" s="93"/>
       <c r="AC107" s="57"/>
       <c r="AE107" s="54"/>
       <c r="AP107" s="40"/>
@@ -21586,7 +22713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:70">
+    <row r="108" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>86</v>
       </c>
@@ -21606,6 +22733,7 @@
       <c r="H108" s="48">
         <v>6057.48</v>
       </c>
+      <c r="J108" s="93"/>
       <c r="AC108" s="57"/>
       <c r="AE108" s="54"/>
       <c r="AP108" s="40"/>
@@ -21706,7 +22834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:70">
+    <row r="109" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>87</v>
       </c>
@@ -21726,6 +22854,7 @@
       <c r="H109" s="48">
         <v>6057.48</v>
       </c>
+      <c r="J109" s="93"/>
       <c r="AE109" s="54"/>
       <c r="AP109" s="40"/>
       <c r="AQ109" s="41">
@@ -21825,7 +22954,7 @@
         <v>1.2839999999999998</v>
       </c>
     </row>
-    <row r="110" spans="1:70" ht="15" thickBot="1">
+    <row r="110" spans="1:70" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
         <v>88</v>
       </c>
@@ -21845,6 +22974,7 @@
       <c r="H110" s="48">
         <v>6057.48</v>
       </c>
+      <c r="J110" s="93"/>
       <c r="AE110" s="54"/>
       <c r="AP110" s="7"/>
       <c r="AQ110" s="41">
@@ -21944,7 +23074,7 @@
         <v>1.2839999999999998</v>
       </c>
     </row>
-    <row r="111" spans="1:70">
+    <row r="111" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>76</v>
       </c>
@@ -21966,7 +23096,7 @@
         <v>6478.05</v>
       </c>
       <c r="I111" s="3"/>
-      <c r="J111" s="3"/>
+      <c r="J111" s="92"/>
       <c r="K111" s="3"/>
       <c r="L111" s="3"/>
       <c r="M111" s="3"/>
@@ -22097,7 +23227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:70">
+    <row r="112" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>79</v>
       </c>
@@ -22117,6 +23247,7 @@
       <c r="H112" s="48">
         <v>6478.05</v>
       </c>
+      <c r="J112" s="93"/>
       <c r="AE112" s="54"/>
       <c r="AP112" s="40"/>
       <c r="AQ112" s="41">
@@ -22217,7 +23348,7 @@
         <v>1.266</v>
       </c>
     </row>
-    <row r="113" spans="1:70">
+    <row r="113" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>81</v>
       </c>
@@ -22237,6 +23368,7 @@
       <c r="H113" s="48">
         <v>6478.05</v>
       </c>
+      <c r="J113" s="93"/>
       <c r="AE113" s="54"/>
       <c r="AP113" s="40"/>
       <c r="AQ113" s="41">
@@ -22337,7 +23469,7 @@
         <v>1.266</v>
       </c>
     </row>
-    <row r="114" spans="1:70">
+    <row r="114" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>82</v>
       </c>
@@ -22357,6 +23489,7 @@
       <c r="H114" s="48">
         <v>6478.05</v>
       </c>
+      <c r="J114" s="93"/>
       <c r="AE114" s="54"/>
       <c r="AP114" s="40"/>
       <c r="AQ114" s="41">
@@ -22457,7 +23590,7 @@
         <v>1.266</v>
       </c>
     </row>
-    <row r="115" spans="1:70">
+    <row r="115" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>84</v>
       </c>
@@ -22477,6 +23610,7 @@
       <c r="H115" s="48">
         <v>6478.05</v>
       </c>
+      <c r="J115" s="93"/>
       <c r="AE115" s="54"/>
       <c r="AP115" s="40"/>
       <c r="AQ115" s="41">
@@ -22576,7 +23710,7 @@
         <v>1.266</v>
       </c>
     </row>
-    <row r="116" spans="1:70">
+    <row r="116" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>85</v>
       </c>
@@ -22596,6 +23730,7 @@
       <c r="H116" s="48">
         <v>6478.05</v>
       </c>
+      <c r="J116" s="93"/>
       <c r="AE116" s="54"/>
       <c r="AP116" s="40"/>
       <c r="AQ116" s="41">
@@ -22695,7 +23830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:70">
+    <row r="117" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>86</v>
       </c>
@@ -22715,6 +23850,7 @@
       <c r="H117" s="48">
         <v>6478.05</v>
       </c>
+      <c r="J117" s="93"/>
       <c r="AE117" s="54"/>
       <c r="AP117" s="40"/>
       <c r="AQ117" s="41">
@@ -22814,7 +23950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:70">
+    <row r="118" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>87</v>
       </c>
@@ -22834,6 +23970,7 @@
       <c r="H118" s="48">
         <v>6478.05</v>
       </c>
+      <c r="J118" s="93"/>
       <c r="AE118" s="54"/>
       <c r="AP118" s="40"/>
       <c r="AQ118" s="41">
@@ -22933,7 +24070,7 @@
         <v>1.266</v>
       </c>
     </row>
-    <row r="119" spans="1:70" ht="15" thickBot="1">
+    <row r="119" spans="1:70" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
         <v>88</v>
       </c>
@@ -22955,7 +24092,7 @@
         <v>6478.05</v>
       </c>
       <c r="I119" s="5"/>
-      <c r="J119" s="5"/>
+      <c r="J119" s="94"/>
       <c r="K119" s="5"/>
       <c r="L119" s="5"/>
       <c r="M119" s="5"/>
@@ -23390,13 +24527,45 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F43DC28-AE43-4EFF-8739-4E0C557B415B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F43DC28-AE43-4EFF-8739-4E0C557B415B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
+    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/ar24-072-experiment/AR24-072-SAM-MasterDataTable.xlsx
+++ b/data/ar24-072-experiment/AR24-072-SAM-MasterDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myteams.gsk.com/sites/BiopharmModelPredictiveControl/Shared Documents/General/data/AR24-072-SAM-MPC-1kL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2760" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{841454D0-012A-4EEA-AA4B-8800E808BAB9}"/>
+  <xr:revisionPtr revIDLastSave="2799" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BC9C39A-EF58-429A-A5B1-4F41E22B258F}"/>
   <bookViews>
-    <workbookView xWindow="41265" yWindow="-1455" windowWidth="25935" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterDataTable" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="94">
   <si>
     <t>Batch Data</t>
   </si>
@@ -318,6 +318,9 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Contaminated</t>
   </si>
 </sst>
 </file>
@@ -1045,7 +1048,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
@@ -1143,6 +1146,22 @@
     <xf numFmtId="22" fontId="0" fillId="41" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="41" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="41" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="26" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="38" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1185,10 +1204,6 @@
     <xf numFmtId="0" fontId="19" fillId="34" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="26" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1305,10 +1320,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1631,90 +1642,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:70" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="81" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="82" t="s">
+      <c r="A1" s="97" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="98" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="82"/>
-      <c r="J1" s="82"/>
-      <c r="K1" s="82"/>
-      <c r="L1" s="82"/>
-      <c r="M1" s="82"/>
-      <c r="N1" s="82"/>
-      <c r="O1" s="82"/>
-      <c r="P1" s="82"/>
-      <c r="Q1" s="82"/>
-      <c r="R1" s="82"/>
-      <c r="S1" s="82"/>
-      <c r="T1" s="82"/>
-      <c r="U1" s="82"/>
-      <c r="V1" s="82"/>
-      <c r="W1" s="82"/>
-      <c r="X1" s="82"/>
-      <c r="Y1" s="82"/>
-      <c r="Z1" s="82"/>
-      <c r="AA1" s="82"/>
-      <c r="AB1" s="82"/>
-      <c r="AC1" s="82"/>
-      <c r="AD1" s="82"/>
-      <c r="AE1" s="82"/>
-      <c r="AF1" s="88" t="s">
+      <c r="I1" s="98"/>
+      <c r="J1" s="98"/>
+      <c r="K1" s="98"/>
+      <c r="L1" s="98"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="98"/>
+      <c r="O1" s="98"/>
+      <c r="P1" s="98"/>
+      <c r="Q1" s="98"/>
+      <c r="R1" s="98"/>
+      <c r="S1" s="98"/>
+      <c r="T1" s="98"/>
+      <c r="U1" s="98"/>
+      <c r="V1" s="98"/>
+      <c r="W1" s="98"/>
+      <c r="X1" s="98"/>
+      <c r="Y1" s="98"/>
+      <c r="Z1" s="98"/>
+      <c r="AA1" s="98"/>
+      <c r="AB1" s="98"/>
+      <c r="AC1" s="98"/>
+      <c r="AD1" s="98"/>
+      <c r="AE1" s="98"/>
+      <c r="AF1" s="104" t="s">
         <v>2</v>
       </c>
-      <c r="AG1" s="89"/>
-      <c r="AH1" s="89"/>
-      <c r="AI1" s="89"/>
-      <c r="AJ1" s="89"/>
-      <c r="AK1" s="89"/>
-      <c r="AL1" s="89"/>
-      <c r="AM1" s="89"/>
-      <c r="AN1" s="89"/>
-      <c r="AO1" s="89"/>
-      <c r="AP1" s="89"/>
-      <c r="AQ1" s="89"/>
-      <c r="AR1" s="89"/>
-      <c r="AS1" s="89"/>
-      <c r="AT1" s="89"/>
-      <c r="AU1" s="89"/>
-      <c r="AV1" s="90"/>
-      <c r="AW1" s="83" t="s">
+      <c r="AG1" s="105"/>
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="105"/>
+      <c r="AL1" s="105"/>
+      <c r="AM1" s="105"/>
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="105"/>
+      <c r="AR1" s="105"/>
+      <c r="AS1" s="105"/>
+      <c r="AT1" s="105"/>
+      <c r="AU1" s="105"/>
+      <c r="AV1" s="106"/>
+      <c r="AW1" s="99" t="s">
         <v>3</v>
       </c>
-      <c r="AX1" s="84"/>
-      <c r="AY1" s="84"/>
-      <c r="AZ1" s="84"/>
-      <c r="BA1" s="85"/>
-      <c r="BB1" s="82" t="s">
+      <c r="AX1" s="100"/>
+      <c r="AY1" s="100"/>
+      <c r="AZ1" s="100"/>
+      <c r="BA1" s="101"/>
+      <c r="BB1" s="98" t="s">
         <v>4</v>
       </c>
-      <c r="BC1" s="86"/>
-      <c r="BD1" s="87"/>
-      <c r="BE1" s="79" t="s">
+      <c r="BC1" s="102"/>
+      <c r="BD1" s="103"/>
+      <c r="BE1" s="95" t="s">
         <v>5</v>
       </c>
-      <c r="BF1" s="80"/>
-      <c r="BG1" s="80"/>
-      <c r="BH1" s="80"/>
-      <c r="BI1" s="80"/>
-      <c r="BJ1" s="80"/>
-      <c r="BK1" s="80"/>
-      <c r="BL1" s="80"/>
-      <c r="BM1" s="80"/>
-      <c r="BN1" s="80"/>
-      <c r="BO1" s="80"/>
-      <c r="BP1" s="80"/>
-      <c r="BQ1" s="77" t="s">
+      <c r="BF1" s="96"/>
+      <c r="BG1" s="96"/>
+      <c r="BH1" s="96"/>
+      <c r="BI1" s="96"/>
+      <c r="BJ1" s="96"/>
+      <c r="BK1" s="96"/>
+      <c r="BL1" s="96"/>
+      <c r="BM1" s="96"/>
+      <c r="BN1" s="96"/>
+      <c r="BO1" s="96"/>
+      <c r="BP1" s="96"/>
+      <c r="BQ1" s="93" t="s">
         <v>6</v>
       </c>
-      <c r="BR1" s="78"/>
+      <c r="BR1" s="94"/>
     </row>
     <row r="2" spans="1:70" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="20" t="s">
@@ -16067,6 +16078,9 @@
       <c r="E69">
         <v>7</v>
       </c>
+      <c r="F69" t="s">
+        <v>93</v>
+      </c>
       <c r="G69" s="35">
         <v>45575.470335648148</v>
       </c>
@@ -17354,162 +17368,187 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:70" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
+    <row r="75" spans="1:70" s="92" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="81" t="s">
         <v>76</v>
       </c>
-      <c r="B75" s="3">
+      <c r="B75" s="82">
         <v>1000</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="C75" s="82" t="s">
         <v>77</v>
       </c>
-      <c r="D75" s="3">
+      <c r="D75" s="82">
         <v>12</v>
       </c>
-      <c r="E75" s="3">
+      <c r="E75" s="82">
         <v>8</v>
       </c>
-      <c r="F75" s="3"/>
-      <c r="G75" s="74"/>
-      <c r="H75" s="3">
+      <c r="F75" s="82"/>
+      <c r="G75" s="83">
+        <v>45576.349305555559</v>
+      </c>
+      <c r="H75" s="82">
         <v>4309.7</v>
       </c>
-      <c r="I75" s="3"/>
-      <c r="J75" s="6">
+      <c r="I75" s="82"/>
+      <c r="J75" s="84">
         <v>3221.7150000000001</v>
       </c>
-      <c r="K75" s="75"/>
-      <c r="L75" s="75"/>
-      <c r="M75" s="75"/>
-      <c r="N75" s="6"/>
-      <c r="O75" s="6"/>
-      <c r="P75" s="6"/>
-      <c r="Q75" s="6"/>
-      <c r="R75" s="75"/>
-      <c r="S75" s="6"/>
-      <c r="T75" s="6"/>
-      <c r="U75" s="6"/>
-      <c r="V75" s="75"/>
-      <c r="W75" s="6"/>
-      <c r="X75" s="6"/>
-      <c r="Y75" s="6"/>
-      <c r="Z75" s="6"/>
-      <c r="AA75" s="6"/>
-      <c r="AB75" s="6"/>
-      <c r="AC75" s="6"/>
-      <c r="AD75" s="6"/>
-      <c r="AE75" s="76"/>
-      <c r="AF75" s="6"/>
-      <c r="AG75" s="75"/>
-      <c r="AH75" s="6"/>
-      <c r="AI75" s="75"/>
-      <c r="AJ75" s="6"/>
-      <c r="AK75" s="6"/>
-      <c r="AL75" s="6"/>
-      <c r="AM75" s="75"/>
-      <c r="AN75" s="75"/>
-      <c r="AO75" s="75">
-        <v>658799.98779296805</v>
-      </c>
-      <c r="AP75" s="6"/>
-      <c r="AQ75" s="32">
+      <c r="K75" s="84">
+        <v>22.3</v>
+      </c>
+      <c r="L75" s="84">
+        <v>21.5</v>
+      </c>
+      <c r="M75" s="84">
+        <v>97</v>
+      </c>
+      <c r="N75" s="84"/>
+      <c r="O75" s="84"/>
+      <c r="P75" s="84"/>
+      <c r="Q75" s="84"/>
+      <c r="R75" s="84">
+        <v>7.06</v>
+      </c>
+      <c r="S75" s="84"/>
+      <c r="T75" s="84"/>
+      <c r="U75" s="84"/>
+      <c r="V75" s="84">
+        <v>0.84</v>
+      </c>
+      <c r="W75" s="84"/>
+      <c r="X75" s="84"/>
+      <c r="Y75" s="84"/>
+      <c r="Z75" s="84"/>
+      <c r="AA75" s="84"/>
+      <c r="AB75" s="84"/>
+      <c r="AC75" s="84"/>
+      <c r="AD75" s="84"/>
+      <c r="AE75" s="85">
+        <v>7.3</v>
+      </c>
+      <c r="AF75" s="84"/>
+      <c r="AG75" s="84">
+        <v>52.5</v>
+      </c>
+      <c r="AH75" s="84"/>
+      <c r="AI75" s="84">
+        <v>34</v>
+      </c>
+      <c r="AJ75" s="84"/>
+      <c r="AK75" s="84"/>
+      <c r="AL75" s="84"/>
+      <c r="AM75" s="84">
+        <v>62332.34765625</v>
+      </c>
+      <c r="AN75" s="84">
+        <v>23036.900390625</v>
+      </c>
+      <c r="AO75" s="84">
+        <v>656400.02441406297</v>
+      </c>
+      <c r="AP75" s="84"/>
+      <c r="AQ75" s="84">
         <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="AR75" s="32">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="AR75" s="84">
         <f t="shared" si="68"/>
-        <v>0</v>
-      </c>
-      <c r="AS75" s="32">
+        <v>283.4185635278526</v>
+      </c>
+      <c r="AS75" s="84">
         <f t="shared" si="55"/>
-        <v>-54921.08203125</v>
-      </c>
-      <c r="AT75" s="32">
+        <v>7411.265625</v>
+      </c>
+      <c r="AT75" s="84">
         <f t="shared" si="56"/>
-        <v>-22041.2578125</v>
-      </c>
-      <c r="AU75" s="32">
+        <v>995.642578125</v>
+      </c>
+      <c r="AU75" s="84">
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AV75" s="66">
+      <c r="AV75" s="86">
         <v>60</v>
       </c>
-      <c r="AW75" s="3">
+      <c r="AW75" s="82">
         <v>592000</v>
       </c>
-      <c r="AX75" s="3">
+      <c r="AX75" s="82">
         <v>34</v>
       </c>
-      <c r="AY75" s="6">
+      <c r="AY75" s="84">
         <v>7.2</v>
       </c>
-      <c r="AZ75" s="6">
+      <c r="AZ75" s="84">
         <v>50</v>
       </c>
-      <c r="BA75" s="9">
+      <c r="BA75" s="87">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="BB75" s="8"/>
-      <c r="BC75" s="9"/>
-      <c r="BD75" s="21">
+      <c r="BB75" s="88"/>
+      <c r="BC75" s="87">
+        <f>4.72364272546421*24*60/BG75</f>
+        <v>1.0362652760015243E-2</v>
+      </c>
+      <c r="BD75" s="89">
         <f>792.953496967818/BG75</f>
-        <v>1.2036331385255102E-3</v>
-      </c>
-      <c r="BE75" s="9">
+        <v>1.2080339236361999E-3</v>
+      </c>
+      <c r="BE75" s="87">
         <f t="shared" si="60"/>
-        <v>0</v>
-      </c>
-      <c r="BF75" s="9">
+        <v>5.6450402099609418</v>
+      </c>
+      <c r="BF75" s="87">
         <f t="shared" si="69"/>
-        <v>0</v>
-      </c>
-      <c r="BG75" s="9">
+        <v>8128.857902343756</v>
+      </c>
+      <c r="BG75" s="87">
         <f t="shared" si="61"/>
-        <v>658799.98779296805</v>
-      </c>
-      <c r="BH75" s="10" t="str">
+        <v>656400.02441406297</v>
+      </c>
+      <c r="BH75" s="87">
         <f t="shared" si="62"/>
-        <v/>
-      </c>
-      <c r="BI75" s="10" t="str">
+        <v>9.4960916114972899E-2</v>
+      </c>
+      <c r="BI75" s="87">
         <f t="shared" si="63"/>
-        <v/>
-      </c>
-      <c r="BJ75" s="10">
+        <v>0.1052911277977196</v>
+      </c>
+      <c r="BJ75" s="87">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="BK75" s="10" t="str">
+        <v>408122.73148010776</v>
+      </c>
+      <c r="BK75" s="87" t="str">
         <f t="shared" si="70"/>
         <v/>
       </c>
-      <c r="BL75" s="10">
-        <f t="shared" si="66"/>
-        <v>0</v>
-      </c>
-      <c r="BM75" s="28" t="str">
+      <c r="BL75" s="87">
+        <f>IF(C75="Julia",BC75*BG75/24,"")</f>
+        <v>283.4185635278526</v>
+      </c>
+      <c r="BM75" s="90" t="str">
         <f t="shared" si="67"/>
         <v/>
       </c>
-      <c r="BN75" s="10" t="str">
+      <c r="BN75" s="87" t="str">
         <f t="shared" si="58"/>
         <v/>
       </c>
-      <c r="BO75" s="10">
+      <c r="BO75" s="87">
         <f t="shared" si="65"/>
         <v>792.95349696781796</v>
       </c>
-      <c r="BP75" s="58">
+      <c r="BP75" s="91">
         <f t="shared" si="71"/>
-        <v>0</v>
-      </c>
-      <c r="BQ75" s="30">
+        <v>736152.11305935739</v>
+      </c>
+      <c r="BQ75" s="90">
         <f t="shared" si="72"/>
-        <v>0</v>
-      </c>
-      <c r="BR75" s="26">
+        <v>283.4185635278526</v>
+      </c>
+      <c r="BR75" s="91">
         <f t="shared" si="73"/>
         <v>792.95349696781796</v>
       </c>
@@ -17530,7 +17569,9 @@
       <c r="E76">
         <v>8</v>
       </c>
-      <c r="G76" s="35"/>
+      <c r="G76" s="35">
+        <v>45576.376423611109</v>
+      </c>
       <c r="H76">
         <v>4309.7</v>
       </c>
@@ -17699,7 +17740,7 @@
         <v/>
       </c>
       <c r="BL76" s="43" t="str">
-        <f t="shared" si="66"/>
+        <f>IF(C76="Julia",BC76*BG76/24,"")</f>
         <v/>
       </c>
       <c r="BM76" s="44">
@@ -17743,7 +17784,9 @@
       <c r="E77">
         <v>8</v>
       </c>
-      <c r="G77" s="35"/>
+      <c r="G77" s="35">
+        <v>45576.377268518518</v>
+      </c>
       <c r="H77">
         <v>4309.7</v>
       </c>
@@ -17961,101 +18004,41 @@
         <v>4309.7</v>
       </c>
       <c r="J78" s="40"/>
-      <c r="K78" s="40">
-        <v>20.071000000000002</v>
-      </c>
-      <c r="L78" s="40">
-        <v>5.5369999999999999</v>
-      </c>
-      <c r="M78" s="40">
-        <v>27.6</v>
-      </c>
-      <c r="N78" s="40">
-        <v>12.68</v>
-      </c>
-      <c r="O78" s="40">
-        <v>439</v>
-      </c>
-      <c r="P78" s="40">
-        <v>5.22</v>
-      </c>
-      <c r="Q78" s="40">
-        <v>0.35</v>
-      </c>
-      <c r="R78" s="40">
-        <v>0.16</v>
-      </c>
+      <c r="K78" s="40"/>
+      <c r="L78" s="40"/>
+      <c r="M78" s="40"/>
+      <c r="N78" s="40"/>
+      <c r="O78" s="40"/>
+      <c r="P78" s="40"/>
+      <c r="Q78" s="40"/>
+      <c r="R78" s="40"/>
       <c r="S78" s="40"/>
-      <c r="T78" s="40">
-        <v>0.15</v>
-      </c>
-      <c r="U78" s="40">
-        <v>0.94</v>
-      </c>
-      <c r="V78" s="40">
-        <v>4.42</v>
-      </c>
-      <c r="W78" s="40">
-        <v>7.0549999999999997</v>
-      </c>
-      <c r="X78" s="40">
-        <v>39.200000000000003</v>
-      </c>
-      <c r="Y78" s="40">
-        <v>0</v>
-      </c>
-      <c r="Z78" s="40">
-        <v>6.92</v>
-      </c>
-      <c r="AA78" s="40">
-        <v>183.1</v>
-      </c>
-      <c r="AB78" s="40">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="AC78" s="40">
-        <v>34.4</v>
-      </c>
-      <c r="AD78" s="40">
-        <v>0</v>
-      </c>
-      <c r="AE78" s="17">
-        <v>7.0190000000000001</v>
-      </c>
-      <c r="AF78" s="40">
-        <v>408</v>
-      </c>
-      <c r="AG78" s="40">
-        <v>-0.2</v>
-      </c>
-      <c r="AH78" s="40">
-        <v>7.085</v>
-      </c>
-      <c r="AI78" s="40">
-        <v>34</v>
-      </c>
-      <c r="AJ78" s="40">
-        <v>6.4</v>
-      </c>
-      <c r="AK78" s="40">
-        <v>3.2</v>
-      </c>
-      <c r="AL78" s="40">
-        <v>0.2</v>
-      </c>
-      <c r="AM78" s="40">
-        <v>19.600000000000001</v>
-      </c>
-      <c r="AN78" s="40">
-        <v>4.5</v>
-      </c>
-      <c r="AO78" s="40">
-        <v>206.1</v>
-      </c>
+      <c r="T78" s="40"/>
+      <c r="U78" s="40"/>
+      <c r="V78" s="40"/>
+      <c r="W78" s="40"/>
+      <c r="X78" s="40"/>
+      <c r="Y78" s="40"/>
+      <c r="Z78" s="40"/>
+      <c r="AA78" s="40"/>
+      <c r="AB78" s="40"/>
+      <c r="AC78" s="40"/>
+      <c r="AD78" s="40"/>
+      <c r="AE78" s="17"/>
+      <c r="AF78" s="40"/>
+      <c r="AG78" s="40"/>
+      <c r="AH78" s="40"/>
+      <c r="AI78" s="40"/>
+      <c r="AJ78" s="40"/>
+      <c r="AK78" s="40"/>
+      <c r="AL78" s="40"/>
+      <c r="AM78" s="40"/>
+      <c r="AN78" s="40"/>
+      <c r="AO78" s="40"/>
       <c r="AP78" s="40"/>
       <c r="AQ78" s="41">
         <f t="shared" si="59"/>
-        <v>-2E-3</v>
+        <v>0</v>
       </c>
       <c r="AR78" s="41">
         <f t="shared" si="68"/>
@@ -18063,11 +18046,11 @@
       </c>
       <c r="AS78" s="41">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>-19.600000000000001</v>
       </c>
       <c r="AT78" s="41">
         <f t="shared" si="75"/>
-        <v>0</v>
+        <v>-4.5</v>
       </c>
       <c r="AU78" s="41">
         <f t="shared" si="76"/>
@@ -18096,23 +18079,23 @@
       <c r="BD78" s="22"/>
       <c r="BE78" s="42">
         <f t="shared" si="60"/>
-        <v>4.5647028000000007E-4</v>
+        <v>0</v>
       </c>
       <c r="BF78" s="42">
         <f t="shared" si="69"/>
-        <v>0.65731720320000009</v>
+        <v>0</v>
       </c>
       <c r="BG78" s="42">
         <f t="shared" si="61"/>
-        <v>206.1</v>
-      </c>
-      <c r="BH78" s="43">
+        <v>178.4</v>
+      </c>
+      <c r="BH78" s="43" t="str">
         <f t="shared" si="62"/>
-        <v>9.5099466278505587E-2</v>
-      </c>
-      <c r="BI78" s="43">
+        <v/>
+      </c>
+      <c r="BI78" s="43" t="str">
         <f t="shared" si="63"/>
-        <v>9.8000000000000004E-2</v>
+        <v/>
       </c>
       <c r="BJ78" s="43">
         <f t="shared" si="64"/>
@@ -18132,7 +18115,7 @@
       </c>
       <c r="BN78" s="43">
         <f t="shared" si="58"/>
-        <v>1.4633099999999999</v>
+        <v>1.3380000000000001</v>
       </c>
       <c r="BO78" s="43" t="str">
         <f t="shared" si="65"/>
@@ -18148,7 +18131,7 @@
       </c>
       <c r="BR78" s="24">
         <f t="shared" si="73"/>
-        <v>1.4633099999999999</v>
+        <v>1.3380000000000001</v>
       </c>
     </row>
     <row r="79" spans="1:70" x14ac:dyDescent="0.3">
@@ -18167,7 +18150,9 @@
       <c r="E79">
         <v>8</v>
       </c>
-      <c r="G79" s="35"/>
+      <c r="G79" s="35">
+        <v>45576.378101851849</v>
+      </c>
       <c r="H79">
         <v>4309.7</v>
       </c>
@@ -18272,7 +18257,7 @@
       </c>
       <c r="AR79" s="41">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>0.10860416666666667</v>
       </c>
       <c r="AS79" s="41">
         <f t="shared" si="74"/>
@@ -18304,7 +18289,9 @@
       <c r="BA79" s="42">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="BB79" s="11"/>
+      <c r="BB79" s="11">
+        <v>1.2999999999999999E-2</v>
+      </c>
       <c r="BD79" s="22"/>
       <c r="BE79" s="42">
         <f t="shared" si="60"/>
@@ -18328,11 +18315,11 @@
       </c>
       <c r="BJ79" s="43">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>156.39000000000001</v>
       </c>
       <c r="BK79" s="43">
         <f t="shared" si="70"/>
-        <v>0</v>
+        <v>0.10860416666666667</v>
       </c>
       <c r="BL79" s="44" t="str">
         <f t="shared" si="66"/>
@@ -18352,11 +18339,11 @@
       </c>
       <c r="BP79" s="55">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>282.08874458874459</v>
       </c>
       <c r="BQ79" s="45">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>0.10860416666666667</v>
       </c>
       <c r="BR79" s="24">
         <f t="shared" si="73"/>
@@ -18379,7 +18366,9 @@
       <c r="E80">
         <v>8</v>
       </c>
-      <c r="G80" s="35"/>
+      <c r="G80" s="35">
+        <v>45576.378946759258</v>
+      </c>
       <c r="H80">
         <v>4309.7</v>
       </c>
@@ -18598,7 +18587,9 @@
       <c r="E81">
         <v>8</v>
       </c>
-      <c r="G81" s="35"/>
+      <c r="G81" s="35">
+        <v>45576.379803240743</v>
+      </c>
       <c r="H81">
         <v>4309.7</v>
       </c>
@@ -18818,7 +18809,9 @@
       <c r="E82">
         <v>8</v>
       </c>
-      <c r="G82" s="35"/>
+      <c r="G82" s="35">
+        <v>45576.380659722221</v>
+      </c>
       <c r="H82">
         <v>4309.7</v>
       </c>
@@ -19031,7 +19024,9 @@
       <c r="E83">
         <v>8</v>
       </c>
-      <c r="G83" s="35"/>
+      <c r="G83" s="35">
+        <v>45576.381516203706</v>
+      </c>
       <c r="H83">
         <v>4309.7</v>
       </c>
@@ -19245,24 +19240,28 @@
         <v>9</v>
       </c>
       <c r="F84" s="3"/>
-      <c r="G84" s="34"/>
+      <c r="G84" s="74">
+        <v>45577.364340277803</v>
+      </c>
       <c r="H84" s="3">
         <v>4805.7299999999996</v>
       </c>
       <c r="I84" s="37"/>
-      <c r="J84" s="91"/>
-      <c r="K84" s="6"/>
-      <c r="L84" s="6"/>
-      <c r="M84" s="6"/>
+      <c r="J84" s="77">
+        <v>3776.085</v>
+      </c>
+      <c r="K84" s="75"/>
+      <c r="L84" s="75"/>
+      <c r="M84" s="75"/>
       <c r="N84" s="6"/>
       <c r="O84" s="6"/>
       <c r="P84" s="6"/>
       <c r="Q84" s="6"/>
-      <c r="R84" s="6"/>
+      <c r="R84" s="75"/>
       <c r="S84" s="6"/>
       <c r="T84" s="6"/>
       <c r="U84" s="6"/>
-      <c r="V84" s="6"/>
+      <c r="V84" s="75"/>
       <c r="W84" s="6"/>
       <c r="X84" s="6"/>
       <c r="Y84" s="6"/>
@@ -19271,17 +19270,17 @@
       <c r="AB84" s="6"/>
       <c r="AC84" s="6"/>
       <c r="AD84" s="6"/>
-      <c r="AE84" s="16"/>
+      <c r="AE84" s="76"/>
       <c r="AF84" s="6"/>
-      <c r="AG84" s="6"/>
+      <c r="AG84" s="75"/>
       <c r="AH84" s="6"/>
-      <c r="AI84" s="6"/>
+      <c r="AI84" s="75"/>
       <c r="AJ84" s="6"/>
       <c r="AK84" s="6"/>
       <c r="AL84" s="6"/>
-      <c r="AM84" s="6"/>
-      <c r="AN84" s="6"/>
-      <c r="AO84" s="6"/>
+      <c r="AM84" s="75"/>
+      <c r="AN84" s="75"/>
+      <c r="AO84" s="75"/>
       <c r="AP84" s="6"/>
       <c r="AQ84" s="32">
         <f t="shared" si="59"/>
@@ -19293,11 +19292,11 @@
       </c>
       <c r="AS84" s="32">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>-62332.34765625</v>
       </c>
       <c r="AT84" s="32">
         <f t="shared" si="75"/>
-        <v>0</v>
+        <v>-23036.900390625</v>
       </c>
       <c r="AU84" s="32">
         <f t="shared" si="76"/>
@@ -19397,59 +19396,123 @@
       <c r="E85">
         <v>9</v>
       </c>
-      <c r="G85" s="35"/>
+      <c r="G85" s="35">
+        <v>45577.342303240737</v>
+      </c>
       <c r="H85">
         <v>4805.7299999999996</v>
       </c>
       <c r="I85" s="48"/>
-      <c r="J85" s="72"/>
-      <c r="K85" s="40"/>
-      <c r="L85" s="40"/>
-      <c r="M85" s="40"/>
-      <c r="N85" s="40"/>
-      <c r="O85" s="40"/>
-      <c r="P85" s="40"/>
-      <c r="Q85" s="40"/>
-      <c r="R85" s="40"/>
+      <c r="J85" s="72">
+        <v>4718.79</v>
+      </c>
+      <c r="K85" s="40">
+        <v>20.309999999999999</v>
+      </c>
+      <c r="L85" s="40">
+        <v>18.126000000000001</v>
+      </c>
+      <c r="M85" s="40">
+        <v>89.2</v>
+      </c>
+      <c r="N85" s="40">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="O85" s="40">
+        <v>336</v>
+      </c>
+      <c r="P85" s="40">
+        <v>1.43</v>
+      </c>
+      <c r="Q85" s="40">
+        <v>0.31</v>
+      </c>
+      <c r="R85" s="40">
+        <v>2.96</v>
+      </c>
       <c r="S85" s="40"/>
-      <c r="T85" s="40"/>
-      <c r="U85" s="40"/>
-      <c r="V85" s="40"/>
-      <c r="W85" s="40"/>
-      <c r="X85" s="40"/>
-      <c r="Y85" s="40"/>
-      <c r="Z85" s="40"/>
-      <c r="AA85" s="40"/>
-      <c r="AB85" s="40"/>
-      <c r="AC85" s="40"/>
-      <c r="AD85" s="40"/>
-      <c r="AE85" s="17"/>
-      <c r="AF85" s="40"/>
-      <c r="AG85" s="40"/>
-      <c r="AH85" s="40"/>
-      <c r="AI85" s="40"/>
-      <c r="AJ85" s="40"/>
-      <c r="AK85" s="40"/>
-      <c r="AL85" s="40"/>
-      <c r="AM85" s="40"/>
-      <c r="AN85" s="40"/>
-      <c r="AO85" s="40"/>
+      <c r="T85" s="40">
+        <v>0.22</v>
+      </c>
+      <c r="U85" s="40">
+        <v>0.15</v>
+      </c>
+      <c r="V85" s="40">
+        <v>1.73</v>
+      </c>
+      <c r="W85" s="40">
+        <v>7.2919999999999998</v>
+      </c>
+      <c r="X85" s="40">
+        <v>37.299999999999997</v>
+      </c>
+      <c r="Y85" s="40">
+        <v>62.2</v>
+      </c>
+      <c r="Z85" s="40">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AA85" s="40">
+        <v>143.19999999999999</v>
+      </c>
+      <c r="AB85" s="40">
+        <v>15.9</v>
+      </c>
+      <c r="AC85" s="40">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="AD85" s="40">
+        <v>50.6</v>
+      </c>
+      <c r="AE85" s="17">
+        <v>7.2510000000000003</v>
+      </c>
+      <c r="AF85" s="40">
+        <v>405</v>
+      </c>
+      <c r="AG85" s="40">
+        <v>50.5</v>
+      </c>
+      <c r="AH85" s="40">
+        <v>7.3040000000000003</v>
+      </c>
+      <c r="AI85" s="40">
+        <v>34</v>
+      </c>
+      <c r="AJ85" s="40">
+        <v>2</v>
+      </c>
+      <c r="AK85" s="40">
+        <v>7.9</v>
+      </c>
+      <c r="AL85" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="AM85" s="40">
+        <v>17.7</v>
+      </c>
+      <c r="AN85" s="40">
+        <v>4</v>
+      </c>
+      <c r="AO85" s="40">
+        <v>197.1</v>
+      </c>
       <c r="AP85" s="40"/>
       <c r="AQ85" s="41">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>0.505</v>
       </c>
       <c r="AR85" s="41">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>8.5743230399999995E-2</v>
       </c>
       <c r="AS85" s="41">
         <f t="shared" si="74"/>
-        <v>-15.6</v>
+        <v>2.0999999999999996</v>
       </c>
       <c r="AT85" s="41">
         <f t="shared" si="75"/>
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AU85" s="41">
         <f t="shared" si="76"/>
@@ -19478,27 +19541,27 @@
       <c r="BD85" s="22"/>
       <c r="BE85" s="42">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>1.4290538400000001E-3</v>
       </c>
       <c r="BF85" s="42">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>2.0578375296000004</v>
       </c>
       <c r="BG85" s="42">
         <f t="shared" si="61"/>
-        <v>176</v>
-      </c>
-      <c r="BH85" s="43" t="str">
+        <v>197.1</v>
+      </c>
+      <c r="BH85" s="43">
         <f t="shared" si="62"/>
-        <v/>
-      </c>
-      <c r="BI85" s="43" t="str">
+        <v>8.9802130898021304E-2</v>
+      </c>
+      <c r="BI85" s="43">
         <f t="shared" si="63"/>
-        <v/>
+        <v>8.8499999999999995E-2</v>
       </c>
       <c r="BJ85" s="43">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>123.470251776</v>
       </c>
       <c r="BK85" s="43" t="str">
         <f t="shared" si="70"/>
@@ -19510,11 +19573,11 @@
       </c>
       <c r="BM85" s="44">
         <f t="shared" si="67"/>
-        <v>0</v>
+        <v>8.5743230399999995E-2</v>
       </c>
       <c r="BN85" s="43">
         <f t="shared" ref="BN85:BN119" si="77">IF(IF(C85&lt;&gt;"Julia",((1.5-R85)*BG85)/400, "")&lt;0,0,IF(C85&lt;&gt;"Julia",((3-R85)*BG85)/400, ""))</f>
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BO85" s="43" t="str">
         <f t="shared" si="65"/>
@@ -19522,15 +19585,15 @@
       </c>
       <c r="BP85" s="55">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>222.70968935064934</v>
       </c>
       <c r="BQ85" s="45">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>8.5743230399999995E-2</v>
       </c>
       <c r="BR85" s="24">
         <f t="shared" si="73"/>
-        <v>1.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:70" x14ac:dyDescent="0.3">
@@ -19549,58 +19612,123 @@
       <c r="E86">
         <v>9</v>
       </c>
-      <c r="G86" s="35"/>
+      <c r="G86" s="35">
+        <v>45577.324907407405</v>
+      </c>
       <c r="H86">
         <v>4805.7299999999996</v>
       </c>
       <c r="I86" s="48"/>
-      <c r="J86" s="72"/>
-      <c r="K86" s="40"/>
-      <c r="L86" s="40"/>
-      <c r="M86" s="40"/>
-      <c r="N86" s="40"/>
-      <c r="O86" s="40"/>
-      <c r="P86" s="40"/>
-      <c r="Q86" s="40"/>
-      <c r="R86" s="40"/>
+      <c r="J86" s="72">
+        <v>4821.33</v>
+      </c>
+      <c r="K86" s="40">
+        <v>19.646000000000001</v>
+      </c>
+      <c r="L86" s="40">
+        <v>17.206</v>
+      </c>
+      <c r="M86" s="40">
+        <v>87.6</v>
+      </c>
+      <c r="N86" s="40">
+        <v>16.239999999999998</v>
+      </c>
+      <c r="O86" s="40">
+        <v>339</v>
+      </c>
+      <c r="P86" s="40">
+        <v>1.41</v>
+      </c>
+      <c r="Q86" s="40">
+        <v>0.32</v>
+      </c>
+      <c r="R86" s="40">
+        <v>2.85</v>
+      </c>
       <c r="S86" s="40"/>
-      <c r="T86" s="40"/>
-      <c r="U86" s="40"/>
-      <c r="W86" s="40"/>
-      <c r="X86" s="40"/>
-      <c r="Y86" s="40"/>
-      <c r="Z86" s="40"/>
-      <c r="AA86" s="40"/>
-      <c r="AB86" s="40"/>
-      <c r="AC86" s="40"/>
-      <c r="AD86" s="40"/>
-      <c r="AE86" s="17"/>
-      <c r="AF86" s="40"/>
-      <c r="AG86" s="40"/>
-      <c r="AH86" s="40"/>
-      <c r="AI86" s="40"/>
-      <c r="AJ86" s="40"/>
-      <c r="AK86" s="40"/>
-      <c r="AL86" s="40"/>
-      <c r="AM86" s="40"/>
-      <c r="AN86" s="40"/>
-      <c r="AO86" s="40"/>
+      <c r="T86" s="40">
+        <v>0.2</v>
+      </c>
+      <c r="U86" s="40">
+        <v>0.17</v>
+      </c>
+      <c r="V86">
+        <v>1.99</v>
+      </c>
+      <c r="W86" s="40">
+        <v>7.298</v>
+      </c>
+      <c r="X86" s="40">
+        <v>31.2</v>
+      </c>
+      <c r="Y86" s="40">
+        <v>64.400000000000006</v>
+      </c>
+      <c r="Z86" s="40">
+        <v>2.11</v>
+      </c>
+      <c r="AA86" s="40">
+        <v>142.5</v>
+      </c>
+      <c r="AB86" s="40">
+        <v>13.5</v>
+      </c>
+      <c r="AC86" s="40">
+        <v>27.3</v>
+      </c>
+      <c r="AD86" s="40">
+        <v>52.5</v>
+      </c>
+      <c r="AE86" s="17">
+        <v>7.2560000000000002</v>
+      </c>
+      <c r="AF86" s="40">
+        <v>411</v>
+      </c>
+      <c r="AG86" s="40">
+        <v>49.6</v>
+      </c>
+      <c r="AH86" s="40">
+        <v>7.306</v>
+      </c>
+      <c r="AI86" s="40">
+        <v>34</v>
+      </c>
+      <c r="AJ86" s="40">
+        <v>2.1</v>
+      </c>
+      <c r="AK86" s="40">
+        <v>7.3</v>
+      </c>
+      <c r="AL86" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="AM86" s="40">
+        <v>17.7</v>
+      </c>
+      <c r="AN86" s="40">
+        <v>4.3</v>
+      </c>
+      <c r="AO86" s="40">
+        <v>196.3</v>
+      </c>
       <c r="AP86" s="40"/>
       <c r="AQ86" s="41">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>0.496</v>
       </c>
       <c r="AR86" s="41">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>8.1060907200000004E-2</v>
       </c>
       <c r="AS86" s="41">
         <f t="shared" si="74"/>
-        <v>-15.3</v>
+        <v>2.3999999999999986</v>
       </c>
       <c r="AT86" s="41">
         <f t="shared" si="75"/>
-        <v>-4.3</v>
+        <v>0</v>
       </c>
       <c r="AU86" s="41">
         <f t="shared" si="76"/>
@@ -19629,27 +19757,27 @@
       <c r="BD86" s="22"/>
       <c r="BE86" s="42">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>1.3510151200000003E-3</v>
       </c>
       <c r="BF86" s="42">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>1.9454617728000005</v>
       </c>
       <c r="BG86" s="42">
         <f t="shared" si="61"/>
-        <v>176</v>
-      </c>
-      <c r="BH86" s="43" t="str">
+        <v>196.3</v>
+      </c>
+      <c r="BH86" s="43">
         <f t="shared" si="62"/>
-        <v/>
-      </c>
-      <c r="BI86" s="43" t="str">
+        <v>9.0168110035659693E-2</v>
+      </c>
+      <c r="BI86" s="43">
         <f t="shared" si="63"/>
-        <v/>
+        <v>8.8499999999999995E-2</v>
       </c>
       <c r="BJ86" s="43">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>116.727706368</v>
       </c>
       <c r="BK86" s="43" t="str">
         <f t="shared" si="70"/>
@@ -19661,11 +19789,11 @@
       </c>
       <c r="BM86" s="44">
         <f t="shared" si="67"/>
-        <v>0</v>
+        <v>8.1060907200000004E-2</v>
       </c>
       <c r="BN86" s="43">
         <f t="shared" si="77"/>
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BO86" s="43" t="str">
         <f t="shared" si="65"/>
@@ -19673,15 +19801,15 @@
       </c>
       <c r="BP86" s="55">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>210.54781090909094</v>
       </c>
       <c r="BQ86" s="45">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>8.1060907200000004E-2</v>
       </c>
       <c r="BR86" s="24">
         <f t="shared" si="73"/>
-        <v>1.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:70" x14ac:dyDescent="0.3">
@@ -19748,11 +19876,11 @@
       </c>
       <c r="AS87" s="41">
         <f t="shared" si="74"/>
-        <v>-19.600000000000001</v>
+        <v>0</v>
       </c>
       <c r="AT87" s="41">
         <f t="shared" si="75"/>
-        <v>-4.5</v>
+        <v>0</v>
       </c>
       <c r="AU87" s="41">
         <f t="shared" si="76"/>
@@ -19852,47 +19980,111 @@
       <c r="E88">
         <v>9</v>
       </c>
-      <c r="G88" s="35"/>
+      <c r="G88" s="35">
+        <v>45577.327361111114</v>
+      </c>
       <c r="H88">
         <v>4805.7299999999996</v>
       </c>
       <c r="I88" s="48"/>
-      <c r="J88" s="72"/>
-      <c r="K88" s="40"/>
-      <c r="L88" s="40"/>
-      <c r="M88" s="40"/>
-      <c r="N88" s="40"/>
-      <c r="O88" s="40"/>
-      <c r="P88" s="40"/>
-      <c r="Q88" s="40"/>
-      <c r="R88" s="40"/>
+      <c r="J88" s="72">
+        <v>4869.1350000000002</v>
+      </c>
+      <c r="K88" s="40">
+        <v>21.117000000000001</v>
+      </c>
+      <c r="L88" s="40">
+        <v>18.507000000000001</v>
+      </c>
+      <c r="M88" s="40">
+        <v>87.6</v>
+      </c>
+      <c r="N88" s="40">
+        <v>16.71</v>
+      </c>
+      <c r="O88" s="40">
+        <v>347</v>
+      </c>
+      <c r="P88" s="40">
+        <v>1.46</v>
+      </c>
+      <c r="Q88" s="40">
+        <v>0.31</v>
+      </c>
+      <c r="R88" s="40">
+        <v>0.96</v>
+      </c>
       <c r="S88" s="40"/>
-      <c r="T88" s="40"/>
-      <c r="U88" s="40"/>
-      <c r="V88" s="40"/>
-      <c r="W88" s="40"/>
-      <c r="X88" s="40"/>
-      <c r="Y88" s="40"/>
-      <c r="Z88" s="40"/>
-      <c r="AA88" s="40"/>
-      <c r="AB88" s="40"/>
-      <c r="AC88" s="40"/>
-      <c r="AD88" s="40"/>
-      <c r="AE88" s="17"/>
-      <c r="AF88" s="40"/>
-      <c r="AG88" s="40"/>
-      <c r="AH88" s="40"/>
-      <c r="AI88" s="40"/>
-      <c r="AJ88" s="40"/>
-      <c r="AK88" s="40"/>
-      <c r="AL88" s="40"/>
-      <c r="AM88" s="40"/>
-      <c r="AN88" s="40"/>
-      <c r="AO88" s="40"/>
+      <c r="T88" s="40">
+        <v>0.25</v>
+      </c>
+      <c r="U88" s="40">
+        <v>0.18</v>
+      </c>
+      <c r="V88" s="40">
+        <v>1.93</v>
+      </c>
+      <c r="W88" s="40">
+        <v>7.3049999999999997</v>
+      </c>
+      <c r="X88" s="40">
+        <v>37</v>
+      </c>
+      <c r="Y88" s="40">
+        <v>54.3</v>
+      </c>
+      <c r="Z88" s="40">
+        <v>1.67</v>
+      </c>
+      <c r="AA88" s="40">
+        <v>152.6</v>
+      </c>
+      <c r="AB88" s="40">
+        <v>16.3</v>
+      </c>
+      <c r="AC88" s="40">
+        <v>32.4</v>
+      </c>
+      <c r="AD88" s="40">
+        <v>44.1</v>
+      </c>
+      <c r="AE88" s="17">
+        <v>7.2640000000000002</v>
+      </c>
+      <c r="AF88" s="40">
+        <v>409</v>
+      </c>
+      <c r="AG88" s="40">
+        <v>49.8</v>
+      </c>
+      <c r="AH88" s="40">
+        <v>7.3040000000000003</v>
+      </c>
+      <c r="AI88" s="40">
+        <v>34</v>
+      </c>
+      <c r="AJ88" s="40">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AK88" s="40">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="AL88" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="AM88" s="40">
+        <v>23.1</v>
+      </c>
+      <c r="AN88" s="40">
+        <v>5</v>
+      </c>
+      <c r="AO88" s="40">
+        <v>200.2</v>
+      </c>
       <c r="AP88" s="40"/>
       <c r="AQ88" s="41">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>0.498</v>
       </c>
       <c r="AR88" s="41">
         <f t="shared" si="68"/>
@@ -19900,11 +20092,11 @@
       </c>
       <c r="AS88" s="41">
         <f t="shared" si="74"/>
-        <v>-20.6</v>
+        <v>2.5</v>
       </c>
       <c r="AT88" s="41">
         <f t="shared" si="75"/>
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="AU88" s="41">
         <f t="shared" si="76"/>
@@ -19932,23 +20124,23 @@
       <c r="BD88" s="22"/>
       <c r="BE88" s="42">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>1.4820405600000002E-3</v>
       </c>
       <c r="BF88" s="42">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>2.1341384064000004</v>
       </c>
       <c r="BG88" s="42">
         <f t="shared" si="61"/>
-        <v>176</v>
-      </c>
-      <c r="BH88" s="43" t="str">
+        <v>200.2</v>
+      </c>
+      <c r="BH88" s="43">
         <f t="shared" si="62"/>
-        <v/>
-      </c>
-      <c r="BI88" s="43" t="str">
+        <v>0.1153846153846154</v>
+      </c>
+      <c r="BI88" s="43">
         <f t="shared" si="63"/>
-        <v/>
+        <v>0.11550000000000001</v>
       </c>
       <c r="BJ88" s="43">
         <f t="shared" si="64"/>
@@ -19968,7 +20160,7 @@
       </c>
       <c r="BN88" s="43">
         <f t="shared" si="77"/>
-        <v>1.32</v>
+        <v>1.0210199999999998</v>
       </c>
       <c r="BO88" s="43" t="str">
         <f t="shared" si="65"/>
@@ -19984,7 +20176,7 @@
       </c>
       <c r="BR88" s="24">
         <f t="shared" si="73"/>
-        <v>1.32</v>
+        <v>1.0210199999999998</v>
       </c>
     </row>
     <row r="89" spans="1:70" x14ac:dyDescent="0.3">
@@ -20003,47 +20195,111 @@
       <c r="E89">
         <v>9</v>
       </c>
-      <c r="G89" s="35"/>
+      <c r="G89" s="35">
+        <v>45577.328217592592</v>
+      </c>
       <c r="H89">
         <v>4805.7299999999996</v>
       </c>
       <c r="I89" s="48"/>
-      <c r="J89" s="72"/>
-      <c r="K89" s="40"/>
-      <c r="L89" s="40"/>
-      <c r="M89" s="40"/>
-      <c r="N89" s="40"/>
-      <c r="O89" s="40"/>
-      <c r="P89" s="40"/>
-      <c r="Q89" s="40"/>
-      <c r="R89" s="40"/>
+      <c r="J89" s="72">
+        <v>5030.49</v>
+      </c>
+      <c r="K89" s="40">
+        <v>21.672000000000001</v>
+      </c>
+      <c r="L89" s="40">
+        <v>18.122</v>
+      </c>
+      <c r="M89" s="40">
+        <v>83.6</v>
+      </c>
+      <c r="N89" s="40">
+        <v>16.41</v>
+      </c>
+      <c r="O89" s="40">
+        <v>351</v>
+      </c>
+      <c r="P89" s="40">
+        <v>1.61</v>
+      </c>
+      <c r="Q89" s="40">
+        <v>0.32</v>
+      </c>
+      <c r="R89" s="40">
+        <v>0.65</v>
+      </c>
       <c r="S89" s="40"/>
-      <c r="T89" s="40"/>
-      <c r="U89" s="40"/>
-      <c r="V89" s="40"/>
-      <c r="W89" s="40"/>
-      <c r="X89" s="40"/>
-      <c r="Y89" s="40"/>
-      <c r="Z89" s="40"/>
-      <c r="AA89" s="40"/>
-      <c r="AB89" s="40"/>
-      <c r="AC89" s="40"/>
-      <c r="AD89" s="40"/>
-      <c r="AE89" s="17"/>
-      <c r="AF89" s="40"/>
-      <c r="AG89" s="40"/>
-      <c r="AH89" s="40"/>
-      <c r="AI89" s="40"/>
-      <c r="AJ89" s="40"/>
-      <c r="AK89" s="40"/>
-      <c r="AL89" s="40"/>
-      <c r="AM89" s="40"/>
-      <c r="AN89" s="40"/>
-      <c r="AO89" s="40"/>
+      <c r="T89" s="40">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="U89" s="40">
+        <v>0.39</v>
+      </c>
+      <c r="V89" s="40">
+        <v>1.93</v>
+      </c>
+      <c r="W89" s="40">
+        <v>7.31</v>
+      </c>
+      <c r="X89" s="40">
+        <v>30.3</v>
+      </c>
+      <c r="Y89" s="40">
+        <v>48.2</v>
+      </c>
+      <c r="Z89" s="40">
+        <v>1.87</v>
+      </c>
+      <c r="AA89" s="40">
+        <v>156.1</v>
+      </c>
+      <c r="AB89" s="40">
+        <v>13.5</v>
+      </c>
+      <c r="AC89" s="40">
+        <v>26.6</v>
+      </c>
+      <c r="AD89" s="40">
+        <v>39</v>
+      </c>
+      <c r="AE89" s="17">
+        <v>7.2679999999999998</v>
+      </c>
+      <c r="AF89" s="40">
+        <v>406</v>
+      </c>
+      <c r="AG89" s="40">
+        <v>50.4</v>
+      </c>
+      <c r="AH89" s="40">
+        <v>7.3019999999999996</v>
+      </c>
+      <c r="AI89" s="40">
+        <v>34</v>
+      </c>
+      <c r="AJ89" s="40">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AK89" s="40">
+        <v>3.6</v>
+      </c>
+      <c r="AL89" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="AM89" s="40">
+        <v>25.1</v>
+      </c>
+      <c r="AN89" s="40">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="AO89" s="40">
+        <v>198.5</v>
+      </c>
       <c r="AP89" s="40"/>
       <c r="AQ89" s="41">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>0.504</v>
       </c>
       <c r="AR89" s="41">
         <f t="shared" si="68"/>
@@ -20051,11 +20307,11 @@
       </c>
       <c r="AS89" s="41">
         <f t="shared" si="74"/>
-        <v>-22.1</v>
+        <v>3</v>
       </c>
       <c r="AT89" s="41">
         <f t="shared" si="75"/>
-        <v>-4.5999999999999996</v>
+        <v>0.30000000000000071</v>
       </c>
       <c r="AU89" s="41">
         <f t="shared" si="76"/>
@@ -20083,23 +20339,23 @@
       <c r="BD89" s="22"/>
       <c r="BE89" s="42">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>1.4388868000000002E-3</v>
       </c>
       <c r="BF89" s="42">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>2.0719969919999999</v>
       </c>
       <c r="BG89" s="42">
         <f t="shared" si="61"/>
-        <v>176</v>
-      </c>
-      <c r="BH89" s="43" t="str">
+        <v>198.5</v>
+      </c>
+      <c r="BH89" s="43">
         <f t="shared" si="62"/>
-        <v/>
-      </c>
-      <c r="BI89" s="43" t="str">
+        <v>0.12644836272040302</v>
+      </c>
+      <c r="BI89" s="43">
         <f t="shared" si="63"/>
-        <v/>
+        <v>0.1255</v>
       </c>
       <c r="BJ89" s="43">
         <f t="shared" si="64"/>
@@ -20154,47 +20410,111 @@
       <c r="E90">
         <v>9</v>
       </c>
-      <c r="G90" s="35"/>
+      <c r="G90" s="35">
+        <v>45577.329062500001</v>
+      </c>
       <c r="H90">
         <v>4805.7299999999996</v>
       </c>
       <c r="I90" s="48"/>
-      <c r="J90" s="72"/>
-      <c r="K90" s="40"/>
-      <c r="L90" s="40"/>
-      <c r="M90" s="40"/>
-      <c r="N90" s="40"/>
-      <c r="O90" s="40"/>
-      <c r="P90" s="40"/>
-      <c r="Q90" s="40"/>
-      <c r="R90" s="40"/>
+      <c r="J90" s="72">
+        <v>5038.74</v>
+      </c>
+      <c r="K90" s="40">
+        <v>22.402000000000001</v>
+      </c>
+      <c r="L90" s="40">
+        <v>19.074000000000002</v>
+      </c>
+      <c r="M90" s="40">
+        <v>85.1</v>
+      </c>
+      <c r="N90" s="40">
+        <v>16.46</v>
+      </c>
+      <c r="O90" s="40">
+        <v>350</v>
+      </c>
+      <c r="P90" s="40">
+        <v>1.57</v>
+      </c>
+      <c r="Q90" s="40">
+        <v>0.31</v>
+      </c>
+      <c r="R90" s="40">
+        <v>0.67</v>
+      </c>
       <c r="S90" s="40"/>
-      <c r="T90" s="40"/>
-      <c r="U90" s="40"/>
-      <c r="V90" s="40"/>
-      <c r="W90" s="40"/>
-      <c r="X90" s="40"/>
-      <c r="Y90" s="40"/>
-      <c r="Z90" s="40"/>
-      <c r="AA90" s="40"/>
-      <c r="AB90" s="40"/>
-      <c r="AC90" s="40"/>
-      <c r="AD90" s="40"/>
-      <c r="AE90" s="17"/>
-      <c r="AF90" s="40"/>
-      <c r="AG90" s="40"/>
-      <c r="AH90" s="40"/>
-      <c r="AI90" s="40"/>
-      <c r="AJ90" s="40"/>
-      <c r="AK90" s="40"/>
-      <c r="AL90" s="40"/>
-      <c r="AM90" s="40"/>
-      <c r="AN90" s="40"/>
-      <c r="AO90" s="40"/>
+      <c r="T90" s="40">
+        <v>0.27</v>
+      </c>
+      <c r="U90" s="40">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="V90" s="40">
+        <v>1.78</v>
+      </c>
+      <c r="W90" s="40">
+        <v>7.3040000000000003</v>
+      </c>
+      <c r="X90" s="40">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="Y90" s="40">
+        <v>42.8</v>
+      </c>
+      <c r="Z90" s="40">
+        <v>1.76</v>
+      </c>
+      <c r="AA90" s="40">
+        <v>154.6</v>
+      </c>
+      <c r="AB90" s="40">
+        <v>15.5</v>
+      </c>
+      <c r="AC90" s="40">
+        <v>31</v>
+      </c>
+      <c r="AD90" s="40">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="AE90" s="17">
+        <v>7.2629999999999999</v>
+      </c>
+      <c r="AF90" s="40">
+        <v>406</v>
+      </c>
+      <c r="AG90" s="40">
+        <v>49.3</v>
+      </c>
+      <c r="AH90" s="40">
+        <v>7.3029999999999999</v>
+      </c>
+      <c r="AI90" s="40">
+        <v>34</v>
+      </c>
+      <c r="AJ90" s="40">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AK90" s="40">
+        <v>3.9</v>
+      </c>
+      <c r="AL90" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="AM90" s="40">
+        <v>25</v>
+      </c>
+      <c r="AN90" s="40">
+        <v>5.2</v>
+      </c>
+      <c r="AO90" s="40">
+        <v>200.1</v>
+      </c>
       <c r="AP90" s="40"/>
       <c r="AQ90" s="41">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>0.49299999999999999</v>
       </c>
       <c r="AR90" s="41">
         <f t="shared" si="68"/>
@@ -20202,11 +20522,11 @@
       </c>
       <c r="AS90" s="41">
         <f t="shared" si="74"/>
-        <v>-22</v>
+        <v>3</v>
       </c>
       <c r="AT90" s="41">
         <f t="shared" si="75"/>
-        <v>-4.9000000000000004</v>
+        <v>0.29999999999999982</v>
       </c>
       <c r="AU90" s="41">
         <f t="shared" si="76"/>
@@ -20234,23 +20554,23 @@
       <c r="BD90" s="22"/>
       <c r="BE90" s="42">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>1.5266829600000002E-3</v>
       </c>
       <c r="BF90" s="42">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>2.1984234624000001</v>
       </c>
       <c r="BG90" s="42">
         <f t="shared" si="61"/>
-        <v>176</v>
-      </c>
-      <c r="BH90" s="43" t="str">
+        <v>200.1</v>
+      </c>
+      <c r="BH90" s="43">
         <f t="shared" si="62"/>
-        <v/>
-      </c>
-      <c r="BI90" s="43" t="str">
+        <v>0.12493753123438281</v>
+      </c>
+      <c r="BI90" s="43">
         <f t="shared" si="63"/>
-        <v/>
+        <v>0.125</v>
       </c>
       <c r="BJ90" s="43">
         <f t="shared" si="64"/>
@@ -20305,59 +20625,123 @@
       <c r="E91">
         <v>9</v>
       </c>
-      <c r="G91" s="35"/>
+      <c r="G91" s="35">
+        <v>45577.329918981479</v>
+      </c>
       <c r="H91">
         <v>4805.7299999999996</v>
       </c>
       <c r="I91" s="48"/>
-      <c r="J91" s="72"/>
-      <c r="K91" s="40"/>
-      <c r="L91" s="40"/>
-      <c r="M91" s="40"/>
-      <c r="N91" s="40"/>
-      <c r="O91" s="40"/>
-      <c r="P91" s="40"/>
-      <c r="Q91" s="40"/>
-      <c r="R91" s="40"/>
+      <c r="J91" s="72">
+        <v>4396.6049999999996</v>
+      </c>
+      <c r="K91" s="40">
+        <v>19.827999999999999</v>
+      </c>
+      <c r="L91" s="40">
+        <v>17.614999999999998</v>
+      </c>
+      <c r="M91" s="40">
+        <v>88.8</v>
+      </c>
+      <c r="N91" s="40">
+        <v>16.71</v>
+      </c>
+      <c r="O91" s="40">
+        <v>351</v>
+      </c>
+      <c r="P91" s="40">
+        <v>1.34</v>
+      </c>
+      <c r="Q91" s="40">
+        <v>0.32</v>
+      </c>
+      <c r="R91" s="40">
+        <v>3.01</v>
+      </c>
       <c r="S91" s="40"/>
-      <c r="T91" s="40"/>
-      <c r="U91" s="40"/>
-      <c r="V91" s="40"/>
-      <c r="W91" s="40"/>
-      <c r="X91" s="40"/>
-      <c r="Y91" s="40"/>
-      <c r="Z91" s="40"/>
-      <c r="AA91" s="40"/>
-      <c r="AB91" s="40"/>
-      <c r="AC91" s="40"/>
-      <c r="AD91" s="40"/>
-      <c r="AE91" s="17"/>
-      <c r="AF91" s="40"/>
-      <c r="AG91" s="40"/>
-      <c r="AH91" s="40"/>
-      <c r="AI91" s="40"/>
-      <c r="AJ91" s="40"/>
-      <c r="AK91" s="40"/>
-      <c r="AL91" s="40"/>
-      <c r="AM91" s="40"/>
-      <c r="AN91" s="40"/>
-      <c r="AO91" s="40"/>
+      <c r="T91" s="40">
+        <v>0.25</v>
+      </c>
+      <c r="U91" s="40">
+        <v>0.15</v>
+      </c>
+      <c r="V91" s="40">
+        <v>2.31</v>
+      </c>
+      <c r="W91" s="40">
+        <v>7.2990000000000004</v>
+      </c>
+      <c r="X91" s="40">
+        <v>51.3</v>
+      </c>
+      <c r="Y91" s="40">
+        <v>57</v>
+      </c>
+      <c r="Z91" s="40">
+        <v>1.99</v>
+      </c>
+      <c r="AA91" s="40">
+        <v>150.1</v>
+      </c>
+      <c r="AB91" s="40">
+        <v>22.2</v>
+      </c>
+      <c r="AC91" s="40">
+        <v>45</v>
+      </c>
+      <c r="AD91" s="40">
+        <v>46.2</v>
+      </c>
+      <c r="AE91" s="17">
+        <v>7.2569999999999997</v>
+      </c>
+      <c r="AF91" s="40">
+        <v>634</v>
+      </c>
+      <c r="AG91" s="40">
+        <v>44.9</v>
+      </c>
+      <c r="AH91" s="40">
+        <v>7.3029999999999999</v>
+      </c>
+      <c r="AI91" s="40">
+        <v>34</v>
+      </c>
+      <c r="AJ91" s="40">
+        <v>2.6</v>
+      </c>
+      <c r="AK91" s="40">
+        <v>7.7</v>
+      </c>
+      <c r="AL91" s="40">
+        <v>0.2</v>
+      </c>
+      <c r="AM91" s="40">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="AN91" s="40">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AO91" s="40">
+        <v>199.3</v>
+      </c>
       <c r="AP91" s="40"/>
       <c r="AQ91" s="41">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>0.44900000000000001</v>
       </c>
       <c r="AR91" s="41">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>8.4256068000000003E-2</v>
       </c>
       <c r="AS91" s="41">
         <f t="shared" si="74"/>
-        <v>-14.4</v>
+        <v>2.7000000000000011</v>
       </c>
       <c r="AT91" s="41">
         <f t="shared" si="75"/>
-        <v>-4.4000000000000004</v>
+        <v>0</v>
       </c>
       <c r="AU91" s="41">
         <f t="shared" si="76"/>
@@ -20385,27 +20769,27 @@
       <c r="BD91" s="22"/>
       <c r="BE91" s="42">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>1.4042677999999999E-3</v>
       </c>
       <c r="BF91" s="42">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>2.022145632</v>
       </c>
       <c r="BG91" s="42">
         <f t="shared" si="61"/>
-        <v>176</v>
-      </c>
-      <c r="BH91" s="43" t="str">
+        <v>199.3</v>
+      </c>
+      <c r="BH91" s="43">
         <f t="shared" si="62"/>
-        <v/>
-      </c>
-      <c r="BI91" s="43" t="str">
+        <v>8.5800301053687911E-2</v>
+      </c>
+      <c r="BI91" s="43">
         <f t="shared" si="63"/>
-        <v/>
+        <v>8.5500000000000007E-2</v>
       </c>
       <c r="BJ91" s="43">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>121.32873791999999</v>
       </c>
       <c r="BK91" s="43" t="str">
         <f t="shared" si="70"/>
@@ -20417,11 +20801,11 @@
       </c>
       <c r="BM91" s="44">
         <f t="shared" si="67"/>
-        <v>0</v>
+        <v>8.4256068000000003E-2</v>
       </c>
       <c r="BN91" s="43">
         <f t="shared" si="77"/>
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BO91" s="43" t="str">
         <f t="shared" si="65"/>
@@ -20429,15 +20813,15 @@
       </c>
       <c r="BP91" s="55">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>218.84692987012988</v>
       </c>
       <c r="BQ91" s="45">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>8.4256068000000003E-2</v>
       </c>
       <c r="BR91" s="24">
         <f t="shared" si="73"/>
-        <v>1.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:70" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -20456,59 +20840,121 @@
       <c r="E92">
         <v>9</v>
       </c>
-      <c r="G92" s="35"/>
+      <c r="G92" s="35">
+        <v>45577.333067129628</v>
+      </c>
       <c r="H92">
         <v>4805.7299999999996</v>
       </c>
       <c r="I92" s="48"/>
       <c r="J92" s="72"/>
-      <c r="K92" s="40"/>
-      <c r="L92" s="40"/>
-      <c r="M92" s="40"/>
-      <c r="N92" s="40"/>
-      <c r="O92" s="40"/>
-      <c r="P92" s="40"/>
-      <c r="Q92" s="40"/>
-      <c r="R92" s="40"/>
+      <c r="K92" s="40">
+        <v>20.274000000000001</v>
+      </c>
+      <c r="L92" s="40">
+        <v>18.190000000000001</v>
+      </c>
+      <c r="M92" s="40">
+        <v>89.7</v>
+      </c>
+      <c r="N92" s="40">
+        <v>16.41</v>
+      </c>
+      <c r="O92" s="40">
+        <v>343</v>
+      </c>
+      <c r="P92" s="40">
+        <v>1.38</v>
+      </c>
+      <c r="Q92" s="40">
+        <v>0.31</v>
+      </c>
+      <c r="R92" s="40">
+        <v>2.62</v>
+      </c>
       <c r="S92" s="40"/>
-      <c r="T92" s="40"/>
-      <c r="U92" s="40"/>
-      <c r="V92" s="40"/>
-      <c r="W92" s="40"/>
-      <c r="X92" s="40"/>
-      <c r="Y92" s="40"/>
-      <c r="Z92" s="40"/>
-      <c r="AA92" s="40"/>
-      <c r="AB92" s="40"/>
-      <c r="AC92" s="40"/>
-      <c r="AD92" s="40"/>
-      <c r="AE92" s="17"/>
-      <c r="AF92" s="40"/>
-      <c r="AG92" s="40"/>
-      <c r="AH92" s="40"/>
-      <c r="AI92" s="40"/>
-      <c r="AJ92" s="40"/>
-      <c r="AK92" s="40"/>
-      <c r="AL92" s="40"/>
-      <c r="AM92" s="40"/>
-      <c r="AN92" s="40"/>
-      <c r="AO92" s="40"/>
+      <c r="T92" s="40">
+        <v>0.21</v>
+      </c>
+      <c r="U92" s="40">
+        <v>0.16</v>
+      </c>
+      <c r="V92" s="40">
+        <v>1.97</v>
+      </c>
+      <c r="W92" s="40">
+        <v>7.3010000000000002</v>
+      </c>
+      <c r="X92" s="40">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="Y92" s="40">
+        <v>59.8</v>
+      </c>
+      <c r="Z92" s="40">
+        <v>2.19</v>
+      </c>
+      <c r="AA92" s="40">
+        <v>144.5</v>
+      </c>
+      <c r="AB92" s="40">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="AC92" s="40">
+        <v>34.4</v>
+      </c>
+      <c r="AD92" s="40">
+        <v>48.5</v>
+      </c>
+      <c r="AE92" s="17">
+        <v>7.2590000000000003</v>
+      </c>
+      <c r="AF92" s="40">
+        <v>424</v>
+      </c>
+      <c r="AG92" s="40">
+        <v>49.6</v>
+      </c>
+      <c r="AH92" s="40">
+        <v>7.306</v>
+      </c>
+      <c r="AI92" s="40">
+        <v>34</v>
+      </c>
+      <c r="AJ92" s="40">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AK92" s="40">
+        <v>7.9</v>
+      </c>
+      <c r="AL92" s="40">
+        <v>0.2</v>
+      </c>
+      <c r="AM92" s="40">
+        <v>16.7</v>
+      </c>
+      <c r="AN92" s="40">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AO92" s="40">
+        <v>197.3</v>
+      </c>
       <c r="AP92" s="7"/>
       <c r="AQ92" s="41">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>0.496</v>
       </c>
       <c r="AR92" s="41">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>8.6133288000000016E-2</v>
       </c>
       <c r="AS92" s="41">
         <f t="shared" si="74"/>
-        <v>-14.6</v>
+        <v>2.0999999999999996</v>
       </c>
       <c r="AT92" s="41">
         <f t="shared" si="75"/>
-        <v>-4.4000000000000004</v>
+        <v>0</v>
       </c>
       <c r="AU92" s="41">
         <f t="shared" si="76"/>
@@ -20536,27 +20982,27 @@
       <c r="BD92" s="22"/>
       <c r="BE92" s="42">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>1.4355548000000002E-3</v>
       </c>
       <c r="BF92" s="42">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>2.0671989120000003</v>
       </c>
       <c r="BG92" s="42">
         <f t="shared" si="61"/>
-        <v>176</v>
-      </c>
-      <c r="BH92" s="43" t="str">
+        <v>197.3</v>
+      </c>
+      <c r="BH92" s="43">
         <f t="shared" si="62"/>
-        <v/>
-      </c>
-      <c r="BI92" s="43" t="str">
+        <v>8.4642676127724276E-2</v>
+      </c>
+      <c r="BI92" s="43">
         <f t="shared" si="63"/>
-        <v/>
+        <v>8.3499999999999991E-2</v>
       </c>
       <c r="BJ92" s="43">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>124.03193472000001</v>
       </c>
       <c r="BK92" s="43" t="str">
         <f t="shared" si="70"/>
@@ -20568,11 +21014,11 @@
       </c>
       <c r="BM92" s="44">
         <f t="shared" si="67"/>
-        <v>0</v>
+        <v>8.6133288000000016E-2</v>
       </c>
       <c r="BN92" s="43">
         <f t="shared" si="77"/>
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BO92" s="43" t="str">
         <f t="shared" si="65"/>
@@ -20580,15 +21026,15 @@
       </c>
       <c r="BP92" s="55">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>223.72282597402602</v>
       </c>
       <c r="BQ92" s="45">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>8.6133288000000016E-2</v>
       </c>
       <c r="BR92" s="24">
         <f t="shared" si="73"/>
-        <v>1.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:70" x14ac:dyDescent="0.3">
@@ -20613,7 +21059,7 @@
         <v>5497.99</v>
       </c>
       <c r="I93" s="37"/>
-      <c r="J93" s="91"/>
+      <c r="J93" s="77"/>
       <c r="K93" s="6"/>
       <c r="L93" s="6"/>
       <c r="M93" s="6"/>
@@ -20808,11 +21254,11 @@
       </c>
       <c r="AS94" s="41">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>-17.7</v>
       </c>
       <c r="AT94" s="41">
         <f t="shared" si="75"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AU94" s="41">
         <f t="shared" si="76"/>
@@ -20960,11 +21406,11 @@
       </c>
       <c r="AS95" s="41">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>-17.7</v>
       </c>
       <c r="AT95" s="41">
         <f t="shared" si="75"/>
-        <v>0</v>
+        <v>-4.3</v>
       </c>
       <c r="AU95" s="41">
         <f t="shared" si="76"/>
@@ -21264,11 +21710,11 @@
       </c>
       <c r="AS97" s="41">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>-23.1</v>
       </c>
       <c r="AT97" s="41">
         <f t="shared" si="75"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AU97" s="41">
         <f t="shared" si="76"/>
@@ -21415,11 +21861,11 @@
       </c>
       <c r="AS98" s="41">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>-25.1</v>
       </c>
       <c r="AT98" s="41">
         <f t="shared" si="75"/>
-        <v>0</v>
+        <v>-4.9000000000000004</v>
       </c>
       <c r="AU98" s="41">
         <f t="shared" si="76"/>
@@ -21566,11 +22012,11 @@
       </c>
       <c r="AS99" s="41">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="AT99" s="41">
         <f t="shared" si="75"/>
-        <v>0</v>
+        <v>-5.2</v>
       </c>
       <c r="AU99" s="41">
         <f t="shared" si="76"/>
@@ -21717,11 +22163,11 @@
       </c>
       <c r="AS100" s="41">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>-17.100000000000001</v>
       </c>
       <c r="AT100" s="41">
         <f t="shared" si="75"/>
-        <v>0</v>
+        <v>-4.4000000000000004</v>
       </c>
       <c r="AU100" s="41">
         <f t="shared" si="76"/>
@@ -21868,11 +22314,11 @@
       </c>
       <c r="AS101" s="41">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>-16.7</v>
       </c>
       <c r="AT101" s="41">
         <f t="shared" si="75"/>
-        <v>0</v>
+        <v>-4.4000000000000004</v>
       </c>
       <c r="AU101" s="41">
         <f t="shared" si="76"/>
@@ -21977,7 +22423,7 @@
         <v>6057.48</v>
       </c>
       <c r="I102" s="3"/>
-      <c r="J102" s="92"/>
+      <c r="J102" s="78"/>
       <c r="K102" s="3"/>
       <c r="L102" s="3"/>
       <c r="M102" s="3"/>
@@ -22128,7 +22574,7 @@
       <c r="H103" s="48">
         <v>6057.48</v>
       </c>
-      <c r="J103" s="93"/>
+      <c r="J103" s="79"/>
       <c r="AE103" s="54"/>
       <c r="AP103" s="40"/>
       <c r="AQ103" s="41">
@@ -22249,7 +22695,7 @@
       <c r="H104" s="48">
         <v>6057.48</v>
       </c>
-      <c r="J104" s="93"/>
+      <c r="J104" s="79"/>
       <c r="T104" s="56"/>
       <c r="AE104" s="54"/>
       <c r="AP104" s="40"/>
@@ -22371,7 +22817,7 @@
       <c r="H105" s="48">
         <v>6057.48</v>
       </c>
-      <c r="J105" s="93"/>
+      <c r="J105" s="79"/>
       <c r="AE105" s="54"/>
       <c r="AP105" s="40"/>
       <c r="AQ105" s="41">
@@ -22492,7 +22938,7 @@
       <c r="H106" s="48">
         <v>6057.48</v>
       </c>
-      <c r="J106" s="93"/>
+      <c r="J106" s="79"/>
       <c r="AE106" s="54"/>
       <c r="AP106" s="40"/>
       <c r="AQ106" s="41">
@@ -22612,7 +23058,7 @@
       <c r="H107" s="48">
         <v>6057.48</v>
       </c>
-      <c r="J107" s="93"/>
+      <c r="J107" s="79"/>
       <c r="AC107" s="57"/>
       <c r="AE107" s="54"/>
       <c r="AP107" s="40"/>
@@ -22733,7 +23179,7 @@
       <c r="H108" s="48">
         <v>6057.48</v>
       </c>
-      <c r="J108" s="93"/>
+      <c r="J108" s="79"/>
       <c r="AC108" s="57"/>
       <c r="AE108" s="54"/>
       <c r="AP108" s="40"/>
@@ -22854,7 +23300,7 @@
       <c r="H109" s="48">
         <v>6057.48</v>
       </c>
-      <c r="J109" s="93"/>
+      <c r="J109" s="79"/>
       <c r="AE109" s="54"/>
       <c r="AP109" s="40"/>
       <c r="AQ109" s="41">
@@ -22974,7 +23420,7 @@
       <c r="H110" s="48">
         <v>6057.48</v>
       </c>
-      <c r="J110" s="93"/>
+      <c r="J110" s="79"/>
       <c r="AE110" s="54"/>
       <c r="AP110" s="7"/>
       <c r="AQ110" s="41">
@@ -23096,7 +23542,7 @@
         <v>6478.05</v>
       </c>
       <c r="I111" s="3"/>
-      <c r="J111" s="92"/>
+      <c r="J111" s="78"/>
       <c r="K111" s="3"/>
       <c r="L111" s="3"/>
       <c r="M111" s="3"/>
@@ -23247,7 +23693,7 @@
       <c r="H112" s="48">
         <v>6478.05</v>
       </c>
-      <c r="J112" s="93"/>
+      <c r="J112" s="79"/>
       <c r="AE112" s="54"/>
       <c r="AP112" s="40"/>
       <c r="AQ112" s="41">
@@ -23368,7 +23814,7 @@
       <c r="H113" s="48">
         <v>6478.05</v>
       </c>
-      <c r="J113" s="93"/>
+      <c r="J113" s="79"/>
       <c r="AE113" s="54"/>
       <c r="AP113" s="40"/>
       <c r="AQ113" s="41">
@@ -23489,7 +23935,7 @@
       <c r="H114" s="48">
         <v>6478.05</v>
       </c>
-      <c r="J114" s="93"/>
+      <c r="J114" s="79"/>
       <c r="AE114" s="54"/>
       <c r="AP114" s="40"/>
       <c r="AQ114" s="41">
@@ -23610,7 +24056,7 @@
       <c r="H115" s="48">
         <v>6478.05</v>
       </c>
-      <c r="J115" s="93"/>
+      <c r="J115" s="79"/>
       <c r="AE115" s="54"/>
       <c r="AP115" s="40"/>
       <c r="AQ115" s="41">
@@ -23730,7 +24176,7 @@
       <c r="H116" s="48">
         <v>6478.05</v>
       </c>
-      <c r="J116" s="93"/>
+      <c r="J116" s="79"/>
       <c r="AE116" s="54"/>
       <c r="AP116" s="40"/>
       <c r="AQ116" s="41">
@@ -23850,7 +24296,7 @@
       <c r="H117" s="48">
         <v>6478.05</v>
       </c>
-      <c r="J117" s="93"/>
+      <c r="J117" s="79"/>
       <c r="AE117" s="54"/>
       <c r="AP117" s="40"/>
       <c r="AQ117" s="41">
@@ -23970,7 +24416,7 @@
       <c r="H118" s="48">
         <v>6478.05</v>
       </c>
-      <c r="J118" s="93"/>
+      <c r="J118" s="79"/>
       <c r="AE118" s="54"/>
       <c r="AP118" s="40"/>
       <c r="AQ118" s="41">
@@ -24092,7 +24538,7 @@
         <v>6478.05</v>
       </c>
       <c r="I119" s="5"/>
-      <c r="J119" s="94"/>
+      <c r="J119" s="80"/>
       <c r="K119" s="5"/>
       <c r="L119" s="5"/>
       <c r="M119" s="5"/>
@@ -24277,6 +24723,33 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="34d8c884-fe7e-4d4f-a833-b92a2823f74b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SharedWithUsers xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B75172DAFC2BB6479729CB287362C7E3" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0fc11b0946794a47057850b4f6c92dd7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="34d8c884-fe7e-4d4f-a833-b92a2823f74b" xmlns:ns3="a198008e-c7f6-4ed0-9865-26ace3c97b59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fb90ec7fe59ed1d44226abab88cd233b" ns2:_="" ns3:_="">
     <xsd:import namespace="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
@@ -24499,34 +24972,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="34d8c884-fe7e-4d4f-a833-b92a2823f74b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <SharedWithUsers xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F43DC28-AE43-4EFF-8739-4E0C557B415B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -24543,29 +25014,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/ar24-072-experiment/AR24-072-SAM-MasterDataTable.xlsx
+++ b/data/ar24-072-experiment/AR24-072-SAM-MasterDataTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myteams.gsk.com/sites/BiopharmModelPredictiveControl/Shared Documents/General/data/AR24-072-SAM-MPC-1kL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2799" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BC9C39A-EF58-429A-A5B1-4F41E22B258F}"/>
+  <xr:revisionPtr revIDLastSave="2902" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49A85049-4F3F-4BC2-A395-E25782361501}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="95">
   <si>
     <t>Batch Data</t>
   </si>
@@ -322,16 +322,18 @@
   <si>
     <t>Contaminated</t>
   </si>
+  <si>
+    <t>Kepware error. Blc action had to be restarted</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.00000"/>
-    <numFmt numFmtId="167" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
   <fonts count="27" x14ac:knownFonts="1">
@@ -536,7 +538,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="42">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -761,12 +763,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1121,7 +1117,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="37" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="37" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="37" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -1143,9 +1138,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="22" fontId="0" fillId="41" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="41" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="41" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="26" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1204,6 +1196,10 @@
     <xf numFmtId="0" fontId="19" fillId="34" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="26" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1320,6 +1316,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1623,11 +1623,13 @@
   <dimension ref="A1:BR119"/>
   <sheetFormatPr defaultColWidth="14.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.6640625" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" customWidth="1"/>
-    <col min="3" max="5" width="10.6640625" customWidth="1"/>
-    <col min="6" max="6" width="28.33203125" customWidth="1"/>
-    <col min="7" max="7" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" customWidth="1"/>
+    <col min="4" max="4" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.77734375" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="19" width="12.6640625" customWidth="1"/>
     <col min="20" max="20" width="15.109375" customWidth="1"/>
     <col min="21" max="21" width="16.109375" customWidth="1"/>
@@ -1642,90 +1644,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:70" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="98" t="s">
+      <c r="A1" s="93" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
+      <c r="H1" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="98"/>
-      <c r="J1" s="98"/>
-      <c r="K1" s="98"/>
-      <c r="L1" s="98"/>
-      <c r="M1" s="98"/>
-      <c r="N1" s="98"/>
-      <c r="O1" s="98"/>
-      <c r="P1" s="98"/>
-      <c r="Q1" s="98"/>
-      <c r="R1" s="98"/>
-      <c r="S1" s="98"/>
-      <c r="T1" s="98"/>
-      <c r="U1" s="98"/>
-      <c r="V1" s="98"/>
-      <c r="W1" s="98"/>
-      <c r="X1" s="98"/>
-      <c r="Y1" s="98"/>
-      <c r="Z1" s="98"/>
-      <c r="AA1" s="98"/>
-      <c r="AB1" s="98"/>
-      <c r="AC1" s="98"/>
-      <c r="AD1" s="98"/>
-      <c r="AE1" s="98"/>
-      <c r="AF1" s="104" t="s">
+      <c r="I1" s="94"/>
+      <c r="J1" s="94"/>
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
+      <c r="M1" s="94"/>
+      <c r="N1" s="94"/>
+      <c r="O1" s="94"/>
+      <c r="P1" s="94"/>
+      <c r="Q1" s="94"/>
+      <c r="R1" s="94"/>
+      <c r="S1" s="94"/>
+      <c r="T1" s="94"/>
+      <c r="U1" s="94"/>
+      <c r="V1" s="94"/>
+      <c r="W1" s="94"/>
+      <c r="X1" s="94"/>
+      <c r="Y1" s="94"/>
+      <c r="Z1" s="94"/>
+      <c r="AA1" s="94"/>
+      <c r="AB1" s="94"/>
+      <c r="AC1" s="94"/>
+      <c r="AD1" s="94"/>
+      <c r="AE1" s="94"/>
+      <c r="AF1" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="AG1" s="105"/>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="105"/>
-      <c r="AV1" s="106"/>
-      <c r="AW1" s="99" t="s">
+      <c r="AG1" s="101"/>
+      <c r="AH1" s="101"/>
+      <c r="AI1" s="101"/>
+      <c r="AJ1" s="101"/>
+      <c r="AK1" s="101"/>
+      <c r="AL1" s="101"/>
+      <c r="AM1" s="101"/>
+      <c r="AN1" s="101"/>
+      <c r="AO1" s="101"/>
+      <c r="AP1" s="101"/>
+      <c r="AQ1" s="101"/>
+      <c r="AR1" s="101"/>
+      <c r="AS1" s="101"/>
+      <c r="AT1" s="101"/>
+      <c r="AU1" s="101"/>
+      <c r="AV1" s="102"/>
+      <c r="AW1" s="95" t="s">
         <v>3</v>
       </c>
-      <c r="AX1" s="100"/>
-      <c r="AY1" s="100"/>
-      <c r="AZ1" s="100"/>
-      <c r="BA1" s="101"/>
-      <c r="BB1" s="98" t="s">
+      <c r="AX1" s="96"/>
+      <c r="AY1" s="96"/>
+      <c r="AZ1" s="96"/>
+      <c r="BA1" s="97"/>
+      <c r="BB1" s="94" t="s">
         <v>4</v>
       </c>
-      <c r="BC1" s="102"/>
-      <c r="BD1" s="103"/>
-      <c r="BE1" s="95" t="s">
+      <c r="BC1" s="98"/>
+      <c r="BD1" s="99"/>
+      <c r="BE1" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="BF1" s="96"/>
-      <c r="BG1" s="96"/>
-      <c r="BH1" s="96"/>
-      <c r="BI1" s="96"/>
-      <c r="BJ1" s="96"/>
-      <c r="BK1" s="96"/>
-      <c r="BL1" s="96"/>
-      <c r="BM1" s="96"/>
-      <c r="BN1" s="96"/>
-      <c r="BO1" s="96"/>
-      <c r="BP1" s="96"/>
-      <c r="BQ1" s="93" t="s">
+      <c r="BF1" s="92"/>
+      <c r="BG1" s="92"/>
+      <c r="BH1" s="92"/>
+      <c r="BI1" s="92"/>
+      <c r="BJ1" s="92"/>
+      <c r="BK1" s="92"/>
+      <c r="BL1" s="92"/>
+      <c r="BM1" s="92"/>
+      <c r="BN1" s="92"/>
+      <c r="BO1" s="92"/>
+      <c r="BP1" s="92"/>
+      <c r="BQ1" s="89" t="s">
         <v>6</v>
       </c>
-      <c r="BR1" s="94"/>
+      <c r="BR1" s="90"/>
     </row>
     <row r="2" spans="1:70" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="20" t="s">
@@ -1932,10 +1934,10 @@
       <c r="BP2" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="BQ2" s="64" t="s">
+      <c r="BQ2" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="BR2" s="65" t="s">
+      <c r="BR2" s="64" t="s">
         <v>75</v>
       </c>
     </row>
@@ -2035,7 +2037,7 @@
       <c r="AU3" s="32">
         <v>0</v>
       </c>
-      <c r="AV3" s="66">
+      <c r="AV3" s="65">
         <v>60</v>
       </c>
       <c r="AW3" s="3">
@@ -2106,7 +2108,7 @@
         <f t="shared" ref="BO3:BO34" si="8">IF(C3="Julia",BD3*BG3,"")</f>
         <v>233.3070779</v>
       </c>
-      <c r="BP3" s="58">
+      <c r="BP3" s="57">
         <f>IF(BK3&lt;&gt;"",BK3/0.000385,IF(BL3&lt;&gt;"",BL3/0.000385,BM3/0.000385))</f>
         <v>445104.4948051949</v>
       </c>
@@ -2257,7 +2259,7 @@
       <c r="AU4" s="41">
         <v>0</v>
       </c>
-      <c r="AV4" s="63">
+      <c r="AV4" s="62">
         <v>2.4</v>
       </c>
       <c r="AW4">
@@ -2473,7 +2475,7 @@
       <c r="AU5" s="41">
         <v>0</v>
       </c>
-      <c r="AV5" s="63">
+      <c r="AV5" s="62">
         <v>2.4</v>
       </c>
       <c r="AW5">
@@ -2689,7 +2691,7 @@
       <c r="AU6" s="41">
         <v>0</v>
       </c>
-      <c r="AV6" s="63">
+      <c r="AV6" s="62">
         <v>2.4</v>
       </c>
       <c r="AW6">
@@ -2904,7 +2906,7 @@
       <c r="AU7" s="41">
         <v>0</v>
       </c>
-      <c r="AV7" s="63">
+      <c r="AV7" s="62">
         <v>2.4</v>
       </c>
       <c r="AW7">
@@ -3118,7 +3120,7 @@
       <c r="AU8" s="41">
         <v>0</v>
       </c>
-      <c r="AV8" s="63">
+      <c r="AV8" s="62">
         <v>2.4</v>
       </c>
       <c r="AW8">
@@ -3340,7 +3342,7 @@
       <c r="AU9" s="41">
         <v>0</v>
       </c>
-      <c r="AV9" s="63">
+      <c r="AV9" s="62">
         <v>2.4</v>
       </c>
       <c r="AW9">
@@ -3562,7 +3564,7 @@
       <c r="AU10" s="41">
         <v>0</v>
       </c>
-      <c r="AV10" s="63">
+      <c r="AV10" s="62">
         <v>2.4</v>
       </c>
       <c r="AW10">
@@ -3777,7 +3779,7 @@
       <c r="AU11" s="41">
         <v>0</v>
       </c>
-      <c r="AV11" s="63">
+      <c r="AV11" s="62">
         <v>2.4</v>
       </c>
       <c r="AW11">
@@ -3873,7 +3875,7 @@
       <c r="F12" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="G12" s="69">
+      <c r="G12" s="68">
         <v>45569.354861111111</v>
       </c>
       <c r="H12" s="2">
@@ -3957,7 +3959,7 @@
         <f t="shared" ref="AU12:AU43" si="25">AP3-AP12</f>
         <v>0</v>
       </c>
-      <c r="AV12" s="66">
+      <c r="AV12" s="65">
         <v>60</v>
       </c>
       <c r="AW12" s="3">
@@ -4028,7 +4030,7 @@
         <f t="shared" si="8"/>
         <v>5358.6430859999991</v>
       </c>
-      <c r="BP12" s="58">
+      <c r="BP12" s="57">
         <f>IF(BK12&lt;&gt;"",BK12/0.000385,IF(BL12&lt;&gt;"",BL12/0.000385,BM12/0.000385))</f>
         <v>419532.46753246756</v>
       </c>
@@ -4060,7 +4062,7 @@
       <c r="F13" t="s">
         <v>89</v>
       </c>
-      <c r="G13" s="70">
+      <c r="G13" s="69">
         <v>45569.398680555554</v>
       </c>
       <c r="H13" s="1">
@@ -4182,7 +4184,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AV13" s="67">
+      <c r="AV13" s="66">
         <v>2.4</v>
       </c>
       <c r="AW13">
@@ -4279,7 +4281,7 @@
       <c r="F14" t="s">
         <v>89</v>
       </c>
-      <c r="G14" s="70">
+      <c r="G14" s="69">
         <v>45569.399525462963</v>
       </c>
       <c r="H14" s="1">
@@ -4401,7 +4403,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AV14" s="67">
+      <c r="AV14" s="66">
         <v>2.4</v>
       </c>
       <c r="AW14">
@@ -4498,7 +4500,7 @@
       <c r="F15" t="s">
         <v>89</v>
       </c>
-      <c r="G15" s="70">
+      <c r="G15" s="69">
         <v>45569.400370370371</v>
       </c>
       <c r="H15" s="1">
@@ -4620,7 +4622,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AV15" s="67">
+      <c r="AV15" s="66">
         <v>2.4</v>
       </c>
       <c r="AW15">
@@ -4719,7 +4721,7 @@
       <c r="F16" t="s">
         <v>89</v>
       </c>
-      <c r="G16" s="70">
+      <c r="G16" s="69">
         <v>45569.40121527778</v>
       </c>
       <c r="H16" s="1">
@@ -4841,7 +4843,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AV16" s="67">
+      <c r="AV16" s="66">
         <v>2.4</v>
       </c>
       <c r="AW16">
@@ -4939,7 +4941,7 @@
       <c r="F17" t="s">
         <v>89</v>
       </c>
-      <c r="G17" s="70">
+      <c r="G17" s="69">
         <v>45569.402071759258</v>
       </c>
       <c r="H17" s="1">
@@ -5061,7 +5063,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AV17" s="67">
+      <c r="AV17" s="66">
         <v>2.4</v>
       </c>
       <c r="AW17">
@@ -5164,7 +5166,7 @@
       <c r="F18" t="s">
         <v>89</v>
       </c>
-      <c r="G18" s="70">
+      <c r="G18" s="69">
         <v>45569.402916666666</v>
       </c>
       <c r="H18" s="1">
@@ -5286,7 +5288,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AV18" s="67">
+      <c r="AV18" s="66">
         <v>2.4</v>
       </c>
       <c r="AW18">
@@ -5389,7 +5391,7 @@
       <c r="F19" t="s">
         <v>89</v>
       </c>
-      <c r="G19" s="70">
+      <c r="G19" s="69">
         <v>45569.403784722221</v>
       </c>
       <c r="H19" s="1">
@@ -5511,7 +5513,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AV19" s="67">
+      <c r="AV19" s="66">
         <v>2.4</v>
       </c>
       <c r="AW19">
@@ -5607,7 +5609,7 @@
       <c r="F20" t="s">
         <v>89</v>
       </c>
-      <c r="G20" s="70">
+      <c r="G20" s="69">
         <v>45569.406643518516</v>
       </c>
       <c r="H20" s="4">
@@ -5729,7 +5731,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AV20" s="67">
+      <c r="AV20" s="66">
         <v>2.4</v>
       </c>
       <c r="AW20">
@@ -5909,7 +5911,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AV21" s="66">
+      <c r="AV21" s="65">
         <v>60</v>
       </c>
       <c r="AW21" s="3">
@@ -5980,7 +5982,7 @@
         <f t="shared" si="8"/>
         <v>4609.1968360000001</v>
       </c>
-      <c r="BP21" s="58">
+      <c r="BP21" s="57">
         <f>IF(BK21&lt;&gt;"",BK21/0.000385,IF(BL21&lt;&gt;"",BL21/0.000385,BM21/0.000385))</f>
         <v>791936.32229354652</v>
       </c>
@@ -6134,7 +6136,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AV22" s="67">
+      <c r="AV22" s="66">
         <v>2.4</v>
       </c>
       <c r="AW22">
@@ -6353,7 +6355,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AV23" s="67">
+      <c r="AV23" s="66">
         <v>2.4</v>
       </c>
       <c r="AW23">
@@ -6572,7 +6574,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AV24" s="67">
+      <c r="AV24" s="66">
         <v>2.4</v>
       </c>
       <c r="AW24">
@@ -6793,7 +6795,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AV25" s="67">
+      <c r="AV25" s="66">
         <v>2.4</v>
       </c>
       <c r="AW25">
@@ -7013,7 +7015,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AV26" s="67">
+      <c r="AV26" s="66">
         <v>2.4</v>
       </c>
       <c r="AW26">
@@ -7238,7 +7240,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AV27" s="67">
+      <c r="AV27" s="66">
         <v>2.4</v>
       </c>
       <c r="AW27">
@@ -7463,7 +7465,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AV28" s="67">
+      <c r="AV28" s="66">
         <v>2.4</v>
       </c>
       <c r="AW28">
@@ -7681,7 +7683,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AV29" s="68">
+      <c r="AV29" s="67">
         <v>2.4</v>
       </c>
       <c r="AW29" s="5">
@@ -7702,7 +7704,7 @@
       <c r="BB29" s="12"/>
       <c r="BC29" s="5"/>
       <c r="BD29" s="23"/>
-      <c r="BE29" s="60">
+      <c r="BE29" s="59">
         <f t="shared" si="1"/>
         <v>1.2264749999999999E-3</v>
       </c>
@@ -7746,7 +7748,7 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="BP29" s="59">
+      <c r="BP29" s="58">
         <f t="shared" si="36"/>
         <v>191.13896103896104</v>
       </c>
@@ -7775,10 +7777,10 @@
       <c r="E30">
         <v>3</v>
       </c>
-      <c r="F30" s="71" t="s">
+      <c r="F30" s="70" t="s">
         <v>91</v>
       </c>
-      <c r="G30" s="69">
+      <c r="G30" s="68">
         <v>45571.368055555555</v>
       </c>
       <c r="H30">
@@ -7862,7 +7864,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AV30" s="67">
+      <c r="AV30" s="66">
         <v>60</v>
       </c>
       <c r="AW30">
@@ -8084,7 +8086,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AV31" s="67">
+      <c r="AV31" s="66">
         <v>2.4</v>
       </c>
       <c r="AW31">
@@ -8300,7 +8302,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AV32" s="67">
+      <c r="AV32" s="66">
         <v>2.4</v>
       </c>
       <c r="AW32">
@@ -8516,7 +8518,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AV33" s="67">
+      <c r="AV33" s="66">
         <v>2.4</v>
       </c>
       <c r="AW33">
@@ -8734,7 +8736,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AV34" s="67">
+      <c r="AV34" s="66">
         <v>2.4</v>
       </c>
       <c r="AW34">
@@ -8951,7 +8953,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AV35" s="67">
+      <c r="AV35" s="66">
         <v>2.4</v>
       </c>
       <c r="AW35">
@@ -9173,7 +9175,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AV36" s="67">
+      <c r="AV36" s="66">
         <v>2.4</v>
       </c>
       <c r="AW36">
@@ -9395,7 +9397,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AV37" s="67">
+      <c r="AV37" s="66">
         <v>2.4</v>
       </c>
       <c r="AW37">
@@ -9610,7 +9612,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AV38" s="68">
+      <c r="AV38" s="67">
         <v>2.4</v>
       </c>
       <c r="AW38">
@@ -9788,7 +9790,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AV39" s="66">
+      <c r="AV39" s="65">
         <v>60</v>
       </c>
       <c r="AW39" s="3">
@@ -9859,7 +9861,7 @@
         <f t="shared" si="49"/>
         <v>2610.0869895953001</v>
       </c>
-      <c r="BP39" s="58">
+      <c r="BP39" s="57">
         <f t="shared" ref="BP39:BP70" si="52">IF(BK39&lt;&gt;"",BK39/0.000385,IF(BL39&lt;&gt;"",BL39/0.000385,BM39/0.000385))</f>
         <v>1380387.0649870131</v>
       </c>
@@ -10010,7 +10012,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AV40" s="67">
+      <c r="AV40" s="66">
         <v>2.4</v>
       </c>
       <c r="AW40">
@@ -10226,7 +10228,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AV41" s="67">
+      <c r="AV41" s="66">
         <v>2.4</v>
       </c>
       <c r="AW41">
@@ -10442,7 +10444,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AV42" s="67">
+      <c r="AV42" s="66">
         <v>2.4</v>
       </c>
       <c r="AW42">
@@ -10660,7 +10662,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AV43" s="67">
+      <c r="AV43" s="66">
         <v>2.4</v>
       </c>
       <c r="AW43">
@@ -10877,7 +10879,7 @@
         <f t="shared" ref="AU44:AU75" si="57">AP35-AP44</f>
         <v>0</v>
       </c>
-      <c r="AV44" s="67">
+      <c r="AV44" s="66">
         <v>2.4</v>
       </c>
       <c r="AW44">
@@ -11099,7 +11101,7 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AV45" s="67">
+      <c r="AV45" s="66">
         <v>2.4</v>
       </c>
       <c r="AW45">
@@ -11320,7 +11322,7 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AV46" s="67">
+      <c r="AV46" s="66">
         <v>2.4</v>
       </c>
       <c r="AW46">
@@ -11534,7 +11536,7 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AV47" s="68">
+      <c r="AV47" s="67">
         <v>2.4</v>
       </c>
       <c r="AW47">
@@ -11712,7 +11714,7 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AV48" s="66">
+      <c r="AV48" s="65">
         <v>60</v>
       </c>
       <c r="AW48" s="3">
@@ -11783,7 +11785,7 @@
         <f t="shared" si="49"/>
         <v>3886.9041343279305</v>
       </c>
-      <c r="BP48" s="58">
+      <c r="BP48" s="57">
         <f t="shared" si="52"/>
         <v>1355095.2071525161</v>
       </c>
@@ -11933,7 +11935,7 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AV49" s="67">
+      <c r="AV49" s="66">
         <v>2.4</v>
       </c>
       <c r="AW49">
@@ -12148,7 +12150,7 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AV50" s="67">
+      <c r="AV50" s="66">
         <v>2.4</v>
       </c>
       <c r="AW50">
@@ -12363,7 +12365,7 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AV51" s="67">
+      <c r="AV51" s="66">
         <v>2.4</v>
       </c>
       <c r="AW51">
@@ -12580,7 +12582,7 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AV52" s="67">
+      <c r="AV52" s="66">
         <v>2.4</v>
       </c>
       <c r="AW52">
@@ -12796,7 +12798,7 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AV53" s="67">
+      <c r="AV53" s="66">
         <v>2.4</v>
       </c>
       <c r="AW53">
@@ -13017,7 +13019,7 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AV54" s="67">
+      <c r="AV54" s="66">
         <v>2.4</v>
       </c>
       <c r="AW54">
@@ -13238,7 +13240,7 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AV55" s="67">
+      <c r="AV55" s="66">
         <v>2.4</v>
       </c>
       <c r="AW55">
@@ -13452,7 +13454,7 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AV56" s="68">
+      <c r="AV56" s="67">
         <v>2.4</v>
       </c>
       <c r="AW56">
@@ -13630,7 +13632,7 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AV57" s="66">
+      <c r="AV57" s="65">
         <v>60</v>
       </c>
       <c r="AW57" s="3">
@@ -13701,7 +13703,7 @@
         <f>IF(C57="Julia",BD57*BG57,"")</f>
         <v>608.54644789999998</v>
       </c>
-      <c r="BP57" s="58">
+      <c r="BP57" s="57">
         <f t="shared" si="52"/>
         <v>761378.37930319167</v>
       </c>
@@ -13770,7 +13772,7 @@
       <c r="U58" s="40">
         <v>0.12</v>
       </c>
-      <c r="V58" s="72">
+      <c r="V58" s="71">
         <v>2.39</v>
       </c>
       <c r="W58" s="40">
@@ -13851,7 +13853,7 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AV58" s="67">
+      <c r="AV58" s="66">
         <v>2.4</v>
       </c>
       <c r="AW58">
@@ -14066,7 +14068,7 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AV59" s="67">
+      <c r="AV59" s="66">
         <v>2.4</v>
       </c>
       <c r="AW59">
@@ -14281,7 +14283,7 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AV60" s="67">
+      <c r="AV60" s="66">
         <v>2.4</v>
       </c>
       <c r="AW60">
@@ -14498,7 +14500,7 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AV61" s="67">
+      <c r="AV61" s="66">
         <v>2.4</v>
       </c>
       <c r="AW61">
@@ -14714,7 +14716,7 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AV62" s="67">
+      <c r="AV62" s="66">
         <v>2.4</v>
       </c>
       <c r="AW62">
@@ -14737,7 +14739,7 @@
         <f>0.00209329980667217*24*60/BG62</f>
         <v>1.5162735018148512E-2</v>
       </c>
-      <c r="BD62" s="73">
+      <c r="BD62" s="72">
         <f>0.00001988/BG62</f>
         <v>9.9999999999999995E-8</v>
       </c>
@@ -14935,7 +14937,7 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AV63" s="67">
+      <c r="AV63" s="66">
         <v>2.4</v>
       </c>
       <c r="AW63">
@@ -14958,7 +14960,7 @@
         <f>0.00188484803018864*24*60/BG63</f>
         <v>1.3557348468889318E-2</v>
       </c>
-      <c r="BD63" s="73">
+      <c r="BD63" s="72">
         <f>0.00002002/BG63</f>
         <v>1.0000000000000001E-7</v>
       </c>
@@ -15156,7 +15158,7 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AV64" s="67">
+      <c r="AV64" s="66">
         <v>2.4</v>
       </c>
       <c r="AW64">
@@ -15289,7 +15291,7 @@
       <c r="U65" s="40">
         <v>0.11</v>
       </c>
-      <c r="V65" s="72">
+      <c r="V65" s="71">
         <v>2.76</v>
       </c>
       <c r="W65" s="40">
@@ -15370,7 +15372,7 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AV65" s="68">
+      <c r="AV65" s="67">
         <v>2.4</v>
       </c>
       <c r="AW65">
@@ -15548,7 +15550,7 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AV66" s="66">
+      <c r="AV66" s="65">
         <v>60</v>
       </c>
       <c r="AW66" s="3">
@@ -15619,7 +15621,7 @@
         <f t="shared" si="49"/>
         <v>994.54931209375104</v>
       </c>
-      <c r="BP66" s="58">
+      <c r="BP66" s="57">
         <f t="shared" si="52"/>
         <v>837360.95535259473</v>
       </c>
@@ -15769,7 +15771,7 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AV67" s="67">
+      <c r="AV67" s="66">
         <v>2.4</v>
       </c>
       <c r="AW67">
@@ -15984,7 +15986,7 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AV68" s="67">
+      <c r="AV68" s="66">
         <v>2.4</v>
       </c>
       <c r="AW68">
@@ -16200,7 +16202,7 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AV69" s="67">
+      <c r="AV69" s="66">
         <v>2.4</v>
       </c>
       <c r="AW69">
@@ -16417,7 +16419,7 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AV70" s="67">
+      <c r="AV70" s="66">
         <v>2.4</v>
       </c>
       <c r="AW70">
@@ -16633,7 +16635,7 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AV71" s="67">
+      <c r="AV71" s="66">
         <v>2.4</v>
       </c>
       <c r="AW71">
@@ -16656,7 +16658,7 @@
         <f>0.00208803891673102*24*60/BG71</f>
         <v>1.5101838473594521E-2</v>
       </c>
-      <c r="BD71" s="73">
+      <c r="BD71" s="72">
         <f>0.00001991/BG71</f>
         <v>1.0000000000000001E-7</v>
       </c>
@@ -16854,7 +16856,7 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AV72" s="67">
+      <c r="AV72" s="66">
         <v>2.4</v>
       </c>
       <c r="AW72">
@@ -16877,7 +16879,7 @@
         <f>0.00210133507001434*24*60/BG72</f>
         <v>1.5106952075989262E-2</v>
       </c>
-      <c r="BD72" s="73">
+      <c r="BD72" s="72">
         <f>0.00002003/BG72</f>
         <v>9.9999999999999995E-8</v>
       </c>
@@ -17075,7 +17077,7 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AV73" s="67">
+      <c r="AV73" s="66">
         <v>2.4</v>
       </c>
       <c r="AW73">
@@ -17289,7 +17291,7 @@
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AV74" s="68">
+      <c r="AV74" s="67">
         <v>2.4</v>
       </c>
       <c r="AW74">
@@ -17368,187 +17370,187 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:70" s="92" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="81" t="s">
+    <row r="75" spans="1:70" s="88" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="B75" s="82">
+      <c r="B75" s="78">
         <v>1000</v>
       </c>
-      <c r="C75" s="82" t="s">
+      <c r="C75" s="78" t="s">
         <v>77</v>
       </c>
-      <c r="D75" s="82">
+      <c r="D75" s="78">
         <v>12</v>
       </c>
-      <c r="E75" s="82">
+      <c r="E75" s="78">
         <v>8</v>
       </c>
-      <c r="F75" s="82"/>
-      <c r="G75" s="83">
+      <c r="F75" s="78"/>
+      <c r="G75" s="79">
         <v>45576.349305555559</v>
       </c>
-      <c r="H75" s="82">
+      <c r="H75" s="78">
         <v>4309.7</v>
       </c>
-      <c r="I75" s="82"/>
-      <c r="J75" s="84">
+      <c r="I75" s="78"/>
+      <c r="J75" s="80">
         <v>3221.7150000000001</v>
       </c>
-      <c r="K75" s="84">
+      <c r="K75" s="80">
         <v>22.3</v>
       </c>
-      <c r="L75" s="84">
+      <c r="L75" s="80">
         <v>21.5</v>
       </c>
-      <c r="M75" s="84">
+      <c r="M75" s="80">
         <v>97</v>
       </c>
-      <c r="N75" s="84"/>
-      <c r="O75" s="84"/>
-      <c r="P75" s="84"/>
-      <c r="Q75" s="84"/>
-      <c r="R75" s="84">
+      <c r="N75" s="80"/>
+      <c r="O75" s="80"/>
+      <c r="P75" s="80"/>
+      <c r="Q75" s="80"/>
+      <c r="R75" s="80">
         <v>7.06</v>
       </c>
-      <c r="S75" s="84"/>
-      <c r="T75" s="84"/>
-      <c r="U75" s="84"/>
-      <c r="V75" s="84">
+      <c r="S75" s="80"/>
+      <c r="T75" s="80"/>
+      <c r="U75" s="80"/>
+      <c r="V75" s="80">
         <v>0.84</v>
       </c>
-      <c r="W75" s="84"/>
-      <c r="X75" s="84"/>
-      <c r="Y75" s="84"/>
-      <c r="Z75" s="84"/>
-      <c r="AA75" s="84"/>
-      <c r="AB75" s="84"/>
-      <c r="AC75" s="84"/>
-      <c r="AD75" s="84"/>
-      <c r="AE75" s="85">
+      <c r="W75" s="80"/>
+      <c r="X75" s="80"/>
+      <c r="Y75" s="80"/>
+      <c r="Z75" s="80"/>
+      <c r="AA75" s="80"/>
+      <c r="AB75" s="80"/>
+      <c r="AC75" s="80"/>
+      <c r="AD75" s="80"/>
+      <c r="AE75" s="81">
         <v>7.3</v>
       </c>
-      <c r="AF75" s="84"/>
-      <c r="AG75" s="84">
+      <c r="AF75" s="80"/>
+      <c r="AG75" s="80">
         <v>52.5</v>
       </c>
-      <c r="AH75" s="84"/>
-      <c r="AI75" s="84">
+      <c r="AH75" s="80"/>
+      <c r="AI75" s="80">
         <v>34</v>
       </c>
-      <c r="AJ75" s="84"/>
-      <c r="AK75" s="84"/>
-      <c r="AL75" s="84"/>
-      <c r="AM75" s="84">
+      <c r="AJ75" s="80"/>
+      <c r="AK75" s="80"/>
+      <c r="AL75" s="80"/>
+      <c r="AM75" s="80">
         <v>62332.34765625</v>
       </c>
-      <c r="AN75" s="84">
+      <c r="AN75" s="80">
         <v>23036.900390625</v>
       </c>
-      <c r="AO75" s="84">
+      <c r="AO75" s="80">
         <v>656400.02441406297</v>
       </c>
-      <c r="AP75" s="84"/>
-      <c r="AQ75" s="84">
+      <c r="AP75" s="80"/>
+      <c r="AQ75" s="80">
         <f t="shared" si="59"/>
         <v>0.52500000000000002</v>
       </c>
-      <c r="AR75" s="84">
+      <c r="AR75" s="80">
         <f t="shared" si="68"/>
         <v>283.4185635278526</v>
       </c>
-      <c r="AS75" s="84">
+      <c r="AS75" s="80">
         <f t="shared" si="55"/>
         <v>7411.265625</v>
       </c>
-      <c r="AT75" s="84">
+      <c r="AT75" s="80">
         <f t="shared" si="56"/>
         <v>995.642578125</v>
       </c>
-      <c r="AU75" s="84">
+      <c r="AU75" s="80">
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AV75" s="86">
+      <c r="AV75" s="82">
         <v>60</v>
       </c>
-      <c r="AW75" s="82">
+      <c r="AW75" s="78">
         <v>592000</v>
       </c>
-      <c r="AX75" s="82">
+      <c r="AX75" s="78">
         <v>34</v>
       </c>
-      <c r="AY75" s="84">
+      <c r="AY75" s="80">
         <v>7.2</v>
       </c>
-      <c r="AZ75" s="84">
+      <c r="AZ75" s="80">
         <v>50</v>
       </c>
-      <c r="BA75" s="87">
+      <c r="BA75" s="83">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="BB75" s="88"/>
-      <c r="BC75" s="87">
+      <c r="BB75" s="84"/>
+      <c r="BC75" s="83">
         <f>4.72364272546421*24*60/BG75</f>
         <v>1.0362652760015243E-2</v>
       </c>
-      <c r="BD75" s="89">
+      <c r="BD75" s="85">
         <f>792.953496967818/BG75</f>
         <v>1.2080339236361999E-3</v>
       </c>
-      <c r="BE75" s="87">
+      <c r="BE75" s="83">
         <f t="shared" si="60"/>
         <v>5.6450402099609418</v>
       </c>
-      <c r="BF75" s="87">
+      <c r="BF75" s="83">
         <f t="shared" si="69"/>
         <v>8128.857902343756</v>
       </c>
-      <c r="BG75" s="87">
+      <c r="BG75" s="83">
         <f t="shared" si="61"/>
         <v>656400.02441406297</v>
       </c>
-      <c r="BH75" s="87">
+      <c r="BH75" s="83">
         <f t="shared" si="62"/>
         <v>9.4960916114972899E-2</v>
       </c>
-      <c r="BI75" s="87">
+      <c r="BI75" s="83">
         <f t="shared" si="63"/>
         <v>0.1052911277977196</v>
       </c>
-      <c r="BJ75" s="87">
+      <c r="BJ75" s="83">
         <f t="shared" si="64"/>
         <v>408122.73148010776</v>
       </c>
-      <c r="BK75" s="87" t="str">
+      <c r="BK75" s="83" t="str">
         <f t="shared" si="70"/>
         <v/>
       </c>
-      <c r="BL75" s="87">
+      <c r="BL75" s="83">
         <f>IF(C75="Julia",BC75*BG75/24,"")</f>
         <v>283.4185635278526</v>
       </c>
-      <c r="BM75" s="90" t="str">
+      <c r="BM75" s="86" t="str">
         <f t="shared" si="67"/>
         <v/>
       </c>
-      <c r="BN75" s="87" t="str">
+      <c r="BN75" s="83" t="str">
         <f t="shared" si="58"/>
         <v/>
       </c>
-      <c r="BO75" s="87">
+      <c r="BO75" s="83">
         <f t="shared" si="65"/>
         <v>792.95349696781796</v>
       </c>
-      <c r="BP75" s="91">
+      <c r="BP75" s="87">
         <f t="shared" si="71"/>
         <v>736152.11305935739</v>
       </c>
-      <c r="BQ75" s="90">
+      <c r="BQ75" s="86">
         <f t="shared" si="72"/>
         <v>283.4185635278526</v>
       </c>
-      <c r="BR75" s="91">
+      <c r="BR75" s="87">
         <f t="shared" si="73"/>
         <v>792.95349696781796</v>
       </c>
@@ -17690,7 +17692,7 @@
         <f t="shared" ref="AU76:AU107" si="76">AP67-AP76</f>
         <v>0</v>
       </c>
-      <c r="AV76" s="67">
+      <c r="AV76" s="66">
         <v>2.4</v>
       </c>
       <c r="AW76">
@@ -17905,7 +17907,7 @@
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="AV77" s="67">
+      <c r="AV77" s="66">
         <v>2.4</v>
       </c>
       <c r="AW77">
@@ -18056,7 +18058,7 @@
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="AV78" s="67">
+      <c r="AV78" s="66">
         <v>2.4</v>
       </c>
       <c r="AW78">
@@ -18271,7 +18273,7 @@
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="AV79" s="67">
+      <c r="AV79" s="66">
         <v>2.4</v>
       </c>
       <c r="AW79">
@@ -18487,7 +18489,7 @@
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="AV80" s="67">
+      <c r="AV80" s="66">
         <v>2.4</v>
       </c>
       <c r="AW80">
@@ -18594,7 +18596,7 @@
         <v>4309.7</v>
       </c>
       <c r="I81" s="48"/>
-      <c r="J81" s="72">
+      <c r="J81" s="71">
         <v>4489.7250000000004</v>
       </c>
       <c r="K81" s="40">
@@ -18709,7 +18711,7 @@
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="AV81" s="67">
+      <c r="AV81" s="66">
         <v>2.4</v>
       </c>
       <c r="AW81">
@@ -18816,7 +18818,7 @@
         <v>4309.7</v>
       </c>
       <c r="I82" s="48"/>
-      <c r="J82" s="72">
+      <c r="J82" s="71">
         <v>3788.91</v>
       </c>
       <c r="K82" s="40">
@@ -18931,7 +18933,7 @@
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="AV82" s="67">
+      <c r="AV82" s="66">
         <v>2.4</v>
       </c>
       <c r="AW82">
@@ -19031,7 +19033,7 @@
         <v>4309.7</v>
       </c>
       <c r="I83" s="48"/>
-      <c r="J83" s="72">
+      <c r="J83" s="71">
         <v>4070.835</v>
       </c>
       <c r="K83" s="40">
@@ -19146,7 +19148,7 @@
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="AV83" s="68">
+      <c r="AV83" s="67">
         <v>2.4</v>
       </c>
       <c r="AW83">
@@ -19223,159 +19225,188 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:70" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
+    <row r="84" spans="1:70" s="88" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="B84" s="3">
+      <c r="B84" s="78">
         <v>1000</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="C84" s="78" t="s">
         <v>77</v>
       </c>
-      <c r="D84" s="3">
+      <c r="D84" s="78">
         <v>12</v>
       </c>
-      <c r="E84" s="3">
+      <c r="E84" s="78">
         <v>9</v>
       </c>
-      <c r="F84" s="3"/>
-      <c r="G84" s="74">
-        <v>45577.364340277803</v>
-      </c>
-      <c r="H84" s="3">
+      <c r="F84" s="103" t="s">
+        <v>94</v>
+      </c>
+      <c r="G84" s="79">
+        <v>45577.337500000001</v>
+      </c>
+      <c r="H84" s="78">
         <v>4805.7299999999996</v>
       </c>
-      <c r="I84" s="37"/>
-      <c r="J84" s="77">
+      <c r="I84" s="104"/>
+      <c r="J84" s="105">
         <v>3776.085</v>
       </c>
-      <c r="K84" s="75"/>
-      <c r="L84" s="75"/>
-      <c r="M84" s="75"/>
-      <c r="N84" s="6"/>
-      <c r="O84" s="6"/>
-      <c r="P84" s="6"/>
-      <c r="Q84" s="6"/>
-      <c r="R84" s="75"/>
-      <c r="S84" s="6"/>
-      <c r="T84" s="6"/>
-      <c r="U84" s="6"/>
-      <c r="V84" s="75"/>
-      <c r="W84" s="6"/>
-      <c r="X84" s="6"/>
-      <c r="Y84" s="6"/>
-      <c r="Z84" s="6"/>
-      <c r="AA84" s="6"/>
-      <c r="AB84" s="6"/>
-      <c r="AC84" s="6"/>
-      <c r="AD84" s="6"/>
-      <c r="AE84" s="76"/>
-      <c r="AF84" s="6"/>
-      <c r="AG84" s="75"/>
-      <c r="AH84" s="6"/>
-      <c r="AI84" s="75"/>
-      <c r="AJ84" s="6"/>
-      <c r="AK84" s="6"/>
-      <c r="AL84" s="6"/>
-      <c r="AM84" s="75"/>
-      <c r="AN84" s="75"/>
-      <c r="AO84" s="75"/>
-      <c r="AP84" s="6"/>
-      <c r="AQ84" s="32">
+      <c r="K84" s="80">
+        <v>22.7</v>
+      </c>
+      <c r="L84" s="80">
+        <v>21.973599999999998</v>
+      </c>
+      <c r="M84" s="80">
+        <v>96.8</v>
+      </c>
+      <c r="N84" s="80"/>
+      <c r="O84" s="80"/>
+      <c r="P84" s="80"/>
+      <c r="Q84" s="80"/>
+      <c r="R84" s="80">
+        <v>7.36</v>
+      </c>
+      <c r="S84" s="80"/>
+      <c r="T84" s="80"/>
+      <c r="U84" s="80"/>
+      <c r="V84" s="80">
+        <v>0.79</v>
+      </c>
+      <c r="W84" s="80"/>
+      <c r="X84" s="80"/>
+      <c r="Y84" s="80"/>
+      <c r="Z84" s="80"/>
+      <c r="AA84" s="80"/>
+      <c r="AB84" s="80"/>
+      <c r="AC84" s="80"/>
+      <c r="AD84" s="80"/>
+      <c r="AE84" s="81">
+        <v>7.4</v>
+      </c>
+      <c r="AF84" s="80"/>
+      <c r="AG84" s="80">
+        <v>50.013606025931502</v>
+      </c>
+      <c r="AH84" s="80"/>
+      <c r="AI84" s="80">
+        <v>33.999922763095803</v>
+      </c>
+      <c r="AJ84" s="80"/>
+      <c r="AK84" s="80"/>
+      <c r="AL84" s="80"/>
+      <c r="AM84" s="80">
+        <v>68897.0546875</v>
+      </c>
+      <c r="AN84" s="80">
+        <v>23830.064453125</v>
+      </c>
+      <c r="AO84" s="80">
+        <v>664000</v>
+      </c>
+      <c r="AP84" s="80"/>
+      <c r="AQ84" s="80">
         <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="AR84" s="32">
+        <v>0.50013606025931501</v>
+      </c>
+      <c r="AR84" s="80">
         <f t="shared" si="68"/>
-        <v>0</v>
-      </c>
-      <c r="AS84" s="32">
+        <v>310.7961517233702</v>
+      </c>
+      <c r="AS84" s="80">
         <f t="shared" si="74"/>
-        <v>-62332.34765625</v>
-      </c>
-      <c r="AT84" s="32">
+        <v>6564.70703125</v>
+      </c>
+      <c r="AT84" s="80">
         <f t="shared" si="75"/>
-        <v>-23036.900390625</v>
-      </c>
-      <c r="AU84" s="32">
+        <v>793.1640625</v>
+      </c>
+      <c r="AU84" s="80">
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="AV84" s="66">
+      <c r="AV84" s="82">
         <v>60</v>
       </c>
-      <c r="AW84" s="3">
+      <c r="AW84" s="78">
         <v>592000</v>
       </c>
-      <c r="AX84" s="3">
+      <c r="AX84" s="78">
         <v>34</v>
       </c>
-      <c r="AY84" s="6">
+      <c r="AY84" s="80">
         <v>7.2</v>
       </c>
-      <c r="AZ84" s="6">
+      <c r="AZ84" s="80">
         <v>50</v>
       </c>
-      <c r="BA84" s="9">
+      <c r="BA84" s="83">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="BB84" s="8"/>
-      <c r="BC84" s="9"/>
-      <c r="BD84" s="21"/>
-      <c r="BE84" s="9">
+      <c r="BB84" s="84"/>
+      <c r="BC84" s="83">
+        <f>5.17993586205617*24*60/BG84</f>
+        <v>1.1233595845423021E-2</v>
+      </c>
+      <c r="BD84" s="85">
+        <v>0</v>
+      </c>
+      <c r="BE84" s="83">
         <f t="shared" si="60"/>
-        <v>0</v>
-      </c>
-      <c r="BF84" s="9">
+        <v>5.8361881599999998</v>
+      </c>
+      <c r="BF84" s="83">
         <f t="shared" si="69"/>
-        <v>0</v>
-      </c>
-      <c r="BG84" s="9">
+        <v>8404.1109503999996</v>
+      </c>
+      <c r="BG84" s="83">
         <f t="shared" si="61"/>
-        <v>591400</v>
-      </c>
-      <c r="BH84" s="10" t="str">
+        <v>664000</v>
+      </c>
+      <c r="BH84" s="83">
         <f t="shared" si="62"/>
-        <v/>
-      </c>
-      <c r="BI84" s="10" t="str">
+        <v>0.10376062452936748</v>
+      </c>
+      <c r="BI84" s="83">
         <f t="shared" si="63"/>
-        <v/>
-      </c>
-      <c r="BJ84" s="10">
+        <v>0.11638015994510136</v>
+      </c>
+      <c r="BJ84" s="83">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="BK84" s="10" t="str">
+        <v>447546.45848165307</v>
+      </c>
+      <c r="BK84" s="83" t="str">
         <f t="shared" si="70"/>
         <v/>
       </c>
-      <c r="BL84" s="10">
+      <c r="BL84" s="83">
         <f t="shared" si="66"/>
-        <v>0</v>
-      </c>
-      <c r="BM84" s="28" t="str">
+        <v>310.7961517233702</v>
+      </c>
+      <c r="BM84" s="86" t="str">
         <f t="shared" si="67"/>
         <v/>
       </c>
-      <c r="BN84" s="10" t="str">
+      <c r="BN84" s="83" t="str">
         <f t="shared" si="58"/>
         <v/>
       </c>
-      <c r="BO84" s="10">
+      <c r="BO84" s="83">
         <f t="shared" si="65"/>
         <v>0</v>
       </c>
-      <c r="BP84" s="58">
+      <c r="BP84" s="87">
         <f t="shared" si="71"/>
-        <v>0</v>
-      </c>
-      <c r="BQ84" s="30">
+        <v>807262.73174901353</v>
+      </c>
+      <c r="BQ84" s="86">
         <f t="shared" si="72"/>
-        <v>0</v>
-      </c>
-      <c r="BR84" s="26">
+        <v>310.7961517233702</v>
+      </c>
+      <c r="BR84" s="87">
         <f t="shared" si="73"/>
         <v>0</v>
       </c>
@@ -19403,7 +19434,7 @@
         <v>4805.7299999999996</v>
       </c>
       <c r="I85" s="48"/>
-      <c r="J85" s="72">
+      <c r="J85" s="71">
         <v>4718.79</v>
       </c>
       <c r="K85" s="40">
@@ -19518,7 +19549,7 @@
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="AV85" s="67">
+      <c r="AV85" s="66">
         <v>2.4</v>
       </c>
       <c r="AW85">
@@ -19619,7 +19650,7 @@
         <v>4805.7299999999996</v>
       </c>
       <c r="I86" s="48"/>
-      <c r="J86" s="72">
+      <c r="J86" s="71">
         <v>4821.33</v>
       </c>
       <c r="K86" s="40">
@@ -19734,7 +19765,7 @@
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="AV86" s="67">
+      <c r="AV86" s="66">
         <v>2.4</v>
       </c>
       <c r="AW86">
@@ -19833,7 +19864,7 @@
         <v>4805.7299999999996</v>
       </c>
       <c r="I87" s="48"/>
-      <c r="J87" s="72"/>
+      <c r="J87" s="71"/>
       <c r="K87" s="40"/>
       <c r="L87" s="40"/>
       <c r="M87" s="40"/>
@@ -19886,7 +19917,7 @@
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="AV87" s="67">
+      <c r="AV87" s="66">
         <v>2.4</v>
       </c>
       <c r="AW87">
@@ -19987,7 +20018,7 @@
         <v>4805.7299999999996</v>
       </c>
       <c r="I88" s="48"/>
-      <c r="J88" s="72">
+      <c r="J88" s="71">
         <v>4869.1350000000002</v>
       </c>
       <c r="K88" s="40">
@@ -20088,7 +20119,7 @@
       </c>
       <c r="AR88" s="41">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>0.11678333333333334</v>
       </c>
       <c r="AS88" s="41">
         <f t="shared" si="74"/>
@@ -20102,7 +20133,7 @@
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="AV88" s="67">
+      <c r="AV88" s="66">
         <v>2.4</v>
       </c>
       <c r="AW88">
@@ -20120,7 +20151,9 @@
       <c r="BA88" s="42">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="BB88" s="11"/>
+      <c r="BB88" s="11">
+        <v>1.4E-2</v>
+      </c>
       <c r="BD88" s="22"/>
       <c r="BE88" s="42">
         <f t="shared" si="60"/>
@@ -20144,11 +20177,11 @@
       </c>
       <c r="BJ88" s="43">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>168.16800000000001</v>
       </c>
       <c r="BK88" s="43">
         <f t="shared" si="70"/>
-        <v>0</v>
+        <v>0.11678333333333334</v>
       </c>
       <c r="BL88" s="44" t="str">
         <f t="shared" si="66"/>
@@ -20168,11 +20201,11 @@
       </c>
       <c r="BP88" s="55">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>303.33333333333337</v>
       </c>
       <c r="BQ88" s="45">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>0.11678333333333334</v>
       </c>
       <c r="BR88" s="24">
         <f t="shared" si="73"/>
@@ -20202,7 +20235,7 @@
         <v>4805.7299999999996</v>
       </c>
       <c r="I89" s="48"/>
-      <c r="J89" s="72">
+      <c r="J89" s="71">
         <v>5030.49</v>
       </c>
       <c r="K89" s="40">
@@ -20303,7 +20336,7 @@
       </c>
       <c r="AR89" s="41">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>0.1231660499721966</v>
       </c>
       <c r="AS89" s="41">
         <f t="shared" si="74"/>
@@ -20317,7 +20350,7 @@
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="AV89" s="67">
+      <c r="AV89" s="66">
         <v>2.4</v>
       </c>
       <c r="AW89">
@@ -20336,7 +20369,14 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="BB89" s="11"/>
-      <c r="BD89" s="22"/>
+      <c r="BC89" s="42">
+        <f>0.00205276749953661*24*60/BG89</f>
+        <v>1.4891613094875156E-2</v>
+      </c>
+      <c r="BD89" s="42">
+        <f>0.216166414682163/BG89</f>
+        <v>1.0889995701872191E-3</v>
+      </c>
       <c r="BE89" s="42">
         <f t="shared" si="60"/>
         <v>1.4388868000000002E-3</v>
@@ -20359,7 +20399,7 @@
       </c>
       <c r="BJ89" s="43">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>177.35911195996312</v>
       </c>
       <c r="BK89" s="43" t="str">
         <f t="shared" si="70"/>
@@ -20367,7 +20407,7 @@
       </c>
       <c r="BL89" s="44">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>0.1231660499721966</v>
       </c>
       <c r="BM89" s="44" t="str">
         <f t="shared" si="67"/>
@@ -20379,19 +20419,19 @@
       </c>
       <c r="BO89" s="43">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>0.21616641468216299</v>
       </c>
       <c r="BP89" s="55">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>319.9118181096016</v>
       </c>
       <c r="BQ89" s="45">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>0.1231660499721966</v>
       </c>
       <c r="BR89" s="24">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>0.21616641468216299</v>
       </c>
     </row>
     <row r="90" spans="1:70" x14ac:dyDescent="0.3">
@@ -20417,7 +20457,7 @@
         <v>4805.7299999999996</v>
       </c>
       <c r="I90" s="48"/>
-      <c r="J90" s="72">
+      <c r="J90" s="71">
         <v>5038.74</v>
       </c>
       <c r="K90" s="40">
@@ -20518,7 +20558,7 @@
       </c>
       <c r="AR90" s="41">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>0.11324635846940699</v>
       </c>
       <c r="AS90" s="41">
         <f t="shared" si="74"/>
@@ -20532,7 +20572,7 @@
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="AV90" s="67">
+      <c r="AV90" s="66">
         <v>2.4</v>
       </c>
       <c r="AW90">
@@ -20551,7 +20591,14 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="BB90" s="11"/>
-      <c r="BD90" s="22"/>
+      <c r="BC90" s="42">
+        <f>0.00188743930782345*24*60/BG90</f>
+        <v>1.3582771630513583E-2</v>
+      </c>
+      <c r="BD90" s="42">
+        <f>0.337429620228796/BG90</f>
+        <v>1.6863049486696452E-3</v>
+      </c>
       <c r="BE90" s="42">
         <f t="shared" si="60"/>
         <v>1.5266829600000002E-3</v>
@@ -20574,7 +20621,7 @@
       </c>
       <c r="BJ90" s="43">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>163.07475619594607</v>
       </c>
       <c r="BK90" s="43" t="str">
         <f t="shared" si="70"/>
@@ -20582,7 +20629,7 @@
       </c>
       <c r="BL90" s="44">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>0.11324635846940699</v>
       </c>
       <c r="BM90" s="44" t="str">
         <f t="shared" si="67"/>
@@ -20594,19 +20641,19 @@
       </c>
       <c r="BO90" s="43">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>0.33742962022879602</v>
       </c>
       <c r="BP90" s="55">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>294.14638563482339</v>
       </c>
       <c r="BQ90" s="45">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>0.11324635846940699</v>
       </c>
       <c r="BR90" s="24">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>0.33742962022879602</v>
       </c>
     </row>
     <row r="91" spans="1:70" x14ac:dyDescent="0.3">
@@ -20632,7 +20679,7 @@
         <v>4805.7299999999996</v>
       </c>
       <c r="I91" s="48"/>
-      <c r="J91" s="72">
+      <c r="J91" s="71">
         <v>4396.6049999999996</v>
       </c>
       <c r="K91" s="40">
@@ -20747,7 +20794,7 @@
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="AV91" s="67">
+      <c r="AV91" s="66">
         <v>2.4</v>
       </c>
       <c r="AW91">
@@ -20847,7 +20894,9 @@
         <v>4805.7299999999996</v>
       </c>
       <c r="I92" s="48"/>
-      <c r="J92" s="72"/>
+      <c r="J92" s="71">
+        <v>4509.6149999999998</v>
+      </c>
       <c r="K92" s="40">
         <v>20.274000000000001</v>
       </c>
@@ -20960,7 +21009,7 @@
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="AV92" s="68">
+      <c r="AV92" s="67">
         <v>2.4</v>
       </c>
       <c r="AW92">
@@ -21054,24 +21103,38 @@
         <v>10</v>
       </c>
       <c r="F93" s="3"/>
-      <c r="G93" s="34"/>
+      <c r="G93" s="35">
+        <v>45578.339583333334</v>
+      </c>
       <c r="H93" s="37">
         <v>5497.99</v>
       </c>
       <c r="I93" s="37"/>
-      <c r="J93" s="77"/>
-      <c r="K93" s="6"/>
-      <c r="L93" s="6"/>
-      <c r="M93" s="6"/>
+      <c r="J93" s="73">
+        <v>4276.6350000000002</v>
+      </c>
+      <c r="K93" s="6">
+        <v>23.6</v>
+      </c>
+      <c r="L93" s="6">
+        <v>22.9</v>
+      </c>
+      <c r="M93" s="6">
+        <v>97.4</v>
+      </c>
       <c r="N93" s="6"/>
       <c r="O93" s="6"/>
       <c r="P93" s="6"/>
       <c r="Q93" s="6"/>
-      <c r="R93" s="6"/>
+      <c r="R93" s="6">
+        <v>7.09</v>
+      </c>
       <c r="S93" s="6"/>
       <c r="T93" s="6"/>
       <c r="U93" s="6"/>
-      <c r="V93" s="39"/>
+      <c r="V93" s="39">
+        <v>0.69</v>
+      </c>
       <c r="W93" s="6"/>
       <c r="X93" s="6"/>
       <c r="Y93" s="6"/>
@@ -21080,29 +21143,41 @@
       <c r="AB93" s="6"/>
       <c r="AC93" s="6"/>
       <c r="AD93" s="6"/>
-      <c r="AE93" s="16"/>
+      <c r="AE93" s="16">
+        <v>7.2930000000000001</v>
+      </c>
       <c r="AF93" s="6"/>
-      <c r="AG93" s="6"/>
+      <c r="AG93" s="6">
+        <v>49.982202181195298</v>
+      </c>
       <c r="AH93" s="6"/>
-      <c r="AI93" s="6"/>
+      <c r="AI93" s="6">
+        <v>34.000841407564501</v>
+      </c>
       <c r="AJ93" s="6"/>
       <c r="AK93" s="6"/>
       <c r="AL93" s="6"/>
-      <c r="AM93" s="6"/>
-      <c r="AN93" s="6"/>
-      <c r="AO93" s="6"/>
+      <c r="AM93" s="6">
+        <v>76268.0703125</v>
+      </c>
+      <c r="AN93" s="6">
+        <v>23830.064453125</v>
+      </c>
+      <c r="AO93" s="6">
+        <v>673500</v>
+      </c>
       <c r="AP93" s="6"/>
       <c r="AQ93" s="32">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>0.49982202181195295</v>
       </c>
       <c r="AR93" s="32">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>335.03617883608439</v>
       </c>
       <c r="AS93" s="32">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>7371.015625</v>
       </c>
       <c r="AT93" s="32">
         <f t="shared" si="75"/>
@@ -21112,7 +21187,7 @@
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="AV93" s="66">
+      <c r="AV93" s="65">
         <v>60</v>
       </c>
       <c r="AW93" s="3">
@@ -21131,31 +21206,37 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="BB93" s="8"/>
-      <c r="BC93" s="9"/>
-      <c r="BD93" s="21"/>
+      <c r="BC93" s="9">
+        <f>5.58393631393474*24*60/BG93</f>
+        <v>1.1938928421775836E-2</v>
+      </c>
+      <c r="BD93" s="21">
+        <f>239.484375/BG93</f>
+        <v>3.5558184855233853E-4</v>
+      </c>
       <c r="BE93" s="9">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>6.1692600000000004</v>
       </c>
       <c r="BF93" s="9">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>8883.7343999999994</v>
       </c>
       <c r="BG93" s="9">
         <f t="shared" si="61"/>
-        <v>591340</v>
-      </c>
-      <c r="BH93" s="10" t="str">
+        <v>673500</v>
+      </c>
+      <c r="BH93" s="10">
         <f t="shared" si="62"/>
-        <v/>
-      </c>
-      <c r="BI93" s="10" t="str">
+        <v>0.11324138131031923</v>
+      </c>
+      <c r="BI93" s="10">
         <f t="shared" si="63"/>
-        <v/>
+        <v>0.12883119985219593</v>
       </c>
       <c r="BJ93" s="10">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>482452.09752396151</v>
       </c>
       <c r="BK93" s="10" t="str">
         <f t="shared" si="70"/>
@@ -21163,7 +21244,7 @@
       </c>
       <c r="BL93" s="10">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>335.03617883608439</v>
       </c>
       <c r="BM93" s="28" t="str">
         <f t="shared" si="67"/>
@@ -21175,19 +21256,19 @@
       </c>
       <c r="BO93" s="10">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="BP93" s="58">
+        <v>239.484375</v>
+      </c>
+      <c r="BP93" s="57">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>870223.84113268682</v>
       </c>
       <c r="BQ93" s="30">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>335.03617883608439</v>
       </c>
       <c r="BR93" s="26">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>239.484375</v>
       </c>
     </row>
     <row r="94" spans="1:70" x14ac:dyDescent="0.3">
@@ -21206,65 +21287,129 @@
       <c r="E94">
         <v>10</v>
       </c>
-      <c r="G94" s="35"/>
+      <c r="G94" s="35">
+        <v>45578.346967592595</v>
+      </c>
       <c r="H94" s="48">
         <v>5497.99</v>
       </c>
       <c r="I94" s="48"/>
-      <c r="J94" s="72"/>
-      <c r="K94" s="40"/>
-      <c r="L94" s="40"/>
-      <c r="M94" s="40"/>
-      <c r="N94" s="40"/>
-      <c r="O94" s="40"/>
-      <c r="P94" s="40"/>
-      <c r="Q94" s="40"/>
-      <c r="R94" s="40"/>
+      <c r="J94" s="71">
+        <v>5162.6400000000003</v>
+      </c>
+      <c r="K94" s="40">
+        <v>19.065999999999999</v>
+      </c>
+      <c r="L94" s="40">
+        <v>17.047000000000001</v>
+      </c>
+      <c r="M94" s="40">
+        <v>89.4</v>
+      </c>
+      <c r="N94" s="40">
+        <v>16.579999999999998</v>
+      </c>
+      <c r="O94" s="40">
+        <v>339</v>
+      </c>
+      <c r="P94" s="40">
+        <v>1.44</v>
+      </c>
+      <c r="Q94" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="R94" s="40">
+        <v>2.79</v>
+      </c>
       <c r="S94" s="40"/>
-      <c r="T94" s="40"/>
-      <c r="U94" s="40"/>
-      <c r="V94" s="40"/>
-      <c r="W94" s="40"/>
-      <c r="X94" s="40"/>
-      <c r="Y94" s="40"/>
-      <c r="Z94" s="40"/>
-      <c r="AA94" s="40"/>
-      <c r="AB94" s="40"/>
-      <c r="AC94" s="40"/>
-      <c r="AD94" s="40"/>
-      <c r="AE94" s="17"/>
-      <c r="AF94" s="40"/>
-      <c r="AG94" s="40"/>
-      <c r="AH94" s="40"/>
-      <c r="AI94" s="40"/>
-      <c r="AJ94" s="40"/>
-      <c r="AK94" s="40"/>
-      <c r="AL94" s="40"/>
-      <c r="AM94" s="40"/>
-      <c r="AN94" s="40"/>
-      <c r="AO94" s="40"/>
+      <c r="T94" s="40">
+        <v>0.22</v>
+      </c>
+      <c r="U94" s="40">
+        <v>0.15</v>
+      </c>
+      <c r="V94" s="40">
+        <v>1.47</v>
+      </c>
+      <c r="W94" s="40">
+        <v>7.2990000000000004</v>
+      </c>
+      <c r="X94" s="40">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="Y94" s="40">
+        <v>62.1</v>
+      </c>
+      <c r="Z94" s="40">
+        <v>1.92</v>
+      </c>
+      <c r="AA94" s="40">
+        <v>148.19999999999999</v>
+      </c>
+      <c r="AB94" s="40">
+        <v>16</v>
+      </c>
+      <c r="AC94" s="40">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="AD94" s="40">
+        <v>50.5</v>
+      </c>
+      <c r="AE94" s="17">
+        <v>7.258</v>
+      </c>
+      <c r="AF94" s="40">
+        <v>409</v>
+      </c>
+      <c r="AG94" s="40">
+        <v>49.9</v>
+      </c>
+      <c r="AH94" s="40">
+        <v>7.3040000000000003</v>
+      </c>
+      <c r="AI94" s="40">
+        <v>34</v>
+      </c>
+      <c r="AJ94" s="40">
+        <v>2</v>
+      </c>
+      <c r="AK94" s="40">
+        <v>9</v>
+      </c>
+      <c r="AL94" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="AM94" s="40">
+        <v>19.7</v>
+      </c>
+      <c r="AN94" s="40">
+        <v>4</v>
+      </c>
+      <c r="AO94" s="40">
+        <v>196.6</v>
+      </c>
       <c r="AP94" s="40"/>
       <c r="AQ94" s="41">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>0.499</v>
       </c>
       <c r="AR94" s="41">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>8.0434564800000011E-2</v>
       </c>
       <c r="AS94" s="41">
         <f t="shared" si="74"/>
-        <v>-17.7</v>
+        <v>2</v>
       </c>
       <c r="AT94" s="41">
         <f t="shared" si="75"/>
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AU94" s="41">
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="AV94" s="67">
+      <c r="AV94" s="66">
         <v>2.4</v>
       </c>
       <c r="AW94">
@@ -21287,27 +21432,27 @@
       <c r="BD94" s="22"/>
       <c r="BE94" s="42">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>1.3405760800000001E-3</v>
       </c>
       <c r="BF94" s="42">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>1.9304295552000001</v>
       </c>
       <c r="BG94" s="42">
         <f t="shared" si="61"/>
-        <v>173.6</v>
-      </c>
-      <c r="BH94" s="43" t="str">
+        <v>196.6</v>
+      </c>
+      <c r="BH94" s="43">
         <f t="shared" si="62"/>
-        <v/>
-      </c>
-      <c r="BI94" s="43" t="str">
+        <v>0.10020345879959308</v>
+      </c>
+      <c r="BI94" s="43">
         <f t="shared" si="63"/>
-        <v/>
+        <v>9.849999999999999E-2</v>
       </c>
       <c r="BJ94" s="43">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>115.82577331200002</v>
       </c>
       <c r="BK94" s="43" t="str">
         <f t="shared" si="70"/>
@@ -21319,11 +21464,11 @@
       </c>
       <c r="BM94" s="44">
         <f t="shared" si="67"/>
-        <v>0</v>
+        <v>8.0434564800000011E-2</v>
       </c>
       <c r="BN94" s="43">
         <f t="shared" si="77"/>
-        <v>1.3019999999999998</v>
+        <v>0</v>
       </c>
       <c r="BO94" s="43" t="str">
         <f t="shared" si="65"/>
@@ -21331,15 +21476,15 @@
       </c>
       <c r="BP94" s="55">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>208.92094753246758</v>
       </c>
       <c r="BQ94" s="45">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>8.0434564800000011E-2</v>
       </c>
       <c r="BR94" s="24">
         <f t="shared" si="73"/>
-        <v>1.3019999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:70" x14ac:dyDescent="0.3">
@@ -21358,65 +21503,129 @@
       <c r="E95">
         <v>10</v>
       </c>
-      <c r="G95" s="35"/>
+      <c r="G95" s="35">
+        <v>45578.3121875</v>
+      </c>
       <c r="H95" s="48">
         <v>5497.99</v>
       </c>
       <c r="I95" s="48"/>
-      <c r="J95" s="72"/>
-      <c r="K95" s="40"/>
-      <c r="L95" s="40"/>
-      <c r="M95" s="40"/>
-      <c r="N95" s="40"/>
-      <c r="O95" s="40"/>
-      <c r="P95" s="40"/>
-      <c r="Q95" s="40"/>
-      <c r="R95" s="40"/>
+      <c r="J95" s="71">
+        <v>5267.97</v>
+      </c>
+      <c r="K95" s="40">
+        <v>25.51</v>
+      </c>
+      <c r="L95" s="40">
+        <v>22.45</v>
+      </c>
+      <c r="M95" s="40">
+        <v>88</v>
+      </c>
+      <c r="N95" s="40">
+        <v>16.07</v>
+      </c>
+      <c r="O95" s="40">
+        <v>341</v>
+      </c>
+      <c r="P95" s="40">
+        <v>1.44</v>
+      </c>
+      <c r="Q95" s="40">
+        <v>0.32</v>
+      </c>
+      <c r="R95" s="40">
+        <v>2.31</v>
+      </c>
       <c r="S95" s="40"/>
-      <c r="T95" s="40"/>
-      <c r="U95" s="40"/>
-      <c r="V95" s="40"/>
-      <c r="W95" s="40"/>
-      <c r="X95" s="40"/>
-      <c r="Y95" s="40"/>
-      <c r="Z95" s="40"/>
-      <c r="AA95" s="40"/>
-      <c r="AB95" s="40"/>
-      <c r="AC95" s="40"/>
-      <c r="AD95" s="40"/>
-      <c r="AE95" s="17"/>
-      <c r="AF95" s="40"/>
-      <c r="AG95" s="40"/>
-      <c r="AH95" s="40"/>
-      <c r="AI95" s="40"/>
-      <c r="AJ95" s="40"/>
-      <c r="AK95" s="40"/>
-      <c r="AL95" s="40"/>
-      <c r="AM95" s="40"/>
-      <c r="AN95" s="40"/>
-      <c r="AO95" s="40"/>
+      <c r="T95" s="40">
+        <v>0.19</v>
+      </c>
+      <c r="U95" s="40">
+        <v>0.18</v>
+      </c>
+      <c r="V95" s="40">
+        <v>1.68</v>
+      </c>
+      <c r="W95" s="40">
+        <v>7.3</v>
+      </c>
+      <c r="X95" s="40">
+        <v>32.299999999999997</v>
+      </c>
+      <c r="Y95" s="40">
+        <v>62.2</v>
+      </c>
+      <c r="Z95" s="40">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="AA95" s="40">
+        <v>143.9</v>
+      </c>
+      <c r="AB95" s="40">
+        <v>14</v>
+      </c>
+      <c r="AC95" s="40">
+        <v>28.3</v>
+      </c>
+      <c r="AD95" s="40">
+        <v>50.7</v>
+      </c>
+      <c r="AE95" s="17">
+        <v>7.258</v>
+      </c>
+      <c r="AF95" s="40">
+        <v>409</v>
+      </c>
+      <c r="AG95" s="40">
+        <v>50.2</v>
+      </c>
+      <c r="AH95" s="40">
+        <v>7.3040000000000003</v>
+      </c>
+      <c r="AI95" s="40">
+        <v>34</v>
+      </c>
+      <c r="AJ95" s="40">
+        <v>2.1</v>
+      </c>
+      <c r="AK95" s="40">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="AL95" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="AM95" s="40">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="AN95" s="40">
+        <v>4.3</v>
+      </c>
+      <c r="AO95" s="40">
+        <v>194.9</v>
+      </c>
       <c r="AP95" s="40"/>
       <c r="AQ95" s="41">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>0.502</v>
       </c>
       <c r="AR95" s="41">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>0.10501212</v>
       </c>
       <c r="AS95" s="41">
         <f t="shared" si="74"/>
-        <v>-17.7</v>
+        <v>1.9000000000000021</v>
       </c>
       <c r="AT95" s="41">
         <f t="shared" si="75"/>
-        <v>-4.3</v>
+        <v>0</v>
       </c>
       <c r="AU95" s="41">
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="AV95" s="67">
+      <c r="AV95" s="66">
         <v>2.4</v>
       </c>
       <c r="AW95">
@@ -21439,27 +21648,27 @@
       <c r="BD95" s="22"/>
       <c r="BE95" s="42">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>1.750202E-3</v>
       </c>
       <c r="BF95" s="42">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>2.5202908799999997</v>
       </c>
       <c r="BG95" s="42">
         <f t="shared" si="61"/>
-        <v>173.6</v>
-      </c>
-      <c r="BH95" s="43" t="str">
+        <v>194.9</v>
+      </c>
+      <c r="BH95" s="43">
         <f t="shared" si="62"/>
-        <v/>
-      </c>
-      <c r="BI95" s="43" t="str">
+        <v>0.10056439199589534</v>
+      </c>
+      <c r="BI95" s="43">
         <f t="shared" si="63"/>
-        <v/>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="BJ95" s="43">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>151.21745280000002</v>
       </c>
       <c r="BK95" s="43" t="str">
         <f t="shared" si="70"/>
@@ -21471,11 +21680,11 @@
       </c>
       <c r="BM95" s="44">
         <f t="shared" si="67"/>
-        <v>0</v>
+        <v>0.10501212</v>
       </c>
       <c r="BN95" s="43">
         <f t="shared" si="77"/>
-        <v>1.3019999999999998</v>
+        <v>0</v>
       </c>
       <c r="BO95" s="43" t="str">
         <f t="shared" si="65"/>
@@ -21483,15 +21692,15 @@
       </c>
       <c r="BP95" s="55">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>272.75875324675326</v>
       </c>
       <c r="BQ95" s="45">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>0.10501212</v>
       </c>
       <c r="BR95" s="24">
         <f t="shared" si="73"/>
-        <v>1.3019999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:70" x14ac:dyDescent="0.3">
@@ -21515,7 +21724,7 @@
         <v>5497.99</v>
       </c>
       <c r="I96" s="48"/>
-      <c r="J96" s="72"/>
+      <c r="J96" s="71"/>
       <c r="K96" s="40"/>
       <c r="L96" s="40"/>
       <c r="M96" s="40"/>
@@ -21568,7 +21777,7 @@
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="AV96" s="67">
+      <c r="AV96" s="66">
         <v>2.4</v>
       </c>
       <c r="AW96">
@@ -21662,65 +21871,129 @@
       <c r="E97">
         <v>10</v>
       </c>
-      <c r="G97" s="35"/>
+      <c r="G97" s="35">
+        <v>45578.316967592589</v>
+      </c>
       <c r="H97" s="48">
         <v>5497.99</v>
       </c>
       <c r="I97" s="48"/>
-      <c r="J97" s="72"/>
-      <c r="K97" s="40"/>
-      <c r="L97" s="40"/>
-      <c r="M97" s="40"/>
-      <c r="N97" s="40"/>
-      <c r="O97" s="40"/>
-      <c r="P97" s="40"/>
-      <c r="Q97" s="40"/>
-      <c r="R97" s="40"/>
+      <c r="J97" s="71">
+        <v>5374.95</v>
+      </c>
+      <c r="K97" s="40">
+        <v>19.515999999999998</v>
+      </c>
+      <c r="L97" s="40">
+        <v>16.885000000000002</v>
+      </c>
+      <c r="M97" s="40">
+        <v>86.5</v>
+      </c>
+      <c r="N97" s="40">
+        <v>16.93</v>
+      </c>
+      <c r="O97" s="40">
+        <v>356</v>
+      </c>
+      <c r="P97" s="40">
+        <v>1.5</v>
+      </c>
+      <c r="Q97" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="R97" s="40">
+        <v>1.75</v>
+      </c>
       <c r="S97" s="40"/>
-      <c r="T97" s="40"/>
-      <c r="U97" s="40"/>
-      <c r="V97" s="40"/>
-      <c r="W97" s="40"/>
-      <c r="X97" s="40"/>
-      <c r="Y97" s="40"/>
-      <c r="Z97" s="40"/>
-      <c r="AA97" s="40"/>
-      <c r="AB97" s="40"/>
-      <c r="AC97" s="40"/>
-      <c r="AD97" s="40"/>
-      <c r="AE97" s="17"/>
-      <c r="AF97" s="40"/>
-      <c r="AG97" s="40"/>
-      <c r="AH97" s="40"/>
-      <c r="AI97" s="40"/>
-      <c r="AJ97" s="40"/>
-      <c r="AK97" s="40"/>
-      <c r="AL97" s="40"/>
-      <c r="AM97" s="40"/>
-      <c r="AN97" s="40"/>
-      <c r="AO97" s="40"/>
+      <c r="T97" s="40">
+        <v>0.25</v>
+      </c>
+      <c r="U97" s="40">
+        <v>0.27</v>
+      </c>
+      <c r="V97" s="40">
+        <v>1.71</v>
+      </c>
+      <c r="W97" s="40">
+        <v>7.298</v>
+      </c>
+      <c r="X97" s="40">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="Y97" s="40">
+        <v>47.1</v>
+      </c>
+      <c r="Z97" s="40">
+        <v>1.62</v>
+      </c>
+      <c r="AA97" s="40">
+        <v>154.19999999999999</v>
+      </c>
+      <c r="AB97" s="40">
+        <v>15.7</v>
+      </c>
+      <c r="AC97" s="40">
+        <v>31.8</v>
+      </c>
+      <c r="AD97" s="40">
+        <v>38.200000000000003</v>
+      </c>
+      <c r="AE97" s="17">
+        <v>7.2569999999999997</v>
+      </c>
+      <c r="AF97" s="40">
+        <v>408</v>
+      </c>
+      <c r="AG97" s="40">
+        <v>49.7</v>
+      </c>
+      <c r="AH97" s="40">
+        <v>7.3029999999999999</v>
+      </c>
+      <c r="AI97" s="40">
+        <v>34</v>
+      </c>
+      <c r="AJ97" s="40">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AK97" s="40">
+        <v>5.3</v>
+      </c>
+      <c r="AL97" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="AM97" s="40">
+        <v>25.9</v>
+      </c>
+      <c r="AN97" s="40">
+        <v>6</v>
+      </c>
+      <c r="AO97" s="40">
+        <v>200.3</v>
+      </c>
       <c r="AP97" s="40"/>
       <c r="AQ97" s="41">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>0.49700000000000005</v>
       </c>
       <c r="AR97" s="41">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>0.11934541666666666</v>
       </c>
       <c r="AS97" s="41">
         <f t="shared" si="74"/>
-        <v>-23.1</v>
+        <v>2.7999999999999972</v>
       </c>
       <c r="AT97" s="41">
         <f t="shared" si="75"/>
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="AU97" s="41">
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="AV97" s="67">
+      <c r="AV97" s="66">
         <v>2.4</v>
       </c>
       <c r="AW97">
@@ -21738,35 +22011,37 @@
       <c r="BA97" s="42">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="BB97" s="11"/>
+      <c r="BB97" s="11">
+        <v>1.43E-2</v>
+      </c>
       <c r="BD97" s="22"/>
       <c r="BE97" s="42">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>1.3528262000000004E-3</v>
       </c>
       <c r="BF97" s="42">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>1.9480697280000006</v>
       </c>
       <c r="BG97" s="42">
         <f t="shared" si="61"/>
-        <v>173.6</v>
-      </c>
-      <c r="BH97" s="43" t="str">
+        <v>200.3</v>
+      </c>
+      <c r="BH97" s="43">
         <f t="shared" si="62"/>
-        <v/>
-      </c>
-      <c r="BI97" s="43" t="str">
+        <v>0.1293060409385921</v>
+      </c>
+      <c r="BI97" s="43">
         <f t="shared" si="63"/>
-        <v/>
+        <v>0.1295</v>
       </c>
       <c r="BJ97" s="43">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>171.85740000000001</v>
       </c>
       <c r="BK97" s="43">
         <f t="shared" si="70"/>
-        <v>0</v>
+        <v>0.11934541666666666</v>
       </c>
       <c r="BL97" s="44" t="str">
         <f t="shared" si="66"/>
@@ -21778,7 +22053,7 @@
       </c>
       <c r="BN97" s="43">
         <f t="shared" si="77"/>
-        <v>1.3019999999999998</v>
+        <v>0</v>
       </c>
       <c r="BO97" s="43" t="str">
         <f t="shared" si="65"/>
@@ -21786,15 +22061,15 @@
       </c>
       <c r="BP97" s="55">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>309.98809523809524</v>
       </c>
       <c r="BQ97" s="45">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>0.11934541666666666</v>
       </c>
       <c r="BR97" s="24">
         <f t="shared" si="73"/>
-        <v>1.3019999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:70" x14ac:dyDescent="0.3">
@@ -21813,65 +22088,129 @@
       <c r="E98">
         <v>10</v>
       </c>
-      <c r="G98" s="35"/>
+      <c r="G98" s="35">
+        <v>45578.321712962963</v>
+      </c>
       <c r="H98" s="48">
         <v>5497.99</v>
       </c>
       <c r="I98" s="48"/>
-      <c r="J98" s="72"/>
-      <c r="K98" s="40"/>
-      <c r="L98" s="40"/>
-      <c r="M98" s="40"/>
-      <c r="N98" s="40"/>
-      <c r="O98" s="40"/>
-      <c r="P98" s="40"/>
-      <c r="Q98" s="40"/>
-      <c r="R98" s="40"/>
+      <c r="J98" s="71">
+        <v>5606.9849999999997</v>
+      </c>
+      <c r="K98" s="40">
+        <v>21.007000000000001</v>
+      </c>
+      <c r="L98" s="40">
+        <v>17.347000000000001</v>
+      </c>
+      <c r="M98" s="40">
+        <v>82.6</v>
+      </c>
+      <c r="N98" s="40">
+        <v>16.649999999999999</v>
+      </c>
+      <c r="O98" s="40">
+        <v>353</v>
+      </c>
+      <c r="P98" s="40">
+        <v>1.77</v>
+      </c>
+      <c r="Q98" s="40">
+        <v>0.33</v>
+      </c>
+      <c r="R98" s="40">
+        <v>0.46</v>
+      </c>
       <c r="S98" s="40"/>
-      <c r="T98" s="40"/>
-      <c r="U98" s="40"/>
-      <c r="V98" s="40"/>
-      <c r="W98" s="40"/>
-      <c r="X98" s="40"/>
-      <c r="Y98" s="40"/>
-      <c r="Z98" s="40"/>
-      <c r="AA98" s="40"/>
-      <c r="AB98" s="40"/>
-      <c r="AC98" s="40"/>
-      <c r="AD98" s="40"/>
-      <c r="AE98" s="17"/>
-      <c r="AF98" s="40"/>
-      <c r="AG98" s="40"/>
-      <c r="AH98" s="40"/>
-      <c r="AI98" s="40"/>
-      <c r="AJ98" s="40"/>
-      <c r="AK98" s="40"/>
-      <c r="AL98" s="40"/>
-      <c r="AM98" s="40"/>
-      <c r="AN98" s="40"/>
-      <c r="AO98" s="40"/>
+      <c r="T98" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="U98" s="40">
+        <v>0.76</v>
+      </c>
+      <c r="V98" s="40">
+        <v>1.65</v>
+      </c>
+      <c r="W98" s="40">
+        <v>7.3120000000000003</v>
+      </c>
+      <c r="X98" s="40">
+        <v>30.8</v>
+      </c>
+      <c r="Y98" s="40">
+        <v>51.4</v>
+      </c>
+      <c r="Z98" s="40">
+        <v>1.87</v>
+      </c>
+      <c r="AA98" s="40">
+        <v>157.80000000000001</v>
+      </c>
+      <c r="AB98" s="40">
+        <v>13.8</v>
+      </c>
+      <c r="AC98" s="40">
+        <v>27.1</v>
+      </c>
+      <c r="AD98" s="40">
+        <v>41.7</v>
+      </c>
+      <c r="AE98" s="17">
+        <v>7.27</v>
+      </c>
+      <c r="AF98" s="40">
+        <v>408</v>
+      </c>
+      <c r="AG98" s="40">
+        <v>49.6</v>
+      </c>
+      <c r="AH98" s="40">
+        <v>7.3</v>
+      </c>
+      <c r="AI98" s="40">
+        <v>34</v>
+      </c>
+      <c r="AJ98" s="40">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AK98" s="40">
+        <v>4.2</v>
+      </c>
+      <c r="AL98" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="AM98" s="40">
+        <v>28.1</v>
+      </c>
+      <c r="AN98" s="40">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="AO98" s="40">
+        <v>197.8</v>
+      </c>
       <c r="AP98" s="40"/>
       <c r="AQ98" s="41">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>0.496</v>
       </c>
       <c r="AR98" s="41">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>0.1015256257609542</v>
       </c>
       <c r="AS98" s="41">
         <f t="shared" si="74"/>
-        <v>-25.1</v>
+        <v>3</v>
       </c>
       <c r="AT98" s="41">
         <f t="shared" si="75"/>
-        <v>-4.9000000000000004</v>
+        <v>0.19999999999999929</v>
       </c>
       <c r="AU98" s="41">
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="AV98" s="67">
+      <c r="AV98" s="66">
         <v>2.4</v>
       </c>
       <c r="AW98">
@@ -21890,30 +22229,37 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="BB98" s="11"/>
-      <c r="BD98" s="22"/>
+      <c r="BC98" s="42">
+        <f>0.00169209376268257*24*60/BG98</f>
+        <v>1.2318579465434279E-2</v>
+      </c>
+      <c r="BD98" s="22">
+        <f>0.562210750207404/BG98</f>
+        <v>2.8423192629292411E-3</v>
+      </c>
       <c r="BE98" s="42">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>1.3724946400000002E-3</v>
       </c>
       <c r="BF98" s="42">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>1.9763922816000004</v>
       </c>
       <c r="BG98" s="42">
         <f t="shared" si="61"/>
-        <v>173.6</v>
-      </c>
-      <c r="BH98" s="43" t="str">
+        <v>197.8</v>
+      </c>
+      <c r="BH98" s="43">
         <f t="shared" si="62"/>
-        <v/>
-      </c>
-      <c r="BI98" s="43" t="str">
+        <v>0.14206268958543983</v>
+      </c>
+      <c r="BI98" s="43">
         <f t="shared" si="63"/>
-        <v/>
+        <v>0.14050000000000001</v>
       </c>
       <c r="BJ98" s="43">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>146.19690109577405</v>
       </c>
       <c r="BK98" s="43" t="str">
         <f t="shared" si="70"/>
@@ -21921,7 +22267,7 @@
       </c>
       <c r="BL98" s="44">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>0.1015256257609542</v>
       </c>
       <c r="BM98" s="44" t="str">
         <f t="shared" si="67"/>
@@ -21933,19 +22279,19 @@
       </c>
       <c r="BO98" s="43">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>0.56221075020740396</v>
       </c>
       <c r="BP98" s="55">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>263.70292405442649</v>
       </c>
       <c r="BQ98" s="45">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>0.1015256257609542</v>
       </c>
       <c r="BR98" s="24">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>0.56221075020740396</v>
       </c>
     </row>
     <row r="99" spans="1:70" x14ac:dyDescent="0.3">
@@ -21964,65 +22310,129 @@
       <c r="E99">
         <v>10</v>
       </c>
-      <c r="G99" s="35"/>
+      <c r="G99" s="35">
+        <v>45578.32775462963</v>
+      </c>
       <c r="H99" s="48">
         <v>5497.99</v>
       </c>
       <c r="I99" s="48"/>
-      <c r="J99" s="72"/>
-      <c r="K99" s="40"/>
-      <c r="L99" s="40"/>
-      <c r="M99" s="40"/>
-      <c r="N99" s="40"/>
-      <c r="O99" s="40"/>
-      <c r="P99" s="40"/>
-      <c r="Q99" s="40"/>
-      <c r="R99" s="40"/>
+      <c r="J99" s="71">
+        <v>5573.97</v>
+      </c>
+      <c r="K99" s="40">
+        <v>22.422000000000001</v>
+      </c>
+      <c r="L99" s="40">
+        <v>18.657</v>
+      </c>
+      <c r="M99" s="40">
+        <v>83.2</v>
+      </c>
+      <c r="N99" s="40">
+        <v>16.41</v>
+      </c>
+      <c r="O99" s="40">
+        <v>349</v>
+      </c>
+      <c r="P99" s="40">
+        <v>1.69</v>
+      </c>
+      <c r="Q99" s="40">
+        <v>0.32</v>
+      </c>
+      <c r="R99" s="40">
+        <v>0.37</v>
+      </c>
       <c r="S99" s="40"/>
-      <c r="T99" s="40"/>
-      <c r="U99" s="40"/>
-      <c r="V99" s="40"/>
-      <c r="W99" s="40"/>
-      <c r="X99" s="40"/>
-      <c r="Y99" s="40"/>
-      <c r="Z99" s="40"/>
-      <c r="AA99" s="40"/>
-      <c r="AB99" s="40"/>
-      <c r="AC99" s="40"/>
-      <c r="AD99" s="40"/>
-      <c r="AE99" s="17"/>
-      <c r="AF99" s="40"/>
-      <c r="AG99" s="40"/>
-      <c r="AH99" s="40"/>
-      <c r="AI99" s="40"/>
-      <c r="AJ99" s="40"/>
-      <c r="AK99" s="40"/>
-      <c r="AL99" s="40"/>
-      <c r="AM99" s="40"/>
-      <c r="AN99" s="40"/>
-      <c r="AO99" s="40"/>
+      <c r="T99" s="40">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="U99" s="40">
+        <v>0.44</v>
+      </c>
+      <c r="V99" s="40">
+        <v>1.46</v>
+      </c>
+      <c r="W99" s="40">
+        <v>7.3120000000000003</v>
+      </c>
+      <c r="X99" s="40">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="Y99" s="40">
+        <v>51.1</v>
+      </c>
+      <c r="Z99" s="40">
+        <v>1.74</v>
+      </c>
+      <c r="AA99" s="40">
+        <v>155.80000000000001</v>
+      </c>
+      <c r="AB99" s="40">
+        <v>15.5</v>
+      </c>
+      <c r="AC99" s="40">
+        <v>30.4</v>
+      </c>
+      <c r="AD99" s="40">
+        <v>41.5</v>
+      </c>
+      <c r="AE99" s="17">
+        <v>7.2709999999999999</v>
+      </c>
+      <c r="AF99" s="40">
+        <v>406</v>
+      </c>
+      <c r="AG99" s="40">
+        <v>50.4</v>
+      </c>
+      <c r="AH99" s="40">
+        <v>7.3049999999999997</v>
+      </c>
+      <c r="AI99" s="40">
+        <v>34</v>
+      </c>
+      <c r="AJ99" s="40">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AK99" s="40">
+        <v>4.5</v>
+      </c>
+      <c r="AL99" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="AM99" s="40">
+        <v>27.7</v>
+      </c>
+      <c r="AN99" s="40">
+        <v>5.5</v>
+      </c>
+      <c r="AO99" s="40">
+        <v>199.6</v>
+      </c>
       <c r="AP99" s="40"/>
       <c r="AQ99" s="41">
         <f t="shared" ref="AQ99:AQ119" si="78">AG99/100</f>
-        <v>0</v>
+        <v>0.504</v>
       </c>
       <c r="AR99" s="41">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>0.1045451240029896</v>
       </c>
       <c r="AS99" s="41">
         <f t="shared" si="74"/>
-        <v>-25</v>
+        <v>2.6999999999999993</v>
       </c>
       <c r="AT99" s="41">
         <f t="shared" si="75"/>
-        <v>-5.2</v>
+        <v>0.29999999999999982</v>
       </c>
       <c r="AU99" s="41">
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="AV99" s="67">
+      <c r="AV99" s="66">
         <v>2.4</v>
       </c>
       <c r="AW99">
@@ -22041,30 +22451,37 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="BB99" s="11"/>
-      <c r="BD99" s="22"/>
+      <c r="BC99" s="42">
+        <f>0.00174241873338316*24*60/BG99</f>
+        <v>1.2570555992343439E-2</v>
+      </c>
+      <c r="BD99" s="22">
+        <f>0.587797316819119/BG99</f>
+        <v>2.9448763367691333E-3</v>
+      </c>
       <c r="BE99" s="42">
         <f t="shared" ref="BE99:BE119" si="79">BA99*L99*BG99/1000</f>
-        <v>0</v>
+        <v>1.48957488E-3</v>
       </c>
       <c r="BF99" s="42">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>2.1449878271999996</v>
       </c>
       <c r="BG99" s="42">
         <f t="shared" ref="BG99:BG119" si="80">IF(ISBLANK(AO99), AW99+SUM(AJ99:AL99,AM99:AN99)-(AV99*(E99+1)), AO99)</f>
-        <v>173.6</v>
-      </c>
-      <c r="BH99" s="43" t="str">
+        <v>199.6</v>
+      </c>
+      <c r="BH99" s="43">
         <f t="shared" ref="BH99:BH119" si="81">IF(ISBLANK(AM99),"",IFERROR(AM99/BG99,0))</f>
-        <v/>
-      </c>
-      <c r="BI99" s="43" t="str">
+        <v>0.13877755511022044</v>
+      </c>
+      <c r="BI99" s="43">
         <f t="shared" ref="BI99:BI119" si="82">IF(ISBLANK(AM99),"",AM99/AW99)</f>
-        <v/>
+        <v>0.13849999999999998</v>
       </c>
       <c r="BJ99" s="43">
         <f t="shared" ref="BJ99:BJ119" si="83">AR99*24*60</f>
-        <v>0</v>
+        <v>150.54497856430501</v>
       </c>
       <c r="BK99" s="43" t="str">
         <f t="shared" si="70"/>
@@ -22072,7 +22489,7 @@
       </c>
       <c r="BL99" s="44">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>0.1045451240029896</v>
       </c>
       <c r="BM99" s="44" t="str">
         <f t="shared" si="67"/>
@@ -22084,19 +22501,19 @@
       </c>
       <c r="BO99" s="43">
         <f t="shared" ref="BO99:BO119" si="84">IF(C99="Julia",BD99*BG99,"")</f>
-        <v>0</v>
+        <v>0.58779731681911895</v>
       </c>
       <c r="BP99" s="55">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>271.54577663114185</v>
       </c>
       <c r="BQ99" s="45">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>0.1045451240029896</v>
       </c>
       <c r="BR99" s="24">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>0.58779731681911895</v>
       </c>
     </row>
     <row r="100" spans="1:70" x14ac:dyDescent="0.3">
@@ -22115,65 +22532,129 @@
       <c r="E100">
         <v>10</v>
       </c>
-      <c r="G100" s="35"/>
+      <c r="G100" s="35">
+        <v>45578.331631944442</v>
+      </c>
       <c r="H100" s="48">
         <v>5497.99</v>
       </c>
       <c r="I100" s="48"/>
-      <c r="J100" s="72"/>
-      <c r="K100" s="40"/>
-      <c r="L100" s="40"/>
-      <c r="M100" s="40"/>
-      <c r="N100" s="40"/>
-      <c r="O100" s="40"/>
-      <c r="P100" s="40"/>
-      <c r="Q100" s="40"/>
-      <c r="R100" s="40"/>
+      <c r="J100" s="71">
+        <v>4825.5749999999998</v>
+      </c>
+      <c r="K100" s="40">
+        <v>18.385000000000002</v>
+      </c>
+      <c r="L100" s="40">
+        <v>16.16</v>
+      </c>
+      <c r="M100" s="40">
+        <v>87.9</v>
+      </c>
+      <c r="N100" s="40">
+        <v>16.809999999999999</v>
+      </c>
+      <c r="O100" s="40">
+        <v>355</v>
+      </c>
+      <c r="P100" s="40">
+        <v>1.42</v>
+      </c>
+      <c r="Q100" s="40">
+        <v>0.31</v>
+      </c>
+      <c r="R100" s="40">
+        <v>2.36</v>
+      </c>
       <c r="S100" s="40"/>
-      <c r="T100" s="40"/>
-      <c r="U100" s="40"/>
-      <c r="V100" s="46"/>
-      <c r="W100" s="40"/>
-      <c r="X100" s="40"/>
-      <c r="Y100" s="40"/>
-      <c r="Z100" s="40"/>
-      <c r="AA100" s="40"/>
-      <c r="AB100" s="40"/>
-      <c r="AC100" s="40"/>
-      <c r="AD100" s="40"/>
-      <c r="AE100" s="17"/>
-      <c r="AF100" s="40"/>
-      <c r="AG100" s="40"/>
-      <c r="AH100" s="40"/>
-      <c r="AI100" s="40"/>
-      <c r="AJ100" s="40"/>
-      <c r="AK100" s="40"/>
-      <c r="AL100" s="40"/>
-      <c r="AM100" s="40"/>
-      <c r="AN100" s="40"/>
-      <c r="AO100" s="40"/>
+      <c r="T100" s="40">
+        <v>0.24</v>
+      </c>
+      <c r="U100" s="40">
+        <v>0.18</v>
+      </c>
+      <c r="V100" s="46">
+        <v>2.09</v>
+      </c>
+      <c r="W100" s="40">
+        <v>7.3049999999999997</v>
+      </c>
+      <c r="X100" s="40">
+        <v>50.3</v>
+      </c>
+      <c r="Y100" s="40">
+        <v>61.2</v>
+      </c>
+      <c r="Z100" s="40">
+        <v>1.96</v>
+      </c>
+      <c r="AA100" s="40">
+        <v>154.19999999999999</v>
+      </c>
+      <c r="AB100" s="40">
+        <v>22.1</v>
+      </c>
+      <c r="AC100" s="40">
+        <v>44.1</v>
+      </c>
+      <c r="AD100" s="40">
+        <v>49.8</v>
+      </c>
+      <c r="AE100" s="17">
+        <v>7.2629999999999999</v>
+      </c>
+      <c r="AF100" s="40">
+        <v>569</v>
+      </c>
+      <c r="AG100" s="40">
+        <v>50.4</v>
+      </c>
+      <c r="AH100" s="40">
+        <v>7.3079999999999998</v>
+      </c>
+      <c r="AI100" s="40">
+        <v>34</v>
+      </c>
+      <c r="AJ100" s="40">
+        <v>2.6</v>
+      </c>
+      <c r="AK100" s="40">
+        <v>8.6</v>
+      </c>
+      <c r="AL100" s="40">
+        <v>0.2</v>
+      </c>
+      <c r="AM100" s="40">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="AN100" s="40">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AO100" s="40">
+        <v>198.3</v>
+      </c>
       <c r="AP100" s="40"/>
       <c r="AQ100" s="41">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>0.504</v>
       </c>
       <c r="AR100" s="41">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>7.6908672000000011E-2</v>
       </c>
       <c r="AS100" s="41">
         <f t="shared" si="74"/>
-        <v>-17.100000000000001</v>
+        <v>2</v>
       </c>
       <c r="AT100" s="41">
         <f t="shared" si="75"/>
-        <v>-4.4000000000000004</v>
+        <v>0</v>
       </c>
       <c r="AU100" s="41">
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="AV100" s="67">
+      <c r="AV100" s="66">
         <v>2.4</v>
       </c>
       <c r="AW100">
@@ -22195,27 +22676,27 @@
       <c r="BD100" s="22"/>
       <c r="BE100" s="42">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>1.2818112000000002E-3</v>
       </c>
       <c r="BF100" s="42">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>1.8458081280000003</v>
       </c>
       <c r="BG100" s="42">
         <f t="shared" si="80"/>
-        <v>173.6</v>
-      </c>
-      <c r="BH100" s="43" t="str">
+        <v>198.3</v>
+      </c>
+      <c r="BH100" s="43">
         <f t="shared" si="81"/>
-        <v/>
-      </c>
-      <c r="BI100" s="43" t="str">
+        <v>9.6318709026727178E-2</v>
+      </c>
+      <c r="BI100" s="43">
         <f t="shared" si="82"/>
-        <v/>
+        <v>9.5500000000000002E-2</v>
       </c>
       <c r="BJ100" s="43">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>110.74848768000001</v>
       </c>
       <c r="BK100" s="43" t="str">
         <f t="shared" si="70"/>
@@ -22227,11 +22708,11 @@
       </c>
       <c r="BM100" s="44">
         <f t="shared" si="67"/>
-        <v>0</v>
+        <v>7.6908672000000011E-2</v>
       </c>
       <c r="BN100" s="43">
         <f t="shared" si="77"/>
-        <v>1.3019999999999998</v>
+        <v>0</v>
       </c>
       <c r="BO100" s="43" t="str">
         <f t="shared" si="84"/>
@@ -22239,15 +22720,15 @@
       </c>
       <c r="BP100" s="55">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>199.76278441558446</v>
       </c>
       <c r="BQ100" s="45">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>7.6908672000000011E-2</v>
       </c>
       <c r="BR100" s="24">
         <f t="shared" si="73"/>
-        <v>1.3019999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:70" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -22266,65 +22747,129 @@
       <c r="E101">
         <v>10</v>
       </c>
-      <c r="G101" s="35"/>
+      <c r="G101" s="35">
+        <v>45578.342094907406</v>
+      </c>
       <c r="H101" s="48">
         <v>5497.99</v>
       </c>
       <c r="I101" s="48"/>
-      <c r="J101" s="72"/>
-      <c r="K101" s="40"/>
-      <c r="L101" s="40"/>
-      <c r="M101" s="40"/>
-      <c r="N101" s="40"/>
-      <c r="O101" s="40"/>
-      <c r="P101" s="40"/>
-      <c r="Q101" s="40"/>
-      <c r="R101" s="40"/>
+      <c r="J101" s="71">
+        <v>5057.43</v>
+      </c>
+      <c r="K101" s="40">
+        <v>19.864000000000001</v>
+      </c>
+      <c r="L101" s="40">
+        <v>17.704000000000001</v>
+      </c>
+      <c r="M101" s="40">
+        <v>89.1</v>
+      </c>
+      <c r="N101" s="40">
+        <v>16.489999999999998</v>
+      </c>
+      <c r="O101" s="40">
+        <v>342</v>
+      </c>
+      <c r="P101" s="40">
+        <v>1.41</v>
+      </c>
+      <c r="Q101" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="R101" s="40">
+        <v>2.4900000000000002</v>
+      </c>
       <c r="S101" s="40"/>
-      <c r="T101" s="40"/>
-      <c r="U101" s="40"/>
-      <c r="V101" s="40"/>
-      <c r="W101" s="40"/>
-      <c r="X101" s="40"/>
-      <c r="Y101" s="40"/>
-      <c r="Z101" s="40"/>
-      <c r="AA101" s="40"/>
-      <c r="AB101" s="40"/>
-      <c r="AC101" s="40"/>
-      <c r="AD101" s="40"/>
-      <c r="AE101" s="17"/>
-      <c r="AF101" s="40"/>
-      <c r="AG101" s="40"/>
-      <c r="AH101" s="40"/>
-      <c r="AI101" s="40"/>
-      <c r="AJ101" s="40"/>
-      <c r="AK101" s="40"/>
-      <c r="AL101" s="40"/>
-      <c r="AM101" s="40"/>
-      <c r="AN101" s="40"/>
-      <c r="AO101" s="40"/>
+      <c r="T101" s="40">
+        <v>0.22</v>
+      </c>
+      <c r="U101" s="40">
+        <v>0.16</v>
+      </c>
+      <c r="V101" s="40">
+        <v>1.72</v>
+      </c>
+      <c r="W101" s="40">
+        <v>7.3120000000000003</v>
+      </c>
+      <c r="X101" s="40">
+        <v>40.1</v>
+      </c>
+      <c r="Y101" s="40">
+        <v>66.8</v>
+      </c>
+      <c r="Z101" s="40">
+        <v>2.15</v>
+      </c>
+      <c r="AA101" s="40">
+        <v>150.6</v>
+      </c>
+      <c r="AB101" s="40">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="AC101" s="40">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="AD101" s="40">
+        <v>54.5</v>
+      </c>
+      <c r="AE101" s="17">
+        <v>7.27</v>
+      </c>
+      <c r="AF101" s="40">
+        <v>440</v>
+      </c>
+      <c r="AG101" s="40">
+        <v>52.7</v>
+      </c>
+      <c r="AH101" s="40">
+        <v>7.3049999999999997</v>
+      </c>
+      <c r="AI101" s="40">
+        <v>34</v>
+      </c>
+      <c r="AJ101" s="40">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AK101" s="40">
+        <v>9.1</v>
+      </c>
+      <c r="AL101" s="40">
+        <v>0.2</v>
+      </c>
+      <c r="AM101" s="40">
+        <v>18.8</v>
+      </c>
+      <c r="AN101" s="40">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AO101" s="40">
+        <v>197</v>
+      </c>
       <c r="AP101" s="7"/>
       <c r="AQ101" s="41">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>0.52700000000000002</v>
       </c>
       <c r="AR101" s="41">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>8.3704512000000009E-2</v>
       </c>
       <c r="AS101" s="41">
         <f t="shared" si="74"/>
-        <v>-16.7</v>
+        <v>2.1000000000000014</v>
       </c>
       <c r="AT101" s="41">
         <f t="shared" si="75"/>
-        <v>-4.4000000000000004</v>
+        <v>0</v>
       </c>
       <c r="AU101" s="41">
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="AV101" s="68">
+      <c r="AV101" s="67">
         <v>2.4</v>
       </c>
       <c r="AW101">
@@ -22346,27 +22891,27 @@
       <c r="BD101" s="22"/>
       <c r="BE101" s="42">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>1.3950752000000002E-3</v>
       </c>
       <c r="BF101" s="42">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>2.0089082880000007</v>
       </c>
       <c r="BG101" s="42">
         <f t="shared" si="80"/>
-        <v>173.6</v>
-      </c>
-      <c r="BH101" s="43" t="str">
+        <v>197</v>
+      </c>
+      <c r="BH101" s="43">
         <f t="shared" si="81"/>
-        <v/>
-      </c>
-      <c r="BI101" s="43" t="str">
+        <v>9.5431472081218272E-2</v>
+      </c>
+      <c r="BI101" s="43">
         <f t="shared" si="82"/>
-        <v/>
+        <v>9.4E-2</v>
       </c>
       <c r="BJ101" s="43">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>120.53449728000001</v>
       </c>
       <c r="BK101" s="43" t="str">
         <f t="shared" si="70"/>
@@ -22378,11 +22923,11 @@
       </c>
       <c r="BM101" s="44">
         <f t="shared" si="67"/>
-        <v>0</v>
+        <v>8.3704512000000009E-2</v>
       </c>
       <c r="BN101" s="43">
         <f t="shared" si="77"/>
-        <v>1.3019999999999998</v>
+        <v>0</v>
       </c>
       <c r="BO101" s="43" t="str">
         <f t="shared" si="84"/>
@@ -22390,15 +22935,15 @@
       </c>
       <c r="BP101" s="55">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>217.41431688311692</v>
       </c>
       <c r="BQ101" s="45">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>8.3704512000000009E-2</v>
       </c>
       <c r="BR101" s="24">
         <f t="shared" si="73"/>
-        <v>1.3019999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:70" x14ac:dyDescent="0.3">
@@ -22418,12 +22963,14 @@
         <v>11</v>
       </c>
       <c r="F102" s="3"/>
-      <c r="G102" s="61"/>
+      <c r="G102" s="60"/>
       <c r="H102" s="37">
         <v>6057.48</v>
       </c>
       <c r="I102" s="3"/>
-      <c r="J102" s="78"/>
+      <c r="J102" s="74">
+        <v>4784.49</v>
+      </c>
       <c r="K102" s="3"/>
       <c r="L102" s="3"/>
       <c r="M102" s="3"/>
@@ -22444,7 +22991,7 @@
       <c r="AB102" s="3"/>
       <c r="AC102" s="3"/>
       <c r="AD102" s="3"/>
-      <c r="AE102" s="61"/>
+      <c r="AE102" s="60"/>
       <c r="AF102" s="3"/>
       <c r="AG102" s="3"/>
       <c r="AH102" s="3"/>
@@ -22466,17 +23013,17 @@
       </c>
       <c r="AS102" s="32">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>-76268.0703125</v>
       </c>
       <c r="AT102" s="32">
         <f t="shared" si="75"/>
-        <v>0</v>
+        <v>-23830.064453125</v>
       </c>
       <c r="AU102" s="32">
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="AV102" s="66">
+      <c r="AV102" s="65">
         <v>60</v>
       </c>
       <c r="AW102" s="3">
@@ -22541,7 +23088,7 @@
         <f t="shared" si="84"/>
         <v>0</v>
       </c>
-      <c r="BP102" s="58">
+      <c r="BP102" s="57">
         <f t="shared" si="71"/>
         <v>0</v>
       </c>
@@ -22574,20 +23121,111 @@
       <c r="H103" s="48">
         <v>6057.48</v>
       </c>
-      <c r="J103" s="79"/>
-      <c r="AE103" s="54"/>
+      <c r="J103" s="75">
+        <v>5644.7250000000004</v>
+      </c>
+      <c r="K103">
+        <v>19.527999999999999</v>
+      </c>
+      <c r="L103">
+        <v>17.184999999999999</v>
+      </c>
+      <c r="M103">
+        <v>88</v>
+      </c>
+      <c r="N103">
+        <v>16.579999999999998</v>
+      </c>
+      <c r="O103">
+        <v>338</v>
+      </c>
+      <c r="P103">
+        <v>1.46</v>
+      </c>
+      <c r="Q103">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="R103">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="T103">
+        <v>0.25</v>
+      </c>
+      <c r="U103">
+        <v>0.15</v>
+      </c>
+      <c r="V103">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="W103">
+        <v>7.3150000000000004</v>
+      </c>
+      <c r="X103">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="Y103">
+        <v>59</v>
+      </c>
+      <c r="Z103">
+        <v>1.9</v>
+      </c>
+      <c r="AA103">
+        <v>148.69999999999999</v>
+      </c>
+      <c r="AB103">
+        <v>17.5</v>
+      </c>
+      <c r="AC103">
+        <v>34</v>
+      </c>
+      <c r="AD103">
+        <v>48</v>
+      </c>
+      <c r="AE103" s="54">
+        <v>7.274</v>
+      </c>
+      <c r="AF103">
+        <v>409</v>
+      </c>
+      <c r="AG103">
+        <v>49.1</v>
+      </c>
+      <c r="AH103">
+        <v>7.3070000000000004</v>
+      </c>
+      <c r="AI103">
+        <v>33.9</v>
+      </c>
+      <c r="AJ103">
+        <v>2</v>
+      </c>
+      <c r="AK103">
+        <v>10.1</v>
+      </c>
+      <c r="AL103">
+        <v>0.3</v>
+      </c>
+      <c r="AM103">
+        <v>21.7</v>
+      </c>
+      <c r="AN103">
+        <v>4</v>
+      </c>
+      <c r="AO103">
+        <v>196.6</v>
+      </c>
       <c r="AP103" s="40"/>
       <c r="AQ103" s="41">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>0.49099999999999999</v>
       </c>
       <c r="AR103" s="41">
         <f t="shared" ref="AR103:AR119" si="85">BQ103</f>
-        <v>0</v>
+        <v>8.1085703999999995E-2</v>
       </c>
       <c r="AS103" s="41">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT103" s="41">
         <f t="shared" si="75"/>
@@ -22597,7 +23235,7 @@
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="AV103" s="67">
+      <c r="AV103" s="66">
         <v>2.4</v>
       </c>
       <c r="AW103">
@@ -22620,27 +23258,27 @@
       <c r="BD103" s="22"/>
       <c r="BE103" s="42">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>1.3514283999999999E-3</v>
       </c>
       <c r="BF103" s="42">
         <f t="shared" ref="BF103:BF119" si="86">BE103*24*60</f>
-        <v>0</v>
+        <v>1.9460568959999998</v>
       </c>
       <c r="BG103" s="42">
         <f t="shared" si="80"/>
-        <v>171.2</v>
-      </c>
-      <c r="BH103" s="43" t="str">
+        <v>196.6</v>
+      </c>
+      <c r="BH103" s="43">
         <f t="shared" si="81"/>
-        <v/>
-      </c>
-      <c r="BI103" s="43" t="str">
+        <v>0.1103763987792472</v>
+      </c>
+      <c r="BI103" s="43">
         <f t="shared" si="82"/>
-        <v/>
+        <v>0.1085</v>
       </c>
       <c r="BJ103" s="43">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>116.76341375999999</v>
       </c>
       <c r="BK103" s="43" t="str">
         <f t="shared" si="70"/>
@@ -22652,11 +23290,11 @@
       </c>
       <c r="BM103" s="44">
         <f t="shared" si="67"/>
-        <v>0</v>
+        <v>8.1085703999999995E-2</v>
       </c>
       <c r="BN103" s="43">
         <f t="shared" si="77"/>
-        <v>1.2839999999999998</v>
+        <v>0</v>
       </c>
       <c r="BO103" s="43" t="str">
         <f t="shared" si="84"/>
@@ -22664,15 +23302,15 @@
       </c>
       <c r="BP103" s="55">
         <f t="shared" ref="BP103:BP119" si="87">IF(BK103&lt;&gt;"",BK103/0.000385,IF(BL103&lt;&gt;"",BL103/0.000385,BM103/0.000385))</f>
-        <v>0</v>
+        <v>210.61221818181818</v>
       </c>
       <c r="BQ103" s="45">
         <f t="shared" ref="BQ103:BQ119" si="88">IF(BK103&lt;&gt;"",BK103,IF(BL103&lt;&gt;"",BL103,BM103))</f>
-        <v>0</v>
+        <v>8.1085703999999995E-2</v>
       </c>
       <c r="BR103" s="24">
         <f t="shared" ref="BR103:BR119" si="89">IF(BN103&lt;&gt;"",BN103,BO103)</f>
-        <v>1.2839999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:70" x14ac:dyDescent="0.3">
@@ -22695,21 +23333,111 @@
       <c r="H104" s="48">
         <v>6057.48</v>
       </c>
-      <c r="J104" s="79"/>
-      <c r="T104" s="56"/>
-      <c r="AE104" s="54"/>
+      <c r="J104" s="75">
+        <v>5534.5349999999999</v>
+      </c>
+      <c r="K104">
+        <v>19.443000000000001</v>
+      </c>
+      <c r="L104">
+        <v>17.125</v>
+      </c>
+      <c r="M104">
+        <v>88.1</v>
+      </c>
+      <c r="N104">
+        <v>16.71</v>
+      </c>
+      <c r="O104">
+        <v>344</v>
+      </c>
+      <c r="P104">
+        <v>1.45</v>
+      </c>
+      <c r="Q104">
+        <v>0.31</v>
+      </c>
+      <c r="R104">
+        <v>2.23</v>
+      </c>
+      <c r="T104" s="106">
+        <v>0.23</v>
+      </c>
+      <c r="U104">
+        <v>0.2</v>
+      </c>
+      <c r="V104">
+        <v>1.39</v>
+      </c>
+      <c r="W104">
+        <v>7.3170000000000002</v>
+      </c>
+      <c r="X104">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="Y104">
+        <v>62.9</v>
+      </c>
+      <c r="Z104">
+        <v>1.93</v>
+      </c>
+      <c r="AA104">
+        <v>148.69999999999999</v>
+      </c>
+      <c r="AB104">
+        <v>15</v>
+      </c>
+      <c r="AC104">
+        <v>29.1</v>
+      </c>
+      <c r="AD104">
+        <v>51.2</v>
+      </c>
+      <c r="AE104" s="54">
+        <v>7.2750000000000004</v>
+      </c>
+      <c r="AF104">
+        <v>411</v>
+      </c>
+      <c r="AG104">
+        <v>49.5</v>
+      </c>
+      <c r="AH104">
+        <v>7.3070000000000004</v>
+      </c>
+      <c r="AI104">
+        <v>33.9</v>
+      </c>
+      <c r="AJ104">
+        <v>2.1</v>
+      </c>
+      <c r="AK104">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="AL104">
+        <v>0.3</v>
+      </c>
+      <c r="AM104">
+        <v>22.2</v>
+      </c>
+      <c r="AN104">
+        <v>4.3</v>
+      </c>
+      <c r="AO104">
+        <v>195.3</v>
+      </c>
       <c r="AP104" s="40"/>
       <c r="AQ104" s="41">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>0.495</v>
       </c>
       <c r="AR104" s="41">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>8.0268300000000015E-2</v>
       </c>
       <c r="AS104" s="41">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>2.5999999999999979</v>
       </c>
       <c r="AT104" s="41">
         <f t="shared" si="75"/>
@@ -22719,7 +23447,7 @@
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="AV104" s="67">
+      <c r="AV104" s="66">
         <v>2.4</v>
       </c>
       <c r="AW104">
@@ -22742,27 +23470,27 @@
       <c r="BD104" s="22"/>
       <c r="BE104" s="42">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>1.3378050000000001E-3</v>
       </c>
       <c r="BF104" s="42">
         <f t="shared" si="86"/>
-        <v>0</v>
+        <v>1.9264392000000001</v>
       </c>
       <c r="BG104" s="42">
         <f t="shared" si="80"/>
-        <v>171.2</v>
-      </c>
-      <c r="BH104" s="43" t="str">
+        <v>195.3</v>
+      </c>
+      <c r="BH104" s="43">
         <f t="shared" si="81"/>
-        <v/>
-      </c>
-      <c r="BI104" s="43" t="str">
+        <v>0.11367127496159753</v>
+      </c>
+      <c r="BI104" s="43">
         <f t="shared" si="82"/>
-        <v/>
+        <v>0.111</v>
       </c>
       <c r="BJ104" s="43">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>115.58635200000002</v>
       </c>
       <c r="BK104" s="43" t="str">
         <f t="shared" si="70"/>
@@ -22774,11 +23502,11 @@
       </c>
       <c r="BM104" s="44">
         <f t="shared" si="67"/>
-        <v>0</v>
+        <v>8.0268300000000015E-2</v>
       </c>
       <c r="BN104" s="43">
         <f t="shared" si="77"/>
-        <v>1.2839999999999998</v>
+        <v>0</v>
       </c>
       <c r="BO104" s="43" t="str">
         <f t="shared" si="84"/>
@@ -22786,15 +23514,15 @@
       </c>
       <c r="BP104" s="55">
         <f t="shared" si="87"/>
-        <v>0</v>
+        <v>208.48909090909095</v>
       </c>
       <c r="BQ104" s="45">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>8.0268300000000015E-2</v>
       </c>
       <c r="BR104" s="24">
         <f t="shared" si="89"/>
-        <v>1.2839999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:70" x14ac:dyDescent="0.3">
@@ -22817,7 +23545,7 @@
       <c r="H105" s="48">
         <v>6057.48</v>
       </c>
-      <c r="J105" s="79"/>
+      <c r="J105" s="75"/>
       <c r="AE105" s="54"/>
       <c r="AP105" s="40"/>
       <c r="AQ105" s="41">
@@ -22840,7 +23568,7 @@
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="AV105" s="67">
+      <c r="AV105" s="66">
         <v>2.4</v>
       </c>
       <c r="AW105">
@@ -22938,12 +23666,103 @@
       <c r="H106" s="48">
         <v>6057.48</v>
       </c>
-      <c r="J106" s="79"/>
-      <c r="AE106" s="54"/>
+      <c r="J106" s="75">
+        <v>5935.3950000000004</v>
+      </c>
+      <c r="K106">
+        <v>19.686</v>
+      </c>
+      <c r="L106">
+        <v>16.588999999999999</v>
+      </c>
+      <c r="M106">
+        <v>84.3</v>
+      </c>
+      <c r="N106">
+        <v>16.89</v>
+      </c>
+      <c r="O106">
+        <v>358</v>
+      </c>
+      <c r="P106">
+        <v>1.66</v>
+      </c>
+      <c r="Q106">
+        <v>0.31</v>
+      </c>
+      <c r="R106">
+        <v>0.72</v>
+      </c>
+      <c r="T106">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="U106">
+        <v>0.62</v>
+      </c>
+      <c r="V106">
+        <v>1.37</v>
+      </c>
+      <c r="W106">
+        <v>7.3029999999999999</v>
+      </c>
+      <c r="X106">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="Y106">
+        <v>54.7</v>
+      </c>
+      <c r="Z106">
+        <v>1.63</v>
+      </c>
+      <c r="AA106">
+        <v>156.80000000000001</v>
+      </c>
+      <c r="AB106">
+        <v>17</v>
+      </c>
+      <c r="AC106">
+        <v>34</v>
+      </c>
+      <c r="AD106">
+        <v>44.3</v>
+      </c>
+      <c r="AE106" s="54">
+        <v>7.2619999999999996</v>
+      </c>
+      <c r="AF106">
+        <v>411</v>
+      </c>
+      <c r="AG106">
+        <v>47.8</v>
+      </c>
+      <c r="AH106">
+        <v>7.3019999999999996</v>
+      </c>
+      <c r="AI106">
+        <v>33.9</v>
+      </c>
+      <c r="AJ106">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AK106">
+        <v>5.8</v>
+      </c>
+      <c r="AL106">
+        <v>0.3</v>
+      </c>
+      <c r="AM106">
+        <v>28.9</v>
+      </c>
+      <c r="AN106">
+        <v>6</v>
+      </c>
+      <c r="AO106">
+        <v>200.6</v>
+      </c>
       <c r="AP106" s="40"/>
       <c r="AQ106" s="41">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>0.47799999999999998</v>
       </c>
       <c r="AR106" s="41">
         <f t="shared" si="85"/>
@@ -22951,7 +23770,7 @@
       </c>
       <c r="AS106" s="41">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AT106" s="41">
         <f t="shared" si="75"/>
@@ -22961,7 +23780,7 @@
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="AV106" s="67">
+      <c r="AV106" s="66">
         <v>2.4</v>
       </c>
       <c r="AW106">
@@ -22983,23 +23802,23 @@
       <c r="BD106" s="22"/>
       <c r="BE106" s="42">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>1.33110136E-3</v>
       </c>
       <c r="BF106" s="42">
         <f t="shared" si="86"/>
-        <v>0</v>
+        <v>1.9167859584</v>
       </c>
       <c r="BG106" s="42">
         <f t="shared" si="80"/>
-        <v>171.2</v>
-      </c>
-      <c r="BH106" s="43" t="str">
+        <v>200.6</v>
+      </c>
+      <c r="BH106" s="43">
         <f t="shared" si="81"/>
-        <v/>
-      </c>
-      <c r="BI106" s="43" t="str">
+        <v>0.1440677966101695</v>
+      </c>
+      <c r="BI106" s="43">
         <f t="shared" si="82"/>
-        <v/>
+        <v>0.14449999999999999</v>
       </c>
       <c r="BJ106" s="43">
         <f t="shared" si="83"/>
@@ -23019,7 +23838,7 @@
       </c>
       <c r="BN106" s="43">
         <f t="shared" si="77"/>
-        <v>1.2839999999999998</v>
+        <v>1.1434200000000001</v>
       </c>
       <c r="BO106" s="43" t="str">
         <f t="shared" si="84"/>
@@ -23035,7 +23854,7 @@
       </c>
       <c r="BR106" s="24">
         <f t="shared" si="89"/>
-        <v>1.2839999999999998</v>
+        <v>1.1434200000000001</v>
       </c>
     </row>
     <row r="107" spans="1:70" x14ac:dyDescent="0.3">
@@ -23058,13 +23877,103 @@
       <c r="H107" s="48">
         <v>6057.48</v>
       </c>
-      <c r="J107" s="79"/>
-      <c r="AC107" s="57"/>
-      <c r="AE107" s="54"/>
+      <c r="J107" s="75">
+        <v>6029.7</v>
+      </c>
+      <c r="K107">
+        <v>17.741</v>
+      </c>
+      <c r="L107">
+        <v>14.32</v>
+      </c>
+      <c r="M107">
+        <v>80.7</v>
+      </c>
+      <c r="N107">
+        <v>16.829999999999998</v>
+      </c>
+      <c r="O107">
+        <v>359</v>
+      </c>
+      <c r="P107">
+        <v>1.94</v>
+      </c>
+      <c r="Q107">
+        <v>0.35</v>
+      </c>
+      <c r="R107">
+        <v>0.35</v>
+      </c>
+      <c r="T107">
+        <v>0.34</v>
+      </c>
+      <c r="U107">
+        <v>0.87</v>
+      </c>
+      <c r="V107">
+        <v>1.34</v>
+      </c>
+      <c r="W107">
+        <v>7.3079999999999998</v>
+      </c>
+      <c r="X107">
+        <v>33.4</v>
+      </c>
+      <c r="Y107">
+        <v>55.2</v>
+      </c>
+      <c r="Z107">
+        <v>1.92</v>
+      </c>
+      <c r="AA107">
+        <v>161.1</v>
+      </c>
+      <c r="AB107">
+        <v>14.8</v>
+      </c>
+      <c r="AC107" s="56">
+        <v>29.3</v>
+      </c>
+      <c r="AD107">
+        <v>44.7</v>
+      </c>
+      <c r="AE107" s="54">
+        <v>7.266</v>
+      </c>
+      <c r="AF107">
+        <v>405</v>
+      </c>
+      <c r="AG107">
+        <v>51.2</v>
+      </c>
+      <c r="AH107">
+        <v>7.3079999999999998</v>
+      </c>
+      <c r="AI107">
+        <v>33.9</v>
+      </c>
+      <c r="AJ107">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AK107">
+        <v>4.7</v>
+      </c>
+      <c r="AL107">
+        <v>0.3</v>
+      </c>
+      <c r="AM107">
+        <v>30.7</v>
+      </c>
+      <c r="AN107">
+        <v>5.7</v>
+      </c>
+      <c r="AO107">
+        <v>198.1</v>
+      </c>
       <c r="AP107" s="40"/>
       <c r="AQ107" s="41">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>0.51200000000000001</v>
       </c>
       <c r="AR107" s="41">
         <f t="shared" si="85"/>
@@ -23072,17 +23981,17 @@
       </c>
       <c r="AS107" s="41">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>2.5999999999999979</v>
       </c>
       <c r="AT107" s="41">
         <f t="shared" si="75"/>
-        <v>0</v>
+        <v>0.60000000000000053</v>
       </c>
       <c r="AU107" s="41">
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="AV107" s="67">
+      <c r="AV107" s="66">
         <v>2.4</v>
       </c>
       <c r="AW107">
@@ -23104,23 +24013,23 @@
       <c r="BD107" s="22"/>
       <c r="BE107" s="42">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>1.1347168000000001E-3</v>
       </c>
       <c r="BF107" s="42">
         <f t="shared" si="86"/>
-        <v>0</v>
+        <v>1.633992192</v>
       </c>
       <c r="BG107" s="42">
         <f t="shared" si="80"/>
-        <v>171.2</v>
-      </c>
-      <c r="BH107" s="43" t="str">
+        <v>198.1</v>
+      </c>
+      <c r="BH107" s="43">
         <f t="shared" si="81"/>
-        <v/>
-      </c>
-      <c r="BI107" s="43" t="str">
+        <v>0.15497223624432105</v>
+      </c>
+      <c r="BI107" s="43">
         <f t="shared" si="82"/>
-        <v/>
+        <v>0.1535</v>
       </c>
       <c r="BJ107" s="43">
         <f t="shared" si="83"/>
@@ -23179,13 +24088,103 @@
       <c r="H108" s="48">
         <v>6057.48</v>
       </c>
-      <c r="J108" s="79"/>
-      <c r="AC108" s="57"/>
-      <c r="AE108" s="54"/>
+      <c r="J108" s="75">
+        <v>6010.7250000000004</v>
+      </c>
+      <c r="K108">
+        <v>21.222000000000001</v>
+      </c>
+      <c r="L108">
+        <v>17.372</v>
+      </c>
+      <c r="M108">
+        <v>81.900000000000006</v>
+      </c>
+      <c r="N108">
+        <v>16.72</v>
+      </c>
+      <c r="O108">
+        <v>354</v>
+      </c>
+      <c r="P108">
+        <v>1.79</v>
+      </c>
+      <c r="Q108">
+        <v>0.33</v>
+      </c>
+      <c r="R108">
+        <v>0.33</v>
+      </c>
+      <c r="T108">
+        <v>0.31</v>
+      </c>
+      <c r="U108">
+        <v>0.68</v>
+      </c>
+      <c r="V108">
+        <v>1.23</v>
+      </c>
+      <c r="W108">
+        <v>7.3019999999999996</v>
+      </c>
+      <c r="X108">
+        <v>33.4</v>
+      </c>
+      <c r="Y108">
+        <v>61.8</v>
+      </c>
+      <c r="Z108">
+        <v>1.74</v>
+      </c>
+      <c r="AA108">
+        <v>157.69999999999999</v>
+      </c>
+      <c r="AB108">
+        <v>14.6</v>
+      </c>
+      <c r="AC108" s="56">
+        <v>29.3</v>
+      </c>
+      <c r="AD108">
+        <v>50.3</v>
+      </c>
+      <c r="AE108" s="54">
+        <v>7.26</v>
+      </c>
+      <c r="AF108">
+        <v>409</v>
+      </c>
+      <c r="AG108">
+        <v>49.8</v>
+      </c>
+      <c r="AH108">
+        <v>7.3049999999999997</v>
+      </c>
+      <c r="AI108">
+        <v>33.9</v>
+      </c>
+      <c r="AJ108">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AK108">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="AL108">
+        <v>0.4</v>
+      </c>
+      <c r="AM108">
+        <v>30.4</v>
+      </c>
+      <c r="AN108">
+        <v>6.1</v>
+      </c>
+      <c r="AO108">
+        <v>200.1</v>
+      </c>
       <c r="AP108" s="40"/>
       <c r="AQ108" s="41">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>0.498</v>
       </c>
       <c r="AR108" s="41">
         <f t="shared" si="85"/>
@@ -23193,17 +24192,17 @@
       </c>
       <c r="AS108" s="41">
         <f t="shared" ref="AS108:AS119" si="90">AM108-AM99</f>
-        <v>0</v>
+        <v>2.6999999999999993</v>
       </c>
       <c r="AT108" s="41">
         <f t="shared" ref="AT108:AT119" si="91">AN108-AN99</f>
-        <v>0</v>
+        <v>0.59999999999999964</v>
       </c>
       <c r="AU108" s="41">
         <f t="shared" ref="AU108:AU119" si="92">AP99-AP108</f>
         <v>0</v>
       </c>
-      <c r="AV108" s="67">
+      <c r="AV108" s="66">
         <v>2.4</v>
       </c>
       <c r="AW108">
@@ -23225,23 +24224,23 @@
       <c r="BD108" s="22"/>
       <c r="BE108" s="42">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>1.3904548800000001E-3</v>
       </c>
       <c r="BF108" s="42">
         <f t="shared" si="86"/>
-        <v>0</v>
+        <v>2.0022550272000004</v>
       </c>
       <c r="BG108" s="42">
         <f t="shared" si="80"/>
-        <v>171.2</v>
-      </c>
-      <c r="BH108" s="43" t="str">
+        <v>200.1</v>
+      </c>
+      <c r="BH108" s="43">
         <f t="shared" si="81"/>
-        <v/>
-      </c>
-      <c r="BI108" s="43" t="str">
+        <v>0.15192403798100948</v>
+      </c>
+      <c r="BI108" s="43">
         <f t="shared" si="82"/>
-        <v/>
+        <v>0.152</v>
       </c>
       <c r="BJ108" s="43">
         <f t="shared" si="83"/>
@@ -23300,20 +24299,111 @@
       <c r="H109" s="48">
         <v>6057.48</v>
       </c>
-      <c r="J109" s="79"/>
-      <c r="AE109" s="54"/>
+      <c r="J109" s="75">
+        <v>5068.8599999999997</v>
+      </c>
+      <c r="K109">
+        <v>19.187999999999999</v>
+      </c>
+      <c r="L109">
+        <v>16.731000000000002</v>
+      </c>
+      <c r="M109">
+        <v>87.2</v>
+      </c>
+      <c r="N109">
+        <v>16.88</v>
+      </c>
+      <c r="O109">
+        <v>349</v>
+      </c>
+      <c r="P109">
+        <v>1.41</v>
+      </c>
+      <c r="Q109">
+        <v>0.3</v>
+      </c>
+      <c r="R109">
+        <v>1.96</v>
+      </c>
+      <c r="T109">
+        <v>0.26</v>
+      </c>
+      <c r="U109">
+        <v>0.19</v>
+      </c>
+      <c r="V109">
+        <v>1.77</v>
+      </c>
+      <c r="W109">
+        <v>7.3070000000000004</v>
+      </c>
+      <c r="X109">
+        <v>50.3</v>
+      </c>
+      <c r="Y109">
+        <v>59.8</v>
+      </c>
+      <c r="Z109">
+        <v>1.96</v>
+      </c>
+      <c r="AA109">
+        <v>153.30000000000001</v>
+      </c>
+      <c r="AB109">
+        <v>22.3</v>
+      </c>
+      <c r="AC109">
+        <v>44.1</v>
+      </c>
+      <c r="AD109">
+        <v>48.6</v>
+      </c>
+      <c r="AE109" s="54">
+        <v>7.2649999999999997</v>
+      </c>
+      <c r="AF109">
+        <v>522</v>
+      </c>
+      <c r="AG109">
+        <v>51.4</v>
+      </c>
+      <c r="AH109">
+        <v>7.3049999999999997</v>
+      </c>
+      <c r="AI109">
+        <v>34</v>
+      </c>
+      <c r="AJ109">
+        <v>2.6</v>
+      </c>
+      <c r="AK109">
+        <v>9.9</v>
+      </c>
+      <c r="AL109">
+        <v>0.2</v>
+      </c>
+      <c r="AM109">
+        <v>21.1</v>
+      </c>
+      <c r="AN109">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AO109">
+        <v>198.6</v>
+      </c>
       <c r="AP109" s="40"/>
       <c r="AQ109" s="41">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>0.51400000000000001</v>
       </c>
       <c r="AR109" s="41">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>7.9746638400000014E-2</v>
       </c>
       <c r="AS109" s="41">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT109" s="41">
         <f t="shared" si="91"/>
@@ -23323,7 +24413,7 @@
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="AV109" s="67">
+      <c r="AV109" s="66">
         <v>2.4</v>
       </c>
       <c r="AW109">
@@ -23345,27 +24435,27 @@
       <c r="BD109" s="22"/>
       <c r="BE109" s="42">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>1.3291106400000001E-3</v>
       </c>
       <c r="BF109" s="42">
         <f t="shared" si="86"/>
-        <v>0</v>
+        <v>1.9139193215999999</v>
       </c>
       <c r="BG109" s="42">
         <f t="shared" si="80"/>
-        <v>171.2</v>
-      </c>
-      <c r="BH109" s="43" t="str">
+        <v>198.6</v>
+      </c>
+      <c r="BH109" s="43">
         <f t="shared" si="81"/>
-        <v/>
-      </c>
-      <c r="BI109" s="43" t="str">
+        <v>0.10624370594159115</v>
+      </c>
+      <c r="BI109" s="43">
         <f t="shared" si="82"/>
-        <v/>
+        <v>0.10550000000000001</v>
       </c>
       <c r="BJ109" s="43">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>114.83515929600001</v>
       </c>
       <c r="BK109" s="43" t="str">
         <f t="shared" si="70"/>
@@ -23377,11 +24467,11 @@
       </c>
       <c r="BM109" s="44">
         <f t="shared" si="67"/>
-        <v>0</v>
+        <v>7.9746638400000014E-2</v>
       </c>
       <c r="BN109" s="43">
         <f t="shared" si="77"/>
-        <v>1.2839999999999998</v>
+        <v>0</v>
       </c>
       <c r="BO109" s="43" t="str">
         <f t="shared" si="84"/>
@@ -23389,15 +24479,15 @@
       </c>
       <c r="BP109" s="55">
         <f t="shared" si="87"/>
-        <v>0</v>
+        <v>207.13412571428577</v>
       </c>
       <c r="BQ109" s="45">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>7.9746638400000014E-2</v>
       </c>
       <c r="BR109" s="24">
         <f t="shared" si="89"/>
-        <v>1.2839999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:70" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -23420,20 +24510,111 @@
       <c r="H110" s="48">
         <v>6057.48</v>
       </c>
-      <c r="J110" s="79"/>
-      <c r="AE110" s="54"/>
+      <c r="J110" s="75">
+        <v>5375.8649999999998</v>
+      </c>
+      <c r="K110">
+        <v>18.661000000000001</v>
+      </c>
+      <c r="L110">
+        <v>16.321999999999999</v>
+      </c>
+      <c r="M110">
+        <v>87.5</v>
+      </c>
+      <c r="N110">
+        <v>16.64</v>
+      </c>
+      <c r="O110">
+        <v>346</v>
+      </c>
+      <c r="P110">
+        <v>1.43</v>
+      </c>
+      <c r="Q110">
+        <v>0.3</v>
+      </c>
+      <c r="R110">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="T110">
+        <v>0.22</v>
+      </c>
+      <c r="U110">
+        <v>0.2</v>
+      </c>
+      <c r="V110">
+        <v>1.53</v>
+      </c>
+      <c r="W110">
+        <v>7.2969999999999997</v>
+      </c>
+      <c r="X110">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="Y110">
+        <v>51.4</v>
+      </c>
+      <c r="Z110">
+        <v>2.11</v>
+      </c>
+      <c r="AA110">
+        <v>153.6</v>
+      </c>
+      <c r="AB110">
+        <v>17</v>
+      </c>
+      <c r="AC110">
+        <v>34.5</v>
+      </c>
+      <c r="AD110">
+        <v>41.7</v>
+      </c>
+      <c r="AE110" s="54">
+        <v>7.2549999999999999</v>
+      </c>
+      <c r="AF110">
+        <v>441</v>
+      </c>
+      <c r="AG110">
+        <v>50.3</v>
+      </c>
+      <c r="AH110">
+        <v>7.3049999999999997</v>
+      </c>
+      <c r="AI110">
+        <v>34</v>
+      </c>
+      <c r="AJ110">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AK110">
+        <v>10.3</v>
+      </c>
+      <c r="AL110">
+        <v>0.2</v>
+      </c>
+      <c r="AM110">
+        <v>20.9</v>
+      </c>
+      <c r="AN110">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AO110">
+        <v>197.2</v>
+      </c>
       <c r="AP110" s="7"/>
       <c r="AQ110" s="41">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>0.503</v>
       </c>
       <c r="AR110" s="41">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>7.7248761599999993E-2</v>
       </c>
       <c r="AS110" s="41">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>2.0999999999999979</v>
       </c>
       <c r="AT110" s="41">
         <f t="shared" si="91"/>
@@ -23443,7 +24624,7 @@
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="AV110" s="68">
+      <c r="AV110" s="67">
         <v>2.4</v>
       </c>
       <c r="AW110">
@@ -23465,27 +24646,27 @@
       <c r="BD110" s="22"/>
       <c r="BE110" s="42">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>1.2874793600000001E-3</v>
       </c>
       <c r="BF110" s="42">
         <f t="shared" si="86"/>
-        <v>0</v>
+        <v>1.8539702784000001</v>
       </c>
       <c r="BG110" s="42">
         <f t="shared" si="80"/>
-        <v>171.2</v>
-      </c>
-      <c r="BH110" s="43" t="str">
+        <v>197.2</v>
+      </c>
+      <c r="BH110" s="43">
         <f t="shared" si="81"/>
-        <v/>
-      </c>
-      <c r="BI110" s="43" t="str">
+        <v>0.10598377281947262</v>
+      </c>
+      <c r="BI110" s="43">
         <f t="shared" si="82"/>
-        <v/>
+        <v>0.1045</v>
       </c>
       <c r="BJ110" s="43">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>111.238216704</v>
       </c>
       <c r="BK110" s="43" t="str">
         <f t="shared" si="70"/>
@@ -23497,11 +24678,11 @@
       </c>
       <c r="BM110" s="44">
         <f t="shared" si="67"/>
-        <v>0</v>
+        <v>7.7248761599999993E-2</v>
       </c>
       <c r="BN110" s="43">
         <f t="shared" si="77"/>
-        <v>1.2839999999999998</v>
+        <v>0</v>
       </c>
       <c r="BO110" s="43" t="str">
         <f t="shared" si="84"/>
@@ -23509,15 +24690,15 @@
       </c>
       <c r="BP110" s="55">
         <f t="shared" si="87"/>
-        <v>0</v>
+        <v>200.64613402597402</v>
       </c>
       <c r="BQ110" s="45">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>7.7248761599999993E-2</v>
       </c>
       <c r="BR110" s="24">
         <f t="shared" si="89"/>
-        <v>1.2839999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:70" x14ac:dyDescent="0.3">
@@ -23537,12 +24718,12 @@
         <v>12</v>
       </c>
       <c r="F111" s="3"/>
-      <c r="G111" s="61"/>
+      <c r="G111" s="60"/>
       <c r="H111" s="37">
         <v>6478.05</v>
       </c>
       <c r="I111" s="3"/>
-      <c r="J111" s="78"/>
+      <c r="J111" s="74"/>
       <c r="K111" s="3"/>
       <c r="L111" s="3"/>
       <c r="M111" s="3"/>
@@ -23563,7 +24744,7 @@
       <c r="AB111" s="3"/>
       <c r="AC111" s="3"/>
       <c r="AD111" s="3"/>
-      <c r="AE111" s="61"/>
+      <c r="AE111" s="60"/>
       <c r="AF111" s="3"/>
       <c r="AG111" s="3"/>
       <c r="AH111" s="3"/>
@@ -23595,7 +24776,7 @@
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="AV111" s="66">
+      <c r="AV111" s="65">
         <v>60</v>
       </c>
       <c r="AW111" s="3">
@@ -23660,7 +24841,7 @@
         <f t="shared" si="84"/>
         <v>0</v>
       </c>
-      <c r="BP111" s="58">
+      <c r="BP111" s="57">
         <f t="shared" si="87"/>
         <v>0</v>
       </c>
@@ -23693,7 +24874,7 @@
       <c r="H112" s="48">
         <v>6478.05</v>
       </c>
-      <c r="J112" s="79"/>
+      <c r="J112" s="75"/>
       <c r="AE112" s="54"/>
       <c r="AP112" s="40"/>
       <c r="AQ112" s="41">
@@ -23706,17 +24887,17 @@
       </c>
       <c r="AS112" s="41">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>-21.7</v>
       </c>
       <c r="AT112" s="41">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AU112" s="41">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="AV112" s="67">
+      <c r="AV112" s="66">
         <v>2.4</v>
       </c>
       <c r="AW112">
@@ -23814,7 +24995,7 @@
       <c r="H113" s="48">
         <v>6478.05</v>
       </c>
-      <c r="J113" s="79"/>
+      <c r="J113" s="75"/>
       <c r="AE113" s="54"/>
       <c r="AP113" s="40"/>
       <c r="AQ113" s="41">
@@ -23827,17 +25008,17 @@
       </c>
       <c r="AS113" s="41">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>-22.2</v>
       </c>
       <c r="AT113" s="41">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>-4.3</v>
       </c>
       <c r="AU113" s="41">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="AV113" s="67">
+      <c r="AV113" s="66">
         <v>2.4</v>
       </c>
       <c r="AW113">
@@ -23935,7 +25116,7 @@
       <c r="H114" s="48">
         <v>6478.05</v>
       </c>
-      <c r="J114" s="79"/>
+      <c r="J114" s="75"/>
       <c r="AE114" s="54"/>
       <c r="AP114" s="40"/>
       <c r="AQ114" s="41">
@@ -23958,7 +25139,7 @@
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="AV114" s="67">
+      <c r="AV114" s="66">
         <v>2.4</v>
       </c>
       <c r="AW114">
@@ -24056,7 +25237,7 @@
       <c r="H115" s="48">
         <v>6478.05</v>
       </c>
-      <c r="J115" s="79"/>
+      <c r="J115" s="75"/>
       <c r="AE115" s="54"/>
       <c r="AP115" s="40"/>
       <c r="AQ115" s="41">
@@ -24069,17 +25250,17 @@
       </c>
       <c r="AS115" s="41">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>-28.9</v>
       </c>
       <c r="AT115" s="41">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AU115" s="41">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="AV115" s="67">
+      <c r="AV115" s="66">
         <v>2.4</v>
       </c>
       <c r="AW115">
@@ -24176,7 +25357,7 @@
       <c r="H116" s="48">
         <v>6478.05</v>
       </c>
-      <c r="J116" s="79"/>
+      <c r="J116" s="75"/>
       <c r="AE116" s="54"/>
       <c r="AP116" s="40"/>
       <c r="AQ116" s="41">
@@ -24189,17 +25370,17 @@
       </c>
       <c r="AS116" s="41">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>-30.7</v>
       </c>
       <c r="AT116" s="41">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>-5.7</v>
       </c>
       <c r="AU116" s="41">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="AV116" s="67">
+      <c r="AV116" s="66">
         <v>2.4</v>
       </c>
       <c r="AW116">
@@ -24296,7 +25477,7 @@
       <c r="H117" s="48">
         <v>6478.05</v>
       </c>
-      <c r="J117" s="79"/>
+      <c r="J117" s="75"/>
       <c r="AE117" s="54"/>
       <c r="AP117" s="40"/>
       <c r="AQ117" s="41">
@@ -24309,17 +25490,17 @@
       </c>
       <c r="AS117" s="41">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>-30.4</v>
       </c>
       <c r="AT117" s="41">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>-6.1</v>
       </c>
       <c r="AU117" s="41">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="AV117" s="67">
+      <c r="AV117" s="66">
         <v>2.4</v>
       </c>
       <c r="AW117">
@@ -24416,7 +25597,7 @@
       <c r="H118" s="48">
         <v>6478.05</v>
       </c>
-      <c r="J118" s="79"/>
+      <c r="J118" s="75"/>
       <c r="AE118" s="54"/>
       <c r="AP118" s="40"/>
       <c r="AQ118" s="41">
@@ -24429,17 +25610,17 @@
       </c>
       <c r="AS118" s="41">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>-21.1</v>
       </c>
       <c r="AT118" s="41">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>-4.4000000000000004</v>
       </c>
       <c r="AU118" s="41">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="AV118" s="67">
+      <c r="AV118" s="66">
         <v>2.4</v>
       </c>
       <c r="AW118">
@@ -24533,12 +25714,12 @@
         <v>12</v>
       </c>
       <c r="F119" s="5"/>
-      <c r="G119" s="62"/>
+      <c r="G119" s="61"/>
       <c r="H119" s="38">
         <v>6478.05</v>
       </c>
       <c r="I119" s="5"/>
-      <c r="J119" s="80"/>
+      <c r="J119" s="76"/>
       <c r="K119" s="5"/>
       <c r="L119" s="5"/>
       <c r="M119" s="5"/>
@@ -24559,7 +25740,7 @@
       <c r="AB119" s="5"/>
       <c r="AC119" s="5"/>
       <c r="AD119" s="5"/>
-      <c r="AE119" s="62"/>
+      <c r="AE119" s="61"/>
       <c r="AF119" s="5"/>
       <c r="AG119" s="5"/>
       <c r="AH119" s="5"/>
@@ -24581,17 +25762,17 @@
       </c>
       <c r="AS119" s="33">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>-20.9</v>
       </c>
       <c r="AT119" s="33">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>-4.4000000000000004</v>
       </c>
       <c r="AU119" s="33">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="AV119" s="68">
+      <c r="AV119" s="67">
         <v>2.4</v>
       </c>
       <c r="AW119" s="5">
@@ -24656,7 +25837,7 @@
         <f t="shared" si="84"/>
         <v/>
       </c>
-      <c r="BP119" s="59">
+      <c r="BP119" s="58">
         <f t="shared" si="87"/>
         <v>0</v>
       </c>
